--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -44688,29 +44688,29 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>roy_1127</t>
+          <t>zhouxiongjia</t>
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1441</v>
+        <v>109</v>
       </c>
       <c r="D141" s="27" t="n">
-        <v>2043</v>
+        <v>1500</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="F141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H141" s="19" t="n">
-        <v>-1</v>
+      <c r="H141" s="23" t="n">
+        <v>11860</v>
       </c>
       <c r="I141" s="19" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="J141" s="19" t="n">
         <v>-1</v>
@@ -44796,17 +44796,17 @@
       <c r="AK141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AL141" s="19" t="n">
-        <v>-1</v>
+      <c r="AL141" s="20" t="n">
+        <v>11941</v>
       </c>
       <c r="AM141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN141" s="19" t="n">
-        <v>-1</v>
+        <v>46.7</v>
+      </c>
+      <c r="AN141" s="23" t="n">
+        <v>16430</v>
       </c>
       <c r="AO141" s="19" t="n">
-        <v>0</v>
+        <v>34.4</v>
       </c>
       <c r="AP141" s="19" t="n">
         <v>-1</v>
@@ -44832,11 +44832,11 @@
       <c r="AW141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AX141" s="19" t="n">
-        <v>-1</v>
+      <c r="AX141" s="20" t="n">
+        <v>12477</v>
       </c>
       <c r="AY141" s="19" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AZ141" s="19" t="n">
         <v>-1</v>
@@ -44844,11 +44844,11 @@
       <c r="BA141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB141" s="19" t="n">
-        <v>-1</v>
+      <c r="BB141" s="20" t="n">
+        <v>11351</v>
       </c>
       <c r="BC141" s="19" t="n">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="BD141" s="19" t="n">
         <v>-1</v>
@@ -44856,11 +44856,11 @@
       <c r="BE141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BF141" s="19" t="n">
-        <v>-1</v>
+      <c r="BF141" s="20" t="n">
+        <v>12932</v>
       </c>
       <c r="BG141" s="19" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="BH141" s="19" t="n">
         <v>-1</v>
@@ -44868,17 +44868,17 @@
       <c r="BI141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BJ141" s="19" t="n">
-        <v>-1</v>
+      <c r="BJ141" s="15" t="n">
+        <v>5660</v>
       </c>
       <c r="BK141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL141" s="19" t="n">
-        <v>-1</v>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BL141" s="15" t="n">
+        <v>2319</v>
       </c>
       <c r="BM141" s="19" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="BN141" s="19" t="n">
         <v>-1</v>
@@ -44892,11 +44892,11 @@
       <c r="BQ141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BR141" s="19" t="n">
-        <v>-1</v>
+      <c r="BR141" s="20" t="n">
+        <v>5357</v>
       </c>
       <c r="BS141" s="19" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="BT141" s="19" t="n">
         <v>-1</v>
@@ -44904,119 +44904,124 @@
       <c r="BU141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BV141" s="19" t="n">
-        <v>-1</v>
+      <c r="BV141" s="15" t="n">
+        <v>5100</v>
       </c>
       <c r="BW141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX141" s="19" t="n">
-        <v>-1</v>
+        <v>77.8</v>
+      </c>
+      <c r="BX141" s="20" t="n">
+        <v>13040</v>
       </c>
       <c r="BY141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ141" s="19" t="n">
-        <v>-1</v>
+        <v>37.6</v>
+      </c>
+      <c r="BZ141" s="20" t="n">
+        <v>13057</v>
       </c>
       <c r="CA141" s="19" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="CB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CG141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CH141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CI141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CJ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CK141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CL141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CM141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CN141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CO141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CP141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CR141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CS141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CV141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CW141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CX141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CZ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DA141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DG141" s="19" t="n">
         <v>0</v>
+      </c>
+      <c r="DH141" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft-Logo</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -45025,14 +45030,14 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>yuanlu0210</t>
+          <t>roy_1127</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1413</v>
+        <v>1441</v>
       </c>
       <c r="D142" s="24" t="n">
-        <v>2079</v>
+        <v>2043</v>
       </c>
       <c r="E142" s="12" t="n">
         <v>0</v>
@@ -45055,53 +45060,53 @@
       <c r="K142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L142" s="15" t="n">
-        <v>3694</v>
+      <c r="L142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="M142" s="14" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="N142" s="20" t="n">
-        <v>2513</v>
+        <v>0</v>
+      </c>
+      <c r="N142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O142" s="14" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="P142" s="20" t="n">
-        <v>6727</v>
+        <v>0</v>
+      </c>
+      <c r="P142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Q142" s="14" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="R142" s="15" t="n">
-        <v>601</v>
+        <v>0</v>
+      </c>
+      <c r="R142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="S142" s="14" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="T142" s="20" t="n">
-        <v>2688</v>
+        <v>0</v>
+      </c>
+      <c r="T142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U142" s="14" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="V142" s="15" t="n">
-        <v>1800</v>
+        <v>0</v>
+      </c>
+      <c r="V142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="W142" s="14" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="X142" s="13" t="n">
-        <v>2006</v>
+        <v>0</v>
+      </c>
+      <c r="X142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Y142" s="14" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="Z142" s="20" t="n">
-        <v>3202</v>
+        <v>0</v>
+      </c>
+      <c r="Z142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AA142" s="14" t="n">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB142" s="14" t="n">
         <v>-1</v>
@@ -45115,11 +45120,11 @@
       <c r="AE142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AF142" s="20" t="n">
-        <v>1727</v>
+      <c r="AF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AG142" s="14" t="n">
-        <v>84.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH142" s="14" t="n">
         <v>-1</v>
@@ -45127,23 +45132,23 @@
       <c r="AI142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ142" s="15" t="n">
-        <v>1577</v>
+      <c r="AJ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AK142" s="14" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="AL142" s="15" t="n">
-        <v>1341</v>
+        <v>0</v>
+      </c>
+      <c r="AL142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AM142" s="14" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="AN142" s="20" t="n">
-        <v>2132</v>
+        <v>0</v>
+      </c>
+      <c r="AN142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AO142" s="14" t="n">
-        <v>83.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP142" s="14" t="n">
         <v>-1</v>
@@ -45151,17 +45156,17 @@
       <c r="AQ142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AR142" s="15" t="n">
-        <v>1294</v>
+      <c r="AR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AS142" s="14" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="AT142" s="15" t="n">
-        <v>913</v>
+        <v>0</v>
+      </c>
+      <c r="AT142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AU142" s="14" t="n">
-        <v>68.7</v>
+        <v>0</v>
       </c>
       <c r="AV142" s="14" t="n">
         <v>-1</v>
@@ -45169,167 +45174,167 @@
       <c r="AW142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX142" s="15" t="n">
-        <v>1869</v>
+      <c r="AX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY142" s="14" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="AZ142" s="15" t="n">
-        <v>3511</v>
+        <v>0</v>
+      </c>
+      <c r="AZ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BA142" s="14" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="BB142" s="15" t="n">
-        <v>1031</v>
+        <v>0</v>
+      </c>
+      <c r="BB142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BC142" s="14" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="BD142" s="15" t="n">
-        <v>4017</v>
+        <v>0</v>
+      </c>
+      <c r="BD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BE142" s="14" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BF142" s="15" t="n">
-        <v>1218</v>
+        <v>0</v>
+      </c>
+      <c r="BF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BG142" s="14" t="n">
-        <v>91</v>
-      </c>
-      <c r="BH142" s="15" t="n">
-        <v>3023</v>
+        <v>0</v>
+      </c>
+      <c r="BH142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BI142" s="14" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="BJ142" s="15" t="n">
-        <v>1376</v>
+        <v>0</v>
+      </c>
+      <c r="BJ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BK142" s="14" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="BL142" s="15" t="n">
-        <v>1365</v>
+        <v>0</v>
+      </c>
+      <c r="BL142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM142" s="14" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="BN142" s="15" t="n">
-        <v>2536</v>
+        <v>0</v>
+      </c>
+      <c r="BN142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BO142" s="14" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="BP142" s="13" t="n">
-        <v>1095</v>
+        <v>0</v>
+      </c>
+      <c r="BP142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ142" s="14" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="BR142" s="20" t="n">
-        <v>5801</v>
+        <v>0</v>
+      </c>
+      <c r="BR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BS142" s="14" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="BT142" s="15" t="n">
-        <v>2558</v>
+        <v>0</v>
+      </c>
+      <c r="BT142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BU142" s="14" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="BV142" s="15" t="n">
-        <v>4905</v>
+        <v>0</v>
+      </c>
+      <c r="BV142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BW142" s="14" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="BX142" s="15" t="n">
-        <v>2755</v>
+        <v>0</v>
+      </c>
+      <c r="BX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BY142" s="14" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="BZ142" s="15" t="n">
-        <v>1451</v>
+        <v>0</v>
+      </c>
+      <c r="BZ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CA142" s="14" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="CB142" s="15" t="n">
-        <v>1828</v>
+        <v>0</v>
+      </c>
+      <c r="CB142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CC142" s="14" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="CD142" s="15" t="n">
-        <v>4755</v>
+        <v>0</v>
+      </c>
+      <c r="CD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CE142" s="14" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="CF142" s="20" t="n">
-        <v>7964</v>
+        <v>0</v>
+      </c>
+      <c r="CF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CG142" s="14" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="CH142" s="15" t="n">
-        <v>3722</v>
+        <v>0</v>
+      </c>
+      <c r="CH142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CI142" s="14" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="CJ142" s="13" t="n">
-        <v>373</v>
+        <v>0</v>
+      </c>
+      <c r="CJ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CK142" s="14" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="CL142" s="15" t="n">
-        <v>2089</v>
+        <v>0</v>
+      </c>
+      <c r="CL142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CM142" s="14" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="CN142" s="15" t="n">
-        <v>3889</v>
+        <v>0</v>
+      </c>
+      <c r="CN142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CO142" s="14" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="CP142" s="15" t="n">
-        <v>872</v>
+        <v>0</v>
+      </c>
+      <c r="CP142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ142" s="14" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="CR142" s="23" t="n">
-        <v>12175</v>
+        <v>0</v>
+      </c>
+      <c r="CR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CS142" s="14" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="CT142" s="15" t="n">
-        <v>1343</v>
+        <v>0</v>
+      </c>
+      <c r="CT142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CU142" s="14" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="CV142" s="15" t="n">
-        <v>3691</v>
+        <v>0</v>
+      </c>
+      <c r="CV142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CW142" s="14" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="CX142" s="15" t="n">
-        <v>789</v>
+        <v>0</v>
+      </c>
+      <c r="CX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY142" s="14" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="CZ142" s="14" t="n">
         <v>-1</v>
@@ -45337,28 +45342,23 @@
       <c r="DA142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB142" s="13" t="n">
-        <v>250</v>
+      <c r="DB142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DC142" s="14" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="DD142" s="15" t="n">
-        <v>600</v>
+        <v>0</v>
+      </c>
+      <c r="DD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DE142" s="14" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="DF142" s="15" t="n">
-        <v>934</v>
+        <v>0</v>
+      </c>
+      <c r="DF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DG142" s="14" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="DH142" s="1" t="inlineStr">
-        <is>
-          <t>Dropbox-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -45367,14 +45367,14 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>zrts</t>
+          <t>yuanlu0210</t>
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1297</v>
-      </c>
-      <c r="D143" s="22" t="n">
-        <v>2637</v>
+        <v>1413</v>
+      </c>
+      <c r="D143" s="27" t="n">
+        <v>2079</v>
       </c>
       <c r="E143" s="12" t="n">
         <v>0</v>
@@ -45397,305 +45397,310 @@
       <c r="K143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L143" s="13" t="n">
-        <v>49</v>
+      <c r="L143" s="15" t="n">
+        <v>3694</v>
       </c>
       <c r="M143" s="19" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="N143" s="19" t="n">
-        <v>-1</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="N143" s="20" t="n">
+        <v>2513</v>
       </c>
       <c r="O143" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" s="13" t="n">
-        <v>153</v>
+        <v>74.5</v>
+      </c>
+      <c r="P143" s="20" t="n">
+        <v>6727</v>
       </c>
       <c r="Q143" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="R143" s="13" t="n">
-        <v>73</v>
+        <v>63.7</v>
+      </c>
+      <c r="R143" s="15" t="n">
+        <v>601</v>
       </c>
       <c r="S143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="T143" s="13" t="n">
-        <v>58</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="T143" s="20" t="n">
+        <v>2688</v>
       </c>
       <c r="U143" s="19" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="V143" s="13" t="n">
-        <v>208</v>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="V143" s="15" t="n">
+        <v>1800</v>
       </c>
       <c r="W143" s="19" t="n">
-        <v>99.2</v>
+        <v>88.3</v>
       </c>
       <c r="X143" s="13" t="n">
-        <v>1081</v>
+        <v>2006</v>
       </c>
       <c r="Y143" s="19" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="Z143" s="19" t="n">
-        <v>-1</v>
+        <v>93.2</v>
+      </c>
+      <c r="Z143" s="20" t="n">
+        <v>3202</v>
       </c>
       <c r="AA143" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" s="15" t="n">
-        <v>1040</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AB143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC143" s="19" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="AD143" s="20" t="n">
-        <v>1317</v>
+        <v>0</v>
+      </c>
+      <c r="AD143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AE143" s="19" t="n">
-        <v>85.7</v>
+        <v>0</v>
       </c>
       <c r="AF143" s="20" t="n">
-        <v>2768</v>
+        <v>1727</v>
       </c>
       <c r="AG143" s="19" t="n">
-        <v>81</v>
-      </c>
-      <c r="AH143" s="13" t="n">
-        <v>148</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="AH143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI143" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="AJ143" s="13" t="n">
-        <v>98</v>
+        <v>0</v>
+      </c>
+      <c r="AJ143" s="15" t="n">
+        <v>1577</v>
       </c>
       <c r="AK143" s="19" t="n">
-        <v>99.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AL143" s="15" t="n">
-        <v>84</v>
+        <v>1341</v>
       </c>
       <c r="AM143" s="19" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="AN143" s="15" t="n">
-        <v>322</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="AN143" s="20" t="n">
+        <v>2132</v>
       </c>
       <c r="AO143" s="19" t="n">
-        <v>94</v>
-      </c>
-      <c r="AP143" s="13" t="n">
-        <v>30</v>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="AP143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ143" s="19" t="n">
-        <v>99.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR143" s="15" t="n">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="AS143" s="19" t="n">
         <v>57.1</v>
       </c>
-      <c r="AT143" s="13" t="n">
-        <v>270</v>
+      <c r="AT143" s="15" t="n">
+        <v>913</v>
       </c>
       <c r="AU143" s="19" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="AV143" s="13" t="n">
-        <v>118</v>
+        <v>68.7</v>
+      </c>
+      <c r="AV143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW143" s="19" t="n">
-        <v>99.5</v>
+        <v>0</v>
       </c>
       <c r="AX143" s="15" t="n">
+        <v>1869</v>
+      </c>
+      <c r="AY143" s="19" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AZ143" s="15" t="n">
+        <v>3511</v>
+      </c>
+      <c r="BA143" s="19" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="BB143" s="15" t="n">
         <v>1031</v>
       </c>
-      <c r="AY143" s="19" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="AZ143" s="13" t="n">
-        <v>158</v>
-      </c>
-      <c r="BA143" s="19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="BB143" s="15" t="n">
-        <v>2284</v>
-      </c>
       <c r="BC143" s="19" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="BD143" s="13" t="n">
-        <v>127</v>
+        <v>91.8</v>
+      </c>
+      <c r="BD143" s="15" t="n">
+        <v>4017</v>
       </c>
       <c r="BE143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="BF143" s="13" t="n">
-        <v>6</v>
+        <v>82.3</v>
+      </c>
+      <c r="BF143" s="15" t="n">
+        <v>1218</v>
       </c>
       <c r="BG143" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="BH143" s="13" t="n">
-        <v>130</v>
+        <v>91</v>
+      </c>
+      <c r="BH143" s="15" t="n">
+        <v>3023</v>
       </c>
       <c r="BI143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="BJ143" s="13" t="n">
-        <v>348</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BJ143" s="15" t="n">
+        <v>1376</v>
       </c>
       <c r="BK143" s="19" t="n">
-        <v>98.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="BL143" s="15" t="n">
-        <v>393</v>
+        <v>1365</v>
       </c>
       <c r="BM143" s="19" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="BN143" s="13" t="n">
-        <v>258</v>
+        <v>89.2</v>
+      </c>
+      <c r="BN143" s="15" t="n">
+        <v>2536</v>
       </c>
       <c r="BO143" s="19" t="n">
-        <v>99</v>
+        <v>84.7</v>
       </c>
       <c r="BP143" s="13" t="n">
-        <v>97</v>
+        <v>1095</v>
       </c>
       <c r="BQ143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="BR143" s="13" t="n">
-        <v>161</v>
+        <v>95.8</v>
+      </c>
+      <c r="BR143" s="20" t="n">
+        <v>5801</v>
       </c>
       <c r="BS143" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="BT143" s="13" t="n">
-        <v>70</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="BT143" s="15" t="n">
+        <v>2558</v>
       </c>
       <c r="BU143" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="BV143" s="13" t="n">
-        <v>141</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="BV143" s="15" t="n">
+        <v>4905</v>
       </c>
       <c r="BW143" s="19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="BX143" s="13" t="n">
-        <v>482</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="BX143" s="15" t="n">
+        <v>2755</v>
       </c>
       <c r="BY143" s="19" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="BZ143" s="13" t="n">
-        <v>108</v>
+        <v>83.90000000000001</v>
+      </c>
+      <c r="BZ143" s="15" t="n">
+        <v>1451</v>
       </c>
       <c r="CA143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CB143" s="13" t="n">
-        <v>129</v>
+        <v>90.2</v>
+      </c>
+      <c r="CB143" s="15" t="n">
+        <v>1828</v>
       </c>
       <c r="CC143" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CD143" s="13" t="n">
-        <v>90</v>
+        <v>88.7</v>
+      </c>
+      <c r="CD143" s="15" t="n">
+        <v>4755</v>
       </c>
       <c r="CE143" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="CF143" s="15" t="n">
-        <v>64</v>
+        <v>77.2</v>
+      </c>
+      <c r="CF143" s="20" t="n">
+        <v>7964</v>
       </c>
       <c r="CG143" s="19" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="CH143" s="13" t="n">
-        <v>383</v>
+        <v>56.5</v>
+      </c>
+      <c r="CH143" s="15" t="n">
+        <v>3722</v>
       </c>
       <c r="CI143" s="19" t="n">
-        <v>98.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="CJ143" s="13" t="n">
-        <v>63</v>
+        <v>373</v>
       </c>
       <c r="CK143" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="CL143" s="13" t="n">
-        <v>165</v>
+        <v>98.2</v>
+      </c>
+      <c r="CL143" s="15" t="n">
+        <v>2089</v>
       </c>
       <c r="CM143" s="19" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="CN143" s="20" t="n">
-        <v>5648</v>
+        <v>86.2</v>
+      </c>
+      <c r="CN143" s="15" t="n">
+        <v>3889</v>
       </c>
       <c r="CO143" s="19" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="CP143" s="13" t="n">
-        <v>58</v>
+        <v>77.3</v>
+      </c>
+      <c r="CP143" s="15" t="n">
+        <v>872</v>
       </c>
       <c r="CQ143" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="CR143" s="13" t="n">
-        <v>95</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="CR143" s="23" t="n">
+        <v>12175</v>
       </c>
       <c r="CS143" s="19" t="n">
-        <v>99.5</v>
+        <v>26.5</v>
       </c>
       <c r="CT143" s="15" t="n">
-        <v>366</v>
+        <v>1343</v>
       </c>
       <c r="CU143" s="19" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="CV143" s="19" t="n">
-        <v>-1</v>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="CV143" s="15" t="n">
+        <v>3691</v>
       </c>
       <c r="CW143" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX143" s="19" t="n">
-        <v>-1</v>
+        <v>73.7</v>
+      </c>
+      <c r="CX143" s="15" t="n">
+        <v>789</v>
       </c>
       <c r="CY143" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ143" s="20" t="n">
-        <v>2347</v>
+        <v>91</v>
+      </c>
+      <c r="CZ143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA143" s="19" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="DB143" s="13" t="n">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="DC143" s="19" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="DD143" s="13" t="n">
-        <v>20</v>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="DD143" s="15" t="n">
+        <v>600</v>
       </c>
       <c r="DE143" s="19" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="DF143" s="13" t="n">
-        <v>195</v>
+        <v>91.7</v>
+      </c>
+      <c r="DF143" s="15" t="n">
+        <v>934</v>
       </c>
       <c r="DG143" s="19" t="n">
-        <v>98.7</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="DH143" s="1" t="inlineStr">
+        <is>
+          <t>Dropbox-Logo</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -45704,14 +45709,14 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>cyzh</t>
+          <t>zrts</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>1155</v>
-      </c>
-      <c r="D144" s="25" t="n">
-        <v>2342</v>
+        <v>1297</v>
+      </c>
+      <c r="D144" s="21" t="n">
+        <v>2637</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>0</v>
@@ -45734,11 +45739,11 @@
       <c r="K144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L144" s="14" t="n">
-        <v>-1</v>
+      <c r="L144" s="13" t="n">
+        <v>49</v>
       </c>
       <c r="M144" s="14" t="n">
-        <v>0</v>
+        <v>99.8</v>
       </c>
       <c r="N144" s="14" t="n">
         <v>-1</v>
@@ -45746,263 +45751,263 @@
       <c r="O144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P144" s="20" t="n">
-        <v>11707</v>
+      <c r="P144" s="13" t="n">
+        <v>153</v>
       </c>
       <c r="Q144" s="14" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="R144" s="15" t="n">
-        <v>1797</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="R144" s="13" t="n">
+        <v>73</v>
       </c>
       <c r="S144" s="14" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="T144" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="U144" s="14" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="V144" s="13" t="n">
+        <v>208</v>
+      </c>
+      <c r="W144" s="14" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="X144" s="13" t="n">
+        <v>1081</v>
+      </c>
+      <c r="Y144" s="14" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Z144" s="14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA144" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="15" t="n">
+        <v>1040</v>
+      </c>
+      <c r="AC144" s="14" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="AD144" s="20" t="n">
+        <v>1317</v>
+      </c>
+      <c r="AE144" s="14" t="n">
         <v>85.7</v>
       </c>
-      <c r="T144" s="20" t="n">
-        <v>1689</v>
-      </c>
-      <c r="U144" s="14" t="n">
-        <v>83</v>
-      </c>
-      <c r="V144" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" s="23" t="n">
-        <v>11018</v>
-      </c>
-      <c r="AA144" s="14" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="AB144" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" s="15" t="n">
-        <v>229</v>
-      </c>
-      <c r="AE144" s="14" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="AF144" s="15" t="n">
-        <v>662</v>
+      <c r="AF144" s="20" t="n">
+        <v>2768</v>
       </c>
       <c r="AG144" s="14" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="AH144" s="20" t="n">
-        <v>2790</v>
+        <v>81</v>
+      </c>
+      <c r="AH144" s="13" t="n">
+        <v>148</v>
       </c>
       <c r="AI144" s="14" t="n">
-        <v>79.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AJ144" s="13" t="n">
-        <v>407</v>
+        <v>98</v>
       </c>
       <c r="AK144" s="14" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="AL144" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM144" s="14" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AN144" s="15" t="n">
+        <v>322</v>
+      </c>
+      <c r="AO144" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP144" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ144" s="14" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="AR144" s="15" t="n">
+        <v>1296</v>
+      </c>
+      <c r="AS144" s="14" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="AT144" s="13" t="n">
+        <v>270</v>
+      </c>
+      <c r="AU144" s="14" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="AV144" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="AW144" s="14" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="AX144" s="15" t="n">
+        <v>1031</v>
+      </c>
+      <c r="AY144" s="14" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AZ144" s="13" t="n">
+        <v>158</v>
+      </c>
+      <c r="BA144" s="14" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BB144" s="15" t="n">
+        <v>2284</v>
+      </c>
+      <c r="BC144" s="14" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="BD144" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="BE144" s="14" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BF144" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG144" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH144" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="BI144" s="14" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BJ144" s="13" t="n">
+        <v>348</v>
+      </c>
+      <c r="BK144" s="14" t="n">
         <v>98.7</v>
       </c>
-      <c r="AL144" s="15" t="n">
-        <v>98</v>
-      </c>
-      <c r="AM144" s="14" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="AN144" s="15" t="n">
-        <v>227</v>
-      </c>
-      <c r="AO144" s="14" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="AP144" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AQ144" s="14" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="AR144" s="20" t="n">
-        <v>1523</v>
-      </c>
-      <c r="AS144" s="14" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="AT144" s="13" t="n">
-        <v>399</v>
-      </c>
-      <c r="AU144" s="14" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="AV144" s="13" t="n">
-        <v>93</v>
-      </c>
-      <c r="AW144" s="14" t="n">
+      <c r="BL144" s="15" t="n">
+        <v>393</v>
+      </c>
+      <c r="BM144" s="14" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="BN144" s="13" t="n">
+        <v>258</v>
+      </c>
+      <c r="BO144" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="BP144" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="BQ144" s="14" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="AX144" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AY144" s="14" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="AZ144" s="13" t="n">
-        <v>530</v>
-      </c>
-      <c r="BA144" s="14" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="BB144" s="13" t="n">
-        <v>188</v>
-      </c>
-      <c r="BC144" s="14" t="n">
+      <c r="BR144" s="13" t="n">
+        <v>161</v>
+      </c>
+      <c r="BS144" s="14" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="BD144" s="13" t="n">
-        <v>1007</v>
-      </c>
-      <c r="BE144" s="14" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="BF144" s="13" t="n">
-        <v>220</v>
-      </c>
-      <c r="BG144" s="14" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="BH144" s="13" t="n">
-        <v>819</v>
-      </c>
-      <c r="BI144" s="14" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="BJ144" s="15" t="n">
-        <v>443</v>
-      </c>
-      <c r="BK144" s="14" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="BL144" s="13" t="n">
-        <v>105</v>
-      </c>
-      <c r="BM144" s="14" t="n">
+      <c r="BT144" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU144" s="14" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="BV144" s="13" t="n">
+        <v>141</v>
+      </c>
+      <c r="BW144" s="14" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="BX144" s="13" t="n">
+        <v>482</v>
+      </c>
+      <c r="BY144" s="14" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="BZ144" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="CA144" s="14" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="BN144" s="13" t="n">
-        <v>175</v>
-      </c>
-      <c r="BO144" s="14" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="BP144" s="13" t="n">
-        <v>1424</v>
-      </c>
-      <c r="BQ144" s="14" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="BR144" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BS144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT144" s="13" t="n">
-        <v>278</v>
-      </c>
-      <c r="BU144" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="BV144" s="13" t="n">
-        <v>117</v>
-      </c>
-      <c r="BW144" s="14" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="BX144" s="13" t="n">
-        <v>1880</v>
-      </c>
-      <c r="BY144" s="14" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="BZ144" s="13" t="n">
-        <v>188</v>
-      </c>
-      <c r="CA144" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
       <c r="CB144" s="13" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="CC144" s="14" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="CD144" s="13" t="n">
-        <v>852</v>
+        <v>90</v>
       </c>
       <c r="CE144" s="14" t="n">
-        <v>96.8</v>
+        <v>99.7</v>
       </c>
       <c r="CF144" s="15" t="n">
-        <v>690</v>
+        <v>64</v>
       </c>
       <c r="CG144" s="14" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="CH144" s="20" t="n">
-        <v>4945</v>
+        <v>94.7</v>
+      </c>
+      <c r="CH144" s="13" t="n">
+        <v>383</v>
       </c>
       <c r="CI144" s="14" t="n">
-        <v>67.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="CJ144" s="13" t="n">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="CK144" s="14" t="n">
-        <v>98.8</v>
+        <v>99.7</v>
       </c>
       <c r="CL144" s="13" t="n">
-        <v>226</v>
+        <v>165</v>
       </c>
       <c r="CM144" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="CN144" s="15" t="n">
-        <v>536</v>
+        <v>99.3</v>
+      </c>
+      <c r="CN144" s="20" t="n">
+        <v>5648</v>
       </c>
       <c r="CO144" s="14" t="n">
-        <v>92.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="CP144" s="13" t="n">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="CQ144" s="14" t="n">
-        <v>99.3</v>
+        <v>99.7</v>
       </c>
       <c r="CR144" s="13" t="n">
-        <v>257</v>
+        <v>95</v>
       </c>
       <c r="CS144" s="14" t="n">
-        <v>98.8</v>
+        <v>99.5</v>
       </c>
       <c r="CT144" s="15" t="n">
-        <v>168</v>
+        <v>366</v>
       </c>
       <c r="CU144" s="14" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="CV144" s="13" t="n">
-        <v>156</v>
+        <v>93.2</v>
+      </c>
+      <c r="CV144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CW144" s="14" t="n">
-        <v>99.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CX144" s="14" t="n">
         <v>-1</v>
@@ -46010,34 +46015,29 @@
       <c r="CY144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CZ144" s="13" t="n">
-        <v>110</v>
+      <c r="CZ144" s="20" t="n">
+        <v>2347</v>
       </c>
       <c r="DA144" s="14" t="n">
-        <v>99.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="DB144" s="13" t="n">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="DC144" s="14" t="n">
-        <v>97.8</v>
+        <v>99.8</v>
       </c>
       <c r="DD144" s="13" t="n">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="DE144" s="14" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="DF144" s="13" t="n">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="DG144" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="DH144" s="1" t="inlineStr">
-        <is>
-          <t>Baidu-Logo</t>
-        </is>
+        <v>98.7</v>
       </c>
     </row>
     <row r="145">
@@ -46046,14 +46046,14 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>fatyuan</t>
+          <t>cyzh</t>
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>1118</v>
-      </c>
-      <c r="D145" s="27" t="n">
-        <v>1629</v>
+        <v>1155</v>
+      </c>
+      <c r="D145" s="26" t="n">
+        <v>2342</v>
       </c>
       <c r="E145" s="12" t="n">
         <v>0</v>
@@ -46088,23 +46088,23 @@
       <c r="O145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P145" s="19" t="n">
-        <v>-1</v>
+      <c r="P145" s="20" t="n">
+        <v>11707</v>
       </c>
       <c r="Q145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R145" s="19" t="n">
-        <v>-1</v>
+        <v>44.3</v>
+      </c>
+      <c r="R145" s="15" t="n">
+        <v>1797</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T145" s="19" t="n">
-        <v>-1</v>
+        <v>85.7</v>
+      </c>
+      <c r="T145" s="20" t="n">
+        <v>1689</v>
       </c>
       <c r="U145" s="19" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="V145" s="19" t="n">
         <v>-1</v>
@@ -46118,11 +46118,11 @@
       <c r="Y145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="19" t="n">
-        <v>-1</v>
+      <c r="Z145" s="23" t="n">
+        <v>11018</v>
       </c>
       <c r="AA145" s="19" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="AB145" s="19" t="n">
         <v>-1</v>
@@ -46130,125 +46130,125 @@
       <c r="AC145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AD145" s="19" t="n">
-        <v>-1</v>
+      <c r="AD145" s="15" t="n">
+        <v>229</v>
       </c>
       <c r="AE145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF145" s="19" t="n">
-        <v>-1</v>
+        <v>94.2</v>
+      </c>
+      <c r="AF145" s="15" t="n">
+        <v>662</v>
       </c>
       <c r="AG145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH145" s="19" t="n">
-        <v>-1</v>
+        <v>92.8</v>
+      </c>
+      <c r="AH145" s="20" t="n">
+        <v>2790</v>
       </c>
       <c r="AI145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ145" s="19" t="n">
-        <v>-1</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AJ145" s="13" t="n">
+        <v>407</v>
       </c>
       <c r="AK145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL145" s="19" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="AL145" s="15" t="n">
+        <v>98</v>
       </c>
       <c r="AM145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN145" s="19" t="n">
-        <v>-1</v>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AN145" s="15" t="n">
+        <v>227</v>
       </c>
       <c r="AO145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP145" s="19" t="n">
-        <v>-1</v>
+        <v>94.3</v>
+      </c>
+      <c r="AP145" s="13" t="n">
+        <v>80</v>
       </c>
       <c r="AQ145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR145" s="19" t="n">
-        <v>-1</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="AR145" s="20" t="n">
+        <v>1523</v>
       </c>
       <c r="AS145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT145" s="19" t="n">
-        <v>-1</v>
+        <v>45.5</v>
+      </c>
+      <c r="AT145" s="13" t="n">
+        <v>399</v>
       </c>
       <c r="AU145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV145" s="19" t="n">
-        <v>-1</v>
+        <v>88.5</v>
+      </c>
+      <c r="AV145" s="13" t="n">
+        <v>93</v>
       </c>
       <c r="AW145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX145" s="19" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="AX145" s="13" t="n">
+        <v>500</v>
       </c>
       <c r="AY145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ145" s="19" t="n">
-        <v>-1</v>
+        <v>98.5</v>
+      </c>
+      <c r="AZ145" s="13" t="n">
+        <v>530</v>
       </c>
       <c r="BA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB145" s="19" t="n">
-        <v>-1</v>
+        <v>98.5</v>
+      </c>
+      <c r="BB145" s="13" t="n">
+        <v>188</v>
       </c>
       <c r="BC145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD145" s="19" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BD145" s="13" t="n">
+        <v>1007</v>
       </c>
       <c r="BE145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF145" s="19" t="n">
-        <v>-1</v>
+        <v>96.8</v>
+      </c>
+      <c r="BF145" s="13" t="n">
+        <v>220</v>
       </c>
       <c r="BG145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH145" s="19" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="BH145" s="13" t="n">
+        <v>819</v>
       </c>
       <c r="BI145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ145" s="19" t="n">
-        <v>-1</v>
+        <v>97.2</v>
+      </c>
+      <c r="BJ145" s="15" t="n">
+        <v>443</v>
       </c>
       <c r="BK145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL145" s="19" t="n">
-        <v>-1</v>
+        <v>93.40000000000001</v>
+      </c>
+      <c r="BL145" s="13" t="n">
+        <v>105</v>
       </c>
       <c r="BM145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN145" s="19" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BN145" s="13" t="n">
+        <v>175</v>
       </c>
       <c r="BO145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP145" s="19" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="BP145" s="13" t="n">
+        <v>1424</v>
       </c>
       <c r="BQ145" s="19" t="n">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="BR145" s="19" t="n">
         <v>-1</v>
@@ -46256,95 +46256,95 @@
       <c r="BS145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT145" s="19" t="n">
-        <v>-1</v>
+      <c r="BT145" s="13" t="n">
+        <v>278</v>
       </c>
       <c r="BU145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV145" s="19" t="n">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="BV145" s="13" t="n">
+        <v>117</v>
       </c>
       <c r="BW145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX145" s="19" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BX145" s="13" t="n">
+        <v>1880</v>
       </c>
       <c r="BY145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ145" s="19" t="n">
-        <v>-1</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BZ145" s="13" t="n">
+        <v>188</v>
       </c>
       <c r="CA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB145" s="19" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="CB145" s="13" t="n">
+        <v>112</v>
       </c>
       <c r="CC145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD145" s="19" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CD145" s="13" t="n">
+        <v>852</v>
       </c>
       <c r="CE145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF145" s="19" t="n">
-        <v>-1</v>
+        <v>96.8</v>
+      </c>
+      <c r="CF145" s="15" t="n">
+        <v>690</v>
       </c>
       <c r="CG145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH145" s="19" t="n">
-        <v>-1</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="CH145" s="20" t="n">
+        <v>4945</v>
       </c>
       <c r="CI145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ145" s="19" t="n">
-        <v>-1</v>
+        <v>67.90000000000001</v>
+      </c>
+      <c r="CJ145" s="13" t="n">
+        <v>254</v>
       </c>
       <c r="CK145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL145" s="19" t="n">
-        <v>-1</v>
+        <v>98.8</v>
+      </c>
+      <c r="CL145" s="13" t="n">
+        <v>226</v>
       </c>
       <c r="CM145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN145" s="19" t="n">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="CN145" s="15" t="n">
+        <v>536</v>
       </c>
       <c r="CO145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP145" s="19" t="n">
-        <v>-1</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="CP145" s="13" t="n">
+        <v>136</v>
       </c>
       <c r="CQ145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR145" s="19" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="CR145" s="13" t="n">
+        <v>257</v>
       </c>
       <c r="CS145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT145" s="19" t="n">
-        <v>-1</v>
+        <v>98.8</v>
+      </c>
+      <c r="CT145" s="15" t="n">
+        <v>168</v>
       </c>
       <c r="CU145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV145" s="19" t="n">
-        <v>-1</v>
+        <v>94.2</v>
+      </c>
+      <c r="CV145" s="13" t="n">
+        <v>156</v>
       </c>
       <c r="CW145" s="19" t="n">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="CX145" s="19" t="n">
         <v>-1</v>
@@ -46352,29 +46352,34 @@
       <c r="CY145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ145" s="19" t="n">
-        <v>-1</v>
+      <c r="CZ145" s="13" t="n">
+        <v>110</v>
       </c>
       <c r="DA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB145" s="19" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="DB145" s="13" t="n">
+        <v>403</v>
       </c>
       <c r="DC145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD145" s="19" t="n">
-        <v>-1</v>
+        <v>97.8</v>
+      </c>
+      <c r="DD145" s="13" t="n">
+        <v>193</v>
       </c>
       <c r="DE145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF145" s="19" t="n">
-        <v>-1</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="DF145" s="13" t="n">
+        <v>91</v>
       </c>
       <c r="DG145" s="19" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="DH145" s="1" t="inlineStr">
+        <is>
+          <t>Baidu-Logo</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -46383,14 +46388,14 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>bill04128682</t>
+          <t>fatyuan</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>875</v>
+        <v>1118</v>
       </c>
       <c r="D146" s="24" t="n">
-        <v>2094</v>
+        <v>1629</v>
       </c>
       <c r="E146" s="12" t="n">
         <v>0</v>
@@ -46437,11 +46442,11 @@
       <c r="S146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="20" t="n">
-        <v>5125</v>
+      <c r="T146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U146" s="14" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="V146" s="14" t="n">
         <v>-1</v>
@@ -46569,11 +46574,11 @@
       <c r="BK146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BL146" s="15" t="n">
-        <v>1644</v>
+      <c r="BL146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM146" s="14" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="BN146" s="14" t="n">
         <v>-1</v>
@@ -46581,11 +46586,11 @@
       <c r="BO146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BP146" s="13" t="n">
-        <v>1445</v>
+      <c r="BP146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ146" s="14" t="n">
-        <v>94.5</v>
+        <v>0</v>
       </c>
       <c r="BR146" s="14" t="n">
         <v>-1</v>
@@ -46599,17 +46604,17 @@
       <c r="BU146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV146" s="13" t="n">
-        <v>1248</v>
+      <c r="BV146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BW146" s="14" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="BX146" s="15" t="n">
-        <v>2582</v>
+        <v>0</v>
+      </c>
+      <c r="BX146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BY146" s="14" t="n">
-        <v>84.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ146" s="14" t="n">
         <v>-1</v>
@@ -46617,17 +46622,17 @@
       <c r="CA146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CB146" s="15" t="n">
-        <v>5511</v>
+      <c r="CB146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CC146" s="14" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="CD146" s="13" t="n">
-        <v>1501</v>
+        <v>0</v>
+      </c>
+      <c r="CD146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CE146" s="14" t="n">
-        <v>94.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CF146" s="14" t="n">
         <v>-1</v>
@@ -46683,11 +46688,11 @@
       <c r="CW146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CX146" s="15" t="n">
-        <v>1143</v>
+      <c r="CX146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY146" s="14" t="n">
-        <v>89.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CZ146" s="14" t="n">
         <v>-1</v>
@@ -46712,11 +46717,6 @@
       </c>
       <c r="DG146" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="DH146" s="1" t="inlineStr">
-        <is>
-          <t>JumpTrade-Logo</t>
-        </is>
       </c>
     </row>
     <row r="147">
@@ -46725,14 +46725,14 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>ShangqiYang</t>
+          <t>bill04128682</t>
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="D147" s="27" t="n">
-        <v>2067</v>
+        <v>2094</v>
       </c>
       <c r="E147" s="12" t="n">
         <v>0</v>
@@ -46767,23 +46767,23 @@
       <c r="O147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P147" s="20" t="n">
-        <v>5462</v>
+      <c r="P147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Q147" s="19" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="R147" s="15" t="n">
-        <v>434</v>
+        <v>0</v>
+      </c>
+      <c r="R147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S147" s="19" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="T147" s="15" t="n">
-        <v>194</v>
+        <v>0</v>
+      </c>
+      <c r="T147" s="20" t="n">
+        <v>5125</v>
       </c>
       <c r="U147" s="19" t="n">
-        <v>94.2</v>
+        <v>68.8</v>
       </c>
       <c r="V147" s="19" t="n">
         <v>-1</v>
@@ -46803,17 +46803,17 @@
       <c r="AA147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AB147" s="15" t="n">
-        <v>1106</v>
+      <c r="AB147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC147" s="19" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="AD147" s="20" t="n">
-        <v>6161</v>
+        <v>0</v>
+      </c>
+      <c r="AD147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AE147" s="19" t="n">
-        <v>69.8</v>
+        <v>0</v>
       </c>
       <c r="AF147" s="19" t="n">
         <v>-1</v>
@@ -46827,17 +46827,17 @@
       <c r="AI147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ147" s="15" t="n">
-        <v>1205</v>
+      <c r="AJ147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AK147" s="19" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="AL147" s="20" t="n">
-        <v>1794</v>
+        <v>0</v>
+      </c>
+      <c r="AL147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AM147" s="19" t="n">
-        <v>83.5</v>
+        <v>0</v>
       </c>
       <c r="AN147" s="19" t="n">
         <v>-1</v>
@@ -46845,17 +46845,17 @@
       <c r="AO147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP147" s="15" t="n">
-        <v>1892</v>
+      <c r="AP147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ147" s="19" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="AR147" s="13" t="n">
-        <v>932</v>
+        <v>0</v>
+      </c>
+      <c r="AR147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AS147" s="19" t="n">
-        <v>72.7</v>
+        <v>0</v>
       </c>
       <c r="AT147" s="19" t="n">
         <v>-1</v>
@@ -46863,23 +46863,23 @@
       <c r="AU147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AV147" s="15" t="n">
-        <v>2797</v>
+      <c r="AV147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW147" s="19" t="n">
-        <v>82</v>
-      </c>
-      <c r="AX147" s="15" t="n">
-        <v>2563</v>
+        <v>0</v>
+      </c>
+      <c r="AX147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY147" s="19" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="AZ147" s="13" t="n">
-        <v>2062</v>
+        <v>0</v>
+      </c>
+      <c r="AZ147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BA147" s="19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="BB147" s="19" t="n">
         <v>-1</v>
@@ -46887,47 +46887,47 @@
       <c r="BC147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD147" s="15" t="n">
-        <v>3440</v>
+      <c r="BD147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BE147" s="19" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="BF147" s="15" t="n">
-        <v>811</v>
+        <v>0</v>
+      </c>
+      <c r="BF147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BG147" s="19" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="BH147" s="15" t="n">
-        <v>2869</v>
+        <v>0</v>
+      </c>
+      <c r="BH147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI147" s="19" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="BJ147" s="20" t="n">
-        <v>6941</v>
+        <v>0</v>
+      </c>
+      <c r="BJ147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BK147" s="19" t="n">
-        <v>64.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL147" s="15" t="n">
-        <v>1023</v>
+        <v>1644</v>
       </c>
       <c r="BM147" s="19" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="BN147" s="15" t="n">
-        <v>3416</v>
+        <v>88</v>
+      </c>
+      <c r="BN147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BO147" s="19" t="n">
-        <v>81.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="BP147" s="13" t="n">
-        <v>1987</v>
+        <v>1445</v>
       </c>
       <c r="BQ147" s="19" t="n">
-        <v>92.5</v>
+        <v>94.5</v>
       </c>
       <c r="BR147" s="19" t="n">
         <v>-1</v>
@@ -46935,23 +46935,23 @@
       <c r="BS147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT147" s="15" t="n">
-        <v>4241</v>
+      <c r="BT147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU147" s="19" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="BV147" s="15" t="n">
-        <v>2400</v>
+        <v>0</v>
+      </c>
+      <c r="BV147" s="13" t="n">
+        <v>1248</v>
       </c>
       <c r="BW147" s="19" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="BX147" s="13" t="n">
-        <v>1815</v>
+        <v>95.8</v>
+      </c>
+      <c r="BX147" s="15" t="n">
+        <v>2582</v>
       </c>
       <c r="BY147" s="19" t="n">
-        <v>92.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="BZ147" s="19" t="n">
         <v>-1</v>
@@ -46960,22 +46960,22 @@
         <v>0</v>
       </c>
       <c r="CB147" s="15" t="n">
-        <v>1061</v>
+        <v>5511</v>
       </c>
       <c r="CC147" s="19" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="CD147" s="19" t="n">
-        <v>-1</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="CD147" s="13" t="n">
+        <v>1501</v>
       </c>
       <c r="CE147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF147" s="20" t="n">
-        <v>1228</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="CF147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG147" s="19" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="CH147" s="19" t="n">
         <v>-1</v>
@@ -46989,11 +46989,11 @@
       <c r="CK147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CL147" s="15" t="n">
-        <v>3505</v>
+      <c r="CL147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM147" s="19" t="n">
-        <v>80.2</v>
+        <v>0</v>
       </c>
       <c r="CN147" s="19" t="n">
         <v>-1</v>
@@ -47001,11 +47001,11 @@
       <c r="CO147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CP147" s="15" t="n">
-        <v>3155</v>
+      <c r="CP147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ147" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="CR147" s="19" t="n">
         <v>-1</v>
@@ -47013,51 +47013,51 @@
       <c r="CS147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CT147" s="23" t="n">
-        <v>7147</v>
+      <c r="CT147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CU147" s="19" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="CV147" s="20" t="n">
-        <v>6907</v>
+        <v>0</v>
+      </c>
+      <c r="CV147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW147" s="19" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="CX147" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="CX147" s="15" t="n">
+        <v>1143</v>
       </c>
       <c r="CY147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ147" s="15" t="n">
-        <v>648</v>
+        <v>89.09999999999999</v>
+      </c>
+      <c r="CZ147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA147" s="19" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="DB147" s="15" t="n">
-        <v>3047</v>
+        <v>0</v>
+      </c>
+      <c r="DB147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DC147" s="19" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="DD147" s="20" t="n">
-        <v>781</v>
+        <v>0</v>
+      </c>
+      <c r="DD147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE147" s="19" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="DF147" s="15" t="n">
-        <v>1651</v>
+        <v>0</v>
+      </c>
+      <c r="DF147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DG147" s="19" t="n">
-        <v>83.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="DH147" s="1" t="inlineStr">
         <is>
-          <t>Facebook-Logo</t>
+          <t>JumpTrade-Logo</t>
         </is>
       </c>
     </row>
@@ -47067,14 +47067,14 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>deadstorm</t>
+          <t>ShangqiYang</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>758</v>
+        <v>870</v>
       </c>
       <c r="D148" s="24" t="n">
-        <v>1433</v>
+        <v>2067</v>
       </c>
       <c r="E148" s="12" t="n">
         <v>0</v>
@@ -47109,23 +47109,23 @@
       <c r="O148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P148" s="14" t="n">
-        <v>-1</v>
+      <c r="P148" s="20" t="n">
+        <v>5462</v>
       </c>
       <c r="Q148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" s="14" t="n">
-        <v>-1</v>
+        <v>68.7</v>
+      </c>
+      <c r="R148" s="15" t="n">
+        <v>434</v>
       </c>
       <c r="S148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" s="14" t="n">
-        <v>-1</v>
+        <v>92.7</v>
+      </c>
+      <c r="T148" s="15" t="n">
+        <v>194</v>
       </c>
       <c r="U148" s="14" t="n">
-        <v>0</v>
+        <v>94.2</v>
       </c>
       <c r="V148" s="14" t="n">
         <v>-1</v>
@@ -47145,17 +47145,17 @@
       <c r="AA148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AB148" s="14" t="n">
-        <v>-1</v>
+      <c r="AB148" s="15" t="n">
+        <v>1106</v>
       </c>
       <c r="AC148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD148" s="14" t="n">
-        <v>-1</v>
+        <v>91.3</v>
+      </c>
+      <c r="AD148" s="20" t="n">
+        <v>6161</v>
       </c>
       <c r="AE148" s="14" t="n">
-        <v>0</v>
+        <v>69.8</v>
       </c>
       <c r="AF148" s="14" t="n">
         <v>-1</v>
@@ -47169,17 +47169,17 @@
       <c r="AI148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ148" s="14" t="n">
-        <v>-1</v>
+      <c r="AJ148" s="15" t="n">
+        <v>1205</v>
       </c>
       <c r="AK148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL148" s="14" t="n">
-        <v>-1</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="AL148" s="20" t="n">
+        <v>1794</v>
       </c>
       <c r="AM148" s="14" t="n">
-        <v>0</v>
+        <v>83.5</v>
       </c>
       <c r="AN148" s="14" t="n">
         <v>-1</v>
@@ -47187,17 +47187,17 @@
       <c r="AO148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP148" s="14" t="n">
-        <v>-1</v>
+      <c r="AP148" s="15" t="n">
+        <v>1892</v>
       </c>
       <c r="AQ148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR148" s="14" t="n">
-        <v>-1</v>
+        <v>38.5</v>
+      </c>
+      <c r="AR148" s="13" t="n">
+        <v>932</v>
       </c>
       <c r="AS148" s="14" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="AT148" s="14" t="n">
         <v>-1</v>
@@ -47205,23 +47205,23 @@
       <c r="AU148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV148" s="14" t="n">
-        <v>-1</v>
+      <c r="AV148" s="15" t="n">
+        <v>2797</v>
       </c>
       <c r="AW148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX148" s="14" t="n">
-        <v>-1</v>
+        <v>82</v>
+      </c>
+      <c r="AX148" s="15" t="n">
+        <v>2563</v>
       </c>
       <c r="AY148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ148" s="14" t="n">
-        <v>-1</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="AZ148" s="13" t="n">
+        <v>2062</v>
       </c>
       <c r="BA148" s="14" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="BB148" s="14" t="n">
         <v>-1</v>
@@ -47229,47 +47229,47 @@
       <c r="BC148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BD148" s="14" t="n">
-        <v>-1</v>
+      <c r="BD148" s="15" t="n">
+        <v>3440</v>
       </c>
       <c r="BE148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF148" s="14" t="n">
-        <v>-1</v>
+        <v>84.2</v>
+      </c>
+      <c r="BF148" s="15" t="n">
+        <v>811</v>
       </c>
       <c r="BG148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH148" s="14" t="n">
-        <v>-1</v>
+        <v>92.3</v>
+      </c>
+      <c r="BH148" s="15" t="n">
+        <v>2869</v>
       </c>
       <c r="BI148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ148" s="14" t="n">
-        <v>-1</v>
+        <v>85.09999999999999</v>
+      </c>
+      <c r="BJ148" s="20" t="n">
+        <v>6941</v>
       </c>
       <c r="BK148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL148" s="14" t="n">
-        <v>-1</v>
+        <v>64.40000000000001</v>
+      </c>
+      <c r="BL148" s="15" t="n">
+        <v>1023</v>
       </c>
       <c r="BM148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN148" s="14" t="n">
-        <v>-1</v>
+        <v>90.7</v>
+      </c>
+      <c r="BN148" s="15" t="n">
+        <v>3416</v>
       </c>
       <c r="BO148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP148" s="14" t="n">
-        <v>-1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="BP148" s="13" t="n">
+        <v>1987</v>
       </c>
       <c r="BQ148" s="14" t="n">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="BR148" s="14" t="n">
         <v>-1</v>
@@ -47277,23 +47277,23 @@
       <c r="BS148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BT148" s="14" t="n">
-        <v>-1</v>
+      <c r="BT148" s="15" t="n">
+        <v>4241</v>
       </c>
       <c r="BU148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV148" s="14" t="n">
-        <v>-1</v>
+        <v>79.5</v>
+      </c>
+      <c r="BV148" s="15" t="n">
+        <v>2400</v>
       </c>
       <c r="BW148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX148" s="14" t="n">
-        <v>-1</v>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="BX148" s="13" t="n">
+        <v>1815</v>
       </c>
       <c r="BY148" s="14" t="n">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="BZ148" s="14" t="n">
         <v>-1</v>
@@ -47301,11 +47301,11 @@
       <c r="CA148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CB148" s="14" t="n">
-        <v>-1</v>
+      <c r="CB148" s="15" t="n">
+        <v>1061</v>
       </c>
       <c r="CC148" s="14" t="n">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="CD148" s="14" t="n">
         <v>-1</v>
@@ -47313,11 +47313,11 @@
       <c r="CE148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CF148" s="14" t="n">
-        <v>-1</v>
+      <c r="CF148" s="20" t="n">
+        <v>1228</v>
       </c>
       <c r="CG148" s="14" t="n">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="CH148" s="14" t="n">
         <v>-1</v>
@@ -47331,11 +47331,11 @@
       <c r="CK148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL148" s="14" t="n">
-        <v>-1</v>
+      <c r="CL148" s="15" t="n">
+        <v>3505</v>
       </c>
       <c r="CM148" s="14" t="n">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="CN148" s="14" t="n">
         <v>-1</v>
@@ -47343,11 +47343,11 @@
       <c r="CO148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CP148" s="14" t="n">
-        <v>-1</v>
+      <c r="CP148" s="15" t="n">
+        <v>3155</v>
       </c>
       <c r="CQ148" s="14" t="n">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="CR148" s="14" t="n">
         <v>-1</v>
@@ -47355,17 +47355,17 @@
       <c r="CS148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CT148" s="14" t="n">
-        <v>-1</v>
+      <c r="CT148" s="23" t="n">
+        <v>7147</v>
       </c>
       <c r="CU148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV148" s="14" t="n">
-        <v>-1</v>
+        <v>49.8</v>
+      </c>
+      <c r="CV148" s="20" t="n">
+        <v>6907</v>
       </c>
       <c r="CW148" s="14" t="n">
-        <v>0</v>
+        <v>50.1</v>
       </c>
       <c r="CX148" s="14" t="n">
         <v>-1</v>
@@ -47373,29 +47373,34 @@
       <c r="CY148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CZ148" s="14" t="n">
-        <v>-1</v>
+      <c r="CZ148" s="15" t="n">
+        <v>648</v>
       </c>
       <c r="DA148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB148" s="14" t="n">
-        <v>-1</v>
+        <v>91.7</v>
+      </c>
+      <c r="DB148" s="15" t="n">
+        <v>3047</v>
       </c>
       <c r="DC148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD148" s="14" t="n">
-        <v>-1</v>
+        <v>78.5</v>
+      </c>
+      <c r="DD148" s="20" t="n">
+        <v>781</v>
       </c>
       <c r="DE148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF148" s="14" t="n">
-        <v>-1</v>
+        <v>85.7</v>
+      </c>
+      <c r="DF148" s="15" t="n">
+        <v>1651</v>
       </c>
       <c r="DG148" s="14" t="n">
-        <v>0</v>
+        <v>83.59999999999999</v>
+      </c>
+      <c r="DH148" s="1" t="inlineStr">
+        <is>
+          <t>Facebook-Logo</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -47404,14 +47409,14 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>wawawamei</t>
+          <t>deadstorm</t>
         </is>
       </c>
       <c r="C149" s="17" t="n">
-        <v>587</v>
+        <v>758</v>
       </c>
       <c r="D149" s="27" t="n">
-        <v>1412</v>
+        <v>1433</v>
       </c>
       <c r="E149" s="12" t="n">
         <v>0</v>
@@ -47452,11 +47457,11 @@
       <c r="Q149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R149" s="20" t="n">
-        <v>4257</v>
+      <c r="R149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S149" s="19" t="n">
-        <v>67.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="T149" s="19" t="n">
         <v>-1</v>
@@ -47470,11 +47475,11 @@
       <c r="W149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="23" t="n">
-        <v>21358</v>
+      <c r="X149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y149" s="19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z149" s="19" t="n">
         <v>-1</v>
@@ -47536,11 +47541,11 @@
       <c r="AS149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AT149" s="23" t="n">
-        <v>2653</v>
+      <c r="AT149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AU149" s="19" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV149" s="19" t="n">
         <v>-1</v>
@@ -47554,11 +47559,11 @@
       <c r="AY149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AZ149" s="20" t="n">
-        <v>18684</v>
+      <c r="AZ149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BA149" s="19" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
       <c r="BB149" s="19" t="n">
         <v>-1</v>
@@ -47578,11 +47583,11 @@
       <c r="BG149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH149" s="23" t="n">
-        <v>20053</v>
+      <c r="BH149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI149" s="19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BJ149" s="19" t="n">
         <v>-1</v>
@@ -47602,11 +47607,11 @@
       <c r="BO149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BP149" s="23" t="n">
-        <v>16477</v>
+      <c r="BP149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ149" s="19" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="BR149" s="19" t="n">
         <v>-1</v>
@@ -47614,11 +47619,11 @@
       <c r="BS149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT149" s="23" t="n">
-        <v>20720</v>
+      <c r="BT149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU149" s="19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="BV149" s="19" t="n">
         <v>-1</v>
@@ -47626,11 +47631,11 @@
       <c r="BW149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BX149" s="23" t="n">
-        <v>14803</v>
+      <c r="BX149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BY149" s="19" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="BZ149" s="19" t="n">
         <v>-1</v>
@@ -47644,17 +47649,17 @@
       <c r="CC149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD149" s="23" t="n">
-        <v>19936</v>
+      <c r="CD149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CE149" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CF149" s="20" t="n">
-        <v>8638</v>
+        <v>0</v>
+      </c>
+      <c r="CF149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG149" s="19" t="n">
-        <v>53.7</v>
+        <v>0</v>
       </c>
       <c r="CH149" s="19" t="n">
         <v>-1</v>
@@ -47668,11 +47673,11 @@
       <c r="CK149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CL149" s="23" t="n">
-        <v>13824</v>
+      <c r="CL149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM149" s="19" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="CN149" s="19" t="n">
         <v>-1</v>
@@ -47686,11 +47691,11 @@
       <c r="CQ149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CR149" s="23" t="n">
-        <v>12726</v>
+      <c r="CR149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CS149" s="19" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="CT149" s="19" t="n">
         <v>-1</v>
@@ -47710,29 +47715,29 @@
       <c r="CY149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ149" s="20" t="n">
-        <v>4479</v>
+      <c r="CZ149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA149" s="19" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="DB149" s="23" t="n">
-        <v>13243</v>
+        <v>0</v>
+      </c>
+      <c r="DB149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DC149" s="19" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="DD149" s="20" t="n">
-        <v>2112</v>
+        <v>0</v>
+      </c>
+      <c r="DD149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE149" s="19" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="DF149" s="20" t="n">
-        <v>3925</v>
+        <v>0</v>
+      </c>
+      <c r="DF149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DG149" s="19" t="n">
-        <v>62.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -47741,14 +47746,14 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>wawawamei</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>258</v>
+        <v>587</v>
       </c>
       <c r="D150" s="24" t="n">
-        <v>-1</v>
+        <v>1412</v>
       </c>
       <c r="E150" s="12" t="n">
         <v>0</v>
@@ -47760,321 +47765,316 @@
         <v>0</v>
       </c>
       <c r="H150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="N150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="R150" s="14" t="n">
-        <v>-2</v>
+      <c r="R150" s="20" t="n">
+        <v>4257</v>
       </c>
       <c r="S150" s="14" t="n">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="T150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="V150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="W150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="X150" s="14" t="n">
-        <v>-2</v>
+      <c r="X150" s="23" t="n">
+        <v>21358</v>
       </c>
       <c r="Y150" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AA150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AC150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AD150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AF150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AH150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AJ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AL150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AN150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AP150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AQ150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AR150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AT150" s="14" t="n">
-        <v>-2</v>
+      <c r="AT150" s="23" t="n">
+        <v>2653</v>
       </c>
       <c r="AU150" s="14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AV150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AX150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AY150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AZ150" s="14" t="n">
-        <v>-2</v>
+      <c r="AZ150" s="20" t="n">
+        <v>18684</v>
       </c>
       <c r="BA150" s="14" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="BB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BC150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BD150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BF150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH150" s="14" t="n">
-        <v>-2</v>
+      <c r="BH150" s="23" t="n">
+        <v>20053</v>
       </c>
       <c r="BI150" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BJ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BL150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BN150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BO150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BP150" s="14" t="n">
-        <v>-2</v>
+      <c r="BP150" s="23" t="n">
+        <v>16477</v>
       </c>
       <c r="BQ150" s="14" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="BR150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BT150" s="14" t="n">
-        <v>-2</v>
+      <c r="BT150" s="23" t="n">
+        <v>20720</v>
       </c>
       <c r="BU150" s="14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="BV150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BW150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BX150" s="14" t="n">
-        <v>-2</v>
+      <c r="BX150" s="23" t="n">
+        <v>14803</v>
       </c>
       <c r="BY150" s="14" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="BZ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CA150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CD150" s="14" t="n">
-        <v>-2</v>
+      <c r="CD150" s="23" t="n">
+        <v>19936</v>
       </c>
       <c r="CE150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF150" s="14" t="n">
-        <v>-2</v>
+        <v>10.5</v>
+      </c>
+      <c r="CF150" s="20" t="n">
+        <v>8638</v>
       </c>
       <c r="CG150" s="14" t="n">
-        <v>0</v>
+        <v>53.7</v>
       </c>
       <c r="CH150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CI150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CJ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL150" s="14" t="n">
-        <v>-2</v>
+      <c r="CL150" s="23" t="n">
+        <v>13824</v>
       </c>
       <c r="CM150" s="14" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="CN150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CP150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CQ150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CR150" s="14" t="n">
-        <v>-2</v>
+      <c r="CR150" s="23" t="n">
+        <v>12726</v>
       </c>
       <c r="CS150" s="14" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="CT150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CV150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CX150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CZ150" s="14" t="n">
-        <v>-2</v>
+      <c r="CZ150" s="20" t="n">
+        <v>4479</v>
       </c>
       <c r="DA150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB150" s="14" t="n">
-        <v>-2</v>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="DB150" s="23" t="n">
+        <v>13243</v>
       </c>
       <c r="DC150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD150" s="14" t="n">
-        <v>-2</v>
+        <v>13.1</v>
+      </c>
+      <c r="DD150" s="20" t="n">
+        <v>2112</v>
       </c>
       <c r="DE150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF150" s="14" t="n">
-        <v>-2</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="DF150" s="20" t="n">
+        <v>3925</v>
       </c>
       <c r="DG150" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH150" s="1" t="inlineStr">
-        <is>
-          <t>Microsoft-Logo</t>
-        </is>
+        <v>62.9</v>
       </c>
     </row>
     <row r="151">

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -39973,7 +39973,7 @@
         <v>49.5</v>
       </c>
       <c r="F127" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G127" s="19" t="n">
         <v>0</v>
@@ -44731,7 +44731,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G141" s="19" t="n">
         <v>0</v>

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -44718,7 +44718,7 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>Googlehsiehhh</t>
+          <t>googlehsiehhh</t>
         </is>
       </c>
       <c r="C141" s="17" t="n">

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -43370,23 +43370,23 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>silencea</t>
+          <t>googlehsiehhh</t>
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1040</v>
+        <v>1708</v>
       </c>
       <c r="D137" s="27" t="n">
-        <v>2099</v>
+        <v>-1</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>28.9</v>
+        <v>31.1</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>6782</v>
+        <v>5895</v>
       </c>
       <c r="G137" s="19" t="n">
-        <v>57.9</v>
+        <v>62.1</v>
       </c>
       <c r="H137" s="19" t="n">
         <v>-1</v>
@@ -43400,185 +43400,185 @@
       <c r="K137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="19" t="n">
-        <v>-1</v>
+      <c r="L137" s="20" t="n">
+        <v>2341</v>
       </c>
       <c r="M137" s="19" t="n">
-        <v>0</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N137" s="20" t="n">
-        <v>2169</v>
+        <v>1697</v>
       </c>
       <c r="O137" s="19" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="P137" s="20" t="n">
-        <v>3377</v>
+        <v>81.3</v>
+      </c>
+      <c r="P137" s="15" t="n">
+        <v>1636</v>
       </c>
       <c r="Q137" s="19" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="R137" s="15" t="n">
-        <v>1551</v>
+        <v>86.2</v>
+      </c>
+      <c r="R137" s="20" t="n">
+        <v>3367</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>87</v>
-      </c>
-      <c r="T137" s="19" t="n">
-        <v>-1</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="T137" s="15" t="n">
+        <v>1116</v>
       </c>
       <c r="U137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" s="19" t="n">
-        <v>-1</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="V137" s="15" t="n">
+        <v>1114</v>
       </c>
       <c r="W137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" s="15" t="n">
-        <v>801</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="X137" s="20" t="n">
+        <v>2316</v>
       </c>
       <c r="Y137" s="19" t="n">
-        <v>91.3</v>
+        <v>79.2</v>
       </c>
       <c r="Z137" s="15" t="n">
-        <v>4077</v>
+        <v>613</v>
       </c>
       <c r="AA137" s="19" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="AB137" s="19" t="n">
-        <v>-1</v>
+        <v>92.2</v>
+      </c>
+      <c r="AB137" s="20" t="n">
+        <v>1589</v>
       </c>
       <c r="AC137" s="19" t="n">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="AD137" s="15" t="n">
-        <v>3462</v>
+        <v>1071</v>
       </c>
       <c r="AE137" s="19" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="AF137" s="19" t="n">
-        <v>-1</v>
+        <v>90.8</v>
+      </c>
+      <c r="AF137" s="15" t="n">
+        <v>541</v>
       </c>
       <c r="AG137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" s="20" t="n">
-        <v>3383</v>
+        <v>92.2</v>
+      </c>
+      <c r="AH137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI137" s="19" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="AJ137" s="15" t="n">
-        <v>2044</v>
+        <v>1588</v>
       </c>
       <c r="AK137" s="19" t="n">
-        <v>87.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AL137" s="13" t="n">
-        <v>85</v>
+        <v>2180</v>
       </c>
       <c r="AM137" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="AN137" s="20" t="n">
-        <v>4845</v>
+        <v>92.7</v>
+      </c>
+      <c r="AN137" s="15" t="n">
+        <v>1407</v>
       </c>
       <c r="AO137" s="19" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AP137" s="15" t="n">
+        <v>3650</v>
+      </c>
+      <c r="AQ137" s="19" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="AR137" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS137" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT137" s="20" t="n">
+        <v>2431</v>
+      </c>
+      <c r="AU137" s="19" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="AV137" s="20" t="n">
+        <v>2509</v>
+      </c>
+      <c r="AW137" s="19" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AX137" s="13" t="n">
+        <v>529</v>
+      </c>
+      <c r="AY137" s="19" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AZ137" s="20" t="n">
+        <v>4336</v>
+      </c>
+      <c r="BA137" s="19" t="n">
         <v>74.3</v>
       </c>
-      <c r="AP137" s="15" t="n">
-        <v>3244</v>
-      </c>
-      <c r="AQ137" s="19" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="AR137" s="15" t="n">
-        <v>891</v>
-      </c>
-      <c r="AS137" s="19" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="AT137" s="20" t="n">
-        <v>2318</v>
-      </c>
-      <c r="AU137" s="19" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="AV137" s="15" t="n">
-        <v>634</v>
-      </c>
-      <c r="AW137" s="19" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="AX137" s="13" t="n">
-        <v>906</v>
-      </c>
-      <c r="AY137" s="19" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="AZ137" s="20" t="n">
-        <v>5747</v>
-      </c>
-      <c r="BA137" s="19" t="n">
-        <v>69.2</v>
-      </c>
       <c r="BB137" s="20" t="n">
-        <v>7837</v>
+        <v>1127</v>
       </c>
       <c r="BC137" s="19" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="BD137" s="15" t="n">
-        <v>1458</v>
+        <v>86.5</v>
+      </c>
+      <c r="BD137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BE137" s="19" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="BF137" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BF137" s="13" t="n">
+        <v>791</v>
       </c>
       <c r="BG137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH137" s="19" t="n">
-        <v>-1</v>
+        <v>76.90000000000001</v>
+      </c>
+      <c r="BH137" s="15" t="n">
+        <v>980</v>
       </c>
       <c r="BI137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ137" s="19" t="n">
-        <v>-1</v>
+        <v>66.8</v>
+      </c>
+      <c r="BJ137" s="15" t="n">
+        <v>2535</v>
       </c>
       <c r="BK137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL137" s="19" t="n">
-        <v>-1</v>
+        <v>83.2</v>
+      </c>
+      <c r="BL137" s="15" t="n">
+        <v>769</v>
       </c>
       <c r="BM137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN137" s="19" t="n">
-        <v>-1</v>
+        <v>92.7</v>
+      </c>
+      <c r="BN137" s="15" t="n">
+        <v>2560</v>
       </c>
       <c r="BO137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP137" s="15" t="n">
-        <v>4839</v>
+        <v>87.5</v>
+      </c>
+      <c r="BP137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ137" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="BR137" s="15" t="n">
-        <v>2386</v>
+        <v>0</v>
+      </c>
+      <c r="BR137" s="13" t="n">
+        <v>652</v>
       </c>
       <c r="BS137" s="19" t="n">
-        <v>87.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="BT137" s="19" t="n">
         <v>-1</v>
@@ -43587,118 +43587,123 @@
         <v>0</v>
       </c>
       <c r="BV137" s="13" t="n">
-        <v>1104</v>
+        <v>1329</v>
       </c>
       <c r="BW137" s="19" t="n">
-        <v>96.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="BX137" s="15" t="n">
-        <v>1063</v>
+        <v>2382</v>
       </c>
       <c r="BY137" s="19" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="BZ137" s="15" t="n">
+        <v>931</v>
+      </c>
+      <c r="CA137" s="19" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="BZ137" s="20" t="n">
-        <v>3840</v>
-      </c>
-      <c r="CA137" s="19" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="CB137" s="15" t="n">
-        <v>1604</v>
+      <c r="CB137" s="20" t="n">
+        <v>4252</v>
       </c>
       <c r="CC137" s="19" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="CD137" s="19" t="n">
-        <v>-1</v>
+        <v>72.7</v>
+      </c>
+      <c r="CD137" s="13" t="n">
+        <v>1170</v>
       </c>
       <c r="CE137" s="19" t="n">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="CF137" s="20" t="n">
-        <v>6386</v>
+        <v>2641</v>
       </c>
       <c r="CG137" s="19" t="n">
-        <v>65.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="CH137" s="13" t="n">
-        <v>2041</v>
+        <v>904</v>
       </c>
       <c r="CI137" s="19" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="CJ137" s="19" t="n">
-        <v>-1</v>
+        <v>96.7</v>
+      </c>
+      <c r="CJ137" s="15" t="n">
+        <v>4508</v>
       </c>
       <c r="CK137" s="19" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="CL137" s="13" t="n">
-        <v>1220</v>
+        <v>814</v>
       </c>
       <c r="CM137" s="19" t="n">
-        <v>95.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="CN137" s="15" t="n">
-        <v>2344</v>
+        <v>2892</v>
       </c>
       <c r="CO137" s="19" t="n">
-        <v>87.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="CP137" s="15" t="n">
-        <v>920</v>
+        <v>3061</v>
       </c>
       <c r="CQ137" s="19" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="CR137" s="19" t="n">
-        <v>-1</v>
+        <v>84.5</v>
+      </c>
+      <c r="CR137" s="13" t="n">
+        <v>1642</v>
       </c>
       <c r="CS137" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT137" s="15" t="n">
-        <v>445</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="CT137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CU137" s="19" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="CV137" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="CV137" s="13" t="n">
+        <v>600</v>
       </c>
       <c r="CW137" s="19" t="n">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="CX137" s="13" t="n">
-        <v>988</v>
+        <v>1980</v>
       </c>
       <c r="CY137" s="19" t="n">
-        <v>95.3</v>
+        <v>90.7</v>
       </c>
       <c r="CZ137" s="13" t="n">
-        <v>279</v>
+        <v>458</v>
       </c>
       <c r="DA137" s="19" t="n">
-        <v>98.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="DB137" s="15" t="n">
-        <v>589</v>
+        <v>365</v>
       </c>
       <c r="DC137" s="19" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="DD137" s="15" t="n">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="DE137" s="19" t="n">
         <v>90.7</v>
       </c>
-      <c r="DF137" s="20" t="n">
-        <v>7710</v>
+      <c r="DF137" s="15" t="n">
+        <v>1495</v>
       </c>
       <c r="DG137" s="19" t="n">
-        <v>53</v>
+        <v>87.8</v>
+      </c>
+      <c r="DH137" s="1" t="inlineStr">
+        <is>
+          <t>Google-Logo</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -43707,23 +43712,23 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>nK7WNyyDON</t>
+          <t>silencea</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>54</v>
+        <v>1040</v>
       </c>
       <c r="D138" s="26" t="n">
-        <v>1418</v>
+        <v>2099</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="F138" s="24" t="n">
-        <v>9516</v>
+        <v>28.9</v>
+      </c>
+      <c r="F138" s="20" t="n">
+        <v>6782</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>40</v>
+        <v>57.9</v>
       </c>
       <c r="H138" s="14" t="n">
         <v>-1</v>
@@ -43731,311 +43736,311 @@
       <c r="I138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="24" t="n">
-        <v>12325</v>
+      <c r="J138" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L138" s="24" t="n">
-        <v>10590</v>
+        <v>0</v>
+      </c>
+      <c r="L138" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="M138" s="14" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="N138" s="24" t="n">
-        <v>12929</v>
+        <v>0</v>
+      </c>
+      <c r="N138" s="20" t="n">
+        <v>2169</v>
       </c>
       <c r="O138" s="14" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="P138" s="14" t="n">
-        <v>-1</v>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="P138" s="20" t="n">
+        <v>3377</v>
       </c>
       <c r="Q138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" s="24" t="n">
-        <v>10441</v>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="R138" s="15" t="n">
+        <v>1551</v>
       </c>
       <c r="S138" s="14" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="T138" s="24" t="n">
-        <v>12326</v>
+        <v>87</v>
+      </c>
+      <c r="T138" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U138" s="14" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="V138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="W138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="14" t="n">
-        <v>-2</v>
+      <c r="X138" s="15" t="n">
+        <v>801</v>
       </c>
       <c r="Y138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" s="14" t="n">
-        <v>-2</v>
+        <v>91.3</v>
+      </c>
+      <c r="Z138" s="15" t="n">
+        <v>4077</v>
       </c>
       <c r="AA138" s="14" t="n">
-        <v>0</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AB138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AC138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AD138" s="14" t="n">
-        <v>-2</v>
+      <c r="AD138" s="15" t="n">
+        <v>3462</v>
       </c>
       <c r="AE138" s="14" t="n">
-        <v>0</v>
+        <v>81.5</v>
       </c>
       <c r="AF138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH138" s="14" t="n">
-        <v>-2</v>
+      <c r="AH138" s="20" t="n">
+        <v>3383</v>
       </c>
       <c r="AI138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" s="14" t="n">
-        <v>-2</v>
+        <v>76</v>
+      </c>
+      <c r="AJ138" s="15" t="n">
+        <v>2044</v>
       </c>
       <c r="AK138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL138" s="14" t="n">
-        <v>-2</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="AL138" s="13" t="n">
+        <v>85</v>
       </c>
       <c r="AM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN138" s="14" t="n">
-        <v>-2</v>
+        <v>99.7</v>
+      </c>
+      <c r="AN138" s="20" t="n">
+        <v>4845</v>
       </c>
       <c r="AO138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP138" s="14" t="n">
-        <v>-2</v>
+        <v>74.3</v>
+      </c>
+      <c r="AP138" s="15" t="n">
+        <v>3244</v>
       </c>
       <c r="AQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR138" s="14" t="n">
-        <v>-2</v>
+        <v>84.2</v>
+      </c>
+      <c r="AR138" s="15" t="n">
+        <v>891</v>
       </c>
       <c r="AS138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT138" s="14" t="n">
-        <v>-2</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AT138" s="20" t="n">
+        <v>2318</v>
       </c>
       <c r="AU138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV138" s="14" t="n">
-        <v>-2</v>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AV138" s="15" t="n">
+        <v>634</v>
       </c>
       <c r="AW138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX138" s="14" t="n">
-        <v>-2</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="AX138" s="13" t="n">
+        <v>906</v>
       </c>
       <c r="AY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ138" s="14" t="n">
-        <v>-2</v>
+        <v>97.09999999999999</v>
+      </c>
+      <c r="AZ138" s="20" t="n">
+        <v>5747</v>
       </c>
       <c r="BA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB138" s="14" t="n">
-        <v>-2</v>
+        <v>69.2</v>
+      </c>
+      <c r="BB138" s="20" t="n">
+        <v>7837</v>
       </c>
       <c r="BC138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD138" s="14" t="n">
-        <v>-2</v>
+        <v>65.8</v>
+      </c>
+      <c r="BD138" s="15" t="n">
+        <v>1458</v>
       </c>
       <c r="BE138" s="14" t="n">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="BF138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BH138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BI138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BJ138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BL138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BN138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BO138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BP138" s="14" t="n">
-        <v>-2</v>
+      <c r="BP138" s="15" t="n">
+        <v>4839</v>
       </c>
       <c r="BQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR138" s="14" t="n">
-        <v>-2</v>
+        <v>80</v>
+      </c>
+      <c r="BR138" s="15" t="n">
+        <v>2386</v>
       </c>
       <c r="BS138" s="14" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="BT138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BU138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV138" s="14" t="n">
-        <v>-2</v>
+      <c r="BV138" s="13" t="n">
+        <v>1104</v>
       </c>
       <c r="BW138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX138" s="14" t="n">
-        <v>-2</v>
+        <v>96.2</v>
+      </c>
+      <c r="BX138" s="15" t="n">
+        <v>1063</v>
       </c>
       <c r="BY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ138" s="14" t="n">
-        <v>-2</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="BZ138" s="20" t="n">
+        <v>3840</v>
       </c>
       <c r="CA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB138" s="14" t="n">
-        <v>-2</v>
+        <v>73.7</v>
+      </c>
+      <c r="CB138" s="15" t="n">
+        <v>1604</v>
       </c>
       <c r="CC138" s="14" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="CD138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CF138" s="14" t="n">
-        <v>-2</v>
+      <c r="CF138" s="20" t="n">
+        <v>6386</v>
       </c>
       <c r="CG138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH138" s="14" t="n">
-        <v>-2</v>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="CH138" s="13" t="n">
+        <v>2041</v>
       </c>
       <c r="CI138" s="14" t="n">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="CJ138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL138" s="14" t="n">
-        <v>-2</v>
+      <c r="CL138" s="13" t="n">
+        <v>1220</v>
       </c>
       <c r="CM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN138" s="14" t="n">
-        <v>-2</v>
+        <v>95.09999999999999</v>
+      </c>
+      <c r="CN138" s="15" t="n">
+        <v>2344</v>
       </c>
       <c r="CO138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP138" s="14" t="n">
-        <v>-2</v>
+        <v>87.2</v>
+      </c>
+      <c r="CP138" s="15" t="n">
+        <v>920</v>
       </c>
       <c r="CQ138" s="14" t="n">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="CR138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CS138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CT138" s="14" t="n">
-        <v>-2</v>
+      <c r="CT138" s="15" t="n">
+        <v>445</v>
       </c>
       <c r="CU138" s="14" t="n">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="CV138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CX138" s="14" t="n">
-        <v>-2</v>
+      <c r="CX138" s="13" t="n">
+        <v>988</v>
       </c>
       <c r="CY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ138" s="14" t="n">
-        <v>-2</v>
+        <v>95.3</v>
+      </c>
+      <c r="CZ138" s="13" t="n">
+        <v>279</v>
       </c>
       <c r="DA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB138" s="14" t="n">
-        <v>-2</v>
+        <v>98.8</v>
+      </c>
+      <c r="DB138" s="15" t="n">
+        <v>589</v>
       </c>
       <c r="DC138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD138" s="14" t="n">
-        <v>-2</v>
+        <v>92.3</v>
+      </c>
+      <c r="DD138" s="15" t="n">
+        <v>841</v>
       </c>
       <c r="DE138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF138" s="14" t="n">
-        <v>-2</v>
+        <v>90.7</v>
+      </c>
+      <c r="DF138" s="20" t="n">
+        <v>7710</v>
       </c>
       <c r="DG138" s="14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="139">
@@ -44044,47 +44049,47 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>wawawamei</t>
+          <t>nK7WNyyDON</t>
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>636</v>
+        <v>54</v>
       </c>
       <c r="D139" s="27" t="n">
-        <v>1411</v>
+        <v>1418</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F139" s="19" t="n">
-        <v>-1</v>
+        <v>28.8</v>
+      </c>
+      <c r="F139" s="24" t="n">
+        <v>9516</v>
       </c>
       <c r="G139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="24" t="n">
-        <v>10801</v>
+        <v>40</v>
+      </c>
+      <c r="H139" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="I139" s="19" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="J139" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="J139" s="24" t="n">
+        <v>12325</v>
       </c>
       <c r="K139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="19" t="n">
-        <v>-1</v>
+        <v>17.6</v>
+      </c>
+      <c r="L139" s="24" t="n">
+        <v>10590</v>
       </c>
       <c r="M139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" s="19" t="n">
-        <v>-1</v>
+        <v>26.7</v>
+      </c>
+      <c r="N139" s="24" t="n">
+        <v>12929</v>
       </c>
       <c r="O139" s="19" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="P139" s="19" t="n">
         <v>-1</v>
@@ -44092,287 +44097,287 @@
       <c r="Q139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R139" s="19" t="n">
-        <v>-1</v>
+      <c r="R139" s="24" t="n">
+        <v>10441</v>
       </c>
       <c r="S139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="19" t="n">
-        <v>-1</v>
+        <v>31.1</v>
+      </c>
+      <c r="T139" s="24" t="n">
+        <v>12326</v>
       </c>
       <c r="U139" s="19" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="V139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="X139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Y139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Z139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AA139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AB139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AC139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AD139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AE139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AF139" s="20" t="n">
-        <v>4257</v>
+      <c r="AF139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AG139" s="19" t="n">
-        <v>67.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AJ139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AL139" s="24" t="n">
-        <v>21358</v>
+      <c r="AL139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AM139" s="19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AN139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AP139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AQ139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AR139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AT139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AV139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AX139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AZ139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BA139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BB139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BC139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BD139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BE139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BF139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BG139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH139" s="24" t="n">
-        <v>2653</v>
+      <c r="BH139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BI139" s="19" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="BJ139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BK139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BL139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BM139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BN139" s="20" t="n">
-        <v>18684</v>
+      <c r="BN139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BO139" s="19" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
       <c r="BP139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BQ139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BR139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BS139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BT139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BU139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BV139" s="24" t="n">
-        <v>20053</v>
+      <c r="BV139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BW139" s="19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BX139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BY139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BZ139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CA139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CB139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CC139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD139" s="24" t="n">
-        <v>16477</v>
+      <c r="CD139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CE139" s="19" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="CF139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CG139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CH139" s="24" t="n">
-        <v>20720</v>
+      <c r="CH139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CI139" s="19" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="CJ139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CK139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CL139" s="24" t="n">
-        <v>14803</v>
+      <c r="CL139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CM139" s="19" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="CN139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CO139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CP139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CR139" s="24" t="n">
-        <v>19936</v>
+      <c r="CR139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CS139" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CT139" s="20" t="n">
-        <v>8638</v>
+        <v>0</v>
+      </c>
+      <c r="CT139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CU139" s="19" t="n">
-        <v>53.7</v>
+        <v>0</v>
       </c>
       <c r="CV139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CW139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CX139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ139" s="24" t="n">
-        <v>13824</v>
+      <c r="CZ139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DA139" s="19" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="DB139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DC139" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DD139" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DE139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DF139" s="24" t="n">
-        <v>12726</v>
+      <c r="DF139" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG139" s="19" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -44381,335 +44386,335 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>kaijie_zhang</t>
+          <t>wawawamei</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>374</v>
+        <v>636</v>
       </c>
       <c r="D140" s="26" t="n">
-        <v>1698</v>
+        <v>1411</v>
       </c>
       <c r="E140" s="12" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="F140" s="24" t="n">
-        <v>14048</v>
+      <c r="F140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H140" s="14" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="H140" s="24" t="n">
+        <v>10801</v>
       </c>
       <c r="I140" s="14" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="J140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="N140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="R140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="T140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="V140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="W140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="Z140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AA140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AB140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AC140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AD140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AF140" s="14" t="n">
-        <v>-2</v>
+      <c r="AF140" s="20" t="n">
+        <v>4257</v>
       </c>
       <c r="AG140" s="14" t="n">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AH140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AJ140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AL140" s="14" t="n">
-        <v>-2</v>
+      <c r="AL140" s="24" t="n">
+        <v>21358</v>
       </c>
       <c r="AM140" s="14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AN140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AP140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AQ140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AR140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AT140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AV140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AX140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AY140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AZ140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BA140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BB140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BC140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BD140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BF140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH140" s="14" t="n">
-        <v>-2</v>
+      <c r="BH140" s="24" t="n">
+        <v>2653</v>
       </c>
       <c r="BI140" s="14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BJ140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BL140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BN140" s="14" t="n">
-        <v>-2</v>
+      <c r="BN140" s="20" t="n">
+        <v>18684</v>
       </c>
       <c r="BO140" s="14" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="BP140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BQ140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BR140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BT140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BU140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV140" s="14" t="n">
-        <v>-2</v>
+      <c r="BV140" s="24" t="n">
+        <v>20053</v>
       </c>
       <c r="BW140" s="14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BX140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BZ140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CA140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CB140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CD140" s="14" t="n">
-        <v>-2</v>
+      <c r="CD140" s="24" t="n">
+        <v>16477</v>
       </c>
       <c r="CE140" s="14" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="CF140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CG140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CH140" s="14" t="n">
-        <v>-2</v>
+      <c r="CH140" s="24" t="n">
+        <v>20720</v>
       </c>
       <c r="CI140" s="14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="CJ140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL140" s="14" t="n">
-        <v>-2</v>
+      <c r="CL140" s="24" t="n">
+        <v>14803</v>
       </c>
       <c r="CM140" s="14" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="CN140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CP140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CQ140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CR140" s="14" t="n">
-        <v>-2</v>
+      <c r="CR140" s="24" t="n">
+        <v>19936</v>
       </c>
       <c r="CS140" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT140" s="14" t="n">
-        <v>-2</v>
+        <v>10.5</v>
+      </c>
+      <c r="CT140" s="20" t="n">
+        <v>8638</v>
       </c>
       <c r="CU140" s="14" t="n">
-        <v>0</v>
+        <v>53.7</v>
       </c>
       <c r="CV140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CX140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CZ140" s="14" t="n">
-        <v>-2</v>
+      <c r="CZ140" s="24" t="n">
+        <v>13824</v>
       </c>
       <c r="DA140" s="14" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="DB140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC140" s="14" t="n">
         <v>0</v>
       </c>
       <c r="DD140" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DE140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DF140" s="14" t="n">
-        <v>-2</v>
+      <c r="DF140" s="24" t="n">
+        <v>12726</v>
       </c>
       <c r="DG140" s="14" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="141">
@@ -44718,23 +44723,23 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>googlehsiehhh</t>
+          <t>kaijie_zhang</t>
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1708</v>
+        <v>374</v>
       </c>
       <c r="D141" s="27" t="n">
-        <v>-1</v>
+        <v>1698</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="19" t="n">
-        <v>-1</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F141" s="24" t="n">
+        <v>14048</v>
       </c>
       <c r="G141" s="19" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="H141" s="19" t="n">
         <v>-1</v>
@@ -44743,315 +44748,310 @@
         <v>0</v>
       </c>
       <c r="J141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L141" s="20" t="n">
-        <v>2341</v>
+      <c r="L141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="M141" s="19" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="N141" s="20" t="n">
-        <v>1697</v>
+        <v>0</v>
+      </c>
+      <c r="N141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="O141" s="19" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="P141" s="15" t="n">
-        <v>1636</v>
+        <v>0</v>
+      </c>
+      <c r="P141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="Q141" s="19" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="R141" s="20" t="n">
-        <v>3367</v>
+        <v>0</v>
+      </c>
+      <c r="R141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="S141" s="19" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="T141" s="15" t="n">
-        <v>1116</v>
+        <v>0</v>
+      </c>
+      <c r="T141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="U141" s="19" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="V141" s="15" t="n">
-        <v>1114</v>
+        <v>0</v>
+      </c>
+      <c r="V141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="W141" s="19" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="X141" s="20" t="n">
-        <v>2316</v>
+        <v>0</v>
+      </c>
+      <c r="X141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="Y141" s="19" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="Z141" s="15" t="n">
-        <v>613</v>
+        <v>0</v>
+      </c>
+      <c r="Z141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AA141" s="19" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="AB141" s="20" t="n">
-        <v>1589</v>
+        <v>0</v>
+      </c>
+      <c r="AB141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AC141" s="19" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="AD141" s="15" t="n">
-        <v>1071</v>
+        <v>0</v>
+      </c>
+      <c r="AD141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AE141" s="19" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="AF141" s="15" t="n">
-        <v>541</v>
+        <v>0</v>
+      </c>
+      <c r="AF141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AG141" s="19" t="n">
-        <v>92.2</v>
+        <v>0</v>
       </c>
       <c r="AH141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ141" s="15" t="n">
-        <v>1588</v>
+      <c r="AJ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AK141" s="19" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="AL141" s="13" t="n">
-        <v>2180</v>
+        <v>0</v>
+      </c>
+      <c r="AL141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AM141" s="19" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="AN141" s="15" t="n">
-        <v>1407</v>
+        <v>0</v>
+      </c>
+      <c r="AN141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AO141" s="19" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="AP141" s="15" t="n">
-        <v>3650</v>
+        <v>0</v>
+      </c>
+      <c r="AP141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AQ141" s="19" t="n">
-        <v>82.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AT141" s="20" t="n">
-        <v>2431</v>
+      <c r="AT141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AU141" s="19" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="AV141" s="20" t="n">
-        <v>2509</v>
+        <v>0</v>
+      </c>
+      <c r="AV141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AW141" s="19" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="AX141" s="13" t="n">
-        <v>529</v>
+        <v>0</v>
+      </c>
+      <c r="AX141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AY141" s="19" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="AZ141" s="20" t="n">
-        <v>4336</v>
+        <v>0</v>
+      </c>
+      <c r="AZ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BA141" s="19" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="BB141" s="20" t="n">
-        <v>1127</v>
+        <v>0</v>
+      </c>
+      <c r="BB141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BC141" s="19" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="BD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BE141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BF141" s="13" t="n">
-        <v>791</v>
+      <c r="BF141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BG141" s="19" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="BH141" s="15" t="n">
-        <v>980</v>
+        <v>0</v>
+      </c>
+      <c r="BH141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BI141" s="19" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="BJ141" s="15" t="n">
-        <v>2535</v>
+        <v>0</v>
+      </c>
+      <c r="BJ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BK141" s="19" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="BL141" s="15" t="n">
-        <v>769</v>
+        <v>0</v>
+      </c>
+      <c r="BL141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BM141" s="19" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="BN141" s="15" t="n">
-        <v>2560</v>
+        <v>0</v>
+      </c>
+      <c r="BN141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BO141" s="19" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="BP141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BQ141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BR141" s="13" t="n">
-        <v>652</v>
+      <c r="BR141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BS141" s="19" t="n">
-        <v>97.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BU141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BV141" s="13" t="n">
-        <v>1329</v>
+      <c r="BV141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BW141" s="19" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="BX141" s="15" t="n">
-        <v>2382</v>
+        <v>0</v>
+      </c>
+      <c r="BX141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BY141" s="19" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="BZ141" s="15" t="n">
-        <v>931</v>
+        <v>0</v>
+      </c>
+      <c r="BZ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CA141" s="19" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="CB141" s="20" t="n">
-        <v>4252</v>
+        <v>0</v>
+      </c>
+      <c r="CB141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CC141" s="19" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="CD141" s="13" t="n">
-        <v>1170</v>
+        <v>0</v>
+      </c>
+      <c r="CD141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CE141" s="19" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="CF141" s="20" t="n">
-        <v>2641</v>
+        <v>0</v>
+      </c>
+      <c r="CF141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CG141" s="19" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="CH141" s="13" t="n">
-        <v>904</v>
+        <v>0</v>
+      </c>
+      <c r="CH141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CI141" s="19" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="CJ141" s="15" t="n">
-        <v>4508</v>
+        <v>0</v>
+      </c>
+      <c r="CJ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CK141" s="19" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="CL141" s="13" t="n">
-        <v>814</v>
+        <v>0</v>
+      </c>
+      <c r="CL141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CM141" s="19" t="n">
-        <v>96.7</v>
-      </c>
-      <c r="CN141" s="15" t="n">
-        <v>2892</v>
+        <v>0</v>
+      </c>
+      <c r="CN141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CO141" s="19" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="CP141" s="15" t="n">
-        <v>3061</v>
+        <v>0</v>
+      </c>
+      <c r="CP141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ141" s="19" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="CR141" s="13" t="n">
-        <v>1642</v>
+        <v>0</v>
+      </c>
+      <c r="CR141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CS141" s="19" t="n">
-        <v>93.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="CT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CV141" s="13" t="n">
-        <v>600</v>
+      <c r="CV141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CW141" s="19" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="CX141" s="13" t="n">
-        <v>1980</v>
+        <v>0</v>
+      </c>
+      <c r="CX141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CY141" s="19" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="CZ141" s="13" t="n">
-        <v>458</v>
+        <v>0</v>
+      </c>
+      <c r="CZ141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DA141" s="19" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="DB141" s="15" t="n">
-        <v>365</v>
+        <v>0</v>
+      </c>
+      <c r="DB141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DC141" s="19" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="DD141" s="15" t="n">
-        <v>838</v>
+        <v>0</v>
+      </c>
+      <c r="DD141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DE141" s="19" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="DF141" s="15" t="n">
-        <v>1495</v>
+        <v>0</v>
+      </c>
+      <c r="DF141" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG141" s="19" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="DH141" s="1" t="inlineStr">
-        <is>
-          <t>Google-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="142">

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:DH172"/>
+  <dimension ref="A2:DH173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -41660,335 +41660,340 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>user7754K</t>
+          <t>tinyfish1</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>88</v>
+        <v>2098</v>
       </c>
       <c r="D132" s="26" t="n">
-        <v>1593</v>
+        <v>-1</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="F132" s="25" t="n">
-        <v>15030</v>
+        <v>46</v>
+      </c>
+      <c r="F132" s="15" t="n">
+        <v>655</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H132" s="25" t="n">
-        <v>12575</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="H132" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="I132" s="14" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J132" s="20" t="n">
-        <v>3809</v>
+        <v>0</v>
+      </c>
+      <c r="J132" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="L132" s="25" t="n">
-        <v>12025</v>
+        <v>0</v>
+      </c>
+      <c r="L132" s="13" t="n">
+        <v>154</v>
       </c>
       <c r="M132" s="14" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N132" s="20" t="n">
-        <v>5731</v>
+        <v>99.2</v>
+      </c>
+      <c r="N132" s="13" t="n">
+        <v>531</v>
       </c>
       <c r="O132" s="14" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="P132" s="20" t="n">
-        <v>4422</v>
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P132" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Q132" s="14" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="R132" s="20" t="n">
-        <v>5674</v>
+        <v>0</v>
+      </c>
+      <c r="R132" s="15" t="n">
+        <v>1186</v>
       </c>
       <c r="S132" s="14" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="T132" s="20" t="n">
-        <v>5040</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="T132" s="13" t="n">
+        <v>302</v>
       </c>
       <c r="U132" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="V132" s="20" t="n">
-        <v>6495</v>
+        <v>98.40000000000001</v>
+      </c>
+      <c r="V132" s="15" t="n">
+        <v>1179</v>
       </c>
       <c r="W132" s="14" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="X132" s="20" t="n">
-        <v>6696</v>
+        <v>88.5</v>
+      </c>
+      <c r="X132" s="15" t="n">
+        <v>104</v>
       </c>
       <c r="Y132" s="14" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="Z132" s="20" t="n">
-        <v>9509</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z132" s="15" t="n">
+        <v>1022</v>
       </c>
       <c r="AA132" s="14" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="AB132" s="25" t="n">
-        <v>9551</v>
+        <v>90.2</v>
+      </c>
+      <c r="AB132" s="15" t="n">
+        <v>552</v>
       </c>
       <c r="AC132" s="14" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="AD132" s="14" t="n">
-        <v>-1</v>
+        <v>92.5</v>
+      </c>
+      <c r="AD132" s="15" t="n">
+        <v>922</v>
       </c>
       <c r="AE132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" s="14" t="n">
-        <v>-2</v>
+        <v>89.3</v>
+      </c>
+      <c r="AF132" s="15" t="n">
+        <v>2707</v>
       </c>
       <c r="AG132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" s="14" t="n">
-        <v>-2</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="AH132" s="13" t="n">
+        <v>198</v>
       </c>
       <c r="AI132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" s="14" t="n">
-        <v>-2</v>
+        <v>99</v>
+      </c>
+      <c r="AJ132" s="15" t="n">
+        <v>285</v>
       </c>
       <c r="AK132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" s="14" t="n">
-        <v>-2</v>
+        <v>93.8</v>
+      </c>
+      <c r="AL132" s="13" t="n">
+        <v>482</v>
       </c>
       <c r="AM132" s="14" t="n">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="AN132" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP132" s="14" t="n">
-        <v>-2</v>
+      <c r="AP132" s="15" t="n">
+        <v>546</v>
       </c>
       <c r="AQ132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR132" s="14" t="n">
-        <v>-2</v>
+        <v>93.2</v>
+      </c>
+      <c r="AR132" s="15" t="n">
+        <v>1042</v>
       </c>
       <c r="AS132" s="14" t="n">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="AT132" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV132" s="14" t="n">
-        <v>-2</v>
+      <c r="AV132" s="15" t="n">
+        <v>232</v>
       </c>
       <c r="AW132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX132" s="14" t="n">
-        <v>-2</v>
+        <v>94.2</v>
+      </c>
+      <c r="AX132" s="15" t="n">
+        <v>285</v>
       </c>
       <c r="AY132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ132" s="14" t="n">
-        <v>-2</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AZ132" s="13" t="n">
+        <v>791</v>
       </c>
       <c r="BA132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB132" s="14" t="n">
-        <v>-2</v>
+        <v>97.5</v>
+      </c>
+      <c r="BB132" s="15" t="n">
+        <v>298</v>
       </c>
       <c r="BC132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD132" s="14" t="n">
-        <v>-2</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="BD132" s="20" t="n">
+        <v>2425</v>
       </c>
       <c r="BE132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF132" s="14" t="n">
-        <v>-2</v>
+        <v>82.5</v>
+      </c>
+      <c r="BF132" s="15" t="n">
+        <v>799</v>
       </c>
       <c r="BG132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH132" s="14" t="n">
-        <v>-2</v>
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BH132" s="13" t="n">
+        <v>349</v>
       </c>
       <c r="BI132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ132" s="14" t="n">
-        <v>-2</v>
+        <v>89.8</v>
+      </c>
+      <c r="BJ132" s="15" t="n">
+        <v>522</v>
       </c>
       <c r="BK132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL132" s="14" t="n">
-        <v>-2</v>
+        <v>80</v>
+      </c>
+      <c r="BL132" s="15" t="n">
+        <v>3221</v>
       </c>
       <c r="BM132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN132" s="14" t="n">
-        <v>-2</v>
+        <v>80</v>
+      </c>
+      <c r="BN132" s="13" t="n">
+        <v>194</v>
       </c>
       <c r="BO132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP132" s="14" t="n">
-        <v>-2</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BP132" s="13" t="n">
+        <v>1462</v>
       </c>
       <c r="BQ132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR132" s="14" t="n">
-        <v>-2</v>
+        <v>95.7</v>
+      </c>
+      <c r="BR132" s="15" t="n">
+        <v>1431</v>
       </c>
       <c r="BS132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT132" s="14" t="n">
-        <v>-2</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="BT132" s="13" t="n">
+        <v>1691</v>
       </c>
       <c r="BU132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV132" s="14" t="n">
-        <v>-2</v>
+        <v>94.7</v>
+      </c>
+      <c r="BV132" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="BW132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX132" s="14" t="n">
-        <v>-2</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BX132" s="13" t="n">
+        <v>259</v>
       </c>
       <c r="BY132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ132" s="14" t="n">
-        <v>-2</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BZ132" s="15" t="n">
+        <v>1196</v>
       </c>
       <c r="CA132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB132" s="14" t="n">
-        <v>-2</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="CB132" s="15" t="n">
+        <v>1600</v>
       </c>
       <c r="CC132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD132" s="14" t="n">
-        <v>-2</v>
+        <v>88.2</v>
+      </c>
+      <c r="CD132" s="13" t="n">
+        <v>151</v>
       </c>
       <c r="CE132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF132" s="14" t="n">
-        <v>-2</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="CF132" s="13" t="n">
+        <v>150</v>
       </c>
       <c r="CG132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH132" s="14" t="n">
-        <v>-2</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="CH132" s="15" t="n">
+        <v>574</v>
       </c>
       <c r="CI132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ132" s="14" t="n">
-        <v>-2</v>
+        <v>92.8</v>
+      </c>
+      <c r="CJ132" s="13" t="n">
+        <v>113</v>
       </c>
       <c r="CK132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL132" s="14" t="n">
-        <v>-2</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CL132" s="13" t="n">
+        <v>592</v>
       </c>
       <c r="CM132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN132" s="14" t="n">
-        <v>-2</v>
+        <v>98</v>
+      </c>
+      <c r="CN132" s="13" t="n">
+        <v>65</v>
       </c>
       <c r="CO132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP132" s="14" t="n">
-        <v>-2</v>
+        <v>99.7</v>
+      </c>
+      <c r="CP132" s="13" t="n">
+        <v>156</v>
       </c>
       <c r="CQ132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR132" s="14" t="n">
-        <v>-2</v>
+        <v>99.5</v>
+      </c>
+      <c r="CR132" s="13" t="n">
+        <v>140</v>
       </c>
       <c r="CS132" s="14" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="CT132" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV132" s="14" t="n">
-        <v>-2</v>
+      <c r="CV132" s="15" t="n">
+        <v>235</v>
       </c>
       <c r="CW132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX132" s="14" t="n">
-        <v>-2</v>
+        <v>94</v>
+      </c>
+      <c r="CX132" s="13" t="n">
+        <v>119</v>
       </c>
       <c r="CY132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ132" s="14" t="n">
-        <v>-2</v>
+        <v>99.5</v>
+      </c>
+      <c r="CZ132" s="13" t="n">
+        <v>117</v>
       </c>
       <c r="DA132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB132" s="14" t="n">
-        <v>-2</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="DB132" s="13" t="n">
+        <v>649</v>
       </c>
       <c r="DC132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD132" s="14" t="n">
-        <v>-2</v>
+        <v>97.3</v>
+      </c>
+      <c r="DD132" s="13" t="n">
+        <v>105</v>
       </c>
       <c r="DE132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF132" s="14" t="n">
-        <v>-2</v>
+        <v>99.5</v>
+      </c>
+      <c r="DF132" s="15" t="n">
+        <v>1237</v>
       </c>
       <c r="DG132" s="14" t="n">
-        <v>0</v>
+        <v>88.7</v>
+      </c>
+      <c r="DH132" s="1" t="inlineStr">
+        <is>
+          <t>Snapchat-Logo</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -41997,29 +42002,29 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>randytanpty</t>
+          <t>lrcwxy</t>
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="D133" s="27" t="n">
-        <v>2089</v>
+        <v>1730</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="F133" s="19" t="n">
-        <v>-1</v>
+        <v>46</v>
+      </c>
+      <c r="F133" s="15" t="n">
+        <v>641</v>
       </c>
       <c r="G133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="20" t="n">
-        <v>2054</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="H133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="I133" s="19" t="n">
-        <v>80.2</v>
+        <v>0</v>
       </c>
       <c r="J133" s="19" t="n">
         <v>-1</v>
@@ -42027,305 +42032,310 @@
       <c r="K133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L133" s="20" t="n">
-        <v>4898</v>
+      <c r="L133" s="15" t="n">
+        <v>603</v>
       </c>
       <c r="M133" s="19" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="N133" s="20" t="n">
-        <v>1765</v>
+        <v>91.7</v>
+      </c>
+      <c r="N133" s="15" t="n">
+        <v>906</v>
       </c>
       <c r="O133" s="19" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="P133" s="20" t="n">
-        <v>2060</v>
+        <v>90</v>
+      </c>
+      <c r="P133" s="15" t="n">
+        <v>392</v>
       </c>
       <c r="Q133" s="19" t="n">
-        <v>79.5</v>
+        <v>93</v>
       </c>
       <c r="R133" s="15" t="n">
-        <v>1206</v>
+        <v>1643</v>
       </c>
       <c r="S133" s="19" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="T133" s="19" t="n">
-        <v>-1</v>
+        <v>86.2</v>
+      </c>
+      <c r="T133" s="15" t="n">
+        <v>1585</v>
       </c>
       <c r="U133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="20" t="n">
-        <v>3372</v>
+        <v>86.8</v>
+      </c>
+      <c r="V133" s="15" t="n">
+        <v>2028</v>
       </c>
       <c r="W133" s="19" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="X133" s="15" t="n">
-        <v>1360</v>
+        <v>83.8</v>
+      </c>
+      <c r="X133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y133" s="19" t="n">
-        <v>87.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="15" t="n">
-        <v>750</v>
+        <v>1045</v>
       </c>
       <c r="AA133" s="19" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="AB133" s="19" t="n">
-        <v>-1</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="AB133" s="13" t="n">
+        <v>179</v>
       </c>
       <c r="AC133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" s="20" t="n">
-        <v>1341</v>
+        <v>99.2</v>
+      </c>
+      <c r="AD133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AE133" s="19" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="AF133" s="15" t="n">
-        <v>2127</v>
+        <v>0</v>
+      </c>
+      <c r="AF133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AG133" s="19" t="n">
-        <v>86.7</v>
+        <v>0</v>
       </c>
       <c r="AH133" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ133" s="25" t="n">
-        <v>9920</v>
+      <c r="AJ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AK133" s="19" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="AL133" s="13" t="n">
-        <v>511</v>
+        <v>0</v>
+      </c>
+      <c r="AL133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AM133" s="19" t="n">
-        <v>98.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN133" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP133" s="15" t="n">
-        <v>1114</v>
+      <c r="AP133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AQ133" s="19" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="AR133" s="15" t="n">
-        <v>731</v>
+        <v>0</v>
+      </c>
+      <c r="AR133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AS133" s="19" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="AT133" s="20" t="n">
-        <v>5134</v>
+        <v>0</v>
+      </c>
+      <c r="AT133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AU133" s="19" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="AV133" s="15" t="n">
-        <v>461</v>
+        <v>0</v>
+      </c>
+      <c r="AV133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AW133" s="19" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="AX133" s="20" t="n">
-        <v>11247</v>
+        <v>0</v>
+      </c>
+      <c r="AX133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AY133" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AZ133" s="13" t="n">
-        <v>978</v>
+        <v>0</v>
+      </c>
+      <c r="AZ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BA133" s="19" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="BB133" s="15" t="n">
-        <v>1174</v>
+        <v>0</v>
+      </c>
+      <c r="BB133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BC133" s="19" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="BD133" s="20" t="n">
-        <v>1230</v>
+        <v>0</v>
+      </c>
+      <c r="BD133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BE133" s="19" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="BF133" s="15" t="n">
-        <v>959</v>
+        <v>0</v>
+      </c>
+      <c r="BF133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BG133" s="19" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="BH133" s="13" t="n">
-        <v>848</v>
+        <v>0</v>
+      </c>
+      <c r="BH133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BI133" s="19" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="BJ133" s="13" t="n">
-        <v>213</v>
+        <v>0</v>
+      </c>
+      <c r="BJ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BK133" s="19" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="BL133" s="20" t="n">
-        <v>4513</v>
+        <v>0</v>
+      </c>
+      <c r="BL133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BM133" s="19" t="n">
-        <v>69</v>
-      </c>
-      <c r="BN133" s="15" t="n">
-        <v>1859</v>
+        <v>0</v>
+      </c>
+      <c r="BN133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BO133" s="19" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="BP133" s="13" t="n">
-        <v>1090</v>
+        <v>0</v>
+      </c>
+      <c r="BP133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ133" s="19" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="BR133" s="15" t="n">
-        <v>1510</v>
+        <v>0</v>
+      </c>
+      <c r="BR133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BS133" s="19" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="BT133" s="15" t="n">
-        <v>2021</v>
+        <v>0</v>
+      </c>
+      <c r="BT133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BU133" s="19" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="BV133" s="15" t="n">
-        <v>5121</v>
+        <v>0</v>
+      </c>
+      <c r="BV133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BW133" s="19" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="BX133" s="13" t="n">
-        <v>1869</v>
+        <v>0</v>
+      </c>
+      <c r="BX133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BY133" s="19" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="BZ133" s="15" t="n">
-        <v>1936</v>
+        <v>0</v>
+      </c>
+      <c r="BZ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CA133" s="19" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="CB133" s="15" t="n">
-        <v>1574</v>
+        <v>0</v>
+      </c>
+      <c r="CB133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CC133" s="19" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="CD133" s="15" t="n">
-        <v>1329</v>
+        <v>0</v>
+      </c>
+      <c r="CD133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CE133" s="19" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="CF133" s="15" t="n">
-        <v>3485</v>
+        <v>0</v>
+      </c>
+      <c r="CF133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CG133" s="19" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="CH133" s="20" t="n">
-        <v>3426</v>
+        <v>0</v>
+      </c>
+      <c r="CH133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CI133" s="19" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="CJ133" s="13" t="n">
-        <v>1481</v>
+        <v>0</v>
+      </c>
+      <c r="CJ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CK133" s="19" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="CL133" s="15" t="n">
-        <v>1926</v>
+        <v>0</v>
+      </c>
+      <c r="CL133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CM133" s="19" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="CN133" s="13" t="n">
-        <v>1411</v>
+        <v>0</v>
+      </c>
+      <c r="CN133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CO133" s="19" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="CP133" s="15" t="n">
-        <v>651</v>
+        <v>0</v>
+      </c>
+      <c r="CP133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ133" s="19" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="CR133" s="15" t="n">
-        <v>1006</v>
+        <v>0</v>
+      </c>
+      <c r="CR133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CS133" s="19" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="CT133" s="15" t="n">
-        <v>5393</v>
+        <v>0</v>
+      </c>
+      <c r="CT133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CU133" s="19" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="CV133" s="15" t="n">
-        <v>1079</v>
+        <v>0</v>
+      </c>
+      <c r="CV133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CW133" s="19" t="n">
-        <v>90.5</v>
+        <v>0</v>
       </c>
       <c r="CX133" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ133" s="15" t="n">
-        <v>4818</v>
+      <c r="CZ133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DA133" s="19" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="DB133" s="15" t="n">
-        <v>1961</v>
+        <v>0</v>
+      </c>
+      <c r="DB133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DC133" s="19" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="DD133" s="15" t="n">
-        <v>1025</v>
+        <v>0</v>
+      </c>
+      <c r="DD133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DE133" s="19" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="DF133" s="20" t="n">
-        <v>7317</v>
+        <v>0</v>
+      </c>
+      <c r="DF133" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG133" s="19" t="n">
-        <v>52.7</v>
+        <v>0</v>
+      </c>
+      <c r="DH133" s="1" t="inlineStr">
+        <is>
+          <t>Amazon-Logo</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -42334,340 +42344,335 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>lichuan199010</t>
+          <t>user7754K</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1968</v>
+        <v>88</v>
       </c>
       <c r="D134" s="26" t="n">
-        <v>1846</v>
+        <v>1593</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F134" s="20" t="n">
-        <v>2891</v>
+        <v>45.7</v>
+      </c>
+      <c r="F134" s="25" t="n">
+        <v>15030</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="H134" s="14" t="n">
-        <v>-1</v>
+        <v>18.2</v>
+      </c>
+      <c r="H134" s="25" t="n">
+        <v>12575</v>
       </c>
       <c r="I134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="14" t="n">
-        <v>-1</v>
+        <v>24.8</v>
+      </c>
+      <c r="J134" s="20" t="n">
+        <v>3809</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="13" t="n">
-        <v>208</v>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="L134" s="25" t="n">
+        <v>12025</v>
       </c>
       <c r="M134" s="14" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="N134" s="13" t="n">
-        <v>182</v>
+        <v>19.3</v>
+      </c>
+      <c r="N134" s="20" t="n">
+        <v>5731</v>
       </c>
       <c r="O134" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="P134" s="14" t="n">
-        <v>-1</v>
+        <v>58.4</v>
+      </c>
+      <c r="P134" s="20" t="n">
+        <v>4422</v>
       </c>
       <c r="Q134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" s="15" t="n">
-        <v>683</v>
+        <v>67.5</v>
+      </c>
+      <c r="R134" s="20" t="n">
+        <v>5674</v>
       </c>
       <c r="S134" s="14" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="T134" s="13" t="n">
-        <v>737</v>
+        <v>59.6</v>
+      </c>
+      <c r="T134" s="20" t="n">
+        <v>5040</v>
       </c>
       <c r="U134" s="14" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="V134" s="15" t="n">
-        <v>1239</v>
+        <v>64</v>
+      </c>
+      <c r="V134" s="20" t="n">
+        <v>6495</v>
       </c>
       <c r="W134" s="14" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="X134" s="15" t="n">
-        <v>1132</v>
+        <v>54.2</v>
+      </c>
+      <c r="X134" s="20" t="n">
+        <v>6696</v>
       </c>
       <c r="Y134" s="14" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z134" s="15" t="n">
-        <v>1329</v>
+        <v>53.4</v>
+      </c>
+      <c r="Z134" s="20" t="n">
+        <v>9509</v>
       </c>
       <c r="AA134" s="14" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="AB134" s="15" t="n">
-        <v>2196</v>
+        <v>45.7</v>
+      </c>
+      <c r="AB134" s="25" t="n">
+        <v>9551</v>
       </c>
       <c r="AC134" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AD134" s="13" t="n">
-        <v>187</v>
+        <v>41.4</v>
+      </c>
+      <c r="AD134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AE134" s="14" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="AF134" s="20" t="n">
-        <v>5350</v>
+        <v>0</v>
+      </c>
+      <c r="AF134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AG134" s="14" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="AH134" s="15" t="n">
-        <v>533</v>
+        <v>0</v>
+      </c>
+      <c r="AH134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AI134" s="14" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="AJ134" s="20" t="n">
-        <v>4847</v>
+        <v>0</v>
+      </c>
+      <c r="AJ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AK134" s="14" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AL134" s="13" t="n">
-        <v>613</v>
+        <v>0</v>
+      </c>
+      <c r="AL134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AM134" s="14" t="n">
-        <v>97.7</v>
+        <v>0</v>
       </c>
       <c r="AN134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP134" s="15" t="n">
-        <v>449</v>
+      <c r="AP134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AQ134" s="14" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="AR134" s="15" t="n">
-        <v>1602</v>
+        <v>0</v>
+      </c>
+      <c r="AR134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AS134" s="14" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="AT134" s="15" t="n">
-        <v>647</v>
+        <v>0</v>
+      </c>
+      <c r="AT134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AU134" s="14" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="AV134" s="20" t="n">
-        <v>1094</v>
+        <v>0</v>
+      </c>
+      <c r="AV134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AW134" s="14" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="AX134" s="15" t="n">
-        <v>969</v>
+        <v>0</v>
+      </c>
+      <c r="AX134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AY134" s="14" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="AZ134" s="15" t="n">
-        <v>3703</v>
+        <v>0</v>
+      </c>
+      <c r="AZ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BA134" s="14" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="BB134" s="15" t="n">
-        <v>317</v>
+        <v>0</v>
+      </c>
+      <c r="BB134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BC134" s="14" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="BD134" s="20" t="n">
-        <v>3825</v>
+        <v>0</v>
+      </c>
+      <c r="BD134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BE134" s="14" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="BF134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BG134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH134" s="13" t="n">
-        <v>352</v>
+      <c r="BH134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BI134" s="14" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="BJ134" s="15" t="n">
-        <v>701</v>
+        <v>0</v>
+      </c>
+      <c r="BJ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BK134" s="14" t="n">
-        <v>74.8</v>
+        <v>0</v>
       </c>
       <c r="BL134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BM134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BN134" s="13" t="n">
-        <v>306</v>
+      <c r="BN134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BO134" s="14" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="BP134" s="13" t="n">
-        <v>1615</v>
+        <v>0</v>
+      </c>
+      <c r="BP134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ134" s="14" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="BR134" s="15" t="n">
-        <v>619</v>
+        <v>0</v>
+      </c>
+      <c r="BR134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BS134" s="14" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="BT134" s="13" t="n">
-        <v>1314</v>
+        <v>0</v>
+      </c>
+      <c r="BT134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BU134" s="14" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="BV134" s="15" t="n">
-        <v>1013</v>
+        <v>0</v>
+      </c>
+      <c r="BV134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BW134" s="14" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="BX134" s="13" t="n">
-        <v>1900</v>
+        <v>0</v>
+      </c>
+      <c r="BX134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BY134" s="14" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="BZ134" s="15" t="n">
-        <v>1213</v>
+        <v>0</v>
+      </c>
+      <c r="BZ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CA134" s="14" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="CB134" s="20" t="n">
-        <v>3784</v>
+        <v>0</v>
+      </c>
+      <c r="CB134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CC134" s="14" t="n">
-        <v>74</v>
-      </c>
-      <c r="CD134" s="13" t="n">
-        <v>218</v>
+        <v>0</v>
+      </c>
+      <c r="CD134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CE134" s="14" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="CF134" s="13" t="n">
-        <v>1865</v>
+        <v>0</v>
+      </c>
+      <c r="CF134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CG134" s="14" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="CH134" s="15" t="n">
-        <v>545</v>
+        <v>0</v>
+      </c>
+      <c r="CH134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CI134" s="14" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="CJ134" s="13" t="n">
-        <v>948</v>
+        <v>0</v>
+      </c>
+      <c r="CJ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CK134" s="14" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="CL134" s="13" t="n">
-        <v>811</v>
+        <v>0</v>
+      </c>
+      <c r="CL134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CM134" s="14" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="CN134" s="13" t="n">
-        <v>660</v>
+        <v>0</v>
+      </c>
+      <c r="CN134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CO134" s="14" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="CP134" s="15" t="n">
-        <v>654</v>
+        <v>0</v>
+      </c>
+      <c r="CP134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ134" s="14" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="CR134" s="13" t="n">
-        <v>123</v>
+        <v>0</v>
+      </c>
+      <c r="CR134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CS134" s="14" t="n">
-        <v>99.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CT134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV134" s="15" t="n">
-        <v>429</v>
+      <c r="CV134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CW134" s="14" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="CX134" s="13" t="n">
-        <v>296</v>
+        <v>0</v>
+      </c>
+      <c r="CX134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CY134" s="14" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="CZ134" s="13" t="n">
-        <v>721</v>
+        <v>0</v>
+      </c>
+      <c r="CZ134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DA134" s="14" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="DB134" s="15" t="n">
-        <v>1301</v>
+        <v>0</v>
+      </c>
+      <c r="DB134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DC134" s="14" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="DD134" s="15" t="n">
-        <v>1024</v>
+        <v>0</v>
+      </c>
+      <c r="DD134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DE134" s="14" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="DF134" s="15" t="n">
-        <v>2225</v>
+        <v>0</v>
+      </c>
+      <c r="DF134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DG134" s="14" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="DH134" s="1" t="inlineStr">
-        <is>
-          <t>Coupang-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -42676,340 +42681,335 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Golden_Fish</t>
+          <t>randytanpty</t>
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>10</v>
+        <v>424</v>
       </c>
       <c r="D135" s="27" t="n">
-        <v>1688</v>
+        <v>2089</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="F135" s="25" t="n">
-        <v>11261</v>
+        <v>40.1</v>
+      </c>
+      <c r="F135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="G135" s="19" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="H135" s="25" t="n">
-        <v>10448</v>
+        <v>0</v>
+      </c>
+      <c r="H135" s="20" t="n">
+        <v>2054</v>
       </c>
       <c r="I135" s="19" t="n">
-        <v>35</v>
+        <v>80.2</v>
       </c>
       <c r="J135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L135" s="19" t="n">
-        <v>-2</v>
+      <c r="L135" s="20" t="n">
+        <v>4898</v>
       </c>
       <c r="M135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="19" t="n">
-        <v>-2</v>
+        <v>63.2</v>
+      </c>
+      <c r="N135" s="20" t="n">
+        <v>1765</v>
       </c>
       <c r="O135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="19" t="n">
-        <v>-2</v>
+        <v>80.3</v>
+      </c>
+      <c r="P135" s="20" t="n">
+        <v>2060</v>
       </c>
       <c r="Q135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" s="19" t="n">
-        <v>-2</v>
+        <v>79.5</v>
+      </c>
+      <c r="R135" s="15" t="n">
+        <v>1206</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="T135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="19" t="n">
-        <v>-2</v>
+      <c r="V135" s="20" t="n">
+        <v>3372</v>
       </c>
       <c r="W135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="19" t="n">
-        <v>-2</v>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="X135" s="15" t="n">
+        <v>1360</v>
       </c>
       <c r="Y135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" s="19" t="n">
-        <v>-2</v>
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z135" s="15" t="n">
+        <v>750</v>
       </c>
       <c r="AA135" s="19" t="n">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="AB135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AC135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AD135" s="19" t="n">
-        <v>-2</v>
+      <c r="AD135" s="20" t="n">
+        <v>1341</v>
       </c>
       <c r="AE135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" s="19" t="n">
-        <v>-2</v>
+        <v>81.7</v>
+      </c>
+      <c r="AF135" s="15" t="n">
+        <v>2127</v>
       </c>
       <c r="AG135" s="19" t="n">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="AH135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ135" s="19" t="n">
-        <v>-2</v>
+      <c r="AJ135" s="25" t="n">
+        <v>9920</v>
       </c>
       <c r="AK135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL135" s="19" t="n">
-        <v>-2</v>
+        <v>43.9</v>
+      </c>
+      <c r="AL135" s="13" t="n">
+        <v>511</v>
       </c>
       <c r="AM135" s="19" t="n">
-        <v>0</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AN135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP135" s="19" t="n">
-        <v>-2</v>
+      <c r="AP135" s="15" t="n">
+        <v>1114</v>
       </c>
       <c r="AQ135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR135" s="19" t="n">
-        <v>-2</v>
+        <v>91.40000000000001</v>
+      </c>
+      <c r="AR135" s="15" t="n">
+        <v>731</v>
       </c>
       <c r="AS135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT135" s="19" t="n">
-        <v>-2</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="AT135" s="20" t="n">
+        <v>5134</v>
       </c>
       <c r="AU135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV135" s="19" t="n">
-        <v>-2</v>
+        <v>73.2</v>
+      </c>
+      <c r="AV135" s="15" t="n">
+        <v>461</v>
       </c>
       <c r="AW135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" s="19" t="n">
-        <v>-2</v>
+        <v>93.5</v>
+      </c>
+      <c r="AX135" s="20" t="n">
+        <v>11247</v>
       </c>
       <c r="AY135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" s="19" t="n">
-        <v>-2</v>
+        <v>48</v>
+      </c>
+      <c r="AZ135" s="13" t="n">
+        <v>978</v>
       </c>
       <c r="BA135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB135" s="19" t="n">
-        <v>-2</v>
+        <v>96.90000000000001</v>
+      </c>
+      <c r="BB135" s="15" t="n">
+        <v>1174</v>
       </c>
       <c r="BC135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD135" s="19" t="n">
-        <v>-2</v>
+        <v>90.7</v>
+      </c>
+      <c r="BD135" s="20" t="n">
+        <v>1230</v>
       </c>
       <c r="BE135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF135" s="19" t="n">
-        <v>-2</v>
+        <v>86.2</v>
+      </c>
+      <c r="BF135" s="15" t="n">
+        <v>959</v>
       </c>
       <c r="BG135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH135" s="19" t="n">
-        <v>-2</v>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="BH135" s="13" t="n">
+        <v>848</v>
       </c>
       <c r="BI135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ135" s="19" t="n">
-        <v>-2</v>
+        <v>75.2</v>
+      </c>
+      <c r="BJ135" s="13" t="n">
+        <v>213</v>
       </c>
       <c r="BK135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL135" s="19" t="n">
-        <v>-2</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="BL135" s="20" t="n">
+        <v>4513</v>
       </c>
       <c r="BM135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN135" s="19" t="n">
-        <v>-2</v>
+        <v>69</v>
+      </c>
+      <c r="BN135" s="15" t="n">
+        <v>1859</v>
       </c>
       <c r="BO135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP135" s="19" t="n">
-        <v>-2</v>
+        <v>89.5</v>
+      </c>
+      <c r="BP135" s="13" t="n">
+        <v>1090</v>
       </c>
       <c r="BQ135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR135" s="19" t="n">
-        <v>-2</v>
+        <v>96.8</v>
+      </c>
+      <c r="BR135" s="15" t="n">
+        <v>1510</v>
       </c>
       <c r="BS135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT135" s="19" t="n">
-        <v>-2</v>
+        <v>90.3</v>
+      </c>
+      <c r="BT135" s="15" t="n">
+        <v>2021</v>
       </c>
       <c r="BU135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV135" s="19" t="n">
-        <v>-2</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BV135" s="15" t="n">
+        <v>5121</v>
       </c>
       <c r="BW135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX135" s="19" t="n">
-        <v>-2</v>
+        <v>78.2</v>
+      </c>
+      <c r="BX135" s="13" t="n">
+        <v>1869</v>
       </c>
       <c r="BY135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ135" s="19" t="n">
-        <v>-2</v>
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BZ135" s="15" t="n">
+        <v>1936</v>
       </c>
       <c r="CA135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB135" s="19" t="n">
-        <v>-2</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="CB135" s="15" t="n">
+        <v>1574</v>
       </c>
       <c r="CC135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD135" s="19" t="n">
-        <v>-2</v>
+        <v>88.3</v>
+      </c>
+      <c r="CD135" s="15" t="n">
+        <v>1329</v>
       </c>
       <c r="CE135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF135" s="19" t="n">
-        <v>-2</v>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="CF135" s="15" t="n">
+        <v>3485</v>
       </c>
       <c r="CG135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH135" s="19" t="n">
-        <v>-2</v>
+        <v>81.8</v>
+      </c>
+      <c r="CH135" s="20" t="n">
+        <v>3426</v>
       </c>
       <c r="CI135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ135" s="19" t="n">
-        <v>-2</v>
+        <v>76.8</v>
+      </c>
+      <c r="CJ135" s="13" t="n">
+        <v>1481</v>
       </c>
       <c r="CK135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL135" s="19" t="n">
-        <v>-2</v>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="CL135" s="15" t="n">
+        <v>1926</v>
       </c>
       <c r="CM135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN135" s="19" t="n">
-        <v>-2</v>
+        <v>88.5</v>
+      </c>
+      <c r="CN135" s="13" t="n">
+        <v>1411</v>
       </c>
       <c r="CO135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP135" s="19" t="n">
-        <v>-2</v>
+        <v>94.3</v>
+      </c>
+      <c r="CP135" s="15" t="n">
+        <v>651</v>
       </c>
       <c r="CQ135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR135" s="19" t="n">
-        <v>-2</v>
+        <v>92.8</v>
+      </c>
+      <c r="CR135" s="15" t="n">
+        <v>1006</v>
       </c>
       <c r="CS135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT135" s="19" t="n">
-        <v>-2</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="CT135" s="15" t="n">
+        <v>5393</v>
       </c>
       <c r="CU135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV135" s="19" t="n">
-        <v>-2</v>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="CV135" s="15" t="n">
+        <v>1079</v>
       </c>
       <c r="CW135" s="19" t="n">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="CX135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ135" s="19" t="n">
-        <v>-2</v>
+      <c r="CZ135" s="15" t="n">
+        <v>4818</v>
       </c>
       <c r="DA135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB135" s="19" t="n">
-        <v>-2</v>
+        <v>72.3</v>
+      </c>
+      <c r="DB135" s="15" t="n">
+        <v>1961</v>
       </c>
       <c r="DC135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD135" s="19" t="n">
-        <v>-2</v>
+        <v>86.7</v>
+      </c>
+      <c r="DD135" s="15" t="n">
+        <v>1025</v>
       </c>
       <c r="DE135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF135" s="19" t="n">
-        <v>-2</v>
+        <v>90.3</v>
+      </c>
+      <c r="DF135" s="20" t="n">
+        <v>7317</v>
       </c>
       <c r="DG135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH135" s="1" t="inlineStr">
-        <is>
-          <t>Facebook-Logo</t>
-        </is>
+        <v>52.7</v>
       </c>
     </row>
     <row r="136">
@@ -43018,23 +43018,23 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>gude8997</t>
+          <t>lichuan199010</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>1019</v>
+        <v>1968</v>
       </c>
       <c r="D136" s="26" t="n">
-        <v>2052</v>
+        <v>1846</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="F136" s="25" t="n">
-        <v>3988</v>
+        <v>38.5</v>
+      </c>
+      <c r="F136" s="20" t="n">
+        <v>2891</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>67.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H136" s="14" t="n">
         <v>-1</v>
@@ -43048,17 +43048,17 @@
       <c r="K136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L136" s="14" t="n">
-        <v>-1</v>
+      <c r="L136" s="13" t="n">
+        <v>208</v>
       </c>
       <c r="M136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="14" t="n">
-        <v>-1</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="N136" s="13" t="n">
+        <v>182</v>
       </c>
       <c r="O136" s="14" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="P136" s="14" t="n">
         <v>-1</v>
@@ -43066,125 +43066,125 @@
       <c r="Q136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="R136" s="25" t="n">
-        <v>6778</v>
+      <c r="R136" s="15" t="n">
+        <v>683</v>
       </c>
       <c r="S136" s="14" t="n">
-        <v>48.7</v>
+        <v>91.3</v>
       </c>
       <c r="T136" s="13" t="n">
-        <v>765</v>
+        <v>737</v>
       </c>
       <c r="U136" s="14" t="n">
-        <v>96</v>
+        <v>96.2</v>
       </c>
       <c r="V136" s="15" t="n">
-        <v>1020</v>
+        <v>1239</v>
       </c>
       <c r="W136" s="14" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="X136" s="14" t="n">
-        <v>-1</v>
+        <v>88.2</v>
+      </c>
+      <c r="X136" s="15" t="n">
+        <v>1132</v>
       </c>
       <c r="Y136" s="14" t="n">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="Z136" s="15" t="n">
-        <v>1797</v>
+        <v>1329</v>
       </c>
       <c r="AA136" s="14" t="n">
-        <v>86.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="AB136" s="15" t="n">
-        <v>2590</v>
+        <v>2196</v>
       </c>
       <c r="AC136" s="14" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="AD136" s="20" t="n">
-        <v>2668</v>
+        <v>85</v>
+      </c>
+      <c r="AD136" s="13" t="n">
+        <v>187</v>
       </c>
       <c r="AE136" s="14" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AF136" s="15" t="n">
-        <v>3433</v>
+        <v>98.8</v>
+      </c>
+      <c r="AF136" s="20" t="n">
+        <v>5350</v>
       </c>
       <c r="AG136" s="14" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="AH136" s="14" t="n">
-        <v>-1</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AH136" s="15" t="n">
+        <v>533</v>
       </c>
       <c r="AI136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" s="14" t="n">
-        <v>-1</v>
+        <v>92.2</v>
+      </c>
+      <c r="AJ136" s="20" t="n">
+        <v>4847</v>
       </c>
       <c r="AK136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL136" s="25" t="n">
-        <v>13125</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AL136" s="13" t="n">
+        <v>613</v>
       </c>
       <c r="AM136" s="14" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="AN136" s="13" t="n">
-        <v>2505</v>
+        <v>97.7</v>
+      </c>
+      <c r="AN136" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AO136" s="14" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="AP136" s="13" t="n">
-        <v>235</v>
+        <v>0</v>
+      </c>
+      <c r="AP136" s="15" t="n">
+        <v>449</v>
       </c>
       <c r="AQ136" s="14" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="AR136" s="25" t="n">
-        <v>11031</v>
+        <v>93.5</v>
+      </c>
+      <c r="AR136" s="15" t="n">
+        <v>1602</v>
       </c>
       <c r="AS136" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="AT136" s="20" t="n">
-        <v>2228</v>
+        <v>89.7</v>
+      </c>
+      <c r="AT136" s="15" t="n">
+        <v>647</v>
       </c>
       <c r="AU136" s="14" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="AV136" s="14" t="n">
-        <v>-1</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AV136" s="20" t="n">
+        <v>1094</v>
       </c>
       <c r="AW136" s="14" t="n">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AX136" s="15" t="n">
-        <v>347</v>
+        <v>969</v>
       </c>
       <c r="AY136" s="14" t="n">
-        <v>93.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AZ136" s="15" t="n">
-        <v>3398</v>
+        <v>3703</v>
       </c>
       <c r="BA136" s="14" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="BB136" s="25" t="n">
-        <v>14146</v>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="BB136" s="15" t="n">
+        <v>317</v>
       </c>
       <c r="BC136" s="14" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="BD136" s="14" t="n">
-        <v>-1</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="BD136" s="20" t="n">
+        <v>3825</v>
       </c>
       <c r="BE136" s="14" t="n">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="BF136" s="14" t="n">
         <v>-1</v>
@@ -43192,119 +43192,119 @@
       <c r="BG136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH136" s="15" t="n">
-        <v>1291</v>
+      <c r="BH136" s="13" t="n">
+        <v>352</v>
       </c>
       <c r="BI136" s="14" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="BJ136" s="14" t="n">
-        <v>-1</v>
+        <v>89.7</v>
+      </c>
+      <c r="BJ136" s="15" t="n">
+        <v>701</v>
       </c>
       <c r="BK136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL136" s="15" t="n">
-        <v>2016</v>
+        <v>74.8</v>
+      </c>
+      <c r="BL136" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM136" s="14" t="n">
-        <v>85.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="BN136" s="13" t="n">
-        <v>558</v>
+        <v>306</v>
       </c>
       <c r="BO136" s="14" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="BP136" s="14" t="n">
-        <v>-1</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BP136" s="13" t="n">
+        <v>1615</v>
       </c>
       <c r="BQ136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR136" s="20" t="n">
-        <v>7546</v>
+        <v>95.3</v>
+      </c>
+      <c r="BR136" s="15" t="n">
+        <v>619</v>
       </c>
       <c r="BS136" s="14" t="n">
-        <v>66.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BT136" s="13" t="n">
-        <v>614</v>
+        <v>1314</v>
       </c>
       <c r="BU136" s="14" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="BV136" s="14" t="n">
-        <v>-1</v>
+        <v>95.90000000000001</v>
+      </c>
+      <c r="BV136" s="15" t="n">
+        <v>1013</v>
       </c>
       <c r="BW136" s="14" t="n">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="BX136" s="13" t="n">
-        <v>309</v>
+        <v>1900</v>
       </c>
       <c r="BY136" s="14" t="n">
-        <v>98.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="BZ136" s="15" t="n">
-        <v>2327</v>
+        <v>1213</v>
       </c>
       <c r="CA136" s="14" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="CB136" s="14" t="n">
-        <v>-1</v>
+        <v>90.5</v>
+      </c>
+      <c r="CB136" s="20" t="n">
+        <v>3784</v>
       </c>
       <c r="CC136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD136" s="15" t="n">
-        <v>2018</v>
+        <v>74</v>
+      </c>
+      <c r="CD136" s="13" t="n">
+        <v>218</v>
       </c>
       <c r="CE136" s="14" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="CF136" s="20" t="n">
-        <v>11809</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="CF136" s="13" t="n">
+        <v>1865</v>
       </c>
       <c r="CG136" s="14" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="CH136" s="14" t="n">
-        <v>-1</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="CH136" s="15" t="n">
+        <v>545</v>
       </c>
       <c r="CI136" s="14" t="n">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="CJ136" s="13" t="n">
-        <v>1325</v>
+        <v>948</v>
       </c>
       <c r="CK136" s="14" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="CL136" s="14" t="n">
-        <v>-1</v>
+        <v>96.5</v>
+      </c>
+      <c r="CL136" s="13" t="n">
+        <v>811</v>
       </c>
       <c r="CM136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN136" s="14" t="n">
-        <v>-1</v>
+        <v>97.3</v>
+      </c>
+      <c r="CN136" s="13" t="n">
+        <v>660</v>
       </c>
       <c r="CO136" s="14" t="n">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="CP136" s="15" t="n">
-        <v>2694</v>
+        <v>654</v>
       </c>
       <c r="CQ136" s="14" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="CR136" s="15" t="n">
-        <v>2929</v>
+        <v>92.8</v>
+      </c>
+      <c r="CR136" s="13" t="n">
+        <v>123</v>
       </c>
       <c r="CS136" s="14" t="n">
-        <v>85</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="CT136" s="14" t="n">
         <v>-1</v>
@@ -43312,41 +43312,46 @@
       <c r="CU136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV136" s="25" t="n">
-        <v>10833</v>
+      <c r="CV136" s="15" t="n">
+        <v>429</v>
       </c>
       <c r="CW136" s="14" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="CX136" s="14" t="n">
-        <v>-1</v>
+        <v>93.2</v>
+      </c>
+      <c r="CX136" s="13" t="n">
+        <v>296</v>
       </c>
       <c r="CY136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ136" s="14" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="CZ136" s="13" t="n">
+        <v>721</v>
       </c>
       <c r="DA136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB136" s="14" t="n">
-        <v>-1</v>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="DB136" s="15" t="n">
+        <v>1301</v>
       </c>
       <c r="DC136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD136" s="20" t="n">
-        <v>9624</v>
+        <v>89.5</v>
+      </c>
+      <c r="DD136" s="15" t="n">
+        <v>1024</v>
       </c>
       <c r="DE136" s="14" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="DF136" s="14" t="n">
-        <v>-1</v>
+        <v>90.3</v>
+      </c>
+      <c r="DF136" s="15" t="n">
+        <v>2225</v>
       </c>
       <c r="DG136" s="14" t="n">
-        <v>0</v>
+        <v>83.7</v>
+      </c>
+      <c r="DH136" s="1" t="inlineStr">
+        <is>
+          <t>Coupang-Logo</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -43355,339 +43360,339 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>kirasj</t>
+          <t>Golden_Fish</t>
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1037</v>
+        <v>10</v>
       </c>
       <c r="D137" s="27" t="n">
-        <v>1523</v>
+        <v>1688</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="F137" s="25" t="n">
-        <v>15106</v>
+        <v>11261</v>
       </c>
       <c r="G137" s="19" t="n">
-        <v>17.8</v>
+        <v>34.9</v>
       </c>
       <c r="H137" s="25" t="n">
-        <v>8331</v>
+        <v>10448</v>
       </c>
       <c r="I137" s="19" t="n">
-        <v>45.1</v>
+        <v>35</v>
       </c>
       <c r="J137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="25" t="n">
-        <v>7601</v>
+      <c r="L137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="M137" s="19" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="N137" s="25" t="n">
-        <v>12798</v>
+        <v>0</v>
+      </c>
+      <c r="N137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="O137" s="19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="P137" s="25" t="n">
-        <v>7083</v>
+        <v>0</v>
+      </c>
+      <c r="P137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="Q137" s="19" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="R137" s="25" t="n">
-        <v>9259</v>
+        <v>0</v>
+      </c>
+      <c r="R137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="T137" s="25" t="n">
-        <v>7615</v>
+        <v>0</v>
+      </c>
+      <c r="T137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="U137" s="19" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="V137" s="25" t="n">
-        <v>10709</v>
+        <v>0</v>
+      </c>
+      <c r="V137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="W137" s="19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Y137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Z137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AA137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AB137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AC137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AD137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AE137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AF137" s="25" t="n">
-        <v>20149</v>
+      <c r="AF137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AG137" s="19" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AH137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AJ137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AL137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AN137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AP137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AQ137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AR137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AT137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AV137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AX137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AZ137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BA137" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BB137" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BC137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD137" s="25" t="n">
-        <v>18968</v>
+      <c r="BD137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BE137" s="19" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="BF137" s="25" t="n">
-        <v>2389</v>
+        <v>0</v>
+      </c>
+      <c r="BF137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BG137" s="19" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="BH137" s="25" t="n">
-        <v>2563</v>
+        <v>0</v>
+      </c>
+      <c r="BH137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BI137" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BJ137" s="25" t="n">
-        <v>2558</v>
+        <v>0</v>
+      </c>
+      <c r="BJ137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BK137" s="19" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="BL137" s="25" t="n">
-        <v>10823</v>
+        <v>0</v>
+      </c>
+      <c r="BL137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BM137" s="19" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="BN137" s="25" t="n">
-        <v>23740</v>
+        <v>0</v>
+      </c>
+      <c r="BN137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BO137" s="19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BP137" s="20" t="n">
-        <v>8328</v>
+        <v>0</v>
+      </c>
+      <c r="BP137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ137" s="19" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="BR137" s="25" t="n">
-        <v>21148</v>
+        <v>0</v>
+      </c>
+      <c r="BR137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BS137" s="19" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="BT137" s="25" t="n">
-        <v>17808</v>
+        <v>0</v>
+      </c>
+      <c r="BT137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BU137" s="19" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="BV137" s="20" t="n">
-        <v>10032</v>
+        <v>0</v>
+      </c>
+      <c r="BV137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BW137" s="19" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="BX137" s="25" t="n">
-        <v>14622</v>
+        <v>0</v>
+      </c>
+      <c r="BX137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BY137" s="19" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="BZ137" s="20" t="n">
-        <v>7780</v>
+        <v>0</v>
+      </c>
+      <c r="BZ137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CA137" s="19" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="CB137" s="25" t="n">
-        <v>13062</v>
+        <v>0</v>
+      </c>
+      <c r="CB137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CC137" s="19" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="CD137" s="25" t="n">
-        <v>10147</v>
+        <v>0</v>
+      </c>
+      <c r="CD137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CE137" s="19" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="CF137" s="20" t="n">
-        <v>5644</v>
+        <v>0</v>
+      </c>
+      <c r="CF137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CG137" s="19" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="CH137" s="20" t="n">
-        <v>2228</v>
+        <v>0</v>
+      </c>
+      <c r="CH137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CI137" s="19" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="CJ137" s="25" t="n">
-        <v>14946</v>
+        <v>0</v>
+      </c>
+      <c r="CJ137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CK137" s="19" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="CL137" s="20" t="n">
-        <v>16403</v>
+        <v>0</v>
+      </c>
+      <c r="CL137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CM137" s="19" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="CN137" s="20" t="n">
-        <v>7338</v>
+        <v>0</v>
+      </c>
+      <c r="CN137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CO137" s="19" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="CP137" s="20" t="n">
-        <v>9746</v>
+        <v>0</v>
+      </c>
+      <c r="CP137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ137" s="19" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="CR137" s="20" t="n">
-        <v>11001</v>
+        <v>0</v>
+      </c>
+      <c r="CR137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CS137" s="19" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="CT137" s="20" t="n">
-        <v>9079</v>
+        <v>0</v>
+      </c>
+      <c r="CT137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CU137" s="19" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="CV137" s="25" t="n">
-        <v>12055</v>
+        <v>0</v>
+      </c>
+      <c r="CV137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CW137" s="19" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="CX137" s="25" t="n">
-        <v>10231</v>
+        <v>0</v>
+      </c>
+      <c r="CX137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CY137" s="19" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="CZ137" s="20" t="n">
-        <v>5573</v>
+        <v>0</v>
+      </c>
+      <c r="CZ137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DA137" s="19" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="DB137" s="20" t="n">
-        <v>4356</v>
+        <v>0</v>
+      </c>
+      <c r="DB137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DC137" s="19" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="DD137" s="25" t="n">
-        <v>11009</v>
+        <v>0</v>
+      </c>
+      <c r="DD137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DE137" s="19" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="DF137" s="25" t="n">
-        <v>13032</v>
+        <v>0</v>
+      </c>
+      <c r="DF137" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG137" s="19" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="DH137" s="1" t="inlineStr">
         <is>
-          <t>Google-Logo</t>
+          <t>Facebook-Logo</t>
         </is>
       </c>
     </row>
@@ -43697,29 +43702,29 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>kaijie_zhang</t>
+          <t>gude8997</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>381</v>
+        <v>1019</v>
       </c>
       <c r="D138" s="26" t="n">
-        <v>1665</v>
+        <v>2052</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>31.1</v>
+        <v>33.6</v>
       </c>
       <c r="F138" s="25" t="n">
-        <v>9402</v>
+        <v>3988</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="H138" s="25" t="n">
-        <v>13804</v>
+        <v>67.3</v>
+      </c>
+      <c r="H138" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="I138" s="14" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="J138" s="14" t="n">
         <v>-1</v>
@@ -43728,301 +43733,301 @@
         <v>0</v>
       </c>
       <c r="L138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="N138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="R138" s="14" t="n">
-        <v>-2</v>
+      <c r="R138" s="25" t="n">
+        <v>6778</v>
       </c>
       <c r="S138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="14" t="n">
-        <v>-2</v>
+        <v>48.7</v>
+      </c>
+      <c r="T138" s="13" t="n">
+        <v>765</v>
       </c>
       <c r="U138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="14" t="n">
-        <v>-2</v>
+        <v>96</v>
+      </c>
+      <c r="V138" s="15" t="n">
+        <v>1020</v>
       </c>
       <c r="W138" s="14" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="14" t="n">
-        <v>-2</v>
+      <c r="Z138" s="15" t="n">
+        <v>1797</v>
       </c>
       <c r="AA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" s="14" t="n">
-        <v>-2</v>
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AB138" s="15" t="n">
+        <v>2590</v>
       </c>
       <c r="AC138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" s="14" t="n">
-        <v>-2</v>
+        <v>83.2</v>
+      </c>
+      <c r="AD138" s="20" t="n">
+        <v>2668</v>
       </c>
       <c r="AE138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF138" s="14" t="n">
-        <v>-2</v>
+        <v>73.5</v>
+      </c>
+      <c r="AF138" s="15" t="n">
+        <v>3433</v>
       </c>
       <c r="AG138" s="14" t="n">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AH138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AJ138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AL138" s="14" t="n">
-        <v>-2</v>
+      <c r="AL138" s="25" t="n">
+        <v>13125</v>
       </c>
       <c r="AM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN138" s="14" t="n">
-        <v>-2</v>
+        <v>36.4</v>
+      </c>
+      <c r="AN138" s="13" t="n">
+        <v>2505</v>
       </c>
       <c r="AO138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP138" s="14" t="n">
-        <v>-2</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AP138" s="13" t="n">
+        <v>235</v>
       </c>
       <c r="AQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR138" s="14" t="n">
-        <v>-2</v>
+        <v>99.2</v>
+      </c>
+      <c r="AR138" s="25" t="n">
+        <v>11031</v>
       </c>
       <c r="AS138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT138" s="14" t="n">
-        <v>-2</v>
+        <v>48.3</v>
+      </c>
+      <c r="AT138" s="20" t="n">
+        <v>2228</v>
       </c>
       <c r="AU138" s="14" t="n">
-        <v>0</v>
+        <v>82.7</v>
       </c>
       <c r="AV138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX138" s="14" t="n">
-        <v>-2</v>
+      <c r="AX138" s="15" t="n">
+        <v>347</v>
       </c>
       <c r="AY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ138" s="14" t="n">
-        <v>-2</v>
+        <v>93.7</v>
+      </c>
+      <c r="AZ138" s="15" t="n">
+        <v>3398</v>
       </c>
       <c r="BA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB138" s="14" t="n">
-        <v>-2</v>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BB138" s="25" t="n">
+        <v>14146</v>
       </c>
       <c r="BC138" s="14" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="BD138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BF138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH138" s="14" t="n">
-        <v>-2</v>
+      <c r="BH138" s="15" t="n">
+        <v>1291</v>
       </c>
       <c r="BI138" s="14" t="n">
-        <v>0</v>
+        <v>57.2</v>
       </c>
       <c r="BJ138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BL138" s="14" t="n">
-        <v>-2</v>
+      <c r="BL138" s="15" t="n">
+        <v>2016</v>
       </c>
       <c r="BM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN138" s="14" t="n">
-        <v>-2</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="BN138" s="13" t="n">
+        <v>558</v>
       </c>
       <c r="BO138" s="14" t="n">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="BP138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BQ138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BR138" s="14" t="n">
-        <v>-2</v>
+      <c r="BR138" s="20" t="n">
+        <v>7546</v>
       </c>
       <c r="BS138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT138" s="14" t="n">
-        <v>-2</v>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="BT138" s="13" t="n">
+        <v>614</v>
       </c>
       <c r="BU138" s="14" t="n">
-        <v>0</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="BV138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BW138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BX138" s="14" t="n">
-        <v>-2</v>
+      <c r="BX138" s="13" t="n">
+        <v>309</v>
       </c>
       <c r="BY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ138" s="14" t="n">
-        <v>-2</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BZ138" s="15" t="n">
+        <v>2327</v>
       </c>
       <c r="CA138" s="14" t="n">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="CB138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CD138" s="14" t="n">
-        <v>-2</v>
+      <c r="CD138" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="CE138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF138" s="14" t="n">
-        <v>-2</v>
+        <v>86.8</v>
+      </c>
+      <c r="CF138" s="20" t="n">
+        <v>11809</v>
       </c>
       <c r="CG138" s="14" t="n">
-        <v>0</v>
+        <v>45.1</v>
       </c>
       <c r="CH138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CI138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CJ138" s="14" t="n">
-        <v>-2</v>
+      <c r="CJ138" s="13" t="n">
+        <v>1325</v>
       </c>
       <c r="CK138" s="14" t="n">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="CL138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CM138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CN138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CP138" s="14" t="n">
-        <v>-2</v>
+      <c r="CP138" s="15" t="n">
+        <v>2694</v>
       </c>
       <c r="CQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR138" s="14" t="n">
-        <v>-2</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="CR138" s="15" t="n">
+        <v>2929</v>
       </c>
       <c r="CS138" s="14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="CT138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV138" s="14" t="n">
-        <v>-2</v>
+      <c r="CV138" s="25" t="n">
+        <v>10833</v>
       </c>
       <c r="CW138" s="14" t="n">
-        <v>0</v>
+        <v>39.5</v>
       </c>
       <c r="CX138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CZ138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DA138" s="14" t="n">
         <v>0</v>
       </c>
       <c r="DB138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DD138" s="14" t="n">
-        <v>-2</v>
+      <c r="DD138" s="20" t="n">
+        <v>9624</v>
       </c>
       <c r="DE138" s="14" t="n">
-        <v>0</v>
+        <v>46.1</v>
       </c>
       <c r="DF138" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DG138" s="14" t="n">
         <v>0</v>
@@ -44034,71 +44039,71 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>wawawamei</t>
+          <t>kirasj</t>
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>643</v>
+        <v>1037</v>
       </c>
       <c r="D139" s="27" t="n">
-        <v>1411</v>
+        <v>1523</v>
       </c>
       <c r="E139" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F139" s="19" t="n">
-        <v>-1</v>
+        <v>31.5</v>
+      </c>
+      <c r="F139" s="25" t="n">
+        <v>15106</v>
       </c>
       <c r="G139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="19" t="n">
-        <v>-1</v>
+        <v>17.8</v>
+      </c>
+      <c r="H139" s="25" t="n">
+        <v>8331</v>
       </c>
       <c r="I139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="25" t="n">
-        <v>10801</v>
+        <v>45.1</v>
+      </c>
+      <c r="J139" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="K139" s="19" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="L139" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="L139" s="25" t="n">
+        <v>7601</v>
       </c>
       <c r="M139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" s="19" t="n">
-        <v>-1</v>
+        <v>43.5</v>
+      </c>
+      <c r="N139" s="25" t="n">
+        <v>12798</v>
       </c>
       <c r="O139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" s="19" t="n">
-        <v>-1</v>
+        <v>14.5</v>
+      </c>
+      <c r="P139" s="25" t="n">
+        <v>7083</v>
       </c>
       <c r="Q139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" s="19" t="n">
-        <v>-1</v>
+        <v>48.9</v>
+      </c>
+      <c r="R139" s="25" t="n">
+        <v>9259</v>
       </c>
       <c r="S139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" s="19" t="n">
-        <v>-1</v>
+        <v>35.4</v>
+      </c>
+      <c r="T139" s="25" t="n">
+        <v>7615</v>
       </c>
       <c r="U139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" s="19" t="n">
-        <v>-1</v>
+        <v>45.7</v>
+      </c>
+      <c r="V139" s="25" t="n">
+        <v>10709</v>
       </c>
       <c r="W139" s="19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="X139" s="19" t="n">
         <v>-1</v>
@@ -44124,17 +44129,17 @@
       <c r="AE139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AF139" s="19" t="n">
-        <v>-1</v>
+      <c r="AF139" s="25" t="n">
+        <v>20149</v>
       </c>
       <c r="AG139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" s="20" t="n">
-        <v>4257</v>
+        <v>6.3</v>
+      </c>
+      <c r="AH139" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI139" s="19" t="n">
-        <v>67.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ139" s="19" t="n">
         <v>-1</v>
@@ -44148,11 +44153,11 @@
       <c r="AM139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AN139" s="25" t="n">
-        <v>21358</v>
+      <c r="AN139" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AO139" s="19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP139" s="19" t="n">
         <v>-1</v>
@@ -44196,173 +44201,178 @@
       <c r="BC139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD139" s="19" t="n">
-        <v>-1</v>
+      <c r="BD139" s="25" t="n">
+        <v>18968</v>
       </c>
       <c r="BE139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF139" s="19" t="n">
-        <v>-1</v>
+        <v>26.5</v>
+      </c>
+      <c r="BF139" s="25" t="n">
+        <v>2389</v>
       </c>
       <c r="BG139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH139" s="19" t="n">
-        <v>-1</v>
+        <v>13.7</v>
+      </c>
+      <c r="BH139" s="25" t="n">
+        <v>2563</v>
       </c>
       <c r="BI139" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BJ139" s="25" t="n">
-        <v>2653</v>
+        <v>2558</v>
       </c>
       <c r="BK139" s="19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BL139" s="19" t="n">
-        <v>-1</v>
+        <v>11.4</v>
+      </c>
+      <c r="BL139" s="25" t="n">
+        <v>10823</v>
       </c>
       <c r="BM139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN139" s="19" t="n">
-        <v>-1</v>
+        <v>34.7</v>
+      </c>
+      <c r="BN139" s="25" t="n">
+        <v>23740</v>
       </c>
       <c r="BO139" s="19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BP139" s="20" t="n">
-        <v>18684</v>
+        <v>8328</v>
       </c>
       <c r="BQ139" s="19" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="BR139" s="19" t="n">
-        <v>-1</v>
+        <v>65.7</v>
+      </c>
+      <c r="BR139" s="25" t="n">
+        <v>21148</v>
       </c>
       <c r="BS139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT139" s="19" t="n">
-        <v>-1</v>
+        <v>19.3</v>
+      </c>
+      <c r="BT139" s="25" t="n">
+        <v>17808</v>
       </c>
       <c r="BU139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV139" s="19" t="n">
-        <v>-1</v>
+        <v>28.8</v>
+      </c>
+      <c r="BV139" s="20" t="n">
+        <v>10032</v>
       </c>
       <c r="BW139" s="19" t="n">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="BX139" s="25" t="n">
-        <v>20053</v>
+        <v>14622</v>
       </c>
       <c r="BY139" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="BZ139" s="19" t="n">
-        <v>-1</v>
+        <v>34.7</v>
+      </c>
+      <c r="BZ139" s="20" t="n">
+        <v>7780</v>
       </c>
       <c r="CA139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB139" s="19" t="n">
-        <v>-1</v>
+        <v>61.3</v>
+      </c>
+      <c r="CB139" s="25" t="n">
+        <v>13062</v>
       </c>
       <c r="CC139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD139" s="19" t="n">
-        <v>-1</v>
+        <v>29.7</v>
+      </c>
+      <c r="CD139" s="25" t="n">
+        <v>10147</v>
       </c>
       <c r="CE139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF139" s="25" t="n">
-        <v>16477</v>
+        <v>43.8</v>
+      </c>
+      <c r="CF139" s="20" t="n">
+        <v>5644</v>
       </c>
       <c r="CG139" s="19" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="CH139" s="19" t="n">
-        <v>-1</v>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="CH139" s="20" t="n">
+        <v>2228</v>
       </c>
       <c r="CI139" s="19" t="n">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="CJ139" s="25" t="n">
-        <v>20720</v>
+        <v>14946</v>
       </c>
       <c r="CK139" s="19" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="CL139" s="19" t="n">
-        <v>-1</v>
+        <v>30.2</v>
+      </c>
+      <c r="CL139" s="20" t="n">
+        <v>16403</v>
       </c>
       <c r="CM139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN139" s="25" t="n">
-        <v>14803</v>
+        <v>34.6</v>
+      </c>
+      <c r="CN139" s="20" t="n">
+        <v>7338</v>
       </c>
       <c r="CO139" s="19" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="CP139" s="19" t="n">
-        <v>-1</v>
+        <v>60.5</v>
+      </c>
+      <c r="CP139" s="20" t="n">
+        <v>9746</v>
       </c>
       <c r="CQ139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR139" s="19" t="n">
-        <v>-1</v>
+        <v>57.7</v>
+      </c>
+      <c r="CR139" s="20" t="n">
+        <v>11001</v>
       </c>
       <c r="CS139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT139" s="25" t="n">
-        <v>19936</v>
+        <v>52.4</v>
+      </c>
+      <c r="CT139" s="20" t="n">
+        <v>9079</v>
       </c>
       <c r="CU139" s="19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CV139" s="20" t="n">
-        <v>8638</v>
+        <v>56.1</v>
+      </c>
+      <c r="CV139" s="25" t="n">
+        <v>12055</v>
       </c>
       <c r="CW139" s="19" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="CX139" s="19" t="n">
-        <v>-1</v>
+        <v>34.3</v>
+      </c>
+      <c r="CX139" s="25" t="n">
+        <v>10231</v>
       </c>
       <c r="CY139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ139" s="19" t="n">
-        <v>-1</v>
+        <v>39.3</v>
+      </c>
+      <c r="CZ139" s="20" t="n">
+        <v>5573</v>
       </c>
       <c r="DA139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB139" s="25" t="n">
-        <v>13824</v>
+        <v>63.7</v>
+      </c>
+      <c r="DB139" s="20" t="n">
+        <v>4356</v>
       </c>
       <c r="DC139" s="19" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="DD139" s="19" t="n">
-        <v>-1</v>
+        <v>71.7</v>
+      </c>
+      <c r="DD139" s="25" t="n">
+        <v>11009</v>
       </c>
       <c r="DE139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF139" s="19" t="n">
-        <v>-1</v>
+        <v>34.8</v>
+      </c>
+      <c r="DF139" s="25" t="n">
+        <v>13032</v>
       </c>
       <c r="DG139" s="19" t="n">
-        <v>0</v>
+        <v>18.6</v>
+      </c>
+      <c r="DH139" s="1" t="inlineStr">
+        <is>
+          <t>Google-Logo</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -44371,29 +44381,29 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>tinyfish1</t>
+          <t>kaijie_zhang</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>2098</v>
+        <v>381</v>
       </c>
       <c r="D140" s="26" t="n">
-        <v>-1</v>
+        <v>1665</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" s="14" t="n">
-        <v>-2</v>
+        <v>31.1</v>
+      </c>
+      <c r="F140" s="25" t="n">
+        <v>9402</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="14" t="n">
-        <v>-1</v>
+        <v>43.2</v>
+      </c>
+      <c r="H140" s="25" t="n">
+        <v>13804</v>
       </c>
       <c r="I140" s="14" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="J140" s="14" t="n">
         <v>-1</v>
@@ -44401,310 +44411,305 @@
       <c r="K140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="13" t="n">
-        <v>154</v>
+      <c r="L140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="M140" s="14" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="N140" s="13" t="n">
-        <v>531</v>
+        <v>0</v>
+      </c>
+      <c r="N140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="O140" s="14" t="n">
-        <v>97.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="P140" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="R140" s="15" t="n">
-        <v>1186</v>
+      <c r="R140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="S140" s="14" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="T140" s="13" t="n">
-        <v>302</v>
+        <v>0</v>
+      </c>
+      <c r="T140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="U140" s="14" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="V140" s="15" t="n">
-        <v>1179</v>
+        <v>0</v>
+      </c>
+      <c r="V140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="W140" s="14" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="X140" s="15" t="n">
-        <v>104</v>
+        <v>0</v>
+      </c>
+      <c r="X140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="Y140" s="14" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Z140" s="15" t="n">
-        <v>1022</v>
+        <v>0</v>
+      </c>
+      <c r="Z140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AA140" s="14" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="AB140" s="15" t="n">
-        <v>552</v>
+        <v>0</v>
+      </c>
+      <c r="AB140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AC140" s="14" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="AD140" s="15" t="n">
-        <v>922</v>
+        <v>0</v>
+      </c>
+      <c r="AD140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AE140" s="14" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="AF140" s="15" t="n">
-        <v>2707</v>
+        <v>0</v>
+      </c>
+      <c r="AF140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AG140" s="14" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="AH140" s="13" t="n">
-        <v>198</v>
+        <v>0</v>
+      </c>
+      <c r="AH140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AI140" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ140" s="15" t="n">
-        <v>285</v>
+        <v>0</v>
+      </c>
+      <c r="AJ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AK140" s="14" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="AL140" s="13" t="n">
-        <v>482</v>
+        <v>0</v>
+      </c>
+      <c r="AL140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AM140" s="14" t="n">
-        <v>98.2</v>
+        <v>0</v>
       </c>
       <c r="AN140" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP140" s="15" t="n">
-        <v>546</v>
+      <c r="AP140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AQ140" s="14" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="AR140" s="15" t="n">
-        <v>1042</v>
+        <v>0</v>
+      </c>
+      <c r="AR140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AS140" s="14" t="n">
-        <v>91.5</v>
+        <v>0</v>
       </c>
       <c r="AT140" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV140" s="15" t="n">
-        <v>232</v>
+      <c r="AV140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AW140" s="14" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="AX140" s="15" t="n">
-        <v>285</v>
+        <v>0</v>
+      </c>
+      <c r="AX140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AY140" s="14" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="AZ140" s="13" t="n">
-        <v>791</v>
+        <v>0</v>
+      </c>
+      <c r="AZ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BA140" s="14" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="BB140" s="15" t="n">
-        <v>298</v>
+        <v>0</v>
+      </c>
+      <c r="BB140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BC140" s="14" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="BD140" s="20" t="n">
-        <v>2425</v>
+        <v>0</v>
+      </c>
+      <c r="BD140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BE140" s="14" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="BF140" s="15" t="n">
-        <v>799</v>
+        <v>0</v>
+      </c>
+      <c r="BF140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BG140" s="14" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="BH140" s="13" t="n">
-        <v>349</v>
+        <v>0</v>
+      </c>
+      <c r="BH140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BI140" s="14" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="BJ140" s="15" t="n">
-        <v>522</v>
+        <v>0</v>
+      </c>
+      <c r="BJ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BK140" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="BL140" s="15" t="n">
-        <v>3221</v>
+        <v>0</v>
+      </c>
+      <c r="BL140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BM140" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="BN140" s="13" t="n">
-        <v>194</v>
+        <v>0</v>
+      </c>
+      <c r="BN140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BO140" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="BP140" s="13" t="n">
-        <v>1462</v>
+        <v>0</v>
+      </c>
+      <c r="BP140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ140" s="14" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="BR140" s="15" t="n">
-        <v>1431</v>
+        <v>0</v>
+      </c>
+      <c r="BR140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BS140" s="14" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="BT140" s="13" t="n">
-        <v>1691</v>
+        <v>0</v>
+      </c>
+      <c r="BT140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BU140" s="14" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="BV140" s="13" t="n">
-        <v>287</v>
+        <v>0</v>
+      </c>
+      <c r="BV140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BW140" s="14" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="BX140" s="13" t="n">
-        <v>259</v>
+        <v>0</v>
+      </c>
+      <c r="BX140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BY140" s="14" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="BZ140" s="15" t="n">
-        <v>1196</v>
+        <v>0</v>
+      </c>
+      <c r="BZ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CA140" s="14" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="CB140" s="15" t="n">
-        <v>1600</v>
+        <v>0</v>
+      </c>
+      <c r="CB140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CC140" s="14" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="CD140" s="13" t="n">
-        <v>151</v>
+        <v>0</v>
+      </c>
+      <c r="CD140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CE140" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="CF140" s="13" t="n">
-        <v>150</v>
+        <v>0</v>
+      </c>
+      <c r="CF140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CG140" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="CH140" s="15" t="n">
-        <v>574</v>
+        <v>0</v>
+      </c>
+      <c r="CH140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CI140" s="14" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="CJ140" s="13" t="n">
-        <v>113</v>
+        <v>0</v>
+      </c>
+      <c r="CJ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CK140" s="14" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CL140" s="13" t="n">
-        <v>592</v>
+        <v>0</v>
+      </c>
+      <c r="CL140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CM140" s="14" t="n">
-        <v>98</v>
-      </c>
-      <c r="CN140" s="13" t="n">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="CN140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CO140" s="14" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="CP140" s="13" t="n">
-        <v>156</v>
+        <v>0</v>
+      </c>
+      <c r="CP140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ140" s="14" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="CR140" s="13" t="n">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="CR140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CS140" s="14" t="n">
-        <v>99.5</v>
+        <v>0</v>
       </c>
       <c r="CT140" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV140" s="15" t="n">
-        <v>235</v>
+      <c r="CV140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CW140" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="CX140" s="13" t="n">
-        <v>119</v>
+        <v>0</v>
+      </c>
+      <c r="CX140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CY140" s="14" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="CZ140" s="13" t="n">
-        <v>117</v>
+        <v>0</v>
+      </c>
+      <c r="CZ140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DA140" s="14" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="DB140" s="13" t="n">
-        <v>649</v>
+        <v>0</v>
+      </c>
+      <c r="DB140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DC140" s="14" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="DD140" s="13" t="n">
-        <v>105</v>
+        <v>0</v>
+      </c>
+      <c r="DD140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DE140" s="14" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="DF140" s="15" t="n">
-        <v>1237</v>
+        <v>0</v>
+      </c>
+      <c r="DF140" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DG140" s="14" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="DH140" s="1" t="inlineStr">
-        <is>
-          <t>Snapchat-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -44713,335 +44718,340 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>roy_1127</t>
+          <t>yuhengc2</t>
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>1497</v>
+        <v>5</v>
       </c>
       <c r="D141" s="27" t="n">
         <v>2043</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="19" t="n">
-        <v>-1</v>
+        <v>24.3</v>
+      </c>
+      <c r="F141" s="25" t="n">
+        <v>13646</v>
       </c>
       <c r="G141" s="19" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="H141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="K141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="L141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="P141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="R141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="T141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="V141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Y141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Z141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AA141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AG141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AH141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AJ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AK141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AL141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AM141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AN141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AO141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AP141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AQ141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AR141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AU141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AV141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AW141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AX141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AZ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BA141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BG141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BH141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BI141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BJ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BK141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BL141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BM141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BN141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BO141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BP141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BQ141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BR141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BS141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BU141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BV141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BW141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BX141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BY141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BZ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CA141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CG141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CH141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CI141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CJ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CK141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CL141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CM141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CN141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CO141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CP141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CR141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CS141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CT141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CV141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CW141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CX141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CZ141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DA141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DB141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DC141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DD141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DE141" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DF141" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DG141" s="19" t="n">
         <v>0</v>
+      </c>
+      <c r="DH141" s="1" t="inlineStr">
+        <is>
+          <t>Apple-Logo</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -45050,17 +45060,17 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>perry304</t>
+          <t>wawawamei</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1342</v>
-      </c>
-      <c r="D142" s="23" t="n">
-        <v>2422</v>
+        <v>643</v>
+      </c>
+      <c r="D142" s="26" t="n">
+        <v>1411</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F142" s="14" t="n">
         <v>-1</v>
@@ -45074,11 +45084,11 @@
       <c r="I142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J142" s="14" t="n">
-        <v>-1</v>
+      <c r="J142" s="25" t="n">
+        <v>10801</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="L142" s="14" t="n">
         <v>-1</v>
@@ -45086,11 +45096,11 @@
       <c r="M142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N142" s="13" t="n">
-        <v>386</v>
+      <c r="N142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O142" s="14" t="n">
-        <v>97.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="P142" s="14" t="n">
         <v>-1</v>
@@ -45110,11 +45120,11 @@
       <c r="U142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="15" t="n">
-        <v>430</v>
+      <c r="V142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="W142" s="14" t="n">
-        <v>92.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="X142" s="14" t="n">
         <v>-1</v>
@@ -45122,11 +45132,11 @@
       <c r="Y142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="15" t="n">
-        <v>842</v>
+      <c r="Z142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AA142" s="14" t="n">
-        <v>91.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB142" s="14" t="n">
         <v>-1</v>
@@ -45134,11 +45144,11 @@
       <c r="AC142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AD142" s="20" t="n">
-        <v>2950</v>
+      <c r="AD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AE142" s="14" t="n">
-        <v>71.8</v>
+        <v>0</v>
       </c>
       <c r="AF142" s="14" t="n">
         <v>-1</v>
@@ -45146,17 +45156,17 @@
       <c r="AG142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH142" s="15" t="n">
-        <v>504</v>
+      <c r="AH142" s="20" t="n">
+        <v>4257</v>
       </c>
       <c r="AI142" s="14" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="AJ142" s="20" t="n">
-        <v>1317</v>
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AJ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AK142" s="14" t="n">
-        <v>84.5</v>
+        <v>0</v>
       </c>
       <c r="AL142" s="14" t="n">
         <v>-1</v>
@@ -45164,11 +45174,11 @@
       <c r="AM142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AN142" s="13" t="n">
-        <v>566</v>
+      <c r="AN142" s="25" t="n">
+        <v>21358</v>
       </c>
       <c r="AO142" s="14" t="n">
-        <v>98.09999999999999</v>
+        <v>13</v>
       </c>
       <c r="AP142" s="14" t="n">
         <v>-1</v>
@@ -45176,11 +45186,11 @@
       <c r="AQ142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AR142" s="15" t="n">
-        <v>791</v>
+      <c r="AR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AS142" s="14" t="n">
-        <v>92.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT142" s="14" t="n">
         <v>-1</v>
@@ -45188,17 +45198,17 @@
       <c r="AU142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV142" s="15" t="n">
-        <v>407</v>
+      <c r="AV142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AW142" s="14" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="AX142" s="15" t="n">
-        <v>322</v>
+        <v>0</v>
+      </c>
+      <c r="AX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY142" s="14" t="n">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="AZ142" s="14" t="n">
         <v>-1</v>
@@ -45230,17 +45240,17 @@
       <c r="BI142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BJ142" s="13" t="n">
-        <v>42</v>
+      <c r="BJ142" s="25" t="n">
+        <v>2653</v>
       </c>
       <c r="BK142" s="14" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="BL142" s="13" t="n">
-        <v>643</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BL142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM142" s="14" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="BN142" s="14" t="n">
         <v>-1</v>
@@ -45248,17 +45258,17 @@
       <c r="BO142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BP142" s="13" t="n">
-        <v>396</v>
+      <c r="BP142" s="20" t="n">
+        <v>18684</v>
       </c>
       <c r="BQ142" s="14" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="BR142" s="15" t="n">
-        <v>478</v>
+        <v>35.4</v>
+      </c>
+      <c r="BR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BS142" s="14" t="n">
-        <v>93.5</v>
+        <v>0</v>
       </c>
       <c r="BT142" s="14" t="n">
         <v>-1</v>
@@ -45266,17 +45276,17 @@
       <c r="BU142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV142" s="15" t="n">
-        <v>947</v>
+      <c r="BV142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BW142" s="14" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="BX142" s="13" t="n">
-        <v>243</v>
+        <v>0</v>
+      </c>
+      <c r="BX142" s="25" t="n">
+        <v>20053</v>
       </c>
       <c r="BY142" s="14" t="n">
-        <v>99.2</v>
+        <v>16</v>
       </c>
       <c r="BZ142" s="14" t="n">
         <v>-1</v>
@@ -45284,11 +45294,11 @@
       <c r="CA142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CB142" s="13" t="n">
-        <v>79</v>
+      <c r="CB142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CC142" s="14" t="n">
-        <v>99.7</v>
+        <v>0</v>
       </c>
       <c r="CD142" s="14" t="n">
         <v>-1</v>
@@ -45296,35 +45306,35 @@
       <c r="CE142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CF142" s="13" t="n">
-        <v>427</v>
+      <c r="CF142" s="25" t="n">
+        <v>16477</v>
       </c>
       <c r="CG142" s="14" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="CH142" s="15" t="n">
-        <v>647</v>
+        <v>22.4</v>
+      </c>
+      <c r="CH142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CI142" s="14" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="CJ142" s="14" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="CJ142" s="25" t="n">
+        <v>20720</v>
       </c>
       <c r="CK142" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL142" s="15" t="n">
-        <v>1983</v>
+        <v>9.1</v>
+      </c>
+      <c r="CL142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CM142" s="14" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="CN142" s="13" t="n">
-        <v>309</v>
+        <v>0</v>
+      </c>
+      <c r="CN142" s="25" t="n">
+        <v>14803</v>
       </c>
       <c r="CO142" s="14" t="n">
-        <v>98.8</v>
+        <v>25.5</v>
       </c>
       <c r="CP142" s="14" t="n">
         <v>-1</v>
@@ -45338,23 +45348,23 @@
       <c r="CS142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CT142" s="14" t="n">
-        <v>-1</v>
+      <c r="CT142" s="25" t="n">
+        <v>19936</v>
       </c>
       <c r="CU142" s="14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CV142" s="20" t="n">
-        <v>6740</v>
+        <v>8638</v>
       </c>
       <c r="CW142" s="14" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="CX142" s="13" t="n">
-        <v>309</v>
+        <v>53.7</v>
+      </c>
+      <c r="CX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY142" s="14" t="n">
-        <v>98.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CZ142" s="14" t="n">
         <v>-1</v>
@@ -45362,23 +45372,23 @@
       <c r="DA142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB142" s="13" t="n">
-        <v>691</v>
+      <c r="DB142" s="25" t="n">
+        <v>13824</v>
       </c>
       <c r="DC142" s="14" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="DD142" s="15" t="n">
-        <v>566</v>
+        <v>26.8</v>
+      </c>
+      <c r="DD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DE142" s="14" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="DF142" s="15" t="n">
-        <v>752</v>
+        <v>0</v>
+      </c>
+      <c r="DF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DG142" s="14" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -45387,14 +45397,14 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>nijiademianbao</t>
+          <t>roy_1127</t>
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>1192</v>
+        <v>1497</v>
       </c>
       <c r="D143" s="27" t="n">
-        <v>1734</v>
+        <v>2043</v>
       </c>
       <c r="E143" s="12" t="n">
         <v>0</v>
@@ -45435,11 +45445,11 @@
       <c r="Q143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R143" s="20" t="n">
-        <v>6377</v>
+      <c r="R143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S143" s="19" t="n">
-        <v>55.8</v>
+        <v>0</v>
       </c>
       <c r="T143" s="19" t="n">
         <v>-1</v>
@@ -45459,17 +45469,17 @@
       <c r="Y143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="20" t="n">
-        <v>8275</v>
+      <c r="Z143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AA143" s="19" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="AB143" s="15" t="n">
-        <v>1134</v>
+        <v>0</v>
+      </c>
+      <c r="AB143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC143" s="19" t="n">
-        <v>89.8</v>
+        <v>0</v>
       </c>
       <c r="AD143" s="19" t="n">
         <v>-1</v>
@@ -45519,11 +45529,11 @@
       <c r="AS143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AT143" s="20" t="n">
-        <v>5346</v>
+      <c r="AT143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AU143" s="19" t="n">
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="AV143" s="19" t="n">
         <v>-1</v>
@@ -45531,17 +45541,17 @@
       <c r="AW143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AX143" s="20" t="n">
-        <v>8544</v>
+      <c r="AX143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY143" s="19" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="AZ143" s="15" t="n">
-        <v>4093</v>
+        <v>0</v>
+      </c>
+      <c r="AZ143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BA143" s="19" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB143" s="19" t="n">
         <v>-1</v>
@@ -45555,17 +45565,17 @@
       <c r="BE143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BF143" s="15" t="n">
-        <v>1711</v>
+      <c r="BF143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BG143" s="19" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="BH143" s="13" t="n">
-        <v>721</v>
+        <v>0</v>
+      </c>
+      <c r="BH143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI143" s="19" t="n">
-        <v>78.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ143" s="19" t="n">
         <v>-1</v>
@@ -45579,11 +45589,11 @@
       <c r="BM143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BN143" s="15" t="n">
-        <v>6502</v>
+      <c r="BN143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BO143" s="19" t="n">
-        <v>75.7</v>
+        <v>0</v>
       </c>
       <c r="BP143" s="19" t="n">
         <v>-1</v>
@@ -45591,11 +45601,11 @@
       <c r="BQ143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BR143" s="20" t="n">
-        <v>12189</v>
+      <c r="BR143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BS143" s="19" t="n">
-        <v>52.2</v>
+        <v>0</v>
       </c>
       <c r="BT143" s="19" t="n">
         <v>-1</v>
@@ -45609,17 +45619,17 @@
       <c r="BW143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BX143" s="25" t="n">
-        <v>15989</v>
+      <c r="BX143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BY143" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BZ143" s="20" t="n">
-        <v>7033</v>
+        <v>0</v>
+      </c>
+      <c r="BZ143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CA143" s="19" t="n">
-        <v>64.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB143" s="19" t="n">
         <v>-1</v>
@@ -45627,11 +45637,11 @@
       <c r="CC143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD143" s="20" t="n">
-        <v>5354</v>
+      <c r="CD143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CE143" s="19" t="n">
-        <v>68.2</v>
+        <v>0</v>
       </c>
       <c r="CF143" s="19" t="n">
         <v>-1</v>
@@ -45687,35 +45697,35 @@
       <c r="CW143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CX143" s="20" t="n">
-        <v>6680</v>
+      <c r="CX143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CY143" s="19" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="CZ143" s="20" t="n">
-        <v>7363</v>
+        <v>0</v>
+      </c>
+      <c r="CZ143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA143" s="19" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="DB143" s="20" t="n">
-        <v>4316</v>
+        <v>0</v>
+      </c>
+      <c r="DB143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DC143" s="19" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="DD143" s="15" t="n">
-        <v>5395</v>
+        <v>0</v>
+      </c>
+      <c r="DD143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE143" s="19" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="DF143" s="20" t="n">
-        <v>8693</v>
+        <v>0</v>
+      </c>
+      <c r="DF143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DG143" s="19" t="n">
-        <v>45.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -45724,14 +45734,14 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>fatyuan</t>
+          <t>perry304</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>1174</v>
-      </c>
-      <c r="D144" s="26" t="n">
-        <v>1629</v>
+        <v>1342</v>
+      </c>
+      <c r="D144" s="23" t="n">
+        <v>2422</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>0</v>
@@ -45760,11 +45770,11 @@
       <c r="M144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N144" s="14" t="n">
-        <v>-1</v>
+      <c r="N144" s="13" t="n">
+        <v>386</v>
       </c>
       <c r="O144" s="14" t="n">
-        <v>0</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P144" s="14" t="n">
         <v>-1</v>
@@ -45784,11 +45794,11 @@
       <c r="U144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="14" t="n">
-        <v>-1</v>
+      <c r="V144" s="15" t="n">
+        <v>430</v>
       </c>
       <c r="W144" s="14" t="n">
-        <v>0</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="X144" s="14" t="n">
         <v>-1</v>
@@ -45796,11 +45806,11 @@
       <c r="Y144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="14" t="n">
-        <v>-1</v>
+      <c r="Z144" s="15" t="n">
+        <v>842</v>
       </c>
       <c r="AA144" s="14" t="n">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AB144" s="14" t="n">
         <v>-1</v>
@@ -45808,11 +45818,11 @@
       <c r="AC144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AD144" s="14" t="n">
-        <v>-1</v>
+      <c r="AD144" s="20" t="n">
+        <v>2950</v>
       </c>
       <c r="AE144" s="14" t="n">
-        <v>0</v>
+        <v>71.8</v>
       </c>
       <c r="AF144" s="14" t="n">
         <v>-1</v>
@@ -45820,17 +45830,17 @@
       <c r="AG144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH144" s="14" t="n">
-        <v>-1</v>
+      <c r="AH144" s="15" t="n">
+        <v>504</v>
       </c>
       <c r="AI144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ144" s="14" t="n">
-        <v>-1</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AJ144" s="20" t="n">
+        <v>1317</v>
       </c>
       <c r="AK144" s="14" t="n">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="AL144" s="14" t="n">
         <v>-1</v>
@@ -45838,11 +45848,11 @@
       <c r="AM144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AN144" s="14" t="n">
-        <v>-1</v>
+      <c r="AN144" s="13" t="n">
+        <v>566</v>
       </c>
       <c r="AO144" s="14" t="n">
-        <v>0</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AP144" s="14" t="n">
         <v>-1</v>
@@ -45850,11 +45860,11 @@
       <c r="AQ144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AR144" s="14" t="n">
-        <v>-1</v>
+      <c r="AR144" s="15" t="n">
+        <v>791</v>
       </c>
       <c r="AS144" s="14" t="n">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AT144" s="14" t="n">
         <v>-1</v>
@@ -45862,17 +45872,17 @@
       <c r="AU144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV144" s="14" t="n">
-        <v>-1</v>
+      <c r="AV144" s="15" t="n">
+        <v>407</v>
       </c>
       <c r="AW144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX144" s="14" t="n">
-        <v>-1</v>
+        <v>93.7</v>
+      </c>
+      <c r="AX144" s="15" t="n">
+        <v>322</v>
       </c>
       <c r="AY144" s="14" t="n">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="AZ144" s="14" t="n">
         <v>-1</v>
@@ -45904,17 +45914,17 @@
       <c r="BI144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BJ144" s="14" t="n">
-        <v>-1</v>
+      <c r="BJ144" s="13" t="n">
+        <v>42</v>
       </c>
       <c r="BK144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL144" s="14" t="n">
-        <v>-1</v>
+        <v>98.8</v>
+      </c>
+      <c r="BL144" s="13" t="n">
+        <v>643</v>
       </c>
       <c r="BM144" s="14" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="BN144" s="14" t="n">
         <v>-1</v>
@@ -45922,17 +45932,17 @@
       <c r="BO144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BP144" s="14" t="n">
-        <v>-1</v>
+      <c r="BP144" s="13" t="n">
+        <v>396</v>
       </c>
       <c r="BQ144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR144" s="14" t="n">
-        <v>-1</v>
+        <v>98.8</v>
+      </c>
+      <c r="BR144" s="15" t="n">
+        <v>478</v>
       </c>
       <c r="BS144" s="14" t="n">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="BT144" s="14" t="n">
         <v>-1</v>
@@ -45940,17 +45950,17 @@
       <c r="BU144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV144" s="14" t="n">
-        <v>-1</v>
+      <c r="BV144" s="15" t="n">
+        <v>947</v>
       </c>
       <c r="BW144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX144" s="14" t="n">
-        <v>-1</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BX144" s="13" t="n">
+        <v>243</v>
       </c>
       <c r="BY144" s="14" t="n">
-        <v>0</v>
+        <v>99.2</v>
       </c>
       <c r="BZ144" s="14" t="n">
         <v>-1</v>
@@ -45958,11 +45968,11 @@
       <c r="CA144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CB144" s="14" t="n">
-        <v>-1</v>
+      <c r="CB144" s="13" t="n">
+        <v>79</v>
       </c>
       <c r="CC144" s="14" t="n">
-        <v>0</v>
+        <v>99.7</v>
       </c>
       <c r="CD144" s="14" t="n">
         <v>-1</v>
@@ -45970,17 +45980,17 @@
       <c r="CE144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CF144" s="14" t="n">
-        <v>-1</v>
+      <c r="CF144" s="13" t="n">
+        <v>427</v>
       </c>
       <c r="CG144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH144" s="14" t="n">
-        <v>-1</v>
+        <v>98.40000000000001</v>
+      </c>
+      <c r="CH144" s="15" t="n">
+        <v>647</v>
       </c>
       <c r="CI144" s="14" t="n">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="CJ144" s="14" t="n">
         <v>-1</v>
@@ -45988,17 +45998,17 @@
       <c r="CK144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL144" s="14" t="n">
-        <v>-1</v>
+      <c r="CL144" s="15" t="n">
+        <v>1983</v>
       </c>
       <c r="CM144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN144" s="14" t="n">
-        <v>-1</v>
+        <v>88.3</v>
+      </c>
+      <c r="CN144" s="13" t="n">
+        <v>309</v>
       </c>
       <c r="CO144" s="14" t="n">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="CP144" s="14" t="n">
         <v>-1</v>
@@ -46018,17 +46028,17 @@
       <c r="CU144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV144" s="14" t="n">
-        <v>-1</v>
+      <c r="CV144" s="20" t="n">
+        <v>6740</v>
       </c>
       <c r="CW144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX144" s="14" t="n">
-        <v>-1</v>
+        <v>61.7</v>
+      </c>
+      <c r="CX144" s="13" t="n">
+        <v>309</v>
       </c>
       <c r="CY144" s="14" t="n">
-        <v>0</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="CZ144" s="14" t="n">
         <v>-1</v>
@@ -46036,23 +46046,23 @@
       <c r="DA144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB144" s="14" t="n">
-        <v>-1</v>
+      <c r="DB144" s="13" t="n">
+        <v>691</v>
       </c>
       <c r="DC144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD144" s="14" t="n">
-        <v>-1</v>
+        <v>97.09999999999999</v>
+      </c>
+      <c r="DD144" s="15" t="n">
+        <v>566</v>
       </c>
       <c r="DE144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF144" s="14" t="n">
-        <v>-1</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="DF144" s="15" t="n">
+        <v>752</v>
       </c>
       <c r="DG144" s="14" t="n">
-        <v>0</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="145">
@@ -46061,14 +46071,14 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>mfk443838746</t>
+          <t>nijiademianbao</t>
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>1109</v>
-      </c>
-      <c r="D145" s="24" t="n">
-        <v>2317</v>
+        <v>1192</v>
+      </c>
+      <c r="D145" s="27" t="n">
+        <v>1734</v>
       </c>
       <c r="E145" s="12" t="n">
         <v>0</v>
@@ -46109,41 +46119,41 @@
       <c r="Q145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R145" s="15" t="n">
-        <v>287</v>
+      <c r="R145" s="20" t="n">
+        <v>6377</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="T145" s="13" t="n">
-        <v>1071</v>
+        <v>55.8</v>
+      </c>
+      <c r="T145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U145" s="19" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="V145" s="15" t="n">
-        <v>418</v>
+        <v>0</v>
+      </c>
+      <c r="V145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W145" s="19" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="X145" s="15" t="n">
-        <v>2329</v>
+        <v>0</v>
+      </c>
+      <c r="X145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y145" s="19" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="Z145" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="Z145" s="20" t="n">
+        <v>8275</v>
       </c>
       <c r="AA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB145" s="19" t="n">
-        <v>-1</v>
+        <v>51.5</v>
+      </c>
+      <c r="AB145" s="15" t="n">
+        <v>1134</v>
       </c>
       <c r="AC145" s="19" t="n">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="AD145" s="19" t="n">
         <v>-1</v>
@@ -46157,11 +46167,11 @@
       <c r="AG145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AH145" s="15" t="n">
-        <v>650</v>
+      <c r="AH145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI145" s="19" t="n">
-        <v>91.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ145" s="19" t="n">
         <v>-1</v>
@@ -46169,17 +46179,17 @@
       <c r="AK145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AL145" s="15" t="n">
-        <v>973</v>
+      <c r="AL145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AM145" s="19" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="AN145" s="13" t="n">
-        <v>166</v>
+        <v>0</v>
+      </c>
+      <c r="AN145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AO145" s="19" t="n">
-        <v>99.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP145" s="19" t="n">
         <v>-1</v>
@@ -46187,209 +46197,209 @@
       <c r="AQ145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AR145" s="13" t="n">
-        <v>572</v>
+      <c r="AR145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AS145" s="19" t="n">
-        <v>98.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT145" s="20" t="n">
-        <v>1501</v>
+        <v>5346</v>
       </c>
       <c r="AU145" s="19" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="AV145" s="20" t="n">
-        <v>5871</v>
+        <v>72.5</v>
+      </c>
+      <c r="AV145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW145" s="19" t="n">
-        <v>70.8</v>
+        <v>0</v>
       </c>
       <c r="AX145" s="20" t="n">
-        <v>4692</v>
+        <v>8544</v>
       </c>
       <c r="AY145" s="19" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="AZ145" s="19" t="n">
-        <v>-1</v>
+        <v>58.1</v>
+      </c>
+      <c r="AZ145" s="15" t="n">
+        <v>4093</v>
       </c>
       <c r="BA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB145" s="20" t="n">
-        <v>2375</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="BB145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BC145" s="19" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="BD145" s="20" t="n">
-        <v>2507</v>
+        <v>0</v>
+      </c>
+      <c r="BD145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BE145" s="19" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BF145" s="13" t="n">
-        <v>367</v>
+        <v>0</v>
+      </c>
+      <c r="BF145" s="15" t="n">
+        <v>1711</v>
       </c>
       <c r="BG145" s="19" t="n">
-        <v>89</v>
+        <v>43.9</v>
       </c>
       <c r="BH145" s="13" t="n">
-        <v>38</v>
+        <v>721</v>
       </c>
       <c r="BI145" s="19" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="BJ145" s="13" t="n">
-        <v>44</v>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="BJ145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BK145" s="19" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="BL145" s="13" t="n">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="BL145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BM145" s="19" t="n">
-        <v>99.7</v>
+        <v>0</v>
       </c>
       <c r="BN145" s="15" t="n">
-        <v>1875</v>
+        <v>6502</v>
       </c>
       <c r="BO145" s="19" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="BP145" s="13" t="n">
-        <v>818</v>
+        <v>75.7</v>
+      </c>
+      <c r="BP145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ145" s="19" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="BR145" s="15" t="n">
-        <v>944</v>
+        <v>0</v>
+      </c>
+      <c r="BR145" s="20" t="n">
+        <v>12189</v>
       </c>
       <c r="BS145" s="19" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="BT145" s="13" t="n">
-        <v>1105</v>
+        <v>52.2</v>
+      </c>
+      <c r="BT145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU145" s="19" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="BV145" s="15" t="n">
-        <v>1743</v>
+        <v>0</v>
+      </c>
+      <c r="BV145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BW145" s="19" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="BX145" s="13" t="n">
-        <v>2301</v>
+        <v>0</v>
+      </c>
+      <c r="BX145" s="25" t="n">
+        <v>15989</v>
       </c>
       <c r="BY145" s="19" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="BZ145" s="15" t="n">
-        <v>3516</v>
+        <v>30</v>
+      </c>
+      <c r="BZ145" s="20" t="n">
+        <v>7033</v>
       </c>
       <c r="CA145" s="19" t="n">
-        <v>82</v>
-      </c>
-      <c r="CB145" s="15" t="n">
-        <v>898</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="CB145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CC145" s="19" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="CD145" s="20" t="n">
-        <v>4150</v>
+        <v>5354</v>
       </c>
       <c r="CE145" s="19" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="CF145" s="13" t="n">
-        <v>1785</v>
+        <v>68.2</v>
+      </c>
+      <c r="CF145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG145" s="19" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="CH145" s="20" t="n">
-        <v>1944</v>
+        <v>0</v>
+      </c>
+      <c r="CH145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CI145" s="19" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="CJ145" s="13" t="n">
-        <v>1632</v>
+        <v>0</v>
+      </c>
+      <c r="CJ145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CK145" s="19" t="n">
-        <v>94</v>
-      </c>
-      <c r="CL145" s="15" t="n">
-        <v>5459</v>
+        <v>0</v>
+      </c>
+      <c r="CL145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM145" s="19" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="CN145" s="15" t="n">
-        <v>2478</v>
+        <v>0</v>
+      </c>
+      <c r="CN145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CO145" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="CP145" s="15" t="n">
-        <v>5705</v>
+        <v>0</v>
+      </c>
+      <c r="CP145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ145" s="19" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="CR145" s="15" t="n">
-        <v>2120</v>
+        <v>0</v>
+      </c>
+      <c r="CR145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CS145" s="19" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="CT145" s="13" t="n">
-        <v>2172</v>
+        <v>0</v>
+      </c>
+      <c r="CT145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CU145" s="19" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="CV145" s="20" t="n">
-        <v>8977</v>
+        <v>0</v>
+      </c>
+      <c r="CV145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW145" s="19" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="CX145" s="13" t="n">
-        <v>198</v>
+        <v>0</v>
+      </c>
+      <c r="CX145" s="20" t="n">
+        <v>6680</v>
       </c>
       <c r="CY145" s="19" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="CZ145" s="19" t="n">
-        <v>-1</v>
+        <v>60.2</v>
+      </c>
+      <c r="CZ145" s="20" t="n">
+        <v>7363</v>
       </c>
       <c r="DA145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB145" s="15" t="n">
-        <v>2596</v>
+        <v>55.3</v>
+      </c>
+      <c r="DB145" s="20" t="n">
+        <v>4316</v>
       </c>
       <c r="DC145" s="19" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="DD145" s="20" t="n">
-        <v>7156</v>
+        <v>71.8</v>
+      </c>
+      <c r="DD145" s="15" t="n">
+        <v>5395</v>
       </c>
       <c r="DE145" s="19" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="DF145" s="15" t="n">
-        <v>1519</v>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="DF145" s="20" t="n">
+        <v>8693</v>
       </c>
       <c r="DG145" s="19" t="n">
-        <v>87.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="146">
@@ -46398,14 +46408,14 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>zhi-zhi</t>
+          <t>fatyuan</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>1070</v>
+        <v>1174</v>
       </c>
       <c r="D146" s="26" t="n">
-        <v>2090</v>
+        <v>1629</v>
       </c>
       <c r="E146" s="12" t="n">
         <v>0</v>
@@ -46434,23 +46444,23 @@
       <c r="M146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N146" s="20" t="n">
-        <v>4934</v>
+      <c r="N146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O146" s="14" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="P146" s="15" t="n">
-        <v>201</v>
+        <v>0</v>
+      </c>
+      <c r="P146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Q146" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="R146" s="15" t="n">
-        <v>261</v>
+        <v>0</v>
+      </c>
+      <c r="R146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="S146" s="14" t="n">
-        <v>93.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="T146" s="14" t="n">
         <v>-1</v>
@@ -46458,23 +46468,23 @@
       <c r="U146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="15" t="n">
-        <v>474</v>
+      <c r="V146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="W146" s="14" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="X146" s="20" t="n">
-        <v>8489</v>
+        <v>0</v>
+      </c>
+      <c r="X146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Y146" s="14" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="Z146" s="20" t="n">
-        <v>8494</v>
+        <v>0</v>
+      </c>
+      <c r="Z146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AA146" s="14" t="n">
-        <v>50.4</v>
+        <v>0</v>
       </c>
       <c r="AB146" s="14" t="n">
         <v>-1</v>
@@ -46494,23 +46504,23 @@
       <c r="AG146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH146" s="15" t="n">
-        <v>912</v>
+      <c r="AH146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AI146" s="14" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="AJ146" s="20" t="n">
-        <v>5636</v>
+        <v>0</v>
+      </c>
+      <c r="AJ146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AK146" s="14" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="AL146" s="15" t="n">
-        <v>1814</v>
+        <v>0</v>
+      </c>
+      <c r="AL146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AM146" s="14" t="n">
-        <v>88.3</v>
+        <v>0</v>
       </c>
       <c r="AN146" s="14" t="n">
         <v>-1</v>
@@ -46518,83 +46528,83 @@
       <c r="AO146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP146" s="15" t="n">
-        <v>1309</v>
+      <c r="AP146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ146" s="14" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="AR146" s="13" t="n">
-        <v>210</v>
+        <v>0</v>
+      </c>
+      <c r="AR146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AS146" s="14" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="AT146" s="20" t="n">
-        <v>2876</v>
+        <v>0</v>
+      </c>
+      <c r="AT146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AU146" s="14" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="AV146" s="20" t="n">
-        <v>3316</v>
+        <v>0</v>
+      </c>
+      <c r="AV146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AW146" s="14" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="AX146" s="20" t="n">
-        <v>1182</v>
+        <v>0</v>
+      </c>
+      <c r="AX146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY146" s="14" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="AZ146" s="15" t="n">
-        <v>4412</v>
+        <v>0</v>
+      </c>
+      <c r="AZ146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BA146" s="14" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="BB146" s="15" t="n">
-        <v>204</v>
+        <v>0</v>
+      </c>
+      <c r="BB146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BC146" s="14" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="BD146" s="20" t="n">
-        <v>8250</v>
+        <v>0</v>
+      </c>
+      <c r="BD146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BE146" s="14" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="BF146" s="13" t="n">
-        <v>284</v>
+        <v>0</v>
+      </c>
+      <c r="BF146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BG146" s="14" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="BH146" s="13" t="n">
-        <v>711</v>
+        <v>0</v>
+      </c>
+      <c r="BH146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BI146" s="14" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="BJ146" s="15" t="n">
-        <v>921</v>
+        <v>0</v>
+      </c>
+      <c r="BJ146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BK146" s="14" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="BL146" s="25" t="n">
-        <v>14295</v>
+        <v>0</v>
+      </c>
+      <c r="BL146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM146" s="14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BN146" s="15" t="n">
-        <v>866</v>
+        <v>0</v>
+      </c>
+      <c r="BN146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BO146" s="14" t="n">
-        <v>92.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BP146" s="14" t="n">
         <v>-1</v>
@@ -46602,23 +46612,23 @@
       <c r="BQ146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BR146" s="15" t="n">
-        <v>2253</v>
+      <c r="BR146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BS146" s="14" t="n">
-        <v>88</v>
-      </c>
-      <c r="BT146" s="15" t="n">
-        <v>2290</v>
+        <v>0</v>
+      </c>
+      <c r="BT146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BU146" s="14" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="BV146" s="15" t="n">
-        <v>948</v>
+        <v>0</v>
+      </c>
+      <c r="BV146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BW146" s="14" t="n">
-        <v>91.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX146" s="14" t="n">
         <v>-1</v>
@@ -46626,11 +46636,11 @@
       <c r="BY146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BZ146" s="15" t="n">
-        <v>637</v>
+      <c r="BZ146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CA146" s="14" t="n">
-        <v>92.7</v>
+        <v>0</v>
       </c>
       <c r="CB146" s="14" t="n">
         <v>-1</v>
@@ -46638,23 +46648,23 @@
       <c r="CC146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CD146" s="15" t="n">
-        <v>1207</v>
+      <c r="CD146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CE146" s="14" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="CF146" s="20" t="n">
-        <v>5293</v>
+        <v>0</v>
+      </c>
+      <c r="CF146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CG146" s="14" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="CH146" s="20" t="n">
-        <v>5932</v>
+        <v>0</v>
+      </c>
+      <c r="CH146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CI146" s="14" t="n">
-        <v>67.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CJ146" s="14" t="n">
         <v>-1</v>
@@ -46662,17 +46672,17 @@
       <c r="CK146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL146" s="15" t="n">
-        <v>2992</v>
+      <c r="CL146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CM146" s="14" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="CN146" s="15" t="n">
-        <v>6362</v>
+        <v>0</v>
+      </c>
+      <c r="CN146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CO146" s="14" t="n">
-        <v>69.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CP146" s="14" t="n">
         <v>-1</v>
@@ -46680,29 +46690,29 @@
       <c r="CQ146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CR146" s="15" t="n">
-        <v>1294</v>
+      <c r="CR146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CS146" s="14" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="CT146" s="13" t="n">
-        <v>2125</v>
+        <v>0</v>
+      </c>
+      <c r="CT146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CU146" s="14" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="CV146" s="20" t="n">
-        <v>3653</v>
+        <v>0</v>
+      </c>
+      <c r="CV146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CW146" s="14" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="CX146" s="20" t="n">
-        <v>6463</v>
+        <v>0</v>
+      </c>
+      <c r="CX146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY146" s="14" t="n">
-        <v>61.1</v>
+        <v>0</v>
       </c>
       <c r="CZ146" s="14" t="n">
         <v>-1</v>
@@ -46710,11 +46720,11 @@
       <c r="DA146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB146" s="20" t="n">
-        <v>4706</v>
+      <c r="DB146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DC146" s="14" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="DD146" s="14" t="n">
         <v>-1</v>
@@ -46722,11 +46732,11 @@
       <c r="DE146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DF146" s="15" t="n">
-        <v>1479</v>
+      <c r="DF146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DG146" s="14" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -46735,14 +46745,14 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>bill04128682</t>
+          <t>mfk443838746</t>
         </is>
       </c>
       <c r="C147" s="17" t="n">
-        <v>931</v>
-      </c>
-      <c r="D147" s="27" t="n">
-        <v>2014</v>
+        <v>1109</v>
+      </c>
+      <c r="D147" s="24" t="n">
+        <v>2317</v>
       </c>
       <c r="E147" s="12" t="n">
         <v>0</v>
@@ -46783,29 +46793,29 @@
       <c r="Q147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R147" s="19" t="n">
-        <v>-1</v>
+      <c r="R147" s="15" t="n">
+        <v>287</v>
       </c>
       <c r="S147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" s="19" t="n">
-        <v>-1</v>
+        <v>93.5</v>
+      </c>
+      <c r="T147" s="13" t="n">
+        <v>1071</v>
       </c>
       <c r="U147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" s="19" t="n">
-        <v>-1</v>
+        <v>94.5</v>
+      </c>
+      <c r="V147" s="15" t="n">
+        <v>418</v>
       </c>
       <c r="W147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" s="19" t="n">
-        <v>-1</v>
+        <v>92.7</v>
+      </c>
+      <c r="X147" s="15" t="n">
+        <v>2329</v>
       </c>
       <c r="Y147" s="19" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="Z147" s="19" t="n">
         <v>-1</v>
@@ -46831,29 +46841,29 @@
       <c r="AG147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AH147" s="19" t="n">
-        <v>-1</v>
+      <c r="AH147" s="15" t="n">
+        <v>650</v>
       </c>
       <c r="AI147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ147" s="20" t="n">
-        <v>5125</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AJ147" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AK147" s="19" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="AL147" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AL147" s="15" t="n">
+        <v>973</v>
       </c>
       <c r="AM147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN147" s="19" t="n">
-        <v>-1</v>
+        <v>91.40000000000001</v>
+      </c>
+      <c r="AN147" s="13" t="n">
+        <v>166</v>
       </c>
       <c r="AO147" s="19" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AP147" s="19" t="n">
         <v>-1</v>
@@ -46861,29 +46871,29 @@
       <c r="AQ147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AR147" s="19" t="n">
-        <v>-1</v>
+      <c r="AR147" s="13" t="n">
+        <v>572</v>
       </c>
       <c r="AS147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT147" s="19" t="n">
-        <v>-1</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AT147" s="20" t="n">
+        <v>1501</v>
       </c>
       <c r="AU147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV147" s="19" t="n">
-        <v>-1</v>
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AV147" s="20" t="n">
+        <v>5871</v>
       </c>
       <c r="AW147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX147" s="19" t="n">
-        <v>-1</v>
+        <v>70.8</v>
+      </c>
+      <c r="AX147" s="20" t="n">
+        <v>4692</v>
       </c>
       <c r="AY147" s="19" t="n">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="AZ147" s="19" t="n">
         <v>-1</v>
@@ -46891,155 +46901,155 @@
       <c r="BA147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB147" s="19" t="n">
-        <v>-1</v>
+      <c r="BB147" s="20" t="n">
+        <v>2375</v>
       </c>
       <c r="BC147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD147" s="19" t="n">
-        <v>-1</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="BD147" s="20" t="n">
+        <v>2507</v>
       </c>
       <c r="BE147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF147" s="19" t="n">
-        <v>-1</v>
+        <v>82.3</v>
+      </c>
+      <c r="BF147" s="13" t="n">
+        <v>367</v>
       </c>
       <c r="BG147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH147" s="19" t="n">
-        <v>-1</v>
+        <v>89</v>
+      </c>
+      <c r="BH147" s="13" t="n">
+        <v>38</v>
       </c>
       <c r="BI147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ147" s="19" t="n">
-        <v>-1</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BJ147" s="13" t="n">
+        <v>44</v>
       </c>
       <c r="BK147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL147" s="19" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="BL147" s="13" t="n">
+        <v>72</v>
       </c>
       <c r="BM147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN147" s="19" t="n">
-        <v>-1</v>
+        <v>99.7</v>
+      </c>
+      <c r="BN147" s="15" t="n">
+        <v>1875</v>
       </c>
       <c r="BO147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP147" s="19" t="n">
-        <v>-1</v>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="BP147" s="13" t="n">
+        <v>818</v>
       </c>
       <c r="BQ147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR147" s="19" t="n">
-        <v>-1</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="BR147" s="15" t="n">
+        <v>944</v>
       </c>
       <c r="BS147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT147" s="19" t="n">
-        <v>-1</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="BT147" s="13" t="n">
+        <v>1105</v>
       </c>
       <c r="BU147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV147" s="19" t="n">
-        <v>-1</v>
+        <v>96.5</v>
+      </c>
+      <c r="BV147" s="15" t="n">
+        <v>1743</v>
       </c>
       <c r="BW147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX147" s="19" t="n">
-        <v>-1</v>
+        <v>89.3</v>
+      </c>
+      <c r="BX147" s="13" t="n">
+        <v>2301</v>
       </c>
       <c r="BY147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ147" s="19" t="n">
-        <v>-1</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="BZ147" s="15" t="n">
+        <v>3516</v>
       </c>
       <c r="CA147" s="19" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="CB147" s="15" t="n">
-        <v>1644</v>
+        <v>898</v>
       </c>
       <c r="CC147" s="19" t="n">
-        <v>88</v>
-      </c>
-      <c r="CD147" s="19" t="n">
-        <v>-1</v>
+        <v>91.2</v>
+      </c>
+      <c r="CD147" s="20" t="n">
+        <v>4150</v>
       </c>
       <c r="CE147" s="19" t="n">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="CF147" s="13" t="n">
-        <v>1445</v>
+        <v>1785</v>
       </c>
       <c r="CG147" s="19" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="CH147" s="19" t="n">
-        <v>-1</v>
+        <v>93.2</v>
+      </c>
+      <c r="CH147" s="20" t="n">
+        <v>1944</v>
       </c>
       <c r="CI147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ147" s="19" t="n">
-        <v>-1</v>
+        <v>82.5</v>
+      </c>
+      <c r="CJ147" s="13" t="n">
+        <v>1632</v>
       </c>
       <c r="CK147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL147" s="13" t="n">
-        <v>1248</v>
+        <v>94</v>
+      </c>
+      <c r="CL147" s="15" t="n">
+        <v>5459</v>
       </c>
       <c r="CM147" s="19" t="n">
-        <v>95.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="CN147" s="15" t="n">
-        <v>2582</v>
+        <v>2478</v>
       </c>
       <c r="CO147" s="19" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="CP147" s="19" t="n">
-        <v>-1</v>
+        <v>85</v>
+      </c>
+      <c r="CP147" s="15" t="n">
+        <v>5705</v>
       </c>
       <c r="CQ147" s="19" t="n">
-        <v>0</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="CR147" s="15" t="n">
-        <v>5511</v>
+        <v>2120</v>
       </c>
       <c r="CS147" s="19" t="n">
-        <v>76.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="CT147" s="13" t="n">
-        <v>1501</v>
+        <v>2172</v>
       </c>
       <c r="CU147" s="19" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="CV147" s="19" t="n">
-        <v>-1</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="CV147" s="20" t="n">
+        <v>8977</v>
       </c>
       <c r="CW147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX147" s="19" t="n">
-        <v>-1</v>
+        <v>52.3</v>
+      </c>
+      <c r="CX147" s="13" t="n">
+        <v>198</v>
       </c>
       <c r="CY147" s="19" t="n">
-        <v>0</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="CZ147" s="19" t="n">
         <v>-1</v>
@@ -47047,28 +47057,23 @@
       <c r="DA147" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DB147" s="19" t="n">
-        <v>-1</v>
+      <c r="DB147" s="15" t="n">
+        <v>2596</v>
       </c>
       <c r="DC147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD147" s="19" t="n">
-        <v>-1</v>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="DD147" s="20" t="n">
+        <v>7156</v>
       </c>
       <c r="DE147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF147" s="19" t="n">
-        <v>-1</v>
+        <v>57.4</v>
+      </c>
+      <c r="DF147" s="15" t="n">
+        <v>1519</v>
       </c>
       <c r="DG147" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH147" s="1" t="inlineStr">
-        <is>
-          <t>JumpTrade-Logo</t>
-        </is>
+        <v>87.3</v>
       </c>
     </row>
     <row r="148">
@@ -47077,14 +47082,14 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>deadstorm</t>
+          <t>zhi-zhi</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>814</v>
+        <v>1070</v>
       </c>
       <c r="D148" s="26" t="n">
-        <v>1433</v>
+        <v>2090</v>
       </c>
       <c r="E148" s="12" t="n">
         <v>0</v>
@@ -47113,23 +47118,23 @@
       <c r="M148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N148" s="14" t="n">
-        <v>-1</v>
+      <c r="N148" s="20" t="n">
+        <v>4934</v>
       </c>
       <c r="O148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" s="14" t="n">
-        <v>-1</v>
+        <v>62.8</v>
+      </c>
+      <c r="P148" s="15" t="n">
+        <v>201</v>
       </c>
       <c r="Q148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" s="14" t="n">
-        <v>-1</v>
+        <v>94</v>
+      </c>
+      <c r="R148" s="15" t="n">
+        <v>261</v>
       </c>
       <c r="S148" s="14" t="n">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="T148" s="14" t="n">
         <v>-1</v>
@@ -47137,23 +47142,23 @@
       <c r="U148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="14" t="n">
-        <v>-1</v>
+      <c r="V148" s="15" t="n">
+        <v>474</v>
       </c>
       <c r="W148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" s="14" t="n">
-        <v>-1</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="X148" s="20" t="n">
+        <v>8489</v>
       </c>
       <c r="Y148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z148" s="14" t="n">
-        <v>-1</v>
+        <v>43.6</v>
+      </c>
+      <c r="Z148" s="20" t="n">
+        <v>8494</v>
       </c>
       <c r="AA148" s="14" t="n">
-        <v>0</v>
+        <v>50.4</v>
       </c>
       <c r="AB148" s="14" t="n">
         <v>-1</v>
@@ -47173,23 +47178,23 @@
       <c r="AG148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH148" s="14" t="n">
-        <v>-1</v>
+      <c r="AH148" s="15" t="n">
+        <v>912</v>
       </c>
       <c r="AI148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ148" s="14" t="n">
-        <v>-1</v>
+        <v>90.3</v>
+      </c>
+      <c r="AJ148" s="20" t="n">
+        <v>5636</v>
       </c>
       <c r="AK148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL148" s="14" t="n">
-        <v>-1</v>
+        <v>66.7</v>
+      </c>
+      <c r="AL148" s="15" t="n">
+        <v>1814</v>
       </c>
       <c r="AM148" s="14" t="n">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="AN148" s="14" t="n">
         <v>-1</v>
@@ -47197,83 +47202,83 @@
       <c r="AO148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP148" s="14" t="n">
-        <v>-1</v>
+      <c r="AP148" s="15" t="n">
+        <v>1309</v>
       </c>
       <c r="AQ148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR148" s="14" t="n">
-        <v>-1</v>
+        <v>90.8</v>
+      </c>
+      <c r="AR148" s="13" t="n">
+        <v>210</v>
       </c>
       <c r="AS148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT148" s="14" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="AT148" s="20" t="n">
+        <v>2876</v>
       </c>
       <c r="AU148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV148" s="14" t="n">
-        <v>-1</v>
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AV148" s="20" t="n">
+        <v>3316</v>
       </c>
       <c r="AW148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX148" s="14" t="n">
-        <v>-1</v>
+        <v>79.2</v>
+      </c>
+      <c r="AX148" s="20" t="n">
+        <v>1182</v>
       </c>
       <c r="AY148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ148" s="14" t="n">
-        <v>-1</v>
+        <v>85.59999999999999</v>
+      </c>
+      <c r="AZ148" s="15" t="n">
+        <v>4412</v>
       </c>
       <c r="BA148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB148" s="14" t="n">
-        <v>-1</v>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="BB148" s="15" t="n">
+        <v>204</v>
       </c>
       <c r="BC148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD148" s="14" t="n">
-        <v>-1</v>
+        <v>94.3</v>
+      </c>
+      <c r="BD148" s="20" t="n">
+        <v>8250</v>
       </c>
       <c r="BE148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF148" s="14" t="n">
-        <v>-1</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="BF148" s="13" t="n">
+        <v>284</v>
       </c>
       <c r="BG148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH148" s="14" t="n">
-        <v>-1</v>
+        <v>91.5</v>
+      </c>
+      <c r="BH148" s="13" t="n">
+        <v>711</v>
       </c>
       <c r="BI148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ148" s="14" t="n">
-        <v>-1</v>
+        <v>79.2</v>
+      </c>
+      <c r="BJ148" s="15" t="n">
+        <v>921</v>
       </c>
       <c r="BK148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL148" s="14" t="n">
-        <v>-1</v>
+        <v>68.5</v>
+      </c>
+      <c r="BL148" s="25" t="n">
+        <v>14295</v>
       </c>
       <c r="BM148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN148" s="14" t="n">
-        <v>-1</v>
+        <v>18.5</v>
+      </c>
+      <c r="BN148" s="15" t="n">
+        <v>866</v>
       </c>
       <c r="BO148" s="14" t="n">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="BP148" s="14" t="n">
         <v>-1</v>
@@ -47281,23 +47286,23 @@
       <c r="BQ148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BR148" s="14" t="n">
-        <v>-1</v>
+      <c r="BR148" s="15" t="n">
+        <v>2253</v>
       </c>
       <c r="BS148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT148" s="14" t="n">
-        <v>-1</v>
+        <v>88</v>
+      </c>
+      <c r="BT148" s="15" t="n">
+        <v>2290</v>
       </c>
       <c r="BU148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV148" s="14" t="n">
-        <v>-1</v>
+        <v>87.8</v>
+      </c>
+      <c r="BV148" s="15" t="n">
+        <v>948</v>
       </c>
       <c r="BW148" s="14" t="n">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="BX148" s="14" t="n">
         <v>-1</v>
@@ -47305,11 +47310,11 @@
       <c r="BY148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BZ148" s="14" t="n">
-        <v>-1</v>
+      <c r="BZ148" s="15" t="n">
+        <v>637</v>
       </c>
       <c r="CA148" s="14" t="n">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="CB148" s="14" t="n">
         <v>-1</v>
@@ -47317,23 +47322,23 @@
       <c r="CC148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CD148" s="14" t="n">
-        <v>-1</v>
+      <c r="CD148" s="15" t="n">
+        <v>1207</v>
       </c>
       <c r="CE148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF148" s="14" t="n">
-        <v>-1</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="CF148" s="20" t="n">
+        <v>5293</v>
       </c>
       <c r="CG148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH148" s="14" t="n">
-        <v>-1</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="CH148" s="20" t="n">
+        <v>5932</v>
       </c>
       <c r="CI148" s="14" t="n">
-        <v>0</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="CJ148" s="14" t="n">
         <v>-1</v>
@@ -47341,17 +47346,17 @@
       <c r="CK148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL148" s="14" t="n">
-        <v>-1</v>
+      <c r="CL148" s="15" t="n">
+        <v>2992</v>
       </c>
       <c r="CM148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN148" s="14" t="n">
-        <v>-1</v>
+        <v>84.90000000000001</v>
+      </c>
+      <c r="CN148" s="15" t="n">
+        <v>6362</v>
       </c>
       <c r="CO148" s="14" t="n">
-        <v>0</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="CP148" s="14" t="n">
         <v>-1</v>
@@ -47359,29 +47364,29 @@
       <c r="CQ148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CR148" s="14" t="n">
-        <v>-1</v>
+      <c r="CR148" s="15" t="n">
+        <v>1294</v>
       </c>
       <c r="CS148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT148" s="14" t="n">
-        <v>-1</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="CT148" s="13" t="n">
+        <v>2125</v>
       </c>
       <c r="CU148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV148" s="14" t="n">
-        <v>-1</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="CV148" s="20" t="n">
+        <v>3653</v>
       </c>
       <c r="CW148" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX148" s="14" t="n">
-        <v>-1</v>
+        <v>74.59999999999999</v>
+      </c>
+      <c r="CX148" s="20" t="n">
+        <v>6463</v>
       </c>
       <c r="CY148" s="14" t="n">
-        <v>0</v>
+        <v>61.1</v>
       </c>
       <c r="CZ148" s="14" t="n">
         <v>-1</v>
@@ -47389,11 +47394,11 @@
       <c r="DA148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB148" s="14" t="n">
-        <v>-1</v>
+      <c r="DB148" s="20" t="n">
+        <v>4706</v>
       </c>
       <c r="DC148" s="14" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="DD148" s="14" t="n">
         <v>-1</v>
@@ -47401,11 +47406,11 @@
       <c r="DE148" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DF148" s="14" t="n">
-        <v>-1</v>
+      <c r="DF148" s="15" t="n">
+        <v>1479</v>
       </c>
       <c r="DG148" s="14" t="n">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="149">
@@ -47414,14 +47419,14 @@
       </c>
       <c r="B149" s="16" t="inlineStr">
         <is>
-          <t>liulaoye135</t>
+          <t>bill04128682</t>
         </is>
       </c>
       <c r="C149" s="17" t="n">
-        <v>613</v>
-      </c>
-      <c r="D149" s="24" t="n">
-        <v>2289</v>
+        <v>931</v>
+      </c>
+      <c r="D149" s="27" t="n">
+        <v>2014</v>
       </c>
       <c r="E149" s="12" t="n">
         <v>0</v>
@@ -47444,11 +47449,11 @@
       <c r="K149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L149" s="15" t="n">
-        <v>505</v>
+      <c r="L149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="M149" s="19" t="n">
-        <v>92.2</v>
+        <v>0</v>
       </c>
       <c r="N149" s="19" t="n">
         <v>-1</v>
@@ -47462,11 +47467,11 @@
       <c r="Q149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R149" s="15" t="n">
-        <v>251</v>
+      <c r="R149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S149" s="19" t="n">
-        <v>93.7</v>
+        <v>0</v>
       </c>
       <c r="T149" s="19" t="n">
         <v>-1</v>
@@ -47486,23 +47491,23 @@
       <c r="Y149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="15" t="n">
-        <v>557</v>
+      <c r="Z149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AA149" s="19" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="AB149" s="15" t="n">
-        <v>1169</v>
+        <v>0</v>
+      </c>
+      <c r="AB149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC149" s="19" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="AD149" s="15" t="n">
-        <v>317</v>
+        <v>0</v>
+      </c>
+      <c r="AD149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AE149" s="19" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AF149" s="19" t="n">
         <v>-1</v>
@@ -47510,77 +47515,77 @@
       <c r="AG149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AH149" s="15" t="n">
-        <v>684</v>
+      <c r="AH149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI149" s="19" t="n">
-        <v>91.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ149" s="20" t="n">
-        <v>1646</v>
+        <v>5125</v>
       </c>
       <c r="AK149" s="19" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="AL149" s="20" t="n">
-        <v>7134</v>
+        <v>68.8</v>
+      </c>
+      <c r="AL149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AM149" s="19" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="AN149" s="13" t="n">
-        <v>1852</v>
+        <v>0</v>
+      </c>
+      <c r="AN149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AO149" s="19" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="AP149" s="20" t="n">
-        <v>2332</v>
+        <v>0</v>
+      </c>
+      <c r="AP149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ149" s="19" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="AR149" s="15" t="n">
-        <v>993</v>
+        <v>0</v>
+      </c>
+      <c r="AR149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AS149" s="19" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="AT149" s="20" t="n">
-        <v>2871</v>
+        <v>0</v>
+      </c>
+      <c r="AT149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AU149" s="19" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="AV149" s="20" t="n">
-        <v>2346</v>
+        <v>0</v>
+      </c>
+      <c r="AV149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW149" s="19" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="AX149" s="20" t="n">
-        <v>1566</v>
+        <v>0</v>
+      </c>
+      <c r="AX149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY149" s="19" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="AZ149" s="13" t="n">
-        <v>340</v>
+        <v>0</v>
+      </c>
+      <c r="AZ149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BA149" s="19" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="BB149" s="20" t="n">
-        <v>3605</v>
+        <v>0</v>
+      </c>
+      <c r="BB149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BC149" s="19" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="BD149" s="20" t="n">
-        <v>3982</v>
+        <v>0</v>
+      </c>
+      <c r="BD149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BE149" s="19" t="n">
-        <v>77.7</v>
+        <v>0</v>
       </c>
       <c r="BF149" s="19" t="n">
         <v>-1</v>
@@ -47600,153 +47605,153 @@
       <c r="BK149" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BL149" s="13" t="n">
-        <v>905</v>
+      <c r="BL149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BM149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BS149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BW149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BY149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB149" s="15" t="n">
+        <v>1644</v>
+      </c>
+      <c r="CC149" s="19" t="n">
+        <v>88</v>
+      </c>
+      <c r="CD149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CE149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF149" s="13" t="n">
+        <v>1445</v>
+      </c>
+      <c r="CG149" s="19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="CH149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CI149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ149" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK149" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL149" s="13" t="n">
+        <v>1248</v>
+      </c>
+      <c r="CM149" s="19" t="n">
         <v>95.8</v>
       </c>
-      <c r="BN149" s="13" t="n">
-        <v>488</v>
-      </c>
-      <c r="BO149" s="19" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="BP149" s="13" t="n">
-        <v>742</v>
-      </c>
-      <c r="BQ149" s="19" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="BR149" s="15" t="n">
-        <v>1440</v>
-      </c>
-      <c r="BS149" s="19" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="BT149" s="15" t="n">
-        <v>3458</v>
-      </c>
-      <c r="BU149" s="19" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="BV149" s="15" t="n">
-        <v>5399</v>
-      </c>
-      <c r="BW149" s="19" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="BX149" s="15" t="n">
-        <v>6328</v>
-      </c>
-      <c r="BY149" s="19" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="BZ149" s="15" t="n">
-        <v>1872</v>
-      </c>
-      <c r="CA149" s="19" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="CB149" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CC149" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD149" s="15" t="n">
-        <v>2815</v>
-      </c>
-      <c r="CE149" s="19" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="CF149" s="13" t="n">
-        <v>1337</v>
-      </c>
-      <c r="CG149" s="19" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="CH149" s="15" t="n">
-        <v>284</v>
-      </c>
-      <c r="CI149" s="19" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="CJ149" s="13" t="n">
-        <v>643</v>
-      </c>
-      <c r="CK149" s="19" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="CL149" s="15" t="n">
-        <v>5722</v>
-      </c>
-      <c r="CM149" s="19" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="CN149" s="13" t="n">
-        <v>801</v>
+      <c r="CN149" s="15" t="n">
+        <v>2582</v>
       </c>
       <c r="CO149" s="19" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="CP149" s="15" t="n">
-        <v>2432</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="CP149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ149" s="19" t="n">
-        <v>86.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="CR149" s="15" t="n">
-        <v>3446</v>
+        <v>5511</v>
       </c>
       <c r="CS149" s="19" t="n">
-        <v>83.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="CT149" s="13" t="n">
-        <v>239</v>
+        <v>1501</v>
       </c>
       <c r="CU149" s="19" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="CV149" s="20" t="n">
-        <v>7539</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="CV149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW149" s="19" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="CX149" s="13" t="n">
-        <v>408</v>
+        <v>0</v>
+      </c>
+      <c r="CX149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CY149" s="19" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="CZ149" s="13" t="n">
-        <v>1252</v>
+        <v>0</v>
+      </c>
+      <c r="CZ149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA149" s="19" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="DB149" s="15" t="n">
-        <v>2179</v>
+        <v>0</v>
+      </c>
+      <c r="DB149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DC149" s="19" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="DD149" s="15" t="n">
-        <v>1543</v>
+        <v>0</v>
+      </c>
+      <c r="DD149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE149" s="19" t="n">
-        <v>88</v>
-      </c>
-      <c r="DF149" s="15" t="n">
-        <v>1070</v>
+        <v>0</v>
+      </c>
+      <c r="DF149" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DG149" s="19" t="n">
-        <v>89.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="DH149" s="1" t="inlineStr">
         <is>
-          <t>Meta-Logo</t>
+          <t>JumpTrade-Logo</t>
         </is>
       </c>
     </row>
@@ -47756,14 +47761,14 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>Q2PPSElacY</t>
+          <t>deadstorm</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>163</v>
+        <v>814</v>
       </c>
       <c r="D150" s="26" t="n">
-        <v>1731</v>
+        <v>1433</v>
       </c>
       <c r="E150" s="12" t="n">
         <v>0</v>
@@ -47852,11 +47857,11 @@
       <c r="AG150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH150" s="20" t="n">
-        <v>2005</v>
+      <c r="AH150" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AI150" s="14" t="n">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ150" s="14" t="n">
         <v>-1</v>
@@ -47900,188 +47905,188 @@
       <c r="AW150" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX150" s="20" t="n">
-        <v>3161</v>
+      <c r="AX150" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY150" s="14" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AZ150" s="20" t="n">
-        <v>7063</v>
+        <v>0</v>
+      </c>
+      <c r="AZ150" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BA150" s="14" t="n">
-        <v>67.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BC150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BD150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BF150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BH150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BI150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BJ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BL150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BN150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BO150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BP150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BQ150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BR150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BT150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BU150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BV150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BW150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BX150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BZ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CA150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CD150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CF150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CG150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CH150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CI150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CJ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CL150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CM150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CN150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CP150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CQ150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CR150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CS150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CT150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CV150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CX150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CZ150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DA150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="DB150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="DD150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DE150" s="14" t="n">
         <v>0</v>
       </c>
       <c r="DF150" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DG150" s="14" t="n">
         <v>0</v>
@@ -48093,14 +48098,14 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>zyx-37</t>
+          <t>liulaoye135</t>
         </is>
       </c>
       <c r="C151" s="17" t="n">
-        <v>133</v>
-      </c>
-      <c r="D151" s="27" t="n">
-        <v>2018</v>
+        <v>613</v>
+      </c>
+      <c r="D151" s="24" t="n">
+        <v>2289</v>
       </c>
       <c r="E151" s="12" t="n">
         <v>0</v>
@@ -48123,11 +48128,11 @@
       <c r="K151" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="19" t="n">
-        <v>-1</v>
+      <c r="L151" s="15" t="n">
+        <v>505</v>
       </c>
       <c r="M151" s="19" t="n">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="N151" s="19" t="n">
         <v>-1</v>
@@ -48135,23 +48140,23 @@
       <c r="O151" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P151" s="20" t="n">
-        <v>2254</v>
+      <c r="P151" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Q151" s="19" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="R151" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="R151" s="15" t="n">
+        <v>251</v>
       </c>
       <c r="S151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="13" t="n">
-        <v>1072</v>
+        <v>93.7</v>
+      </c>
+      <c r="T151" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U151" s="19" t="n">
-        <v>94.5</v>
+        <v>0</v>
       </c>
       <c r="V151" s="19" t="n">
         <v>-1</v>
@@ -48159,273 +48164,273 @@
       <c r="W151" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="X151" s="20" t="n">
-        <v>8557</v>
+      <c r="X151" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y151" s="19" t="n">
-        <v>43.3</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="15" t="n">
-        <v>767</v>
+        <v>557</v>
       </c>
       <c r="AA151" s="19" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AB151" s="15" t="n">
+        <v>1169</v>
+      </c>
+      <c r="AC151" s="19" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AD151" s="15" t="n">
+        <v>317</v>
+      </c>
+      <c r="AE151" s="19" t="n">
+        <v>93</v>
+      </c>
+      <c r="AF151" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="15" t="n">
+        <v>684</v>
+      </c>
+      <c r="AI151" s="19" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="AB151" s="15" t="n">
-        <v>2569</v>
-      </c>
-      <c r="AC151" s="19" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="AD151" s="25" t="n">
-        <v>11671</v>
-      </c>
-      <c r="AE151" s="19" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AF151" s="15" t="n">
-        <v>1806</v>
-      </c>
-      <c r="AG151" s="19" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="AH151" s="20" t="n">
-        <v>5332</v>
-      </c>
-      <c r="AI151" s="19" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="AJ151" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ151" s="20" t="n">
+        <v>1646</v>
       </c>
       <c r="AK151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL151" s="19" t="n">
-        <v>-1</v>
+        <v>83.2</v>
+      </c>
+      <c r="AL151" s="20" t="n">
+        <v>7134</v>
       </c>
       <c r="AM151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN151" s="15" t="n">
-        <v>5216</v>
+        <v>63.6</v>
+      </c>
+      <c r="AN151" s="13" t="n">
+        <v>1852</v>
       </c>
       <c r="AO151" s="19" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="AP151" s="25" t="n">
-        <v>11286</v>
+        <v>93.8</v>
+      </c>
+      <c r="AP151" s="20" t="n">
+        <v>2332</v>
       </c>
       <c r="AQ151" s="19" t="n">
-        <v>48.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AR151" s="15" t="n">
-        <v>2069</v>
+        <v>993</v>
       </c>
       <c r="AS151" s="19" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AT151" s="20" t="n">
+        <v>2871</v>
+      </c>
+      <c r="AU151" s="19" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AV151" s="20" t="n">
+        <v>2346</v>
+      </c>
+      <c r="AW151" s="19" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AX151" s="20" t="n">
+        <v>1566</v>
+      </c>
+      <c r="AY151" s="19" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="AZ151" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="BA151" s="19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BB151" s="20" t="n">
+        <v>3605</v>
+      </c>
+      <c r="BC151" s="19" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="BD151" s="20" t="n">
+        <v>3982</v>
+      </c>
+      <c r="BE151" s="19" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="BF151" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH151" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ151" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL151" s="13" t="n">
+        <v>905</v>
+      </c>
+      <c r="BM151" s="19" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="BN151" s="13" t="n">
+        <v>488</v>
+      </c>
+      <c r="BO151" s="19" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="BP151" s="13" t="n">
+        <v>742</v>
+      </c>
+      <c r="BQ151" s="19" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BR151" s="15" t="n">
+        <v>1440</v>
+      </c>
+      <c r="BS151" s="19" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="BT151" s="15" t="n">
+        <v>3458</v>
+      </c>
+      <c r="BU151" s="19" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BV151" s="15" t="n">
+        <v>5399</v>
+      </c>
+      <c r="BW151" s="19" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BX151" s="15" t="n">
+        <v>6328</v>
+      </c>
+      <c r="BY151" s="19" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="BZ151" s="15" t="n">
+        <v>1872</v>
+      </c>
+      <c r="CA151" s="19" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="AT151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AU151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AY151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BA151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BC151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BE151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BG151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BI151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BK151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BM151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN151" s="19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BO151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BQ151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR151" s="15" t="n">
-        <v>3048</v>
-      </c>
-      <c r="BS151" s="19" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="BT151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BU151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV151" s="15" t="n">
-        <v>5655</v>
-      </c>
-      <c r="BW151" s="19" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="BX151" s="13" t="n">
-        <v>2288</v>
-      </c>
-      <c r="BY151" s="19" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="BZ151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CA151" s="19" t="n">
-        <v>0</v>
-      </c>
       <c r="CB151" s="19" t="n">
         <v>-1</v>
       </c>
       <c r="CC151" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD151" s="19" t="n">
-        <v>-1</v>
+      <c r="CD151" s="15" t="n">
+        <v>2815</v>
       </c>
       <c r="CE151" s="19" t="n">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="CF151" s="13" t="n">
-        <v>1357</v>
+        <v>1337</v>
       </c>
       <c r="CG151" s="19" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="CH151" s="19" t="n">
-        <v>-1</v>
+        <v>94.90000000000001</v>
+      </c>
+      <c r="CH151" s="15" t="n">
+        <v>284</v>
       </c>
       <c r="CI151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ151" s="19" t="n">
-        <v>-1</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="CJ151" s="13" t="n">
+        <v>643</v>
       </c>
       <c r="CK151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL151" s="13" t="n">
-        <v>968</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="CL151" s="15" t="n">
+        <v>5722</v>
       </c>
       <c r="CM151" s="19" t="n">
-        <v>96.7</v>
+        <v>75.7</v>
       </c>
       <c r="CN151" s="13" t="n">
+        <v>801</v>
+      </c>
+      <c r="CO151" s="19" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="CP151" s="15" t="n">
+        <v>2432</v>
+      </c>
+      <c r="CQ151" s="19" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="CR151" s="15" t="n">
+        <v>3446</v>
+      </c>
+      <c r="CS151" s="19" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="CT151" s="13" t="n">
+        <v>239</v>
+      </c>
+      <c r="CU151" s="19" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="CV151" s="20" t="n">
+        <v>7539</v>
+      </c>
+      <c r="CW151" s="19" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="CX151" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="CY151" s="19" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="CZ151" s="13" t="n">
+        <v>1252</v>
+      </c>
+      <c r="DA151" s="19" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="DB151" s="15" t="n">
+        <v>2179</v>
+      </c>
+      <c r="DC151" s="19" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="DD151" s="15" t="n">
         <v>1543</v>
       </c>
-      <c r="CO151" s="19" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="CP151" s="20" t="n">
-        <v>7904</v>
-      </c>
-      <c r="CQ151" s="19" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="CR151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CS151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT151" s="13" t="n">
-        <v>1477</v>
-      </c>
-      <c r="CU151" s="19" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="CV151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CW151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CY151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DA151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB151" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DC151" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD151" s="15" t="n">
-        <v>2888</v>
-      </c>
       <c r="DE151" s="19" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="DF151" s="19" t="n">
-        <v>-1</v>
+        <v>88</v>
+      </c>
+      <c r="DF151" s="15" t="n">
+        <v>1070</v>
       </c>
       <c r="DG151" s="19" t="n">
-        <v>0</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="DH151" s="1" t="inlineStr">
         <is>
-          <t>ByteDance-Logo</t>
+          <t>Meta-Logo</t>
         </is>
       </c>
     </row>
@@ -48435,20 +48440,20 @@
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>lrcwxy</t>
+          <t>Q2PPSElacY</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="D152" s="26" t="n">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="E152" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G152" s="14" t="n">
         <v>0</v>
@@ -48465,41 +48470,41 @@
       <c r="K152" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L152" s="15" t="n">
-        <v>603</v>
+      <c r="L152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="M152" s="14" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="N152" s="15" t="n">
-        <v>906</v>
+        <v>0</v>
+      </c>
+      <c r="N152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O152" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="P152" s="15" t="n">
-        <v>392</v>
+        <v>0</v>
+      </c>
+      <c r="P152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="Q152" s="14" t="n">
-        <v>93</v>
-      </c>
-      <c r="R152" s="15" t="n">
-        <v>1643</v>
+        <v>0</v>
+      </c>
+      <c r="R152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="S152" s="14" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="T152" s="15" t="n">
-        <v>1585</v>
+        <v>0</v>
+      </c>
+      <c r="T152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U152" s="14" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="V152" s="15" t="n">
-        <v>2028</v>
+        <v>0</v>
+      </c>
+      <c r="V152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="W152" s="14" t="n">
-        <v>83.8</v>
+        <v>0</v>
       </c>
       <c r="X152" s="14" t="n">
         <v>-1</v>
@@ -48507,89 +48512,89 @@
       <c r="Y152" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="15" t="n">
-        <v>1045</v>
+      <c r="Z152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AA152" s="14" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="AB152" s="13" t="n">
-        <v>179</v>
+        <v>0</v>
+      </c>
+      <c r="AB152" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AC152" s="14" t="n">
-        <v>99.2</v>
+        <v>0</v>
       </c>
       <c r="AD152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AF152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG152" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AH152" s="14" t="n">
-        <v>-2</v>
+      <c r="AH152" s="20" t="n">
+        <v>2005</v>
       </c>
       <c r="AI152" s="14" t="n">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AJ152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AL152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AN152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AO152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AP152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AQ152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AR152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AT152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU152" s="14" t="n">
         <v>0</v>
       </c>
       <c r="AV152" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW152" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX152" s="14" t="n">
-        <v>-2</v>
+      <c r="AX152" s="20" t="n">
+        <v>3161</v>
       </c>
       <c r="AY152" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ152" s="14" t="n">
-        <v>-2</v>
+        <v>78.2</v>
+      </c>
+      <c r="AZ152" s="20" t="n">
+        <v>7063</v>
       </c>
       <c r="BA152" s="14" t="n">
-        <v>0</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="BB152" s="14" t="n">
         <v>-2</v>
@@ -48765,98 +48770,435 @@
       <c r="DG152" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DH152" s="1" t="inlineStr">
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="n">
+        <v>142</v>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Amazon-Logo</t>
+          <t>zyx-37</t>
         </is>
       </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="28" t="inlineStr">
+      <c r="C153" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="D153" s="27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="20" t="n">
+        <v>2254</v>
+      </c>
+      <c r="Q153" s="19" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="R153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="13" t="n">
+        <v>1072</v>
+      </c>
+      <c r="U153" s="19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="V153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="20" t="n">
+        <v>8557</v>
+      </c>
+      <c r="Y153" s="19" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Z153" s="15" t="n">
+        <v>767</v>
+      </c>
+      <c r="AA153" s="19" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="AB153" s="15" t="n">
+        <v>2569</v>
+      </c>
+      <c r="AC153" s="19" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AD153" s="25" t="n">
+        <v>11671</v>
+      </c>
+      <c r="AE153" s="19" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AF153" s="15" t="n">
+        <v>1806</v>
+      </c>
+      <c r="AG153" s="19" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="AH153" s="20" t="n">
+        <v>5332</v>
+      </c>
+      <c r="AI153" s="19" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="AJ153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN153" s="15" t="n">
+        <v>5216</v>
+      </c>
+      <c r="AO153" s="19" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AP153" s="25" t="n">
+        <v>11286</v>
+      </c>
+      <c r="AQ153" s="19" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="AR153" s="15" t="n">
+        <v>2069</v>
+      </c>
+      <c r="AS153" s="19" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="AT153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AY153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BC153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BG153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BI153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BK153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BM153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN153" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BO153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR153" s="15" t="n">
+        <v>3048</v>
+      </c>
+      <c r="BS153" s="19" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="BT153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BU153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV153" s="15" t="n">
+        <v>5655</v>
+      </c>
+      <c r="BW153" s="19" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="BX153" s="13" t="n">
+        <v>2288</v>
+      </c>
+      <c r="BY153" s="19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="BZ153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CC153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CE153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" s="13" t="n">
+        <v>1357</v>
+      </c>
+      <c r="CG153" s="19" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="CH153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CI153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" s="13" t="n">
+        <v>968</v>
+      </c>
+      <c r="CM153" s="19" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="CN153" s="13" t="n">
+        <v>1543</v>
+      </c>
+      <c r="CO153" s="19" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="CP153" s="20" t="n">
+        <v>7904</v>
+      </c>
+      <c r="CQ153" s="19" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="CR153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT153" s="13" t="n">
+        <v>1477</v>
+      </c>
+      <c r="CU153" s="19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="CV153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CW153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DA153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DC153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD153" s="15" t="n">
+        <v>2888</v>
+      </c>
+      <c r="DE153" s="19" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="DF153" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DG153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH153" s="1" t="inlineStr">
         <is>
-          <t>-1:     absent/zero</t>
+          <t>ByteDance-Logo</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="28" t="inlineStr">
         <is>
-          <t>-2:     not joined</t>
+          <t>-1:     absent/zero</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="28" t="inlineStr">
         <is>
+          <t>-2:     not joined</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="28" t="inlineStr">
+        <is>
           <t>BG Color: # of problems solved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="B161" s="29" t="inlineStr">
-        <is>
-          <t>Full list of daily problems</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="29" t="inlineStr">
         <is>
-          <t>Recommended resources</t>
+          <t>Full list of daily problems</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="29" t="inlineStr">
         <is>
-          <t>See where we are from</t>
+          <t>Recommended resources</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="29" t="inlineStr">
         <is>
-          <t>Cruel System Design Group</t>
+          <t>See where we are from</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="29" t="inlineStr">
         <is>
-          <t>If you are interested in joining this group, please contact: guan.huifeng@gmail.com</t>
+          <t>Cruel System Design Group</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="29" t="inlineStr">
         <is>
-          <t>Make sure you agree with our terms and regulations. Think twice before you apply.</t>
+          <t>If you are interested in joining this group, please contact: guan.huifeng@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="29" t="inlineStr">
         <is>
+          <t>Make sure you agree with our terms and regulations. Think twice before you apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="29" t="inlineStr">
+        <is>
           <t>[Blacklisted Persons]</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="B169" s="29" t="inlineStr">
+    <row r="170">
+      <c r="B170" s="29" t="inlineStr">
         <is>
           <t>Graduated members and archived scores</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>ranking-figure</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>curve-figure</t>
         </is>
@@ -48977,16 +49319,16 @@
     <mergeCell ref="DD10:DE10"/>
     <mergeCell ref="DF9:DG9"/>
     <mergeCell ref="DF10:DG10"/>
-    <mergeCell ref="B161:G161"/>
     <mergeCell ref="B162:G162"/>
     <mergeCell ref="B163:G163"/>
     <mergeCell ref="B164:G164"/>
-    <mergeCell ref="B165:Q165"/>
+    <mergeCell ref="B165:G165"/>
     <mergeCell ref="B166:Q166"/>
     <mergeCell ref="B167:Q167"/>
-    <mergeCell ref="B169:Q169"/>
-    <mergeCell ref="A171:CC171"/>
+    <mergeCell ref="B168:Q168"/>
+    <mergeCell ref="B170:Q170"/>
     <mergeCell ref="A172:CC172"/>
+    <mergeCell ref="A173:CC173"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
@@ -49135,12 +49477,13 @@
     <hyperlink ref="B150" r:id="rId144"/>
     <hyperlink ref="B151" r:id="rId145"/>
     <hyperlink ref="B152" r:id="rId146"/>
-    <hyperlink ref="B161" r:id="rId147"/>
+    <hyperlink ref="B153" r:id="rId147"/>
     <hyperlink ref="B162" r:id="rId148"/>
     <hyperlink ref="B163" r:id="rId149"/>
     <hyperlink ref="B164" r:id="rId150"/>
-    <hyperlink ref="B167" r:id="rId151"/>
-    <hyperlink ref="B169" r:id="rId152"/>
+    <hyperlink ref="B165" r:id="rId151"/>
+    <hyperlink ref="B168" r:id="rId152"/>
+    <hyperlink ref="B170" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -40644,23 +40644,23 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>OneMore14</t>
+          <t>tyrande</t>
         </is>
       </c>
       <c r="C129" s="17" t="n">
-        <v>601</v>
+        <v>22</v>
       </c>
       <c r="D129" s="27" t="n">
-        <v>1967</v>
+        <v>1500</v>
       </c>
       <c r="E129" s="12" t="n">
-        <v>28.4</v>
+        <v>34.6</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>9373</v>
+        <v>5825</v>
       </c>
       <c r="G129" s="19" t="n">
-        <v>56.7</v>
+        <v>69.3</v>
       </c>
       <c r="H129" s="19" t="n">
         <v>-1</v>
@@ -40674,305 +40674,310 @@
       <c r="K129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L129" s="20" t="n">
-        <v>1240</v>
+      <c r="L129" s="23" t="n">
+        <v>9956</v>
       </c>
       <c r="M129" s="19" t="n">
-        <v>84.7</v>
+        <v>42.8</v>
       </c>
       <c r="N129" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P129" s="23" t="n">
-        <v>7654</v>
+      <c r="P129" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="Q129" s="19" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="R129" s="20" t="n">
-        <v>1886</v>
+        <v>0</v>
+      </c>
+      <c r="R129" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="T129" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="20" t="n">
-        <v>2018</v>
+      <c r="V129" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="W129" s="19" t="n">
-        <v>79</v>
-      </c>
-      <c r="X129" s="20" t="n">
-        <v>2041</v>
+        <v>0</v>
+      </c>
+      <c r="X129" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="Y129" s="19" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="Z129" s="20" t="n">
-        <v>1877</v>
+        <v>0</v>
+      </c>
+      <c r="Z129" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="AA129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AM129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AO129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AQ129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AS129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AU129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AY129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BA129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BC129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BE129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BG129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" s="19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BI129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ129" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK129" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL129" s="20" t="n">
+        <v>11055</v>
+      </c>
+      <c r="BM129" s="19" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="BN129" s="20" t="n">
+        <v>2265</v>
+      </c>
+      <c r="BO129" s="19" t="n">
+        <v>83</v>
+      </c>
+      <c r="BP129" s="13" t="n">
+        <v>313</v>
+      </c>
+      <c r="BQ129" s="19" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="BR129" s="13" t="n">
+        <v>336</v>
+      </c>
+      <c r="BS129" s="19" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="BT129" s="13" t="n">
+        <v>378</v>
+      </c>
+      <c r="BU129" s="19" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="BV129" s="13" t="n">
+        <v>681</v>
+      </c>
+      <c r="BW129" s="19" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="BX129" s="13" t="n">
+        <v>447</v>
+      </c>
+      <c r="BY129" s="19" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="BZ129" s="13" t="n">
+        <v>1308</v>
+      </c>
+      <c r="CA129" s="19" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="CB129" s="15" t="n">
+        <v>715</v>
+      </c>
+      <c r="CC129" s="19" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="CD129" s="13" t="n">
+        <v>403</v>
+      </c>
+      <c r="CE129" s="19" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="CF129" s="15" t="n">
+        <v>1692</v>
+      </c>
+      <c r="CG129" s="19" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="CH129" s="13" t="n">
+        <v>454</v>
+      </c>
+      <c r="CI129" s="19" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="CJ129" s="15" t="n">
+        <v>880</v>
+      </c>
+      <c r="CK129" s="19" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="CL129" s="20" t="n">
+        <v>3887</v>
+      </c>
+      <c r="CM129" s="19" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="CN129" s="13" t="n">
+        <v>568</v>
+      </c>
+      <c r="CO129" s="19" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="CP129" s="13" t="n">
+        <v>2055</v>
+      </c>
+      <c r="CQ129" s="19" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="CR129" s="20" t="n">
+        <v>2482</v>
+      </c>
+      <c r="CS129" s="19" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="AB129" s="23" t="n">
-        <v>7793</v>
-      </c>
-      <c r="AC129" s="19" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="AD129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" s="15" t="n">
-        <v>696</v>
-      </c>
-      <c r="AG129" s="19" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="AH129" s="20" t="n">
-        <v>6447</v>
-      </c>
-      <c r="AI129" s="19" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="AJ129" s="20" t="n">
-        <v>3039</v>
-      </c>
-      <c r="AK129" s="19" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="AL129" s="20" t="n">
-        <v>4698</v>
-      </c>
-      <c r="AM129" s="19" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="AN129" s="20" t="n">
-        <v>3630</v>
-      </c>
-      <c r="AO129" s="19" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="AP129" s="20" t="n">
-        <v>6455</v>
-      </c>
-      <c r="AQ129" s="19" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="AR129" s="15" t="n">
-        <v>1623</v>
-      </c>
-      <c r="AS129" s="19" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="AT129" s="20" t="n">
-        <v>2999</v>
-      </c>
-      <c r="AU129" s="19" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AV129" s="23" t="n">
-        <v>20014</v>
-      </c>
-      <c r="AW129" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX129" s="13" t="n">
-        <v>3353</v>
-      </c>
-      <c r="AY129" s="19" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="AZ129" s="20" t="n">
-        <v>6168</v>
-      </c>
-      <c r="BA129" s="19" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB129" s="23" t="n">
-        <v>20242</v>
-      </c>
-      <c r="BC129" s="19" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="BD129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BE129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF129" s="20" t="n">
-        <v>3729</v>
-      </c>
-      <c r="BG129" s="19" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="BH129" s="20" t="n">
-        <v>2635</v>
-      </c>
-      <c r="BI129" s="19" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="BJ129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BK129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL129" s="20" t="n">
-        <v>4145</v>
-      </c>
-      <c r="BM129" s="19" t="n">
-        <v>75</v>
-      </c>
-      <c r="BN129" s="20" t="n">
-        <v>7149</v>
-      </c>
-      <c r="BO129" s="19" t="n">
-        <v>68</v>
-      </c>
-      <c r="BP129" s="15" t="n">
-        <v>1064</v>
-      </c>
-      <c r="BQ129" s="19" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="BR129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BS129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT129" s="15" t="n">
-        <v>890</v>
-      </c>
-      <c r="BU129" s="19" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="BV129" s="15" t="n">
-        <v>2951</v>
-      </c>
-      <c r="BW129" s="19" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="BX129" s="15" t="n">
-        <v>2154</v>
-      </c>
-      <c r="BY129" s="19" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="BZ129" s="15" t="n">
-        <v>4136</v>
-      </c>
-      <c r="CA129" s="19" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="CB129" s="15" t="n">
-        <v>2033</v>
-      </c>
-      <c r="CC129" s="19" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="CD129" s="13" t="n">
-        <v>884</v>
-      </c>
-      <c r="CE129" s="19" t="n">
+      <c r="CT129" s="13" t="n">
+        <v>436</v>
+      </c>
+      <c r="CU129" s="19" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="CV129" s="13" t="n">
+        <v>623</v>
+      </c>
+      <c r="CW129" s="19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="CX129" s="13" t="n">
+        <v>702</v>
+      </c>
+      <c r="CY129" s="19" t="n">
         <v>97.2</v>
       </c>
-      <c r="CF129" s="15" t="n">
-        <v>3987</v>
-      </c>
-      <c r="CG129" s="19" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="CH129" s="13" t="n">
-        <v>1363</v>
-      </c>
-      <c r="CI129" s="19" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="CJ129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CK129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL129" s="15" t="n">
-        <v>497</v>
-      </c>
-      <c r="CM129" s="19" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="CN129" s="15" t="n">
-        <v>1082</v>
-      </c>
-      <c r="CO129" s="19" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="CP129" s="13" t="n">
-        <v>1398</v>
-      </c>
-      <c r="CQ129" s="19" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="CR129" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CS129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT129" s="13" t="n">
-        <v>644</v>
-      </c>
-      <c r="CU129" s="19" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="CV129" s="15" t="n">
-        <v>1857</v>
-      </c>
-      <c r="CW129" s="19" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="CX129" s="13" t="n">
-        <v>683</v>
-      </c>
-      <c r="CY129" s="19" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="CZ129" s="15" t="n">
-        <v>602</v>
+      <c r="CZ129" s="13" t="n">
+        <v>232</v>
       </c>
       <c r="DA129" s="19" t="n">
-        <v>93</v>
+        <v>99.2</v>
       </c>
       <c r="DB129" s="15" t="n">
-        <v>2958</v>
+        <v>1157</v>
       </c>
       <c r="DC129" s="19" t="n">
-        <v>84.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="DD129" s="13" t="n">
-        <v>639</v>
+        <v>2090</v>
       </c>
       <c r="DE129" s="19" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="DF129" s="20" t="n">
-        <v>1189</v>
+        <v>92.2</v>
+      </c>
+      <c r="DF129" s="15" t="n">
+        <v>574</v>
       </c>
       <c r="DG129" s="19" t="n">
-        <v>85</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="DH129" s="1" t="inlineStr">
+        <is>
+          <t>Google-Logo</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -40981,29 +40986,29 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>answerer</t>
+          <t>OneMore14</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>1221</v>
+        <v>601</v>
       </c>
       <c r="D130" s="26" t="n">
-        <v>2006</v>
+        <v>1967</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F130" s="14" t="n">
-        <v>-1</v>
+        <v>28.4</v>
+      </c>
+      <c r="F130" s="20" t="n">
+        <v>9373</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="23" t="n">
-        <v>11049</v>
+        <v>56.7</v>
+      </c>
+      <c r="H130" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="I130" s="14" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="J130" s="14" t="n">
         <v>-1</v>
@@ -41012,58 +41017,58 @@
         <v>0</v>
       </c>
       <c r="L130" s="20" t="n">
-        <v>1708</v>
+        <v>1240</v>
       </c>
       <c r="M130" s="14" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="N130" s="23" t="n">
-        <v>7223</v>
+        <v>84.7</v>
+      </c>
+      <c r="N130" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O130" s="14" t="n">
-        <v>55.3</v>
+        <v>0</v>
       </c>
       <c r="P130" s="23" t="n">
-        <v>3699</v>
+        <v>7654</v>
       </c>
       <c r="Q130" s="14" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="R130" s="14" t="n">
-        <v>-1</v>
+        <v>50.5</v>
+      </c>
+      <c r="R130" s="20" t="n">
+        <v>1886</v>
       </c>
       <c r="S130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" s="20" t="n">
-        <v>2375</v>
+        <v>81</v>
+      </c>
+      <c r="T130" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U130" s="14" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="V130" s="15" t="n">
-        <v>766</v>
+        <v>0</v>
+      </c>
+      <c r="V130" s="20" t="n">
+        <v>2018</v>
       </c>
       <c r="W130" s="14" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="X130" s="14" t="n">
-        <v>-1</v>
+        <v>79</v>
+      </c>
+      <c r="X130" s="20" t="n">
+        <v>2041</v>
       </c>
       <c r="Y130" s="14" t="n">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="Z130" s="20" t="n">
-        <v>2690</v>
+        <v>1877</v>
       </c>
       <c r="AA130" s="14" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="AB130" s="15" t="n">
-        <v>2377</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AB130" s="23" t="n">
+        <v>7793</v>
       </c>
       <c r="AC130" s="14" t="n">
-        <v>82.3</v>
+        <v>43.2</v>
       </c>
       <c r="AD130" s="14" t="n">
         <v>-1</v>
@@ -41072,76 +41077,76 @@
         <v>0</v>
       </c>
       <c r="AF130" s="15" t="n">
-        <v>2037</v>
+        <v>696</v>
       </c>
       <c r="AG130" s="14" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="AH130" s="15" t="n">
-        <v>584</v>
+        <v>91.2</v>
+      </c>
+      <c r="AH130" s="20" t="n">
+        <v>6447</v>
       </c>
       <c r="AI130" s="14" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="AJ130" s="14" t="n">
-        <v>-1</v>
+        <v>54.8</v>
+      </c>
+      <c r="AJ130" s="20" t="n">
+        <v>3039</v>
       </c>
       <c r="AK130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL130" s="15" t="n">
-        <v>735</v>
+        <v>75.8</v>
+      </c>
+      <c r="AL130" s="20" t="n">
+        <v>4698</v>
       </c>
       <c r="AM130" s="14" t="n">
-        <v>91.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="AN130" s="20" t="n">
-        <v>1418</v>
+        <v>3630</v>
       </c>
       <c r="AO130" s="14" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="AP130" s="14" t="n">
-        <v>-1</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AP130" s="20" t="n">
+        <v>6455</v>
       </c>
       <c r="AQ130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR130" s="20" t="n">
-        <v>4828</v>
+        <v>64.8</v>
+      </c>
+      <c r="AR130" s="15" t="n">
+        <v>1623</v>
       </c>
       <c r="AS130" s="14" t="n">
-        <v>64.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AT130" s="20" t="n">
-        <v>3047</v>
+        <v>2999</v>
       </c>
       <c r="AU130" s="14" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="AV130" s="20" t="n">
-        <v>4895</v>
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AV130" s="23" t="n">
+        <v>20014</v>
       </c>
       <c r="AW130" s="14" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="AX130" s="14" t="n">
-        <v>-1</v>
+        <v>11</v>
+      </c>
+      <c r="AX130" s="13" t="n">
+        <v>3353</v>
       </c>
       <c r="AY130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ130" s="15" t="n">
-        <v>888</v>
+        <v>88.7</v>
+      </c>
+      <c r="AZ130" s="20" t="n">
+        <v>6168</v>
       </c>
       <c r="BA130" s="14" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="BB130" s="15" t="n">
-        <v>3346</v>
+        <v>70</v>
+      </c>
+      <c r="BB130" s="23" t="n">
+        <v>20242</v>
       </c>
       <c r="BC130" s="14" t="n">
-        <v>83.90000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="BD130" s="14" t="n">
         <v>-1</v>
@@ -41150,16 +41155,16 @@
         <v>0</v>
       </c>
       <c r="BF130" s="20" t="n">
-        <v>1659</v>
+        <v>3729</v>
       </c>
       <c r="BG130" s="14" t="n">
-        <v>84.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="BH130" s="20" t="n">
-        <v>2653</v>
+        <v>2635</v>
       </c>
       <c r="BI130" s="14" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="BJ130" s="14" t="n">
         <v>-1</v>
@@ -41168,22 +41173,22 @@
         <v>0</v>
       </c>
       <c r="BL130" s="20" t="n">
-        <v>6719</v>
+        <v>4145</v>
       </c>
       <c r="BM130" s="14" t="n">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="BN130" s="20" t="n">
-        <v>797</v>
+        <v>7149</v>
       </c>
       <c r="BO130" s="14" t="n">
-        <v>87.5</v>
+        <v>68</v>
       </c>
       <c r="BP130" s="15" t="n">
-        <v>1105</v>
+        <v>1064</v>
       </c>
       <c r="BQ130" s="14" t="n">
-        <v>62</v>
+        <v>63.2</v>
       </c>
       <c r="BR130" s="14" t="n">
         <v>-1</v>
@@ -41191,125 +41196,125 @@
       <c r="BS130" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BT130" s="13" t="n">
-        <v>284</v>
+      <c r="BT130" s="15" t="n">
+        <v>890</v>
       </c>
       <c r="BU130" s="14" t="n">
-        <v>91.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="BV130" s="15" t="n">
-        <v>1579</v>
+        <v>2951</v>
       </c>
       <c r="BW130" s="14" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="BX130" s="14" t="n">
-        <v>-1</v>
+        <v>81.3</v>
+      </c>
+      <c r="BX130" s="15" t="n">
+        <v>2154</v>
       </c>
       <c r="BY130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ130" s="13" t="n">
-        <v>1886</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BZ130" s="15" t="n">
+        <v>4136</v>
       </c>
       <c r="CA130" s="14" t="n">
-        <v>94.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="CB130" s="15" t="n">
-        <v>780</v>
+        <v>2033</v>
       </c>
       <c r="CC130" s="14" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="CD130" s="14" t="n">
-        <v>-1</v>
+        <v>88.7</v>
+      </c>
+      <c r="CD130" s="13" t="n">
+        <v>884</v>
       </c>
       <c r="CE130" s="14" t="n">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="CF130" s="15" t="n">
-        <v>500</v>
+        <v>3987</v>
       </c>
       <c r="CG130" s="14" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="CH130" s="15" t="n">
-        <v>4135</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="CH130" s="13" t="n">
+        <v>1363</v>
       </c>
       <c r="CI130" s="14" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="CJ130" s="15" t="n">
-        <v>1737</v>
+        <v>95.3</v>
+      </c>
+      <c r="CJ130" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CK130" s="14" t="n">
-        <v>88.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CL130" s="15" t="n">
-        <v>842</v>
+        <v>497</v>
       </c>
       <c r="CM130" s="14" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="CN130" s="14" t="n">
-        <v>-1</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="CN130" s="15" t="n">
+        <v>1082</v>
       </c>
       <c r="CO130" s="14" t="n">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="CP130" s="13" t="n">
-        <v>623</v>
+        <v>1398</v>
       </c>
       <c r="CQ130" s="14" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="CR130" s="14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS130" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT130" s="13" t="n">
+        <v>644</v>
+      </c>
+      <c r="CU130" s="14" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="CR130" s="15" t="n">
-        <v>793</v>
-      </c>
-      <c r="CS130" s="14" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="CT130" s="14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CU130" s="14" t="n">
-        <v>0</v>
-      </c>
       <c r="CV130" s="15" t="n">
-        <v>3865</v>
+        <v>1857</v>
       </c>
       <c r="CW130" s="14" t="n">
-        <v>82</v>
+        <v>88.7</v>
       </c>
       <c r="CX130" s="13" t="n">
-        <v>2052</v>
+        <v>683</v>
       </c>
       <c r="CY130" s="14" t="n">
-        <v>91.8</v>
+        <v>97.3</v>
       </c>
       <c r="CZ130" s="15" t="n">
-        <v>4489</v>
+        <v>602</v>
       </c>
       <c r="DA130" s="14" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="DB130" s="14" t="n">
-        <v>-1</v>
+        <v>93</v>
+      </c>
+      <c r="DB130" s="15" t="n">
+        <v>2958</v>
       </c>
       <c r="DC130" s="14" t="n">
-        <v>0</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="DD130" s="13" t="n">
-        <v>828</v>
+        <v>639</v>
       </c>
       <c r="DE130" s="14" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="DF130" s="23" t="n">
-        <v>12484</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="DF130" s="20" t="n">
+        <v>1189</v>
       </c>
       <c r="DG130" s="14" t="n">
-        <v>32.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="131">
@@ -41318,29 +41323,29 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>kaijie_zhang</t>
+          <t>answerer</t>
         </is>
       </c>
       <c r="C131" s="17" t="n">
-        <v>416</v>
+        <v>1221</v>
       </c>
       <c r="D131" s="27" t="n">
-        <v>1660</v>
+        <v>2006</v>
       </c>
       <c r="E131" s="12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F131" s="23" t="n">
-        <v>16245</v>
+        <v>20.6</v>
+      </c>
+      <c r="F131" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="G131" s="19" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H131" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="H131" s="23" t="n">
+        <v>11049</v>
       </c>
       <c r="I131" s="19" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="J131" s="19" t="n">
         <v>-1</v>
@@ -41348,305 +41353,305 @@
       <c r="K131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L131" s="23" t="n">
-        <v>6290</v>
+      <c r="L131" s="20" t="n">
+        <v>1708</v>
       </c>
       <c r="M131" s="19" t="n">
-        <v>58.3</v>
+        <v>82.8</v>
       </c>
       <c r="N131" s="23" t="n">
-        <v>8443</v>
+        <v>7223</v>
       </c>
       <c r="O131" s="19" t="n">
-        <v>50.3</v>
+        <v>55.3</v>
       </c>
       <c r="P131" s="23" t="n">
-        <v>9197</v>
+        <v>3699</v>
       </c>
       <c r="Q131" s="19" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="R131" s="23" t="n">
-        <v>13804</v>
+        <v>68.3</v>
+      </c>
+      <c r="R131" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S131" s="19" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T131" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="T131" s="20" t="n">
+        <v>2375</v>
       </c>
       <c r="U131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" s="19" t="n">
-        <v>-2</v>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="V131" s="15" t="n">
+        <v>766</v>
       </c>
       <c r="W131" s="19" t="n">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="X131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="19" t="n">
-        <v>-2</v>
+      <c r="Z131" s="20" t="n">
+        <v>2690</v>
       </c>
       <c r="AA131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" s="19" t="n">
-        <v>-2</v>
+        <v>76.3</v>
+      </c>
+      <c r="AB131" s="15" t="n">
+        <v>2377</v>
       </c>
       <c r="AC131" s="19" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="AD131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AF131" s="19" t="n">
-        <v>-2</v>
+      <c r="AF131" s="15" t="n">
+        <v>2037</v>
       </c>
       <c r="AG131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" s="19" t="n">
-        <v>-2</v>
+        <v>83.8</v>
+      </c>
+      <c r="AH131" s="15" t="n">
+        <v>584</v>
       </c>
       <c r="AI131" s="19" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="AJ131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AL131" s="19" t="n">
-        <v>-2</v>
+      <c r="AL131" s="15" t="n">
+        <v>735</v>
       </c>
       <c r="AM131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN131" s="19" t="n">
-        <v>-2</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AN131" s="20" t="n">
+        <v>1418</v>
       </c>
       <c r="AO131" s="19" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="AP131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AQ131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AR131" s="19" t="n">
-        <v>-2</v>
+      <c r="AR131" s="20" t="n">
+        <v>4828</v>
       </c>
       <c r="AS131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT131" s="19" t="n">
-        <v>-2</v>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AT131" s="20" t="n">
+        <v>3047</v>
       </c>
       <c r="AU131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV131" s="19" t="n">
-        <v>-2</v>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AV131" s="20" t="n">
+        <v>4895</v>
       </c>
       <c r="AW131" s="19" t="n">
-        <v>0</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AX131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AY131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AZ131" s="19" t="n">
-        <v>-2</v>
+      <c r="AZ131" s="15" t="n">
+        <v>888</v>
       </c>
       <c r="BA131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB131" s="19" t="n">
-        <v>-2</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="BB131" s="15" t="n">
+        <v>3346</v>
       </c>
       <c r="BC131" s="19" t="n">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="BD131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BF131" s="19" t="n">
-        <v>-2</v>
+      <c r="BF131" s="20" t="n">
+        <v>1659</v>
       </c>
       <c r="BG131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH131" s="19" t="n">
-        <v>-2</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BH131" s="20" t="n">
+        <v>2653</v>
       </c>
       <c r="BI131" s="19" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="BJ131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BL131" s="19" t="n">
-        <v>-2</v>
+      <c r="BL131" s="20" t="n">
+        <v>6719</v>
       </c>
       <c r="BM131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN131" s="19" t="n">
-        <v>-2</v>
+        <v>65.59999999999999</v>
+      </c>
+      <c r="BN131" s="20" t="n">
+        <v>797</v>
       </c>
       <c r="BO131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP131" s="19" t="n">
-        <v>-2</v>
+        <v>87.5</v>
+      </c>
+      <c r="BP131" s="15" t="n">
+        <v>1105</v>
       </c>
       <c r="BQ131" s="19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="BR131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT131" s="19" t="n">
-        <v>-2</v>
+      <c r="BT131" s="13" t="n">
+        <v>284</v>
       </c>
       <c r="BU131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV131" s="19" t="n">
-        <v>-2</v>
+        <v>91.8</v>
+      </c>
+      <c r="BV131" s="15" t="n">
+        <v>1579</v>
       </c>
       <c r="BW131" s="19" t="n">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="BX131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BZ131" s="19" t="n">
-        <v>-2</v>
+      <c r="BZ131" s="13" t="n">
+        <v>1886</v>
       </c>
       <c r="CA131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB131" s="19" t="n">
-        <v>-2</v>
+        <v>94.5</v>
+      </c>
+      <c r="CB131" s="15" t="n">
+        <v>780</v>
       </c>
       <c r="CC131" s="19" t="n">
-        <v>0</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="CD131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CF131" s="19" t="n">
-        <v>-2</v>
+      <c r="CF131" s="15" t="n">
+        <v>500</v>
       </c>
       <c r="CG131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH131" s="19" t="n">
-        <v>-2</v>
+        <v>93.40000000000001</v>
+      </c>
+      <c r="CH131" s="15" t="n">
+        <v>4135</v>
       </c>
       <c r="CI131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ131" s="19" t="n">
-        <v>-2</v>
+        <v>80.8</v>
+      </c>
+      <c r="CJ131" s="15" t="n">
+        <v>1737</v>
       </c>
       <c r="CK131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL131" s="19" t="n">
-        <v>-2</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="CL131" s="15" t="n">
+        <v>842</v>
       </c>
       <c r="CM131" s="19" t="n">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="CN131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CP131" s="19" t="n">
-        <v>-2</v>
+      <c r="CP131" s="13" t="n">
+        <v>623</v>
       </c>
       <c r="CQ131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR131" s="19" t="n">
-        <v>-2</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="CR131" s="15" t="n">
+        <v>793</v>
       </c>
       <c r="CS131" s="19" t="n">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="CT131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CV131" s="19" t="n">
-        <v>-2</v>
+      <c r="CV131" s="15" t="n">
+        <v>3865</v>
       </c>
       <c r="CW131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX131" s="19" t="n">
-        <v>-2</v>
+        <v>82</v>
+      </c>
+      <c r="CX131" s="13" t="n">
+        <v>2052</v>
       </c>
       <c r="CY131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ131" s="19" t="n">
-        <v>-2</v>
+        <v>91.8</v>
+      </c>
+      <c r="CZ131" s="15" t="n">
+        <v>4489</v>
       </c>
       <c r="DA131" s="19" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="DB131" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DD131" s="19" t="n">
-        <v>-2</v>
+      <c r="DD131" s="13" t="n">
+        <v>828</v>
       </c>
       <c r="DE131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF131" s="19" t="n">
-        <v>-2</v>
+        <v>96.90000000000001</v>
+      </c>
+      <c r="DF131" s="23" t="n">
+        <v>12484</v>
       </c>
       <c r="DG131" s="19" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="132">
@@ -41655,23 +41660,23 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>nirodha</t>
+          <t>kaijie_zhang</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>1259</v>
+        <v>416</v>
       </c>
       <c r="D132" s="26" t="n">
-        <v>1979</v>
+        <v>1660</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F132" s="14" t="n">
-        <v>-1</v>
+        <v>13.7</v>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>16245</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="H132" s="14" t="n">
         <v>-1</v>
@@ -41679,311 +41684,311 @@
       <c r="I132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="23" t="n">
-        <v>12877</v>
+      <c r="J132" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="L132" s="14" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="L132" s="23" t="n">
+        <v>6290</v>
       </c>
       <c r="M132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="20" t="n">
-        <v>3294</v>
+        <v>58.3</v>
+      </c>
+      <c r="N132" s="23" t="n">
+        <v>8443</v>
       </c>
       <c r="O132" s="14" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="P132" s="20" t="n">
-        <v>2623</v>
+        <v>50.3</v>
+      </c>
+      <c r="P132" s="23" t="n">
+        <v>9197</v>
       </c>
       <c r="Q132" s="14" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="R132" s="14" t="n">
-        <v>-1</v>
+        <v>43.6</v>
+      </c>
+      <c r="R132" s="23" t="n">
+        <v>13804</v>
       </c>
       <c r="S132" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" s="20" t="n">
-        <v>1143</v>
+        <v>18.9</v>
+      </c>
+      <c r="T132" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U132" s="14" t="n">
-        <v>83</v>
-      </c>
-      <c r="V132" s="20" t="n">
-        <v>3345</v>
+        <v>0</v>
+      </c>
+      <c r="V132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="W132" s="14" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="X132" s="20" t="n">
-        <v>2310</v>
+        <v>0</v>
+      </c>
+      <c r="X132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="Y132" s="14" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="Z132" s="20" t="n">
-        <v>1450</v>
+        <v>0</v>
+      </c>
+      <c r="Z132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AA132" s="14" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="AB132" s="20" t="n">
-        <v>3623</v>
+        <v>0</v>
+      </c>
+      <c r="AB132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AC132" s="14" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="AD132" s="15" t="n">
-        <v>1654</v>
+        <v>0</v>
+      </c>
+      <c r="AD132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AE132" s="14" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="AF132" s="20" t="n">
-        <v>3270</v>
+        <v>0</v>
+      </c>
+      <c r="AF132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AG132" s="14" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="AH132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AI132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ132" s="15" t="n">
-        <v>909</v>
+      <c r="AJ132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AK132" s="14" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="AL132" s="23" t="n">
-        <v>6745</v>
+        <v>0</v>
+      </c>
+      <c r="AL132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AM132" s="14" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="AN132" s="20" t="n">
-        <v>1388</v>
+        <v>0</v>
+      </c>
+      <c r="AN132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AO132" s="14" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="AP132" s="15" t="n">
-        <v>3359</v>
+        <v>0</v>
+      </c>
+      <c r="AP132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AQ132" s="14" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AS132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AT132" s="20" t="n">
-        <v>1478</v>
+      <c r="AT132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AU132" s="14" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="AV132" s="20" t="n">
-        <v>10563</v>
+        <v>0</v>
+      </c>
+      <c r="AV132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AW132" s="14" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="AX132" s="13" t="n">
-        <v>533</v>
+        <v>0</v>
+      </c>
+      <c r="AX132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="AY132" s="14" t="n">
-        <v>98.2</v>
+        <v>0</v>
       </c>
       <c r="AZ132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BA132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BB132" s="20" t="n">
-        <v>5405</v>
+      <c r="BB132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BC132" s="14" t="n">
-        <v>72</v>
-      </c>
-      <c r="BD132" s="15" t="n">
-        <v>600</v>
+        <v>0</v>
+      </c>
+      <c r="BD132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BE132" s="14" t="n">
-        <v>93</v>
-      </c>
-      <c r="BF132" s="20" t="n">
-        <v>2814</v>
+        <v>0</v>
+      </c>
+      <c r="BF132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BG132" s="14" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="BH132" s="20" t="n">
-        <v>1775</v>
+        <v>0</v>
+      </c>
+      <c r="BH132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BI132" s="14" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="BJ132" s="15" t="n">
-        <v>2408</v>
+        <v>0</v>
+      </c>
+      <c r="BJ132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BK132" s="14" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="BL132" s="20" t="n">
-        <v>5811</v>
+        <v>0</v>
+      </c>
+      <c r="BL132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BM132" s="14" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="BN132" s="20" t="n">
-        <v>4272</v>
+        <v>0</v>
+      </c>
+      <c r="BN132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BO132" s="14" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="BP132" s="13" t="n">
-        <v>355</v>
+        <v>0</v>
+      </c>
+      <c r="BP132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ132" s="14" t="n">
-        <v>89.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BS132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BT132" s="15" t="n">
-        <v>823</v>
+      <c r="BT132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BU132" s="14" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="BV132" s="15" t="n">
-        <v>1319</v>
+        <v>0</v>
+      </c>
+      <c r="BV132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BW132" s="14" t="n">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BY132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BZ132" s="13" t="n">
-        <v>889</v>
+      <c r="BZ132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CA132" s="14" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="CB132" s="20" t="n">
-        <v>7797</v>
+        <v>0</v>
+      </c>
+      <c r="CB132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CC132" s="14" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="CD132" s="15" t="n">
-        <v>2454</v>
+        <v>0</v>
+      </c>
+      <c r="CD132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CE132" s="14" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="CF132" s="15" t="n">
-        <v>2458</v>
+        <v>0</v>
+      </c>
+      <c r="CF132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CG132" s="14" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="CH132" s="13" t="n">
-        <v>1445</v>
+        <v>0</v>
+      </c>
+      <c r="CH132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CI132" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="CJ132" s="15" t="n">
-        <v>1306</v>
+        <v>0</v>
+      </c>
+      <c r="CJ132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CK132" s="14" t="n">
-        <v>90.2</v>
+        <v>0</v>
       </c>
       <c r="CL132" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CM132" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CN132" s="15" t="n">
-        <v>959</v>
+      <c r="CN132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CO132" s="14" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="CP132" s="15" t="n">
-        <v>2654</v>
+        <v>0</v>
+      </c>
+      <c r="CP132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ132" s="14" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="CR132" s="20" t="n">
-        <v>2090</v>
+        <v>0</v>
+      </c>
+      <c r="CR132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CS132" s="14" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="CT132" s="15" t="n">
-        <v>2521</v>
+        <v>0</v>
+      </c>
+      <c r="CT132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CU132" s="14" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="CV132" s="15" t="n">
-        <v>2310</v>
+        <v>0</v>
+      </c>
+      <c r="CV132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CW132" s="14" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="CX132" s="15" t="n">
-        <v>4007</v>
+        <v>0</v>
+      </c>
+      <c r="CX132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CY132" s="14" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="CZ132" s="15" t="n">
-        <v>726</v>
+        <v>0</v>
+      </c>
+      <c r="CZ132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DA132" s="14" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="DB132" s="15" t="n">
-        <v>2166</v>
+        <v>0</v>
+      </c>
+      <c r="DB132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DC132" s="14" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="DD132" s="15" t="n">
-        <v>2874</v>
+        <v>0</v>
+      </c>
+      <c r="DD132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DE132" s="14" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="DF132" s="20" t="n">
-        <v>1193</v>
+        <v>0</v>
+      </c>
+      <c r="DF132" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DG132" s="14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -41992,17 +41997,17 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>wangyxwyx</t>
+          <t>nirodha</t>
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>250</v>
+        <v>1259</v>
       </c>
       <c r="D133" s="27" t="n">
-        <v>1742</v>
+        <v>1979</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>8.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="F133" s="19" t="n">
         <v>-1</v>
@@ -42010,17 +42015,17 @@
       <c r="G133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H133" s="23" t="n">
-        <v>17257</v>
+      <c r="H133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="I133" s="19" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="J133" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="J133" s="23" t="n">
+        <v>12877</v>
       </c>
       <c r="K133" s="19" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="L133" s="19" t="n">
         <v>-1</v>
@@ -42028,65 +42033,65 @@
       <c r="M133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N133" s="19" t="n">
-        <v>-1</v>
+      <c r="N133" s="20" t="n">
+        <v>3294</v>
       </c>
       <c r="O133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="23" t="n">
-        <v>13058</v>
+        <v>76.5</v>
+      </c>
+      <c r="P133" s="20" t="n">
+        <v>2623</v>
       </c>
       <c r="Q133" s="19" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R133" s="20" t="n">
-        <v>4497</v>
+        <v>78.2</v>
+      </c>
+      <c r="R133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S133" s="19" t="n">
-        <v>68.5</v>
+        <v>0</v>
       </c>
       <c r="T133" s="20" t="n">
-        <v>1188</v>
+        <v>1143</v>
       </c>
       <c r="U133" s="19" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="V133" s="19" t="n">
-        <v>-1</v>
+        <v>83</v>
+      </c>
+      <c r="V133" s="20" t="n">
+        <v>3345</v>
       </c>
       <c r="W133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" s="19" t="n">
-        <v>-1</v>
+        <v>71.7</v>
+      </c>
+      <c r="X133" s="20" t="n">
+        <v>2310</v>
       </c>
       <c r="Y133" s="19" t="n">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="Z133" s="20" t="n">
-        <v>2688</v>
+        <v>1450</v>
       </c>
       <c r="AA133" s="19" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="AB133" s="23" t="n">
-        <v>14751</v>
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AB133" s="20" t="n">
+        <v>3623</v>
       </c>
       <c r="AC133" s="19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD133" s="19" t="n">
-        <v>-1</v>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AD133" s="15" t="n">
+        <v>1654</v>
       </c>
       <c r="AE133" s="19" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AF133" s="20" t="n">
-        <v>7963</v>
+        <v>3270</v>
       </c>
       <c r="AG133" s="19" t="n">
-        <v>46.1</v>
+        <v>72</v>
       </c>
       <c r="AH133" s="19" t="n">
         <v>-1</v>
@@ -42094,29 +42099,29 @@
       <c r="AI133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ133" s="20" t="n">
-        <v>6946</v>
+      <c r="AJ133" s="15" t="n">
+        <v>909</v>
       </c>
       <c r="AK133" s="19" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="AL133" s="20" t="n">
-        <v>5136</v>
+        <v>90.8</v>
+      </c>
+      <c r="AL133" s="23" t="n">
+        <v>6745</v>
       </c>
       <c r="AM133" s="19" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AN133" s="19" t="n">
-        <v>-1</v>
+        <v>54.2</v>
+      </c>
+      <c r="AN133" s="20" t="n">
+        <v>1388</v>
       </c>
       <c r="AO133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP133" s="19" t="n">
-        <v>-1</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AP133" s="15" t="n">
+        <v>3359</v>
       </c>
       <c r="AQ133" s="19" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AR133" s="19" t="n">
         <v>-1</v>
@@ -42124,23 +42129,23 @@
       <c r="AS133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AT133" s="19" t="n">
-        <v>-1</v>
+      <c r="AT133" s="20" t="n">
+        <v>1478</v>
       </c>
       <c r="AU133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV133" s="19" t="n">
-        <v>-1</v>
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AV133" s="20" t="n">
+        <v>10563</v>
       </c>
       <c r="AW133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX133" s="19" t="n">
-        <v>-1</v>
+        <v>50.9</v>
+      </c>
+      <c r="AX133" s="13" t="n">
+        <v>533</v>
       </c>
       <c r="AY133" s="19" t="n">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="AZ133" s="19" t="n">
         <v>-1</v>
@@ -42148,53 +42153,53 @@
       <c r="BA133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB133" s="19" t="n">
-        <v>-1</v>
+      <c r="BB133" s="20" t="n">
+        <v>5405</v>
       </c>
       <c r="BC133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD133" s="19" t="n">
-        <v>-1</v>
+        <v>72</v>
+      </c>
+      <c r="BD133" s="15" t="n">
+        <v>600</v>
       </c>
       <c r="BE133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF133" s="19" t="n">
-        <v>-1</v>
+        <v>93</v>
+      </c>
+      <c r="BF133" s="20" t="n">
+        <v>2814</v>
       </c>
       <c r="BG133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH133" s="19" t="n">
-        <v>-1</v>
+        <v>80.8</v>
+      </c>
+      <c r="BH133" s="20" t="n">
+        <v>1775</v>
       </c>
       <c r="BI133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ133" s="19" t="n">
-        <v>-1</v>
+        <v>83.40000000000001</v>
+      </c>
+      <c r="BJ133" s="15" t="n">
+        <v>2408</v>
       </c>
       <c r="BK133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL133" s="19" t="n">
-        <v>-1</v>
+        <v>87.3</v>
+      </c>
+      <c r="BL133" s="20" t="n">
+        <v>5811</v>
       </c>
       <c r="BM133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN133" s="19" t="n">
-        <v>-1</v>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="BN133" s="20" t="n">
+        <v>4272</v>
       </c>
       <c r="BO133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP133" s="19" t="n">
-        <v>-1</v>
+        <v>76.8</v>
+      </c>
+      <c r="BP133" s="13" t="n">
+        <v>355</v>
       </c>
       <c r="BQ133" s="19" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BR133" s="19" t="n">
         <v>-1</v>
@@ -42202,59 +42207,59 @@
       <c r="BS133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT133" s="19" t="n">
-        <v>-1</v>
+      <c r="BT133" s="15" t="n">
+        <v>823</v>
       </c>
       <c r="BU133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV133" s="19" t="n">
-        <v>-1</v>
+        <v>71.3</v>
+      </c>
+      <c r="BV133" s="15" t="n">
+        <v>1319</v>
       </c>
       <c r="BW133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX133" s="20" t="n">
-        <v>12930</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="BX133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BY133" s="19" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="BZ133" s="19" t="n">
-        <v>-2</v>
+        <v>0</v>
+      </c>
+      <c r="BZ133" s="13" t="n">
+        <v>889</v>
       </c>
       <c r="CA133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB133" s="19" t="n">
-        <v>-2</v>
+        <v>97.40000000000001</v>
+      </c>
+      <c r="CB133" s="20" t="n">
+        <v>7797</v>
       </c>
       <c r="CC133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD133" s="19" t="n">
-        <v>-2</v>
+        <v>65.8</v>
+      </c>
+      <c r="CD133" s="15" t="n">
+        <v>2454</v>
       </c>
       <c r="CE133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF133" s="19" t="n">
-        <v>-2</v>
+        <v>87.3</v>
+      </c>
+      <c r="CF133" s="15" t="n">
+        <v>2458</v>
       </c>
       <c r="CG133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH133" s="19" t="n">
-        <v>-1</v>
+        <v>86.90000000000001</v>
+      </c>
+      <c r="CH133" s="13" t="n">
+        <v>1445</v>
       </c>
       <c r="CI133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ133" s="19" t="n">
-        <v>-1</v>
+        <v>95</v>
+      </c>
+      <c r="CJ133" s="15" t="n">
+        <v>1306</v>
       </c>
       <c r="CK133" s="19" t="n">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="CL133" s="19" t="n">
         <v>-1</v>
@@ -42262,65 +42267,65 @@
       <c r="CM133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CN133" s="19" t="n">
-        <v>-1</v>
+      <c r="CN133" s="15" t="n">
+        <v>959</v>
       </c>
       <c r="CO133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP133" s="19" t="n">
-        <v>-1</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="CP133" s="15" t="n">
+        <v>2654</v>
       </c>
       <c r="CQ133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR133" s="19" t="n">
-        <v>-1</v>
+        <v>84.90000000000001</v>
+      </c>
+      <c r="CR133" s="20" t="n">
+        <v>2090</v>
       </c>
       <c r="CS133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT133" s="13" t="n">
-        <v>1907</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="CT133" s="15" t="n">
+        <v>2521</v>
       </c>
       <c r="CU133" s="19" t="n">
-        <v>93</v>
+        <v>85.8</v>
       </c>
       <c r="CV133" s="15" t="n">
-        <v>3061</v>
+        <v>2310</v>
       </c>
       <c r="CW133" s="19" t="n">
-        <v>84.7</v>
+        <v>87.2</v>
       </c>
       <c r="CX133" s="15" t="n">
-        <v>5310</v>
+        <v>4007</v>
       </c>
       <c r="CY133" s="19" t="n">
-        <v>73.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="CZ133" s="15" t="n">
-        <v>5122</v>
+        <v>726</v>
       </c>
       <c r="DA133" s="19" t="n">
-        <v>78</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="DB133" s="15" t="n">
-        <v>3532</v>
+        <v>2166</v>
       </c>
       <c r="DC133" s="19" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="DD133" s="19" t="n">
-        <v>-1</v>
+        <v>87.59999999999999</v>
+      </c>
+      <c r="DD133" s="15" t="n">
+        <v>2874</v>
       </c>
       <c r="DE133" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF133" s="19" t="n">
-        <v>-1</v>
+        <v>84.3</v>
+      </c>
+      <c r="DF133" s="20" t="n">
+        <v>1193</v>
       </c>
       <c r="DG133" s="19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="134">
@@ -42329,17 +42334,17 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>gude8997</t>
+          <t>wangyxwyx</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>1054</v>
+        <v>250</v>
       </c>
       <c r="D134" s="26" t="n">
-        <v>1943</v>
+        <v>1742</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F134" s="14" t="n">
         <v>-1</v>
@@ -42347,17 +42352,17 @@
       <c r="G134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H134" s="14" t="n">
-        <v>-1</v>
+      <c r="H134" s="23" t="n">
+        <v>17257</v>
       </c>
       <c r="I134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="23" t="n">
-        <v>15279</v>
+        <v>16.7</v>
+      </c>
+      <c r="J134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="L134" s="14" t="n">
         <v>-1</v>
@@ -42365,29 +42370,29 @@
       <c r="M134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N134" s="20" t="n">
-        <v>6061</v>
+      <c r="N134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O134" s="14" t="n">
-        <v>65.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="P134" s="23" t="n">
-        <v>3817</v>
+        <v>13058</v>
       </c>
       <c r="Q134" s="14" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="R134" s="14" t="n">
-        <v>-1</v>
+        <v>26.2</v>
+      </c>
+      <c r="R134" s="20" t="n">
+        <v>4497</v>
       </c>
       <c r="S134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" s="14" t="n">
-        <v>-1</v>
+        <v>68.5</v>
+      </c>
+      <c r="T134" s="20" t="n">
+        <v>1188</v>
       </c>
       <c r="U134" s="14" t="n">
-        <v>0</v>
+        <v>82.7</v>
       </c>
       <c r="V134" s="14" t="n">
         <v>-1</v>
@@ -42401,29 +42406,29 @@
       <c r="Y134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="14" t="n">
-        <v>-1</v>
+      <c r="Z134" s="20" t="n">
+        <v>2688</v>
       </c>
       <c r="AA134" s="14" t="n">
-        <v>0</v>
+        <v>76.3</v>
       </c>
       <c r="AB134" s="23" t="n">
-        <v>6778</v>
+        <v>14751</v>
       </c>
       <c r="AC134" s="14" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="AD134" s="13" t="n">
-        <v>765</v>
+        <v>5.9</v>
+      </c>
+      <c r="AD134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AE134" s="14" t="n">
-        <v>96</v>
-      </c>
-      <c r="AF134" s="15" t="n">
-        <v>1020</v>
+        <v>0</v>
+      </c>
+      <c r="AF134" s="20" t="n">
+        <v>7963</v>
       </c>
       <c r="AG134" s="14" t="n">
-        <v>89.40000000000001</v>
+        <v>46.1</v>
       </c>
       <c r="AH134" s="14" t="n">
         <v>-1</v>
@@ -42431,29 +42436,29 @@
       <c r="AI134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ134" s="15" t="n">
-        <v>1797</v>
+      <c r="AJ134" s="20" t="n">
+        <v>6946</v>
       </c>
       <c r="AK134" s="14" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="AL134" s="15" t="n">
-        <v>2590</v>
+        <v>57.7</v>
+      </c>
+      <c r="AL134" s="20" t="n">
+        <v>5136</v>
       </c>
       <c r="AM134" s="14" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="AN134" s="20" t="n">
-        <v>2668</v>
+        <v>66.5</v>
+      </c>
+      <c r="AN134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AO134" s="14" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AP134" s="15" t="n">
-        <v>3433</v>
+        <v>0</v>
+      </c>
+      <c r="AP134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ134" s="14" t="n">
-        <v>81.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR134" s="14" t="n">
         <v>-1</v>
@@ -42467,35 +42472,35 @@
       <c r="AU134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AV134" s="23" t="n">
-        <v>13125</v>
+      <c r="AV134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AW134" s="14" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="AX134" s="13" t="n">
-        <v>2505</v>
+        <v>0</v>
+      </c>
+      <c r="AX134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY134" s="14" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="AZ134" s="13" t="n">
-        <v>235</v>
+        <v>0</v>
+      </c>
+      <c r="AZ134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BA134" s="14" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="BB134" s="23" t="n">
-        <v>11031</v>
+        <v>0</v>
+      </c>
+      <c r="BB134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BC134" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="BD134" s="20" t="n">
-        <v>2228</v>
+        <v>0</v>
+      </c>
+      <c r="BD134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BE134" s="14" t="n">
-        <v>82.7</v>
+        <v>0</v>
       </c>
       <c r="BF134" s="14" t="n">
         <v>-1</v>
@@ -42503,23 +42508,23 @@
       <c r="BG134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH134" s="15" t="n">
-        <v>347</v>
+      <c r="BH134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BI134" s="14" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="BJ134" s="15" t="n">
-        <v>3398</v>
+        <v>0</v>
+      </c>
+      <c r="BJ134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BK134" s="14" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="BL134" s="23" t="n">
-        <v>14146</v>
+        <v>0</v>
+      </c>
+      <c r="BL134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BM134" s="14" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="BN134" s="14" t="n">
         <v>-1</v>
@@ -42533,11 +42538,11 @@
       <c r="BQ134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BR134" s="15" t="n">
-        <v>1291</v>
+      <c r="BR134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BS134" s="14" t="n">
-        <v>57.2</v>
+        <v>0</v>
       </c>
       <c r="BT134" s="14" t="n">
         <v>-1</v>
@@ -42545,53 +42550,53 @@
       <c r="BU134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV134" s="15" t="n">
-        <v>2016</v>
+      <c r="BV134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BW134" s="14" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="BX134" s="13" t="n">
-        <v>558</v>
+        <v>0</v>
+      </c>
+      <c r="BX134" s="20" t="n">
+        <v>12930</v>
       </c>
       <c r="BY134" s="14" t="n">
-        <v>98.3</v>
+        <v>51.6</v>
       </c>
       <c r="BZ134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CA134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CB134" s="20" t="n">
-        <v>7546</v>
+      <c r="CB134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CC134" s="14" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="CD134" s="13" t="n">
-        <v>614</v>
+        <v>0</v>
+      </c>
+      <c r="CD134" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CE134" s="14" t="n">
-        <v>98.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CF134" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CG134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CH134" s="13" t="n">
-        <v>309</v>
+      <c r="CH134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CI134" s="14" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="CJ134" s="15" t="n">
-        <v>2327</v>
+        <v>0</v>
+      </c>
+      <c r="CJ134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CK134" s="14" t="n">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CL134" s="14" t="n">
         <v>-1</v>
@@ -42599,17 +42604,17 @@
       <c r="CM134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CN134" s="15" t="n">
-        <v>2018</v>
+      <c r="CN134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CO134" s="14" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="CP134" s="20" t="n">
-        <v>11809</v>
+        <v>0</v>
+      </c>
+      <c r="CP134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ134" s="14" t="n">
-        <v>45.1</v>
+        <v>0</v>
       </c>
       <c r="CR134" s="14" t="n">
         <v>-1</v>
@@ -42618,34 +42623,34 @@
         <v>0</v>
       </c>
       <c r="CT134" s="13" t="n">
-        <v>1325</v>
+        <v>1907</v>
       </c>
       <c r="CU134" s="14" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="CV134" s="14" t="n">
-        <v>-1</v>
+        <v>93</v>
+      </c>
+      <c r="CV134" s="15" t="n">
+        <v>3061</v>
       </c>
       <c r="CW134" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX134" s="14" t="n">
-        <v>-1</v>
+        <v>84.7</v>
+      </c>
+      <c r="CX134" s="15" t="n">
+        <v>5310</v>
       </c>
       <c r="CY134" s="14" t="n">
-        <v>0</v>
+        <v>73.7</v>
       </c>
       <c r="CZ134" s="15" t="n">
-        <v>2694</v>
+        <v>5122</v>
       </c>
       <c r="DA134" s="14" t="n">
-        <v>86.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="DB134" s="15" t="n">
-        <v>2929</v>
+        <v>3532</v>
       </c>
       <c r="DC134" s="14" t="n">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="DD134" s="14" t="n">
         <v>-1</v>
@@ -42653,11 +42658,11 @@
       <c r="DE134" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DF134" s="23" t="n">
-        <v>10833</v>
+      <c r="DF134" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DG134" s="14" t="n">
-        <v>39.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -42666,17 +42671,17 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>cyzh</t>
+          <t>gude8997</t>
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>1246</v>
-      </c>
-      <c r="D135" s="25" t="n">
-        <v>2115</v>
+        <v>1054</v>
+      </c>
+      <c r="D135" s="27" t="n">
+        <v>1943</v>
       </c>
       <c r="E135" s="12" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="F135" s="19" t="n">
         <v>-1</v>
@@ -42684,41 +42689,41 @@
       <c r="G135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H135" s="23" t="n">
-        <v>18839</v>
+      <c r="H135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="I135" s="19" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J135" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="J135" s="23" t="n">
+        <v>15279</v>
       </c>
       <c r="K135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="20" t="n">
-        <v>3126</v>
+        <v>12.4</v>
+      </c>
+      <c r="L135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="M135" s="19" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="N135" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="N135" s="20" t="n">
+        <v>6061</v>
       </c>
       <c r="O135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="20" t="n">
-        <v>2958</v>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="P135" s="23" t="n">
+        <v>3817</v>
       </c>
       <c r="Q135" s="19" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="R135" s="15" t="n">
-        <v>845</v>
+        <v>67.8</v>
+      </c>
+      <c r="R135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="T135" s="19" t="n">
         <v>-1</v>
@@ -42726,11 +42731,11 @@
       <c r="U135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="13" t="n">
-        <v>211</v>
+      <c r="V135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W135" s="19" t="n">
-        <v>98.8</v>
+        <v>0</v>
       </c>
       <c r="X135" s="19" t="n">
         <v>-1</v>
@@ -42738,29 +42743,29 @@
       <c r="Y135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="23" t="n">
-        <v>5468</v>
+      <c r="Z135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AA135" s="19" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="AB135" s="15" t="n">
-        <v>1494</v>
+        <v>0</v>
+      </c>
+      <c r="AB135" s="23" t="n">
+        <v>6778</v>
       </c>
       <c r="AC135" s="19" t="n">
-        <v>87</v>
+        <v>48.7</v>
       </c>
       <c r="AD135" s="13" t="n">
-        <v>131</v>
+        <v>765</v>
       </c>
       <c r="AE135" s="19" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="AF135" s="19" t="n">
-        <v>-1</v>
+        <v>96</v>
+      </c>
+      <c r="AF135" s="15" t="n">
+        <v>1020</v>
       </c>
       <c r="AG135" s="19" t="n">
-        <v>0</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AH135" s="19" t="n">
         <v>-1</v>
@@ -42768,185 +42773,185 @@
       <c r="AI135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ135" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ135" s="15" t="n">
+        <v>1797</v>
       </c>
       <c r="AK135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL135" s="19" t="n">
-        <v>-1</v>
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AL135" s="15" t="n">
+        <v>2590</v>
       </c>
       <c r="AM135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN135" s="19" t="n">
-        <v>-1</v>
+        <v>83.2</v>
+      </c>
+      <c r="AN135" s="20" t="n">
+        <v>2668</v>
       </c>
       <c r="AO135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP135" s="20" t="n">
-        <v>11707</v>
+        <v>73.5</v>
+      </c>
+      <c r="AP135" s="15" t="n">
+        <v>3433</v>
       </c>
       <c r="AQ135" s="19" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="AR135" s="15" t="n">
-        <v>1797</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="AR135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AS135" s="19" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="AT135" s="20" t="n">
-        <v>1689</v>
+        <v>0</v>
+      </c>
+      <c r="AT135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AU135" s="19" t="n">
-        <v>83</v>
-      </c>
-      <c r="AV135" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AV135" s="23" t="n">
+        <v>13125</v>
       </c>
       <c r="AW135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" s="19" t="n">
-        <v>-1</v>
+        <v>36.4</v>
+      </c>
+      <c r="AX135" s="13" t="n">
+        <v>2505</v>
       </c>
       <c r="AY135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" s="23" t="n">
-        <v>11018</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="AZ135" s="13" t="n">
+        <v>235</v>
       </c>
       <c r="BA135" s="19" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="BB135" s="19" t="n">
-        <v>-1</v>
+        <v>99.2</v>
+      </c>
+      <c r="BB135" s="23" t="n">
+        <v>11031</v>
       </c>
       <c r="BC135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD135" s="15" t="n">
-        <v>229</v>
+        <v>48.3</v>
+      </c>
+      <c r="BD135" s="20" t="n">
+        <v>2228</v>
       </c>
       <c r="BE135" s="19" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="BF135" s="15" t="n">
-        <v>662</v>
+        <v>82.7</v>
+      </c>
+      <c r="BF135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BG135" s="19" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="BH135" s="20" t="n">
-        <v>2790</v>
+        <v>0</v>
+      </c>
+      <c r="BH135" s="15" t="n">
+        <v>347</v>
       </c>
       <c r="BI135" s="19" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="BJ135" s="13" t="n">
-        <v>407</v>
+        <v>93.7</v>
+      </c>
+      <c r="BJ135" s="15" t="n">
+        <v>3398</v>
       </c>
       <c r="BK135" s="19" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="BL135" s="15" t="n">
-        <v>98</v>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BL135" s="23" t="n">
+        <v>14146</v>
       </c>
       <c r="BM135" s="19" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="BN135" s="15" t="n">
-        <v>227</v>
+        <v>33.7</v>
+      </c>
+      <c r="BN135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BO135" s="19" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="BP135" s="13" t="n">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="BP135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ135" s="19" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="BR135" s="20" t="n">
-        <v>1523</v>
+        <v>0</v>
+      </c>
+      <c r="BR135" s="15" t="n">
+        <v>1291</v>
       </c>
       <c r="BS135" s="19" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="BT135" s="13" t="n">
-        <v>399</v>
+        <v>57.2</v>
+      </c>
+      <c r="BT135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU135" s="19" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="BV135" s="13" t="n">
-        <v>93</v>
+        <v>0</v>
+      </c>
+      <c r="BV135" s="15" t="n">
+        <v>2016</v>
       </c>
       <c r="BW135" s="19" t="n">
-        <v>99.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="BX135" s="13" t="n">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="BY135" s="19" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="BZ135" s="13" t="n">
-        <v>530</v>
+        <v>98.3</v>
+      </c>
+      <c r="BZ135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CA135" s="19" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="CB135" s="13" t="n">
-        <v>188</v>
+        <v>0</v>
+      </c>
+      <c r="CB135" s="20" t="n">
+        <v>7546</v>
       </c>
       <c r="CC135" s="19" t="n">
-        <v>99.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="CD135" s="13" t="n">
-        <v>1007</v>
+        <v>614</v>
       </c>
       <c r="CE135" s="19" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="CF135" s="13" t="n">
-        <v>220</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="CF135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG135" s="19" t="n">
-        <v>99.3</v>
+        <v>0</v>
       </c>
       <c r="CH135" s="13" t="n">
-        <v>819</v>
+        <v>309</v>
       </c>
       <c r="CI135" s="19" t="n">
-        <v>97.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="CJ135" s="15" t="n">
-        <v>443</v>
+        <v>2327</v>
       </c>
       <c r="CK135" s="19" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="CL135" s="13" t="n">
-        <v>105</v>
+        <v>86.40000000000001</v>
+      </c>
+      <c r="CL135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM135" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CN135" s="13" t="n">
-        <v>175</v>
+        <v>0</v>
+      </c>
+      <c r="CN135" s="15" t="n">
+        <v>2018</v>
       </c>
       <c r="CO135" s="19" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="CP135" s="13" t="n">
-        <v>1424</v>
+        <v>86.8</v>
+      </c>
+      <c r="CP135" s="20" t="n">
+        <v>11809</v>
       </c>
       <c r="CQ135" s="19" t="n">
-        <v>94.59999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="CR135" s="19" t="n">
         <v>-1</v>
@@ -42955,51 +42960,46 @@
         <v>0</v>
       </c>
       <c r="CT135" s="13" t="n">
-        <v>278</v>
+        <v>1325</v>
       </c>
       <c r="CU135" s="19" t="n">
-        <v>99</v>
-      </c>
-      <c r="CV135" s="13" t="n">
-        <v>117</v>
+        <v>95.09999999999999</v>
+      </c>
+      <c r="CV135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW135" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CX135" s="13" t="n">
-        <v>1880</v>
+        <v>0</v>
+      </c>
+      <c r="CX135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CY135" s="19" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="CZ135" s="13" t="n">
-        <v>188</v>
+        <v>0</v>
+      </c>
+      <c r="CZ135" s="15" t="n">
+        <v>2694</v>
       </c>
       <c r="DA135" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="DB135" s="13" t="n">
-        <v>112</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="DB135" s="15" t="n">
+        <v>2929</v>
       </c>
       <c r="DC135" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="DD135" s="13" t="n">
-        <v>852</v>
+        <v>85</v>
+      </c>
+      <c r="DD135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE135" s="19" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="DF135" s="15" t="n">
-        <v>690</v>
+        <v>0</v>
+      </c>
+      <c r="DF135" s="23" t="n">
+        <v>10833</v>
       </c>
       <c r="DG135" s="19" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="DH135" s="1" t="inlineStr">
-        <is>
-          <t>Baidu-Logo</t>
-        </is>
+        <v>39.5</v>
       </c>
     </row>
     <row r="136">
@@ -43008,17 +43008,17 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>roy_1127</t>
+          <t>cyzh</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>1532</v>
-      </c>
-      <c r="D136" s="26" t="n">
-        <v>2043</v>
+        <v>1246</v>
+      </c>
+      <c r="D136" s="24" t="n">
+        <v>2115</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="F136" s="14" t="n">
         <v>-1</v>
@@ -43026,11 +43026,11 @@
       <c r="G136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H136" s="14" t="n">
-        <v>-1</v>
+      <c r="H136" s="23" t="n">
+        <v>18839</v>
       </c>
       <c r="I136" s="14" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="J136" s="14" t="n">
         <v>-1</v>
@@ -43038,11 +43038,11 @@
       <c r="K136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L136" s="14" t="n">
-        <v>-1</v>
+      <c r="L136" s="20" t="n">
+        <v>3126</v>
       </c>
       <c r="M136" s="14" t="n">
-        <v>0</v>
+        <v>76.8</v>
       </c>
       <c r="N136" s="14" t="n">
         <v>-1</v>
@@ -43050,17 +43050,17 @@
       <c r="O136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P136" s="14" t="n">
-        <v>-1</v>
+      <c r="P136" s="20" t="n">
+        <v>2958</v>
       </c>
       <c r="Q136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" s="14" t="n">
-        <v>-1</v>
+        <v>76.7</v>
+      </c>
+      <c r="R136" s="15" t="n">
+        <v>845</v>
       </c>
       <c r="S136" s="14" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="T136" s="14" t="n">
         <v>-1</v>
@@ -43068,11 +43068,11 @@
       <c r="U136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="14" t="n">
-        <v>-1</v>
+      <c r="V136" s="13" t="n">
+        <v>211</v>
       </c>
       <c r="W136" s="14" t="n">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="X136" s="14" t="n">
         <v>-1</v>
@@ -43080,23 +43080,23 @@
       <c r="Y136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="14" t="n">
-        <v>-1</v>
+      <c r="Z136" s="23" t="n">
+        <v>5468</v>
       </c>
       <c r="AA136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" s="14" t="n">
-        <v>-1</v>
+        <v>57.1</v>
+      </c>
+      <c r="AB136" s="15" t="n">
+        <v>1494</v>
       </c>
       <c r="AC136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" s="14" t="n">
-        <v>-1</v>
+        <v>87</v>
+      </c>
+      <c r="AD136" s="13" t="n">
+        <v>131</v>
       </c>
       <c r="AE136" s="14" t="n">
-        <v>0</v>
+        <v>99.3</v>
       </c>
       <c r="AF136" s="14" t="n">
         <v>-1</v>
@@ -43128,23 +43128,23 @@
       <c r="AO136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP136" s="14" t="n">
-        <v>-1</v>
+      <c r="AP136" s="20" t="n">
+        <v>11707</v>
       </c>
       <c r="AQ136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR136" s="14" t="n">
-        <v>-1</v>
+        <v>44.3</v>
+      </c>
+      <c r="AR136" s="15" t="n">
+        <v>1797</v>
       </c>
       <c r="AS136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT136" s="14" t="n">
-        <v>-1</v>
+        <v>85.7</v>
+      </c>
+      <c r="AT136" s="20" t="n">
+        <v>1689</v>
       </c>
       <c r="AU136" s="14" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AV136" s="14" t="n">
         <v>-1</v>
@@ -43158,11 +43158,11 @@
       <c r="AY136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AZ136" s="14" t="n">
-        <v>-1</v>
+      <c r="AZ136" s="23" t="n">
+        <v>11018</v>
       </c>
       <c r="BA136" s="14" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="BB136" s="14" t="n">
         <v>-1</v>
@@ -43170,125 +43170,125 @@
       <c r="BC136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BD136" s="14" t="n">
-        <v>-1</v>
+      <c r="BD136" s="15" t="n">
+        <v>229</v>
       </c>
       <c r="BE136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF136" s="14" t="n">
-        <v>-1</v>
+        <v>94.2</v>
+      </c>
+      <c r="BF136" s="15" t="n">
+        <v>662</v>
       </c>
       <c r="BG136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH136" s="14" t="n">
-        <v>-1</v>
+        <v>92.8</v>
+      </c>
+      <c r="BH136" s="20" t="n">
+        <v>2790</v>
       </c>
       <c r="BI136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ136" s="14" t="n">
-        <v>-1</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BJ136" s="13" t="n">
+        <v>407</v>
       </c>
       <c r="BK136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL136" s="14" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="BL136" s="15" t="n">
+        <v>98</v>
       </c>
       <c r="BM136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN136" s="14" t="n">
-        <v>-1</v>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="BN136" s="15" t="n">
+        <v>227</v>
       </c>
       <c r="BO136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP136" s="14" t="n">
-        <v>-1</v>
+        <v>94.3</v>
+      </c>
+      <c r="BP136" s="13" t="n">
+        <v>80</v>
       </c>
       <c r="BQ136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR136" s="14" t="n">
-        <v>-1</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="BR136" s="20" t="n">
+        <v>1523</v>
       </c>
       <c r="BS136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT136" s="14" t="n">
-        <v>-1</v>
+        <v>45.5</v>
+      </c>
+      <c r="BT136" s="13" t="n">
+        <v>399</v>
       </c>
       <c r="BU136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV136" s="14" t="n">
-        <v>-1</v>
+        <v>88.5</v>
+      </c>
+      <c r="BV136" s="13" t="n">
+        <v>93</v>
       </c>
       <c r="BW136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX136" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="BX136" s="13" t="n">
+        <v>500</v>
       </c>
       <c r="BY136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ136" s="14" t="n">
-        <v>-1</v>
+        <v>98.5</v>
+      </c>
+      <c r="BZ136" s="13" t="n">
+        <v>530</v>
       </c>
       <c r="CA136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB136" s="14" t="n">
-        <v>-1</v>
+        <v>98.5</v>
+      </c>
+      <c r="CB136" s="13" t="n">
+        <v>188</v>
       </c>
       <c r="CC136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD136" s="14" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="CD136" s="13" t="n">
+        <v>1007</v>
       </c>
       <c r="CE136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF136" s="14" t="n">
-        <v>-1</v>
+        <v>96.8</v>
+      </c>
+      <c r="CF136" s="13" t="n">
+        <v>220</v>
       </c>
       <c r="CG136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH136" s="14" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="CH136" s="13" t="n">
+        <v>819</v>
       </c>
       <c r="CI136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ136" s="14" t="n">
-        <v>-1</v>
+        <v>97.2</v>
+      </c>
+      <c r="CJ136" s="15" t="n">
+        <v>443</v>
       </c>
       <c r="CK136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL136" s="14" t="n">
-        <v>-1</v>
+        <v>93.40000000000001</v>
+      </c>
+      <c r="CL136" s="13" t="n">
+        <v>105</v>
       </c>
       <c r="CM136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN136" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CN136" s="13" t="n">
+        <v>175</v>
       </c>
       <c r="CO136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP136" s="14" t="n">
-        <v>-1</v>
+        <v>99.3</v>
+      </c>
+      <c r="CP136" s="13" t="n">
+        <v>1424</v>
       </c>
       <c r="CQ136" s="14" t="n">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="CR136" s="14" t="n">
         <v>-1</v>
@@ -43296,47 +43296,52 @@
       <c r="CS136" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CT136" s="14" t="n">
-        <v>-1</v>
+      <c r="CT136" s="13" t="n">
+        <v>278</v>
       </c>
       <c r="CU136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV136" s="14" t="n">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="CV136" s="13" t="n">
+        <v>117</v>
       </c>
       <c r="CW136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX136" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CX136" s="13" t="n">
+        <v>1880</v>
       </c>
       <c r="CY136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ136" s="14" t="n">
-        <v>-1</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="CZ136" s="13" t="n">
+        <v>188</v>
       </c>
       <c r="DA136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB136" s="14" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="DB136" s="13" t="n">
+        <v>112</v>
       </c>
       <c r="DC136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD136" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DD136" s="13" t="n">
+        <v>852</v>
       </c>
       <c r="DE136" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF136" s="14" t="n">
-        <v>-1</v>
+        <v>96.8</v>
+      </c>
+      <c r="DF136" s="15" t="n">
+        <v>690</v>
       </c>
       <c r="DG136" s="14" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="DH136" s="1" t="inlineStr">
+        <is>
+          <t>Baidu-Logo</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -43345,14 +43350,14 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>zrts</t>
+          <t>roy_1127</t>
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>1388</v>
-      </c>
-      <c r="D137" s="21" t="n">
-        <v>2501</v>
+        <v>1532</v>
+      </c>
+      <c r="D137" s="27" t="n">
+        <v>2043</v>
       </c>
       <c r="E137" s="12" t="n">
         <v>0</v>
@@ -43381,53 +43386,53 @@
       <c r="M137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N137" s="15" t="n">
-        <v>268</v>
+      <c r="N137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="O137" s="19" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="P137" s="23" t="n">
-        <v>4359</v>
+        <v>0</v>
+      </c>
+      <c r="P137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Q137" s="19" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="R137" s="20" t="n">
-        <v>1169</v>
+        <v>0</v>
+      </c>
+      <c r="R137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="T137" s="15" t="n">
-        <v>220</v>
+        <v>0</v>
+      </c>
+      <c r="T137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U137" s="19" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="V137" s="20" t="n">
-        <v>1182</v>
+        <v>0</v>
+      </c>
+      <c r="V137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W137" s="19" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="X137" s="20" t="n">
-        <v>999</v>
+        <v>0</v>
+      </c>
+      <c r="X137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y137" s="19" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="Z137" s="15" t="n">
-        <v>133</v>
+        <v>0</v>
+      </c>
+      <c r="Z137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AA137" s="19" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="AB137" s="20" t="n">
-        <v>2537</v>
+        <v>0</v>
+      </c>
+      <c r="AB137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC137" s="19" t="n">
-        <v>76.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD137" s="19" t="n">
         <v>-1</v>
@@ -43453,11 +43458,11 @@
       <c r="AK137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AL137" s="13" t="n">
-        <v>49</v>
+      <c r="AL137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AM137" s="19" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
       <c r="AN137" s="19" t="n">
         <v>-1</v>
@@ -43465,35 +43470,35 @@
       <c r="AO137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP137" s="13" t="n">
-        <v>153</v>
+      <c r="AP137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ137" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="AR137" s="13" t="n">
-        <v>73</v>
+        <v>0</v>
+      </c>
+      <c r="AR137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AS137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="AT137" s="13" t="n">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="AT137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AU137" s="19" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="AV137" s="13" t="n">
-        <v>208</v>
+        <v>0</v>
+      </c>
+      <c r="AV137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW137" s="19" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="AX137" s="13" t="n">
-        <v>1081</v>
+        <v>0</v>
+      </c>
+      <c r="AX137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY137" s="19" t="n">
-        <v>96.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ137" s="19" t="n">
         <v>-1</v>
@@ -43501,179 +43506,179 @@
       <c r="BA137" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB137" s="15" t="n">
-        <v>1040</v>
+      <c r="BB137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BC137" s="19" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="BD137" s="20" t="n">
-        <v>1317</v>
+        <v>0</v>
+      </c>
+      <c r="BD137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BE137" s="19" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="BF137" s="20" t="n">
-        <v>2768</v>
+        <v>0</v>
+      </c>
+      <c r="BF137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BG137" s="19" t="n">
-        <v>81</v>
-      </c>
-      <c r="BH137" s="13" t="n">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="BH137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI137" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="BJ137" s="13" t="n">
-        <v>98</v>
+        <v>0</v>
+      </c>
+      <c r="BJ137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BK137" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="BL137" s="15" t="n">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="BL137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BM137" s="19" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="BN137" s="15" t="n">
-        <v>322</v>
+        <v>0</v>
+      </c>
+      <c r="BN137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BO137" s="19" t="n">
-        <v>94</v>
-      </c>
-      <c r="BP137" s="13" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="BP137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ137" s="19" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="BR137" s="15" t="n">
-        <v>1296</v>
+        <v>0</v>
+      </c>
+      <c r="BR137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BS137" s="19" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="BT137" s="13" t="n">
-        <v>270</v>
+        <v>0</v>
+      </c>
+      <c r="BT137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU137" s="19" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="BV137" s="13" t="n">
-        <v>118</v>
+        <v>0</v>
+      </c>
+      <c r="BV137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BW137" s="19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="BX137" s="15" t="n">
-        <v>1031</v>
+        <v>0</v>
+      </c>
+      <c r="BX137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BY137" s="19" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="BZ137" s="13" t="n">
-        <v>158</v>
+        <v>0</v>
+      </c>
+      <c r="BZ137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CA137" s="19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="CB137" s="15" t="n">
-        <v>2284</v>
+        <v>0</v>
+      </c>
+      <c r="CB137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CC137" s="19" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="CD137" s="13" t="n">
-        <v>127</v>
+        <v>0</v>
+      </c>
+      <c r="CD137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CE137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CF137" s="13" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="CF137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG137" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="CH137" s="13" t="n">
-        <v>130</v>
+        <v>0</v>
+      </c>
+      <c r="CH137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CI137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CJ137" s="13" t="n">
-        <v>348</v>
+        <v>0</v>
+      </c>
+      <c r="CJ137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CK137" s="19" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="CL137" s="15" t="n">
-        <v>393</v>
+        <v>0</v>
+      </c>
+      <c r="CL137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM137" s="19" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="CN137" s="13" t="n">
-        <v>258</v>
+        <v>0</v>
+      </c>
+      <c r="CN137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CO137" s="19" t="n">
-        <v>99</v>
-      </c>
-      <c r="CP137" s="13" t="n">
-        <v>97</v>
+        <v>0</v>
+      </c>
+      <c r="CP137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="CR137" s="13" t="n">
-        <v>161</v>
+        <v>0</v>
+      </c>
+      <c r="CR137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CS137" s="19" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="CT137" s="13" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="CT137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CU137" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="CV137" s="13" t="n">
-        <v>141</v>
+        <v>0</v>
+      </c>
+      <c r="CV137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW137" s="19" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="CX137" s="13" t="n">
-        <v>482</v>
+        <v>0</v>
+      </c>
+      <c r="CX137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CY137" s="19" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="CZ137" s="13" t="n">
-        <v>108</v>
+        <v>0</v>
+      </c>
+      <c r="CZ137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DA137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="DB137" s="13" t="n">
-        <v>129</v>
+        <v>0</v>
+      </c>
+      <c r="DB137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DC137" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="DD137" s="13" t="n">
-        <v>90</v>
+        <v>0</v>
+      </c>
+      <c r="DD137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DE137" s="19" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="DF137" s="15" t="n">
-        <v>64</v>
+        <v>0</v>
+      </c>
+      <c r="DF137" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="DG137" s="19" t="n">
-        <v>94.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -43682,14 +43687,14 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>nijiademianbao</t>
+          <t>zrts</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>1227</v>
-      </c>
-      <c r="D138" s="26" t="n">
-        <v>1734</v>
+        <v>1388</v>
+      </c>
+      <c r="D138" s="22" t="n">
+        <v>2501</v>
       </c>
       <c r="E138" s="12" t="n">
         <v>0</v>
@@ -43718,53 +43723,53 @@
       <c r="M138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N138" s="14" t="n">
-        <v>-1</v>
+      <c r="N138" s="15" t="n">
+        <v>268</v>
       </c>
       <c r="O138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="14" t="n">
-        <v>-1</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P138" s="23" t="n">
+        <v>4359</v>
       </c>
       <c r="Q138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R138" s="14" t="n">
-        <v>-1</v>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="R138" s="20" t="n">
+        <v>1169</v>
       </c>
       <c r="S138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="14" t="n">
-        <v>-1</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="T138" s="15" t="n">
+        <v>220</v>
       </c>
       <c r="U138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V138" s="14" t="n">
-        <v>-1</v>
+        <v>93.59999999999999</v>
+      </c>
+      <c r="V138" s="20" t="n">
+        <v>1182</v>
       </c>
       <c r="W138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" s="14" t="n">
-        <v>-1</v>
+        <v>83.5</v>
+      </c>
+      <c r="X138" s="20" t="n">
+        <v>999</v>
       </c>
       <c r="Y138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z138" s="14" t="n">
-        <v>-1</v>
+        <v>84.5</v>
+      </c>
+      <c r="Z138" s="15" t="n">
+        <v>133</v>
       </c>
       <c r="AA138" s="14" t="n">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="AB138" s="20" t="n">
-        <v>6377</v>
+        <v>2537</v>
       </c>
       <c r="AC138" s="14" t="n">
-        <v>55.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AD138" s="14" t="n">
         <v>-1</v>
@@ -43784,17 +43789,17 @@
       <c r="AI138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ138" s="20" t="n">
-        <v>8275</v>
+      <c r="AJ138" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AK138" s="14" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="AL138" s="15" t="n">
-        <v>1134</v>
+        <v>0</v>
+      </c>
+      <c r="AL138" s="13" t="n">
+        <v>49</v>
       </c>
       <c r="AM138" s="14" t="n">
-        <v>89.8</v>
+        <v>99.8</v>
       </c>
       <c r="AN138" s="14" t="n">
         <v>-1</v>
@@ -43802,35 +43807,35 @@
       <c r="AO138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AP138" s="14" t="n">
-        <v>-1</v>
+      <c r="AP138" s="13" t="n">
+        <v>153</v>
       </c>
       <c r="AQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR138" s="14" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AR138" s="13" t="n">
+        <v>73</v>
       </c>
       <c r="AS138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT138" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="AT138" s="13" t="n">
+        <v>58</v>
       </c>
       <c r="AU138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV138" s="14" t="n">
-        <v>-1</v>
+        <v>99.8</v>
+      </c>
+      <c r="AV138" s="13" t="n">
+        <v>208</v>
       </c>
       <c r="AW138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX138" s="14" t="n">
-        <v>-1</v>
+        <v>99.2</v>
+      </c>
+      <c r="AX138" s="13" t="n">
+        <v>1081</v>
       </c>
       <c r="AY138" s="14" t="n">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AZ138" s="14" t="n">
         <v>-1</v>
@@ -43838,179 +43843,179 @@
       <c r="BA138" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BB138" s="14" t="n">
-        <v>-1</v>
+      <c r="BB138" s="15" t="n">
+        <v>1040</v>
       </c>
       <c r="BC138" s="14" t="n">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="BD138" s="20" t="n">
-        <v>5346</v>
+        <v>1317</v>
       </c>
       <c r="BE138" s="14" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="BF138" s="14" t="n">
-        <v>-1</v>
+        <v>85.7</v>
+      </c>
+      <c r="BF138" s="20" t="n">
+        <v>2768</v>
       </c>
       <c r="BG138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH138" s="20" t="n">
-        <v>8544</v>
+        <v>81</v>
+      </c>
+      <c r="BH138" s="13" t="n">
+        <v>148</v>
       </c>
       <c r="BI138" s="14" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="BJ138" s="15" t="n">
-        <v>4093</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BJ138" s="13" t="n">
+        <v>98</v>
       </c>
       <c r="BK138" s="14" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="BL138" s="14" t="n">
-        <v>-1</v>
+        <v>99.7</v>
+      </c>
+      <c r="BL138" s="15" t="n">
+        <v>84</v>
       </c>
       <c r="BM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN138" s="14" t="n">
-        <v>-1</v>
+        <v>94.7</v>
+      </c>
+      <c r="BN138" s="15" t="n">
+        <v>322</v>
       </c>
       <c r="BO138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP138" s="15" t="n">
-        <v>1711</v>
+        <v>94</v>
+      </c>
+      <c r="BP138" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="BQ138" s="14" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="BR138" s="13" t="n">
-        <v>721</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BR138" s="15" t="n">
+        <v>1296</v>
       </c>
       <c r="BS138" s="14" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="BT138" s="14" t="n">
-        <v>-1</v>
+        <v>57.1</v>
+      </c>
+      <c r="BT138" s="13" t="n">
+        <v>270</v>
       </c>
       <c r="BU138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV138" s="14" t="n">
-        <v>-1</v>
+        <v>92.2</v>
+      </c>
+      <c r="BV138" s="13" t="n">
+        <v>118</v>
       </c>
       <c r="BW138" s="14" t="n">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="BX138" s="15" t="n">
-        <v>6502</v>
+        <v>1031</v>
       </c>
       <c r="BY138" s="14" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="BZ138" s="14" t="n">
-        <v>-1</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="BZ138" s="13" t="n">
+        <v>158</v>
       </c>
       <c r="CA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB138" s="20" t="n">
-        <v>12189</v>
+        <v>99.5</v>
+      </c>
+      <c r="CB138" s="15" t="n">
+        <v>2284</v>
       </c>
       <c r="CC138" s="14" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="CD138" s="14" t="n">
-        <v>-1</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="CD138" s="13" t="n">
+        <v>127</v>
       </c>
       <c r="CE138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF138" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CF138" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="CG138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH138" s="23" t="n">
-        <v>15989</v>
+        <v>100</v>
+      </c>
+      <c r="CH138" s="13" t="n">
+        <v>130</v>
       </c>
       <c r="CI138" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="CJ138" s="20" t="n">
-        <v>7033</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CJ138" s="13" t="n">
+        <v>348</v>
       </c>
       <c r="CK138" s="14" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="CL138" s="14" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="CL138" s="15" t="n">
+        <v>393</v>
       </c>
       <c r="CM138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN138" s="20" t="n">
-        <v>5354</v>
+        <v>93.3</v>
+      </c>
+      <c r="CN138" s="13" t="n">
+        <v>258</v>
       </c>
       <c r="CO138" s="14" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="CP138" s="14" t="n">
-        <v>-1</v>
+        <v>99</v>
+      </c>
+      <c r="CP138" s="13" t="n">
+        <v>97</v>
       </c>
       <c r="CQ138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR138" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="CR138" s="13" t="n">
+        <v>161</v>
       </c>
       <c r="CS138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT138" s="14" t="n">
-        <v>-1</v>
+        <v>99.40000000000001</v>
+      </c>
+      <c r="CT138" s="13" t="n">
+        <v>70</v>
       </c>
       <c r="CU138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV138" s="14" t="n">
-        <v>-1</v>
+        <v>99.7</v>
+      </c>
+      <c r="CV138" s="13" t="n">
+        <v>141</v>
       </c>
       <c r="CW138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX138" s="14" t="n">
-        <v>-1</v>
+        <v>99.5</v>
+      </c>
+      <c r="CX138" s="13" t="n">
+        <v>482</v>
       </c>
       <c r="CY138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ138" s="14" t="n">
-        <v>-1</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="CZ138" s="13" t="n">
+        <v>108</v>
       </c>
       <c r="DA138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB138" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DB138" s="13" t="n">
+        <v>129</v>
       </c>
       <c r="DC138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD138" s="14" t="n">
-        <v>-1</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="DD138" s="13" t="n">
+        <v>90</v>
       </c>
       <c r="DE138" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF138" s="14" t="n">
-        <v>-1</v>
+        <v>99.7</v>
+      </c>
+      <c r="DF138" s="15" t="n">
+        <v>64</v>
       </c>
       <c r="DG138" s="14" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="139">
@@ -44019,14 +44024,14 @@
       </c>
       <c r="B139" s="16" t="inlineStr">
         <is>
-          <t>fatyuan</t>
+          <t>nijiademianbao</t>
         </is>
       </c>
       <c r="C139" s="17" t="n">
-        <v>1209</v>
+        <v>1227</v>
       </c>
       <c r="D139" s="27" t="n">
-        <v>1629</v>
+        <v>1734</v>
       </c>
       <c r="E139" s="12" t="n">
         <v>0</v>
@@ -44097,11 +44102,11 @@
       <c r="AA139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AB139" s="19" t="n">
-        <v>-1</v>
+      <c r="AB139" s="20" t="n">
+        <v>6377</v>
       </c>
       <c r="AC139" s="19" t="n">
-        <v>0</v>
+        <v>55.8</v>
       </c>
       <c r="AD139" s="19" t="n">
         <v>-1</v>
@@ -44121,17 +44126,17 @@
       <c r="AI139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ139" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ139" s="20" t="n">
+        <v>8275</v>
       </c>
       <c r="AK139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL139" s="19" t="n">
-        <v>-1</v>
+        <v>51.5</v>
+      </c>
+      <c r="AL139" s="15" t="n">
+        <v>1134</v>
       </c>
       <c r="AM139" s="19" t="n">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="AN139" s="19" t="n">
         <v>-1</v>
@@ -44181,11 +44186,11 @@
       <c r="BC139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD139" s="19" t="n">
-        <v>-1</v>
+      <c r="BD139" s="20" t="n">
+        <v>5346</v>
       </c>
       <c r="BE139" s="19" t="n">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="BF139" s="19" t="n">
         <v>-1</v>
@@ -44193,17 +44198,17 @@
       <c r="BG139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH139" s="19" t="n">
-        <v>-1</v>
+      <c r="BH139" s="20" t="n">
+        <v>8544</v>
       </c>
       <c r="BI139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ139" s="19" t="n">
-        <v>-1</v>
+        <v>58.1</v>
+      </c>
+      <c r="BJ139" s="15" t="n">
+        <v>4093</v>
       </c>
       <c r="BK139" s="19" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="BL139" s="19" t="n">
         <v>-1</v>
@@ -44217,17 +44222,17 @@
       <c r="BO139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BP139" s="19" t="n">
-        <v>-1</v>
+      <c r="BP139" s="15" t="n">
+        <v>1711</v>
       </c>
       <c r="BQ139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR139" s="19" t="n">
-        <v>-1</v>
+        <v>43.9</v>
+      </c>
+      <c r="BR139" s="13" t="n">
+        <v>721</v>
       </c>
       <c r="BS139" s="19" t="n">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="BT139" s="19" t="n">
         <v>-1</v>
@@ -44241,11 +44246,11 @@
       <c r="BW139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BX139" s="19" t="n">
-        <v>-1</v>
+      <c r="BX139" s="15" t="n">
+        <v>6502</v>
       </c>
       <c r="BY139" s="19" t="n">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="BZ139" s="19" t="n">
         <v>-1</v>
@@ -44253,11 +44258,11 @@
       <c r="CA139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CB139" s="19" t="n">
-        <v>-1</v>
+      <c r="CB139" s="20" t="n">
+        <v>12189</v>
       </c>
       <c r="CC139" s="19" t="n">
-        <v>0</v>
+        <v>52.2</v>
       </c>
       <c r="CD139" s="19" t="n">
         <v>-1</v>
@@ -44271,17 +44276,17 @@
       <c r="CG139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CH139" s="19" t="n">
-        <v>-1</v>
+      <c r="CH139" s="23" t="n">
+        <v>15989</v>
       </c>
       <c r="CI139" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ139" s="19" t="n">
-        <v>-1</v>
+        <v>30</v>
+      </c>
+      <c r="CJ139" s="20" t="n">
+        <v>7033</v>
       </c>
       <c r="CK139" s="19" t="n">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="CL139" s="19" t="n">
         <v>-1</v>
@@ -44289,11 +44294,11 @@
       <c r="CM139" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CN139" s="19" t="n">
-        <v>-1</v>
+      <c r="CN139" s="20" t="n">
+        <v>5354</v>
       </c>
       <c r="CO139" s="19" t="n">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="CP139" s="19" t="n">
         <v>-1</v>
@@ -44356,14 +44361,14 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>bill04128682</t>
+          <t>fatyuan</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>966</v>
+        <v>1209</v>
       </c>
       <c r="D140" s="26" t="n">
-        <v>2014</v>
+        <v>1629</v>
       </c>
       <c r="E140" s="12" t="n">
         <v>0</v>
@@ -44488,11 +44493,11 @@
       <c r="AS140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AT140" s="20" t="n">
-        <v>5125</v>
+      <c r="AT140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AU140" s="14" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="AV140" s="14" t="n">
         <v>-1</v>
@@ -44620,11 +44625,11 @@
       <c r="CK140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CL140" s="15" t="n">
-        <v>1644</v>
+      <c r="CL140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CM140" s="14" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="CN140" s="14" t="n">
         <v>-1</v>
@@ -44632,11 +44637,11 @@
       <c r="CO140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CP140" s="13" t="n">
-        <v>1445</v>
+      <c r="CP140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ140" s="14" t="n">
-        <v>94.5</v>
+        <v>0</v>
       </c>
       <c r="CR140" s="14" t="n">
         <v>-1</v>
@@ -44650,17 +44655,17 @@
       <c r="CU140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CV140" s="13" t="n">
-        <v>1248</v>
+      <c r="CV140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CW140" s="14" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="CX140" s="15" t="n">
-        <v>2582</v>
+        <v>0</v>
+      </c>
+      <c r="CX140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY140" s="14" t="n">
-        <v>84.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CZ140" s="14" t="n">
         <v>-1</v>
@@ -44668,28 +44673,23 @@
       <c r="DA140" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB140" s="15" t="n">
-        <v>5511</v>
+      <c r="DB140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DC140" s="14" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="DD140" s="13" t="n">
-        <v>1501</v>
+        <v>0</v>
+      </c>
+      <c r="DD140" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DE140" s="14" t="n">
-        <v>94.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="DF140" s="14" t="n">
         <v>-1</v>
       </c>
       <c r="DG140" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="DH140" s="1" t="inlineStr">
-        <is>
-          <t>JumpTrade-Logo</t>
-        </is>
       </c>
     </row>
     <row r="141">
@@ -44698,14 +44698,14 @@
       </c>
       <c r="B141" s="16" t="inlineStr">
         <is>
-          <t>deadstorm</t>
+          <t>bill04128682</t>
         </is>
       </c>
       <c r="C141" s="17" t="n">
-        <v>849</v>
+        <v>966</v>
       </c>
       <c r="D141" s="27" t="n">
-        <v>1433</v>
+        <v>2014</v>
       </c>
       <c r="E141" s="12" t="n">
         <v>0</v>
@@ -44830,11 +44830,11 @@
       <c r="AS141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AT141" s="19" t="n">
-        <v>-1</v>
+      <c r="AT141" s="20" t="n">
+        <v>5125</v>
       </c>
       <c r="AU141" s="19" t="n">
-        <v>0</v>
+        <v>68.8</v>
       </c>
       <c r="AV141" s="19" t="n">
         <v>-1</v>
@@ -44962,11 +44962,11 @@
       <c r="CK141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CL141" s="19" t="n">
-        <v>-1</v>
+      <c r="CL141" s="15" t="n">
+        <v>1644</v>
       </c>
       <c r="CM141" s="19" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="CN141" s="19" t="n">
         <v>-1</v>
@@ -44974,11 +44974,11 @@
       <c r="CO141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CP141" s="19" t="n">
-        <v>-1</v>
+      <c r="CP141" s="13" t="n">
+        <v>1445</v>
       </c>
       <c r="CQ141" s="19" t="n">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="CR141" s="19" t="n">
         <v>-1</v>
@@ -44992,17 +44992,17 @@
       <c r="CU141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CV141" s="19" t="n">
-        <v>-1</v>
+      <c r="CV141" s="13" t="n">
+        <v>1248</v>
       </c>
       <c r="CW141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX141" s="19" t="n">
-        <v>-1</v>
+        <v>95.8</v>
+      </c>
+      <c r="CX141" s="15" t="n">
+        <v>2582</v>
       </c>
       <c r="CY141" s="19" t="n">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="CZ141" s="19" t="n">
         <v>-1</v>
@@ -45010,23 +45010,28 @@
       <c r="DA141" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DB141" s="19" t="n">
-        <v>-1</v>
+      <c r="DB141" s="15" t="n">
+        <v>5511</v>
       </c>
       <c r="DC141" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD141" s="19" t="n">
-        <v>-1</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="DD141" s="13" t="n">
+        <v>1501</v>
       </c>
       <c r="DE141" s="19" t="n">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="DF141" s="19" t="n">
         <v>-1</v>
       </c>
       <c r="DG141" s="19" t="n">
         <v>0</v>
+      </c>
+      <c r="DH141" s="1" t="inlineStr">
+        <is>
+          <t>JumpTrade-Logo</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -45035,14 +45040,14 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>wawawamei</t>
+          <t>deadstorm</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>678</v>
+        <v>849</v>
       </c>
       <c r="D142" s="26" t="n">
-        <v>1411</v>
+        <v>1433</v>
       </c>
       <c r="E142" s="12" t="n">
         <v>0</v>
@@ -45089,11 +45094,11 @@
       <c r="S142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="23" t="n">
-        <v>10801</v>
+      <c r="T142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="U142" s="14" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="V142" s="14" t="n">
         <v>-1</v>
@@ -45161,11 +45166,11 @@
       <c r="AQ142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AR142" s="20" t="n">
-        <v>4257</v>
+      <c r="AR142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AS142" s="14" t="n">
-        <v>67.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT142" s="14" t="n">
         <v>-1</v>
@@ -45179,11 +45184,11 @@
       <c r="AW142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX142" s="23" t="n">
-        <v>21358</v>
+      <c r="AX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY142" s="14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AZ142" s="14" t="n">
         <v>-1</v>
@@ -45245,11 +45250,11 @@
       <c r="BS142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BT142" s="23" t="n">
-        <v>2653</v>
+      <c r="BT142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BU142" s="14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV142" s="14" t="n">
         <v>-1</v>
@@ -45263,11 +45268,11 @@
       <c r="BY142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BZ142" s="20" t="n">
-        <v>18684</v>
+      <c r="BZ142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CA142" s="14" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
       <c r="CB142" s="14" t="n">
         <v>-1</v>
@@ -45287,11 +45292,11 @@
       <c r="CG142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CH142" s="23" t="n">
-        <v>20053</v>
+      <c r="CH142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CI142" s="14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CJ142" s="14" t="n">
         <v>-1</v>
@@ -45311,11 +45316,11 @@
       <c r="CO142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CP142" s="23" t="n">
-        <v>16477</v>
+      <c r="CP142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ142" s="14" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="CR142" s="14" t="n">
         <v>-1</v>
@@ -45323,11 +45328,11 @@
       <c r="CS142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CT142" s="23" t="n">
-        <v>20720</v>
+      <c r="CT142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CU142" s="14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="CV142" s="14" t="n">
         <v>-1</v>
@@ -45335,11 +45340,11 @@
       <c r="CW142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CX142" s="23" t="n">
-        <v>14803</v>
+      <c r="CX142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="CY142" s="14" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="CZ142" s="14" t="n">
         <v>-1</v>
@@ -45353,17 +45358,17 @@
       <c r="DC142" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DD142" s="23" t="n">
-        <v>19936</v>
+      <c r="DD142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DE142" s="14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="DF142" s="20" t="n">
-        <v>8638</v>
+        <v>0</v>
+      </c>
+      <c r="DF142" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="DG142" s="14" t="n">
-        <v>53.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -45372,14 +45377,14 @@
       </c>
       <c r="B143" s="16" t="inlineStr">
         <is>
-          <t>Q2PPSElacY</t>
+          <t>wawawamei</t>
         </is>
       </c>
       <c r="C143" s="17" t="n">
-        <v>198</v>
+        <v>678</v>
       </c>
       <c r="D143" s="27" t="n">
-        <v>1731</v>
+        <v>1411</v>
       </c>
       <c r="E143" s="12" t="n">
         <v>0</v>
@@ -45426,11 +45431,11 @@
       <c r="S143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="19" t="n">
-        <v>-1</v>
+      <c r="T143" s="23" t="n">
+        <v>10801</v>
       </c>
       <c r="U143" s="19" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="V143" s="19" t="n">
         <v>-1</v>
@@ -45499,10 +45504,10 @@
         <v>0</v>
       </c>
       <c r="AR143" s="20" t="n">
-        <v>2005</v>
+        <v>4257</v>
       </c>
       <c r="AS143" s="19" t="n">
-        <v>79.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AT143" s="19" t="n">
         <v>-1</v>
@@ -45516,11 +45521,11 @@
       <c r="AW143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AX143" s="19" t="n">
-        <v>-1</v>
+      <c r="AX143" s="23" t="n">
+        <v>21358</v>
       </c>
       <c r="AY143" s="19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ143" s="19" t="n">
         <v>-1</v>
@@ -45546,161 +45551,161 @@
       <c r="BG143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH143" s="20" t="n">
-        <v>3161</v>
+      <c r="BH143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI143" s="19" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="BJ143" s="20" t="n">
-        <v>7063</v>
+        <v>0</v>
+      </c>
+      <c r="BJ143" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BK143" s="19" t="n">
-        <v>67.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BN143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BO143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BP143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BQ143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BR143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT143" s="19" t="n">
-        <v>-2</v>
+      <c r="BT143" s="23" t="n">
+        <v>2653</v>
       </c>
       <c r="BU143" s="19" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BW143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BX143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BZ143" s="19" t="n">
-        <v>-2</v>
+      <c r="BZ143" s="20" t="n">
+        <v>18684</v>
       </c>
       <c r="CA143" s="19" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="CB143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CD143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CF143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CG143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CH143" s="19" t="n">
-        <v>-2</v>
+      <c r="CH143" s="23" t="n">
+        <v>20053</v>
       </c>
       <c r="CI143" s="19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CJ143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CL143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CM143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CN143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CP143" s="19" t="n">
-        <v>-2</v>
+      <c r="CP143" s="23" t="n">
+        <v>16477</v>
       </c>
       <c r="CQ143" s="19" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="CR143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CS143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CT143" s="19" t="n">
-        <v>-2</v>
+      <c r="CT143" s="23" t="n">
+        <v>20720</v>
       </c>
       <c r="CU143" s="19" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="CV143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CX143" s="19" t="n">
-        <v>-2</v>
+      <c r="CX143" s="23" t="n">
+        <v>14803</v>
       </c>
       <c r="CY143" s="19" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="CZ143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DA143" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DB143" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC143" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DD143" s="19" t="n">
-        <v>-2</v>
+      <c r="DD143" s="23" t="n">
+        <v>19936</v>
       </c>
       <c r="DE143" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF143" s="19" t="n">
-        <v>-2</v>
+        <v>10.5</v>
+      </c>
+      <c r="DF143" s="20" t="n">
+        <v>8638</v>
       </c>
       <c r="DG143" s="19" t="n">
-        <v>0</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="144">
@@ -45709,14 +45714,14 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>OneSwordWestWindCome</t>
+          <t>Q2PPSElacY</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D144" s="26" t="n">
-        <v>1824</v>
+        <v>1731</v>
       </c>
       <c r="E144" s="12" t="n">
         <v>0</v>
@@ -45745,11 +45750,11 @@
       <c r="M144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N144" s="20" t="n">
-        <v>2177</v>
+      <c r="N144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="O144" s="14" t="n">
-        <v>81.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="P144" s="14" t="n">
         <v>-1</v>
@@ -45757,11 +45762,11 @@
       <c r="Q144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="R144" s="15" t="n">
-        <v>256</v>
+      <c r="R144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="S144" s="14" t="n">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="T144" s="14" t="n">
         <v>-1</v>
@@ -45823,23 +45828,23 @@
       <c r="AM144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AN144" s="20" t="n">
-        <v>2027</v>
+      <c r="AN144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AO144" s="14" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="AP144" s="20" t="n">
-        <v>12886</v>
+        <v>0</v>
+      </c>
+      <c r="AP144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ144" s="14" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="AR144" s="14" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AR144" s="20" t="n">
+        <v>2005</v>
       </c>
       <c r="AS144" s="14" t="n">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AT144" s="14" t="n">
         <v>-1</v>
@@ -45853,47 +45858,47 @@
       <c r="AW144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="AX144" s="13" t="n">
-        <v>34</v>
+      <c r="AX144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="AY144" s="14" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="AZ144" s="15" t="n">
-        <v>349</v>
+        <v>0</v>
+      </c>
+      <c r="AZ144" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="BA144" s="14" t="n">
-        <v>93.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB144" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BC144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BD144" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BE144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BF144" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BG144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BH144" s="14" t="n">
-        <v>-2</v>
+      <c r="BH144" s="20" t="n">
+        <v>3161</v>
       </c>
       <c r="BI144" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ144" s="14" t="n">
-        <v>-2</v>
+        <v>78.2</v>
+      </c>
+      <c r="BJ144" s="20" t="n">
+        <v>7063</v>
       </c>
       <c r="BK144" s="14" t="n">
-        <v>0</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="BL144" s="14" t="n">
         <v>-2</v>
@@ -45925,107 +45930,107 @@
       <c r="BU144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BV144" s="23" t="n">
-        <v>12844</v>
+      <c r="BV144" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BW144" s="14" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="BX144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BY144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="BZ144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CA144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CB144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CC144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CD144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CE144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="CF144" s="20" t="n">
-        <v>15972</v>
+      <c r="CF144" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CG144" s="14" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="CH144" s="15" t="n">
-        <v>8693</v>
+        <v>0</v>
+      </c>
+      <c r="CH144" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CI144" s="14" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="CJ144" s="15" t="n">
-        <v>844</v>
+        <v>0</v>
+      </c>
+      <c r="CJ144" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CK144" s="14" t="n">
-        <v>91.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="CL144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CM144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CN144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CO144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CP144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CR144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CS144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CT144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CV144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CW144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CX144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY144" s="14" t="n">
         <v>0</v>
       </c>
       <c r="CZ144" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="DA144" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="DB144" s="15" t="n">
-        <v>1804</v>
+      <c r="DB144" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DC144" s="14" t="n">
-        <v>88.8</v>
+        <v>0</v>
       </c>
       <c r="DD144" s="14" t="n">
         <v>-2</v>
@@ -46038,11 +46043,6 @@
       </c>
       <c r="DG144" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="DH144" s="1" t="inlineStr">
-        <is>
-          <t>ByteDance-Logo</t>
-        </is>
       </c>
     </row>
     <row r="145">
@@ -46051,14 +46051,14 @@
       </c>
       <c r="B145" s="16" t="inlineStr">
         <is>
-          <t>z2dvWZDIvN</t>
+          <t>OneSwordWestWindCome</t>
         </is>
       </c>
       <c r="C145" s="17" t="n">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="D145" s="27" t="n">
-        <v>1691</v>
+        <v>1824</v>
       </c>
       <c r="E145" s="12" t="n">
         <v>0</v>
@@ -46087,125 +46087,125 @@
       <c r="M145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N145" s="19" t="n">
-        <v>-1</v>
+      <c r="N145" s="20" t="n">
+        <v>2177</v>
       </c>
       <c r="O145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" s="23" t="n">
-        <v>8387</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Q145" s="19" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="R145" s="20" t="n">
-        <v>5491</v>
+        <v>0</v>
+      </c>
+      <c r="R145" s="15" t="n">
+        <v>256</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="T145" s="20" t="n">
-        <v>4106</v>
+        <v>93.8</v>
+      </c>
+      <c r="T145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U145" s="19" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="V145" s="20" t="n">
-        <v>2733</v>
+        <v>0</v>
+      </c>
+      <c r="V145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W145" s="19" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="X145" s="20" t="n">
-        <v>1753</v>
+        <v>0</v>
+      </c>
+      <c r="X145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y145" s="19" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z145" s="20" t="n">
-        <v>4244</v>
+        <v>0</v>
+      </c>
+      <c r="Z145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AA145" s="19" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="AB145" s="20" t="n">
-        <v>3063</v>
+        <v>0</v>
+      </c>
+      <c r="AB145" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC145" s="19" t="n">
-        <v>73.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AF145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AG145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AH145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AI145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AJ145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AK145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AL145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AM145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AN145" s="19" t="n">
-        <v>-2</v>
+      <c r="AN145" s="20" t="n">
+        <v>2027</v>
       </c>
       <c r="AO145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP145" s="19" t="n">
-        <v>-2</v>
+        <v>77.5</v>
+      </c>
+      <c r="AP145" s="20" t="n">
+        <v>12886</v>
       </c>
       <c r="AQ145" s="19" t="n">
-        <v>0</v>
+        <v>39.7</v>
       </c>
       <c r="AR145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AS145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AT145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AU145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="AV145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AW145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AX145" s="19" t="n">
-        <v>-2</v>
+      <c r="AX145" s="13" t="n">
+        <v>34</v>
       </c>
       <c r="AY145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ145" s="19" t="n">
-        <v>-2</v>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AZ145" s="15" t="n">
+        <v>349</v>
       </c>
       <c r="BA145" s="19" t="n">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BB145" s="19" t="n">
         <v>-2</v>
@@ -46267,107 +46267,107 @@
       <c r="BU145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BV145" s="19" t="n">
-        <v>-2</v>
+      <c r="BV145" s="23" t="n">
+        <v>12844</v>
       </c>
       <c r="BW145" s="19" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="BX145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="BZ145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CA145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CB145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CD145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CF145" s="19" t="n">
-        <v>-2</v>
+      <c r="CF145" s="20" t="n">
+        <v>15972</v>
       </c>
       <c r="CG145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH145" s="19" t="n">
-        <v>-2</v>
+        <v>37.6</v>
+      </c>
+      <c r="CH145" s="15" t="n">
+        <v>8693</v>
       </c>
       <c r="CI145" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ145" s="19" t="n">
-        <v>-2</v>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="CJ145" s="15" t="n">
+        <v>844</v>
       </c>
       <c r="CK145" s="19" t="n">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="CL145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CM145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CN145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CP145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CQ145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CR145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CS145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CT145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CV145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CW145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CX145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CY145" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CZ145" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DA145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DB145" s="19" t="n">
-        <v>-2</v>
+      <c r="DB145" s="15" t="n">
+        <v>1804</v>
       </c>
       <c r="DC145" s="19" t="n">
-        <v>0</v>
+        <v>88.8</v>
       </c>
       <c r="DD145" s="19" t="n">
         <v>-2</v>
@@ -46375,11 +46375,11 @@
       <c r="DE145" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DF145" s="20" t="n">
-        <v>8674</v>
+      <c r="DF145" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG145" s="19" t="n">
-        <v>53.5</v>
+        <v>0</v>
       </c>
       <c r="DH145" s="1" t="inlineStr">
         <is>
@@ -46393,14 +46393,14 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>Tyrande</t>
+          <t>z2dvWZDIvN</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D146" s="24" t="n">
-        <v>2165</v>
+        <v>76</v>
+      </c>
+      <c r="D146" s="26" t="n">
+        <v>1691</v>
       </c>
       <c r="E146" s="12" t="n">
         <v>0</v>
@@ -46423,59 +46423,59 @@
       <c r="K146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="23" t="n">
-        <v>9956</v>
+      <c r="L146" s="14" t="n">
+        <v>-1</v>
       </c>
       <c r="M146" s="14" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="N146" s="14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P146" s="14" t="n">
-        <v>-2</v>
+      <c r="P146" s="23" t="n">
+        <v>8387</v>
       </c>
       <c r="Q146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" s="14" t="n">
-        <v>-2</v>
+        <v>47.2</v>
+      </c>
+      <c r="R146" s="20" t="n">
+        <v>5491</v>
       </c>
       <c r="S146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" s="14" t="n">
-        <v>-2</v>
+        <v>63.7</v>
+      </c>
+      <c r="T146" s="20" t="n">
+        <v>4106</v>
       </c>
       <c r="U146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" s="14" t="n">
-        <v>-2</v>
+        <v>64.8</v>
+      </c>
+      <c r="V146" s="20" t="n">
+        <v>2733</v>
       </c>
       <c r="W146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" s="14" t="n">
-        <v>-2</v>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="X146" s="20" t="n">
+        <v>1753</v>
       </c>
       <c r="Y146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z146" s="14" t="n">
-        <v>-2</v>
+        <v>80.3</v>
+      </c>
+      <c r="Z146" s="20" t="n">
+        <v>4244</v>
       </c>
       <c r="AA146" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB146" s="14" t="n">
-        <v>-2</v>
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AB146" s="20" t="n">
+        <v>3063</v>
       </c>
       <c r="AC146" s="14" t="n">
-        <v>0</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AD146" s="14" t="n">
         <v>-2</v>
@@ -46574,158 +46574,158 @@
         <v>0</v>
       </c>
       <c r="BJ146" s="14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BK146" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="BL146" s="20" t="n">
-        <v>11055</v>
+      <c r="BL146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BM146" s="14" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="BN146" s="20" t="n">
-        <v>2265</v>
+        <v>0</v>
+      </c>
+      <c r="BN146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BO146" s="14" t="n">
-        <v>83</v>
-      </c>
-      <c r="BP146" s="13" t="n">
-        <v>313</v>
+        <v>0</v>
+      </c>
+      <c r="BP146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ146" s="14" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="BR146" s="13" t="n">
-        <v>336</v>
+        <v>0</v>
+      </c>
+      <c r="BR146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BS146" s="14" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="BT146" s="13" t="n">
-        <v>378</v>
+        <v>0</v>
+      </c>
+      <c r="BT146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BU146" s="14" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="BV146" s="13" t="n">
-        <v>681</v>
+        <v>0</v>
+      </c>
+      <c r="BV146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BW146" s="14" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="BX146" s="13" t="n">
-        <v>447</v>
+        <v>0</v>
+      </c>
+      <c r="BX146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="BY146" s="14" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="BZ146" s="13" t="n">
-        <v>1308</v>
+        <v>0</v>
+      </c>
+      <c r="BZ146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CA146" s="14" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="CB146" s="15" t="n">
-        <v>715</v>
+        <v>0</v>
+      </c>
+      <c r="CB146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CC146" s="14" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="CD146" s="13" t="n">
-        <v>403</v>
+        <v>0</v>
+      </c>
+      <c r="CD146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CE146" s="14" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="CF146" s="15" t="n">
-        <v>1692</v>
+        <v>0</v>
+      </c>
+      <c r="CF146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CG146" s="14" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="CH146" s="13" t="n">
-        <v>454</v>
+        <v>0</v>
+      </c>
+      <c r="CH146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CI146" s="14" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="CJ146" s="15" t="n">
-        <v>880</v>
+        <v>0</v>
+      </c>
+      <c r="CJ146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CK146" s="14" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="CL146" s="20" t="n">
-        <v>3887</v>
+        <v>0</v>
+      </c>
+      <c r="CL146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CM146" s="14" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="CN146" s="13" t="n">
-        <v>568</v>
+        <v>0</v>
+      </c>
+      <c r="CN146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CO146" s="14" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="CP146" s="13" t="n">
-        <v>2055</v>
+        <v>0</v>
+      </c>
+      <c r="CP146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CQ146" s="14" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="CR146" s="20" t="n">
-        <v>2482</v>
+        <v>0</v>
+      </c>
+      <c r="CR146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CS146" s="14" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="CT146" s="13" t="n">
-        <v>436</v>
+        <v>0</v>
+      </c>
+      <c r="CT146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CU146" s="14" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="CV146" s="13" t="n">
-        <v>623</v>
+        <v>0</v>
+      </c>
+      <c r="CV146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CW146" s="14" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="CX146" s="13" t="n">
-        <v>702</v>
+        <v>0</v>
+      </c>
+      <c r="CX146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="CY146" s="14" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="CZ146" s="13" t="n">
-        <v>232</v>
+        <v>0</v>
+      </c>
+      <c r="CZ146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DA146" s="14" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="DB146" s="15" t="n">
-        <v>1157</v>
+        <v>0</v>
+      </c>
+      <c r="DB146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DC146" s="14" t="n">
-        <v>91</v>
-      </c>
-      <c r="DD146" s="13" t="n">
-        <v>2090</v>
+        <v>0</v>
+      </c>
+      <c r="DD146" s="14" t="n">
+        <v>-2</v>
       </c>
       <c r="DE146" s="14" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="DF146" s="15" t="n">
-        <v>574</v>
+        <v>0</v>
+      </c>
+      <c r="DF146" s="20" t="n">
+        <v>8674</v>
       </c>
       <c r="DG146" s="14" t="n">
-        <v>92.59999999999999</v>
+        <v>53.5</v>
       </c>
       <c r="DH146" s="1" t="inlineStr">
         <is>
-          <t>Google-Logo</t>
+          <t>ByteDance-Logo</t>
         </is>
       </c>
     </row>

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -44029,8 +44029,9 @@
     <hyperlink ref="B147" r:id="rId133"/>
     <hyperlink ref="B148" r:id="rId134"/>
     <hyperlink ref="B149" r:id="rId135"/>
-    <hyperlink ref="B152" r:id="rId136"/>
-    <hyperlink ref="B154" r:id="rId137"/>
+    <hyperlink ref="B151" r:id="rId136"/>
+    <hyperlink ref="B152" r:id="rId137"/>
+    <hyperlink ref="B154" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>3400</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="C13" s="17" t="n">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>3118</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>2907</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="C15" s="17" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D15" s="21" t="n">
         <v>2524</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="D16" s="22" t="n">
         <v>2689</v>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D17" s="21" t="n">
         <v>2599</v>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="D18" s="22" t="n">
         <v>2428</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>2759</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>2521</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D21" s="21" t="n">
         <v>2688</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D22" s="22" t="n">
         <v>2624</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>2334</v>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>2514</v>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D25" s="21" t="n">
         <v>2573</v>
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>2423</v>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="C27" s="17" t="n">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D27" s="24" t="n">
         <v>2232</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>2523</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="C29" s="17" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D29" s="24" t="n">
         <v>2374</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>2441</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="C31" s="17" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="D31" s="21" t="n">
         <v>2567</v>
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D32" s="25" t="n">
         <v>2050</v>
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="C33" s="17" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D33" s="24" t="n">
         <v>2221</v>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>2373</v>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="C35" s="17" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="D35" s="24" t="n">
         <v>2207</v>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="D36" s="26" t="n">
         <v>2227</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="C37" s="17" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D37" s="24" t="n">
         <v>2324</v>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D38" s="26" t="n">
         <v>2288</v>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="C39" s="17" t="n">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D39" s="21" t="n">
         <v>2677</v>
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>2423</v>
@@ -10787,7 +10787,7 @@
         </is>
       </c>
       <c r="C41" s="17" t="n">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D41" s="24" t="n">
         <v>2263</v>
@@ -11124,7 +11124,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D42" s="22" t="n">
         <v>2425</v>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="D43" s="24" t="n">
         <v>2396</v>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D44" s="26" t="n">
         <v>2146</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="D45" s="27" t="n">
         <v>2068</v>
@@ -12482,7 +12482,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D46" s="26" t="n">
         <v>2309</v>
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="C47" s="17" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D47" s="24" t="n">
         <v>2243</v>
@@ -13166,7 +13166,7 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D48" s="25" t="n">
         <v>2088</v>
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="C49" s="17" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D49" s="24" t="n">
         <v>2165</v>
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D50" s="26" t="n">
         <v>2319</v>
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="C51" s="17" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D51" s="27" t="n">
         <v>2072</v>
@@ -14524,7 +14524,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D52" s="22" t="n">
         <v>2505</v>
@@ -14861,7 +14861,7 @@
         </is>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D53" s="24" t="n">
         <v>2165</v>
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D54" s="25" t="n">
         <v>2014</v>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="C55" s="17" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D55" s="27" t="n">
         <v>1923</v>
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D56" s="26" t="n">
         <v>2144</v>
@@ -16219,7 +16219,7 @@
         </is>
       </c>
       <c r="C57" s="17" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D57" s="24" t="n">
         <v>2180</v>
@@ -16561,7 +16561,7 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D58" s="26" t="n">
         <v>2221</v>
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="C59" s="17" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D59" s="24" t="n">
         <v>2237</v>
@@ -17240,7 +17240,7 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D60" s="25" t="n">
         <v>2059</v>
@@ -17577,7 +17577,7 @@
         </is>
       </c>
       <c r="C61" s="17" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D61" s="27" t="n">
         <v>2026</v>
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="D62" s="25" t="n">
         <v>2012</v>
@@ -18251,7 +18251,7 @@
         </is>
       </c>
       <c r="C63" s="17" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D63" s="24" t="n">
         <v>2157</v>
@@ -18593,7 +18593,7 @@
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D64" s="26" t="n">
         <v>2147</v>
@@ -18935,7 +18935,7 @@
         </is>
       </c>
       <c r="C65" s="17" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D65" s="24" t="n">
         <v>2204</v>
@@ -19277,7 +19277,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D66" s="25" t="n">
         <v>2002</v>
@@ -19614,7 +19614,7 @@
         </is>
       </c>
       <c r="C67" s="17" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D67" s="24" t="n">
         <v>2317</v>
@@ -19956,7 +19956,7 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D68" s="25" t="n">
         <v>2090</v>
@@ -20293,7 +20293,7 @@
         </is>
       </c>
       <c r="C69" s="17" t="n">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="D69" s="24" t="n">
         <v>2143</v>
@@ -20635,7 +20635,7 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="D70" s="26" t="n">
         <v>2126</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="C71" s="17" t="n">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D71" s="24" t="n">
         <v>2175</v>
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D72" s="26" t="n">
         <v>2120</v>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="C73" s="17" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="D73" s="24" t="n">
         <v>2126</v>
@@ -21993,7 +21993,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D74" s="22" t="n">
         <v>2615</v>
@@ -22330,7 +22330,7 @@
         </is>
       </c>
       <c r="C75" s="17" t="n">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D75" s="24" t="n">
         <v>2206</v>
@@ -22672,7 +22672,7 @@
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D76" s="26" t="n">
         <v>2368</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="C77" s="17" t="n">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="D77" s="27" t="n">
         <v>2053</v>
@@ -23351,7 +23351,7 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D78" s="25" t="n">
         <v>1970</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="C79" s="17" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D79" s="27" t="n">
         <v>1933</v>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D80" s="25" t="n">
         <v>1989</v>
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="C81" s="17" t="n">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D81" s="21" t="n">
         <v>2691</v>
@@ -24704,7 +24704,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D82" s="26" t="n">
         <v>2183</v>
@@ -25046,7 +25046,7 @@
         </is>
       </c>
       <c r="C83" s="17" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D83" s="24" t="n">
         <v>2166</v>
@@ -25383,7 +25383,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="D84" s="25" t="n">
         <v>1914</v>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="C85" s="17" t="n">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="D85" s="27" t="n">
         <v>1963</v>
@@ -26062,7 +26062,7 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D86" s="25" t="n">
         <v>1795</v>
@@ -26399,7 +26399,7 @@
         </is>
       </c>
       <c r="C87" s="17" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D87" s="24" t="n">
         <v>2164</v>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="D88" s="26" t="n">
         <v>2190</v>
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="C89" s="17" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D89" s="27" t="n">
         <v>1787</v>
@@ -27415,7 +27415,7 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="D90" s="26" t="n">
         <v>2108</v>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="C91" s="17" t="n">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D91" s="27" t="n">
         <v>2002</v>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D92" s="25" t="n">
         <v>2073</v>
@@ -28426,7 +28426,7 @@
         </is>
       </c>
       <c r="C93" s="17" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D93" s="27" t="n">
         <v>1850</v>
@@ -28763,7 +28763,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="D94" s="25" t="n">
         <v>1949</v>
@@ -29105,7 +29105,7 @@
         </is>
       </c>
       <c r="C95" s="17" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D95" s="27" t="n">
         <v>1865</v>
@@ -29442,7 +29442,7 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D96" s="25" t="n">
         <v>1762</v>
@@ -29779,7 +29779,7 @@
         </is>
       </c>
       <c r="C97" s="17" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D97" s="27" t="n">
         <v>1835</v>
@@ -30121,7 +30121,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D98" s="25" t="n">
         <v>1681</v>
@@ -30458,7 +30458,7 @@
         </is>
       </c>
       <c r="C99" s="17" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D99" s="27" t="n">
         <v>1740</v>
@@ -30795,7 +30795,7 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D100" s="25" t="n">
         <v>1695</v>
@@ -31132,7 +31132,7 @@
         </is>
       </c>
       <c r="C101" s="17" t="n">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D101" s="27" t="n">
         <v>1854</v>
@@ -31469,7 +31469,7 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D102" s="25" t="n">
         <v>1995</v>
@@ -31811,7 +31811,7 @@
         </is>
       </c>
       <c r="C103" s="17" t="n">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D103" s="24" t="n">
         <v>2125</v>
@@ -32148,7 +32148,7 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D104" s="25" t="n">
         <v>1868</v>
@@ -32485,7 +32485,7 @@
         </is>
       </c>
       <c r="C105" s="17" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D105" s="27" t="n">
         <v>1734</v>
@@ -32822,7 +32822,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="D106" s="25" t="n">
         <v>1689</v>
@@ -33164,7 +33164,7 @@
         </is>
       </c>
       <c r="C107" s="17" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="D107" s="27" t="n">
         <v>1821</v>
@@ -33501,7 +33501,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D108" s="25" t="n">
         <v>1972</v>
@@ -33838,7 +33838,7 @@
         </is>
       </c>
       <c r="C109" s="17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D109" s="27" t="n">
         <v>1632</v>
@@ -34175,7 +34175,7 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="D110" s="25" t="n">
         <v>1870</v>
@@ -34517,7 +34517,7 @@
         </is>
       </c>
       <c r="C111" s="17" t="n">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D111" s="18" t="n">
         <v>2821</v>
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="D112" s="11" t="n">
         <v>2853</v>
@@ -35201,7 +35201,7 @@
         </is>
       </c>
       <c r="C113" s="17" t="n">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="D113" s="27" t="n">
         <v>2063</v>
@@ -35543,7 +35543,7 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D114" s="25" t="n">
         <v>2013</v>
@@ -35885,7 +35885,7 @@
         </is>
       </c>
       <c r="C115" s="17" t="n">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D115" s="27" t="n">
         <v>1518</v>
@@ -36227,7 +36227,7 @@
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D116" s="25" t="n">
         <v>1727</v>
@@ -36564,7 +36564,7 @@
         </is>
       </c>
       <c r="C117" s="17" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D117" s="27" t="n">
         <v>1781</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D118" s="25" t="n">
         <v>1739</v>
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="C119" s="17" t="n">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="D119" s="27" t="n">
         <v>1857</v>
@@ -37580,7 +37580,7 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D120" s="25" t="n">
         <v>1773</v>
@@ -37918,23 +37918,23 @@
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>lukeiscoding</t>
+          <t>Andy0315</t>
         </is>
       </c>
       <c r="C121" s="17" t="n">
-        <v>1047</v>
+        <v>191</v>
       </c>
       <c r="D121" s="27" t="n">
-        <v>1937</v>
+        <v>1500</v>
       </c>
       <c r="E121" s="12" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="F121" s="19" t="n">
-        <v>-1</v>
+        <v>36.1</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>4526</v>
       </c>
       <c r="G121" s="19" t="n">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="H121" s="19" t="n">
         <v>-1</v>
@@ -37942,11 +37942,11 @@
       <c r="I121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J121" s="20" t="n">
-        <v>3941</v>
+      <c r="J121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="K121" s="19" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="L121" s="19" t="n">
         <v>-1</v>
@@ -37954,11 +37954,11 @@
       <c r="M121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N121" s="15" t="n">
-        <v>4534</v>
+      <c r="N121" s="23" t="n">
+        <v>12761</v>
       </c>
       <c r="O121" s="19" t="n">
-        <v>72.59999999999999</v>
+        <v>22</v>
       </c>
       <c r="P121" s="19" t="n">
         <v>-1</v>
@@ -37966,17 +37966,17 @@
       <c r="Q121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R121" s="20" t="n">
-        <v>3394</v>
+      <c r="R121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>71</v>
-      </c>
-      <c r="T121" s="20" t="n">
-        <v>1034</v>
+        <v>0</v>
+      </c>
+      <c r="T121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U121" s="19" t="n">
-        <v>84.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="V121" s="19" t="n">
         <v>-1</v>
@@ -38002,17 +38002,17 @@
       <c r="AC121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AD121" s="15" t="n">
-        <v>894</v>
+      <c r="AD121" s="20" t="n">
+        <v>7949</v>
       </c>
       <c r="AE121" s="19" t="n">
-        <v>91</v>
-      </c>
-      <c r="AF121" s="19" t="n">
-        <v>-1</v>
+        <v>54.5</v>
+      </c>
+      <c r="AF121" s="20" t="n">
+        <v>5348</v>
       </c>
       <c r="AG121" s="19" t="n">
-        <v>0</v>
+        <v>67.7</v>
       </c>
       <c r="AH121" s="19" t="n">
         <v>-1</v>
@@ -38020,17 +38020,17 @@
       <c r="AI121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ121" s="20" t="n">
-        <v>1156</v>
+      <c r="AJ121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AK121" s="19" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="AL121" s="15" t="n">
-        <v>2355</v>
+        <v>0</v>
+      </c>
+      <c r="AL121" s="20" t="n">
+        <v>9462</v>
       </c>
       <c r="AM121" s="19" t="n">
-        <v>86.7</v>
+        <v>56.6</v>
       </c>
       <c r="AN121" s="19" t="n">
         <v>-1</v>
@@ -38038,29 +38038,29 @@
       <c r="AO121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP121" s="20" t="n">
-        <v>3031</v>
+      <c r="AP121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ121" s="19" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="AR121" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AR121" s="20" t="n">
+        <v>3824</v>
       </c>
       <c r="AS121" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT121" s="19" t="n">
-        <v>-1</v>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AT121" s="23" t="n">
+        <v>15746</v>
       </c>
       <c r="AU121" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV121" s="15" t="n">
-        <v>487</v>
+        <v>27.8</v>
+      </c>
+      <c r="AV121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AW121" s="19" t="n">
-        <v>93.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX121" s="19" t="n">
         <v>-1</v>
@@ -38068,190 +38068,185 @@
       <c r="AY121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AZ121" s="19" t="n">
-        <v>-1</v>
+      <c r="AZ121" s="23" t="n">
+        <v>6290</v>
       </c>
       <c r="BA121" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB121" s="15" t="n">
-        <v>511</v>
+        <v>58.3</v>
+      </c>
+      <c r="BB121" s="23" t="n">
+        <v>8443</v>
       </c>
       <c r="BC121" s="19" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="BD121" s="20" t="n">
-        <v>2241</v>
+        <v>50.3</v>
+      </c>
+      <c r="BD121" s="23" t="n">
+        <v>9197</v>
       </c>
       <c r="BE121" s="19" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="BF121" s="20" t="n">
-        <v>1812</v>
+        <v>43.6</v>
+      </c>
+      <c r="BF121" s="23" t="n">
+        <v>13804</v>
       </c>
       <c r="BG121" s="19" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="BH121" s="20" t="n">
-        <v>975</v>
+        <v>18.9</v>
+      </c>
+      <c r="BH121" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI121" s="19" t="n">
-        <v>84</v>
-      </c>
-      <c r="BJ121" s="15" t="n">
-        <v>380</v>
+        <v>0</v>
+      </c>
+      <c r="BJ121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BK121" s="19" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="BL121" s="20" t="n">
-        <v>1226</v>
+        <v>0</v>
+      </c>
+      <c r="BL121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BM121" s="19" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="BN121" s="20" t="n">
-        <v>3111</v>
+        <v>0</v>
+      </c>
+      <c r="BN121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BO121" s="19" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="BP121" s="15" t="n">
-        <v>1129</v>
+        <v>0</v>
+      </c>
+      <c r="BP121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BQ121" s="19" t="n">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BS121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT121" s="15" t="n">
-        <v>1517</v>
+      <c r="BT121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BU121" s="19" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="BV121" s="15" t="n">
-        <v>1164</v>
+        <v>0</v>
+      </c>
+      <c r="BV121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="BW121" s="19" t="n">
-        <v>88.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="BY121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BZ121" s="15" t="n">
-        <v>1097</v>
+      <c r="BZ121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CA121" s="19" t="n">
-        <v>90</v>
-      </c>
-      <c r="CB121" s="15" t="n">
-        <v>726</v>
+        <v>0</v>
+      </c>
+      <c r="CB121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CC121" s="19" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="CD121" s="20" t="n">
-        <v>7483</v>
+        <v>0</v>
+      </c>
+      <c r="CD121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CE121" s="19" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="CF121" s="15" t="n">
-        <v>1040</v>
+        <v>0</v>
+      </c>
+      <c r="CF121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CG121" s="19" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="CH121" s="15" t="n">
-        <v>561</v>
+        <v>0</v>
+      </c>
+      <c r="CH121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CI121" s="19" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="CJ121" s="20" t="n">
-        <v>11611</v>
+        <v>0</v>
+      </c>
+      <c r="CJ121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CK121" s="19" t="n">
-        <v>47</v>
-      </c>
-      <c r="CL121" s="14" t="n">
-        <v>2574</v>
+        <v>0</v>
+      </c>
+      <c r="CL121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="CM121" s="19" t="n">
-        <v>91.3</v>
+        <v>0</v>
       </c>
       <c r="CN121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CO121" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CP121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ121" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CR121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CS121" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CT121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CU121" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CV121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CW121" s="19" t="n">
         <v>0</v>
       </c>
       <c r="CX121" s="19" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CY121" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ121" s="20" t="n">
-        <v>8174</v>
+      <c r="CZ121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DA121" s="19" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="DB121" s="20" t="n">
-        <v>2389</v>
+        <v>0</v>
+      </c>
+      <c r="DB121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DC121" s="19" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="DD121" s="14" t="n">
-        <v>502</v>
+        <v>0</v>
+      </c>
+      <c r="DD121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DE121" s="19" t="n">
-        <v>85</v>
-      </c>
-      <c r="DF121" s="14" t="n">
-        <v>275</v>
+        <v>0</v>
+      </c>
+      <c r="DF121" s="19" t="n">
+        <v>-2</v>
       </c>
       <c r="DG121" s="19" t="n">
-        <v>92</v>
-      </c>
-      <c r="DH121" s="1" t="inlineStr">
-        <is>
-          <t>Walmart-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -38260,23 +38255,23 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Hogwartsss</t>
+          <t>lukeiscoding</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>615</v>
+        <v>1048</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>1904</v>
+        <v>1937</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="F122" s="20" t="n">
-        <v>6608</v>
+        <v>34.6</v>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H122" s="13" t="n">
         <v>-1</v>
@@ -38284,41 +38279,41 @@
       <c r="I122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J122" s="13" t="n">
-        <v>-1</v>
+      <c r="J122" s="20" t="n">
+        <v>3941</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="23" t="n">
-        <v>8964</v>
+        <v>69.2</v>
+      </c>
+      <c r="L122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="N122" s="20" t="n">
-        <v>6213</v>
+        <v>0</v>
+      </c>
+      <c r="N122" s="15" t="n">
+        <v>4534</v>
       </c>
       <c r="O122" s="13" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="P122" s="20" t="n">
-        <v>5504</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="P122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Q122" s="13" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="R122" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="R122" s="20" t="n">
+        <v>3394</v>
       </c>
       <c r="S122" s="13" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="T122" s="20" t="n">
-        <v>2800</v>
+        <v>1034</v>
       </c>
       <c r="U122" s="13" t="n">
-        <v>76.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="V122" s="13" t="n">
         <v>-1</v>
@@ -38326,11 +38321,11 @@
       <c r="W122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="20" t="n">
-        <v>2625</v>
+      <c r="X122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Y122" s="13" t="n">
-        <v>75.7</v>
+        <v>0</v>
       </c>
       <c r="Z122" s="13" t="n">
         <v>-1</v>
@@ -38338,17 +38333,17 @@
       <c r="AA122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB122" s="20" t="n">
-        <v>1138</v>
+      <c r="AB122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AC122" s="13" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="AD122" s="20" t="n">
-        <v>2922</v>
+        <v>0</v>
+      </c>
+      <c r="AD122" s="15" t="n">
+        <v>894</v>
       </c>
       <c r="AE122" s="13" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AF122" s="13" t="n">
         <v>-1</v>
@@ -38362,107 +38357,107 @@
       <c r="AI122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ122" s="13" t="n">
-        <v>-1</v>
+      <c r="AJ122" s="20" t="n">
+        <v>1156</v>
       </c>
       <c r="AK122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL122" s="20" t="n">
-        <v>6235</v>
+        <v>84.8</v>
+      </c>
+      <c r="AL122" s="15" t="n">
+        <v>2355</v>
       </c>
       <c r="AM122" s="13" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN122" s="23" t="n">
-        <v>8847</v>
+        <v>86.7</v>
+      </c>
+      <c r="AN122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AO122" s="13" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="AP122" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AP122" s="20" t="n">
+        <v>3031</v>
       </c>
       <c r="AQ122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR122" s="23" t="n">
-        <v>6516</v>
+        <v>77.5</v>
+      </c>
+      <c r="AR122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AS122" s="13" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="AT122" s="20" t="n">
-        <v>2403</v>
+        <v>0</v>
+      </c>
+      <c r="AT122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AU122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV122" s="15" t="n">
+        <v>487</v>
+      </c>
+      <c r="AW122" s="13" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AX122" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AY122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ122" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" s="15" t="n">
+        <v>511</v>
+      </c>
+      <c r="BC122" s="13" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BD122" s="20" t="n">
+        <v>2241</v>
+      </c>
+      <c r="BE122" s="13" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="BF122" s="20" t="n">
+        <v>1812</v>
+      </c>
+      <c r="BG122" s="13" t="n">
         <v>81.3</v>
       </c>
-      <c r="AV122" s="20" t="n">
-        <v>6941</v>
-      </c>
-      <c r="AW122" s="13" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AX122" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AY122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ122" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BA122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB122" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD122" s="23" t="n">
-        <v>4041</v>
-      </c>
-      <c r="BE122" s="13" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="BF122" s="20" t="n">
-        <v>2405</v>
-      </c>
-      <c r="BG122" s="13" t="n">
-        <v>78.5</v>
-      </c>
       <c r="BH122" s="20" t="n">
-        <v>1128</v>
+        <v>975</v>
       </c>
       <c r="BI122" s="13" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="BJ122" s="13" t="n">
-        <v>-1</v>
+        <v>84</v>
+      </c>
+      <c r="BJ122" s="15" t="n">
+        <v>380</v>
       </c>
       <c r="BK122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL122" s="13" t="n">
-        <v>-1</v>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BL122" s="20" t="n">
+        <v>1226</v>
       </c>
       <c r="BM122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN122" s="13" t="n">
-        <v>-1</v>
+        <v>83.2</v>
+      </c>
+      <c r="BN122" s="20" t="n">
+        <v>3111</v>
       </c>
       <c r="BO122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP122" s="13" t="n">
-        <v>-1</v>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BP122" s="15" t="n">
+        <v>1129</v>
       </c>
       <c r="BQ122" s="13" t="n">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="BR122" s="13" t="n">
         <v>-1</v>
@@ -38470,129 +38465,129 @@
       <c r="BS122" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BT122" s="20" t="n">
-        <v>2742</v>
+      <c r="BT122" s="15" t="n">
+        <v>1517</v>
       </c>
       <c r="BU122" s="13" t="n">
-        <v>74.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="BV122" s="15" t="n">
-        <v>1127</v>
+        <v>1164</v>
       </c>
       <c r="BW122" s="13" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="BX122" s="20" t="n">
-        <v>3416</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BX122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BY122" s="13" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="BZ122" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BZ122" s="15" t="n">
+        <v>1097</v>
       </c>
       <c r="CA122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB122" s="20" t="n">
-        <v>1412</v>
+        <v>90</v>
+      </c>
+      <c r="CB122" s="15" t="n">
+        <v>726</v>
       </c>
       <c r="CC122" s="13" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="CD122" s="13" t="n">
-        <v>-1</v>
+        <v>90.5</v>
+      </c>
+      <c r="CD122" s="20" t="n">
+        <v>7483</v>
       </c>
       <c r="CE122" s="13" t="n">
-        <v>0</v>
+        <v>60.8</v>
       </c>
       <c r="CF122" s="15" t="n">
-        <v>306</v>
+        <v>1040</v>
       </c>
       <c r="CG122" s="13" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="CH122" s="13" t="n">
-        <v>-1</v>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="CH122" s="15" t="n">
+        <v>561</v>
       </c>
       <c r="CI122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ122" s="14" t="n">
-        <v>214</v>
+        <v>92.7</v>
+      </c>
+      <c r="CJ122" s="20" t="n">
+        <v>11611</v>
       </c>
       <c r="CK122" s="13" t="n">
-        <v>99.2</v>
+        <v>47</v>
       </c>
       <c r="CL122" s="14" t="n">
-        <v>556</v>
+        <v>2574</v>
       </c>
       <c r="CM122" s="13" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="CN122" s="20" t="n">
-        <v>8273</v>
+        <v>91.3</v>
+      </c>
+      <c r="CN122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CO122" s="13" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="CP122" s="20" t="n">
-        <v>6412</v>
+        <v>0</v>
+      </c>
+      <c r="CP122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ122" s="13" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="CR122" s="15" t="n">
-        <v>518</v>
+        <v>0</v>
+      </c>
+      <c r="CR122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CS122" s="13" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="CT122" s="20" t="n">
-        <v>1140</v>
+        <v>0</v>
+      </c>
+      <c r="CT122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CU122" s="13" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="CV122" s="20" t="n">
-        <v>2762</v>
+        <v>0</v>
+      </c>
+      <c r="CV122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CW122" s="13" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="CX122" s="14" t="n">
-        <v>366</v>
+        <v>0</v>
+      </c>
+      <c r="CX122" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CY122" s="13" t="n">
-        <v>98.8</v>
+        <v>0</v>
       </c>
       <c r="CZ122" s="20" t="n">
-        <v>6610</v>
+        <v>8174</v>
       </c>
       <c r="DA122" s="13" t="n">
-        <v>66</v>
+        <v>60.4</v>
       </c>
       <c r="DB122" s="20" t="n">
-        <v>2096</v>
+        <v>2389</v>
       </c>
       <c r="DC122" s="13" t="n">
-        <v>83.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="DD122" s="14" t="n">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="DE122" s="13" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="DF122" s="13" t="n">
-        <v>-1</v>
+        <v>85</v>
+      </c>
+      <c r="DF122" s="14" t="n">
+        <v>275</v>
       </c>
       <c r="DG122" s="13" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="DH122" s="1" t="inlineStr">
         <is>
-          <t>Alibaba-Logo</t>
+          <t>Walmart-Logo</t>
         </is>
       </c>
     </row>
@@ -38602,29 +38597,29 @@
       </c>
       <c r="B123" s="16" t="inlineStr">
         <is>
-          <t>fantasy1979</t>
+          <t>Hogwartsss</t>
         </is>
       </c>
       <c r="C123" s="17" t="n">
-        <v>291</v>
+        <v>616</v>
       </c>
       <c r="D123" s="27" t="n">
-        <v>1850</v>
+        <v>1904</v>
       </c>
       <c r="E123" s="12" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="F123" s="23" t="n">
-        <v>15920</v>
+        <v>32</v>
+      </c>
+      <c r="F123" s="20" t="n">
+        <v>6608</v>
       </c>
       <c r="G123" s="19" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H123" s="23" t="n">
-        <v>9693</v>
+        <v>64</v>
+      </c>
+      <c r="H123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="I123" s="19" t="n">
-        <v>38.9</v>
+        <v>0</v>
       </c>
       <c r="J123" s="19" t="n">
         <v>-1</v>
@@ -38632,23 +38627,23 @@
       <c r="K123" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L123" s="20" t="n">
-        <v>3834</v>
+      <c r="L123" s="23" t="n">
+        <v>8964</v>
       </c>
       <c r="M123" s="19" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N123" s="19" t="n">
-        <v>-1</v>
+        <v>44.2</v>
+      </c>
+      <c r="N123" s="20" t="n">
+        <v>6213</v>
       </c>
       <c r="O123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="19" t="n">
-        <v>-1</v>
+        <v>59.3</v>
+      </c>
+      <c r="P123" s="20" t="n">
+        <v>5504</v>
       </c>
       <c r="Q123" s="19" t="n">
-        <v>0</v>
+        <v>53.9</v>
       </c>
       <c r="R123" s="19" t="n">
         <v>-1</v>
@@ -38656,23 +38651,23 @@
       <c r="S123" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="19" t="n">
-        <v>-1</v>
+      <c r="T123" s="20" t="n">
+        <v>2800</v>
       </c>
       <c r="U123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="23" t="n">
-        <v>16029</v>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="V123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W123" s="19" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="X123" s="20" t="n">
-        <v>7247</v>
+        <v>2625</v>
       </c>
       <c r="Y123" s="19" t="n">
-        <v>50.5</v>
+        <v>75.7</v>
       </c>
       <c r="Z123" s="19" t="n">
         <v>-1</v>
@@ -38680,23 +38675,23 @@
       <c r="AA123" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AB123" s="19" t="n">
-        <v>-1</v>
+      <c r="AB123" s="20" t="n">
+        <v>1138</v>
       </c>
       <c r="AC123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="19" t="n">
-        <v>-1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AD123" s="20" t="n">
+        <v>2922</v>
       </c>
       <c r="AE123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="20" t="n">
-        <v>6527</v>
+        <v>77</v>
+      </c>
+      <c r="AF123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AG123" s="19" t="n">
-        <v>62.8</v>
+        <v>0</v>
       </c>
       <c r="AH123" s="19" t="n">
         <v>-1</v>
@@ -38704,233 +38699,238 @@
       <c r="AI123" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ123" s="20" t="n">
-        <v>3070</v>
+      <c r="AJ123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AK123" s="19" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="AL123" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AL123" s="20" t="n">
+        <v>6235</v>
       </c>
       <c r="AM123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN123" s="19" t="n">
-        <v>-1</v>
+        <v>68</v>
+      </c>
+      <c r="AN123" s="23" t="n">
+        <v>8847</v>
       </c>
       <c r="AO123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP123" s="20" t="n">
-        <v>2847</v>
+        <v>39.2</v>
+      </c>
+      <c r="AP123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ123" s="19" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="AR123" s="20" t="n">
-        <v>1069</v>
+        <v>0</v>
+      </c>
+      <c r="AR123" s="23" t="n">
+        <v>6516</v>
       </c>
       <c r="AS123" s="19" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="AT123" s="19" t="n">
-        <v>-1</v>
+        <v>55.9</v>
+      </c>
+      <c r="AT123" s="20" t="n">
+        <v>2403</v>
       </c>
       <c r="AU123" s="19" t="n">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="AV123" s="20" t="n">
-        <v>6427</v>
+        <v>6941</v>
       </c>
       <c r="AW123" s="19" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AX123" s="20" t="n">
-        <v>1911</v>
+        <v>62.5</v>
+      </c>
+      <c r="AX123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY123" s="19" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AZ123" s="15" t="n">
-        <v>369</v>
+        <v>0</v>
+      </c>
+      <c r="AZ123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BA123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" s="23" t="n">
+        <v>4041</v>
+      </c>
+      <c r="BE123" s="19" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="BF123" s="20" t="n">
+        <v>2405</v>
+      </c>
+      <c r="BG123" s="19" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="BH123" s="20" t="n">
+        <v>1128</v>
+      </c>
+      <c r="BI123" s="19" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="BJ123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BS123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT123" s="20" t="n">
+        <v>2742</v>
+      </c>
+      <c r="BU123" s="19" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BV123" s="15" t="n">
+        <v>1127</v>
+      </c>
+      <c r="BW123" s="19" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="BX123" s="20" t="n">
+        <v>3416</v>
+      </c>
+      <c r="BY123" s="19" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BZ123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB123" s="20" t="n">
+        <v>1412</v>
+      </c>
+      <c r="CC123" s="19" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="CD123" s="19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CE123" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" s="15" t="n">
+        <v>306</v>
+      </c>
+      <c r="CG123" s="19" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="BB123" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD123" s="14" t="n">
-        <v>193</v>
-      </c>
-      <c r="BE123" s="19" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="BF123" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH123" s="15" t="n">
-        <v>542</v>
-      </c>
-      <c r="BI123" s="19" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="BJ123" s="23" t="n">
-        <v>6837</v>
-      </c>
-      <c r="BK123" s="19" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="BL123" s="23" t="n">
-        <v>13842</v>
-      </c>
-      <c r="BM123" s="19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN123" s="23" t="n">
-        <v>15348</v>
-      </c>
-      <c r="BO123" s="19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BP123" s="23" t="n">
-        <v>9941</v>
-      </c>
-      <c r="BQ123" s="19" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="BR123" s="20" t="n">
-        <v>3387</v>
-      </c>
-      <c r="BS123" s="19" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="BT123" s="20" t="n">
-        <v>2711</v>
-      </c>
-      <c r="BU123" s="19" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="BV123" s="15" t="n">
-        <v>2424</v>
-      </c>
-      <c r="BW123" s="19" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="BX123" s="23" t="n">
-        <v>10075</v>
-      </c>
-      <c r="BY123" s="19" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="BZ123" s="20" t="n">
-        <v>6072</v>
-      </c>
-      <c r="CA123" s="19" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="CB123" s="20" t="n">
-        <v>3632</v>
-      </c>
-      <c r="CC123" s="19" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="CD123" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CE123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF123" s="20" t="n">
-        <v>2977</v>
-      </c>
-      <c r="CG123" s="19" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="CH123" s="20" t="n">
-        <v>4707</v>
+      <c r="CH123" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CI123" s="19" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="CJ123" s="20" t="n">
-        <v>2377</v>
+        <v>0</v>
+      </c>
+      <c r="CJ123" s="14" t="n">
+        <v>214</v>
       </c>
       <c r="CK123" s="19" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="CL123" s="19" t="n">
-        <v>-2</v>
+        <v>99.2</v>
+      </c>
+      <c r="CL123" s="14" t="n">
+        <v>556</v>
       </c>
       <c r="CM123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN123" s="19" t="n">
-        <v>-2</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="CN123" s="20" t="n">
+        <v>8273</v>
       </c>
       <c r="CO123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP123" s="19" t="n">
-        <v>-2</v>
+        <v>63.2</v>
+      </c>
+      <c r="CP123" s="20" t="n">
+        <v>6412</v>
       </c>
       <c r="CQ123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR123" s="19" t="n">
-        <v>-2</v>
+        <v>68.7</v>
+      </c>
+      <c r="CR123" s="15" t="n">
+        <v>518</v>
       </c>
       <c r="CS123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT123" s="19" t="n">
-        <v>-2</v>
+        <v>93.3</v>
+      </c>
+      <c r="CT123" s="20" t="n">
+        <v>1140</v>
       </c>
       <c r="CU123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV123" s="19" t="n">
-        <v>-2</v>
+        <v>86.3</v>
+      </c>
+      <c r="CV123" s="20" t="n">
+        <v>2762</v>
       </c>
       <c r="CW123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX123" s="19" t="n">
-        <v>-2</v>
+        <v>79.7</v>
+      </c>
+      <c r="CX123" s="14" t="n">
+        <v>366</v>
       </c>
       <c r="CY123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ123" s="19" t="n">
-        <v>-2</v>
+        <v>98.8</v>
+      </c>
+      <c r="CZ123" s="20" t="n">
+        <v>6610</v>
       </c>
       <c r="DA123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB123" s="19" t="n">
-        <v>-2</v>
+        <v>66</v>
+      </c>
+      <c r="DB123" s="20" t="n">
+        <v>2096</v>
       </c>
       <c r="DC123" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD123" s="19" t="n">
-        <v>-2</v>
+        <v>83.5</v>
+      </c>
+      <c r="DD123" s="14" t="n">
+        <v>452</v>
       </c>
       <c r="DE123" s="19" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="DF123" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DG123" s="19" t="n">
         <v>0</v>
+      </c>
+      <c r="DH123" s="1" t="inlineStr">
+        <is>
+          <t>Alibaba-Logo</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -38939,29 +38939,29 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cyzh</t>
+          <t>fantasy1979</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>1386</v>
+        <v>292</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>1867</v>
+        <v>1850</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>4.2</v>
+        <v>30.6</v>
       </c>
       <c r="F124" s="23" t="n">
-        <v>19525</v>
+        <v>15920</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H124" s="13" t="n">
-        <v>-1</v>
+        <v>22.4</v>
+      </c>
+      <c r="H124" s="23" t="n">
+        <v>9693</v>
       </c>
       <c r="I124" s="13" t="n">
-        <v>0</v>
+        <v>38.9</v>
       </c>
       <c r="J124" s="13" t="n">
         <v>-1</v>
@@ -38969,11 +38969,11 @@
       <c r="K124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L124" s="23" t="n">
-        <v>16526</v>
+      <c r="L124" s="20" t="n">
+        <v>3834</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N124" s="13" t="n">
         <v>-1</v>
@@ -38981,11 +38981,11 @@
       <c r="O124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P124" s="20" t="n">
-        <v>5611</v>
+      <c r="P124" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Q124" s="13" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="R124" s="13" t="n">
         <v>-1</v>
@@ -38999,17 +38999,17 @@
       <c r="U124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="13" t="n">
-        <v>-1</v>
+      <c r="V124" s="23" t="n">
+        <v>16029</v>
       </c>
       <c r="W124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" s="13" t="n">
-        <v>-1</v>
+        <v>12.2</v>
+      </c>
+      <c r="X124" s="20" t="n">
+        <v>7247</v>
       </c>
       <c r="Y124" s="13" t="n">
-        <v>0</v>
+        <v>50.5</v>
       </c>
       <c r="Z124" s="13" t="n">
         <v>-1</v>
@@ -39029,11 +39029,11 @@
       <c r="AE124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AF124" s="13" t="n">
-        <v>-1</v>
+      <c r="AF124" s="20" t="n">
+        <v>6527</v>
       </c>
       <c r="AG124" s="13" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="AH124" s="13" t="n">
         <v>-1</v>
@@ -39042,10 +39042,10 @@
         <v>0</v>
       </c>
       <c r="AJ124" s="20" t="n">
-        <v>9944</v>
+        <v>3070</v>
       </c>
       <c r="AK124" s="13" t="n">
-        <v>45.6</v>
+        <v>76.3</v>
       </c>
       <c r="AL124" s="13" t="n">
         <v>-1</v>
@@ -39053,23 +39053,23 @@
       <c r="AM124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AN124" s="23" t="n">
-        <v>14016</v>
+      <c r="AN124" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AO124" s="13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AP124" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AP124" s="20" t="n">
+        <v>2847</v>
       </c>
       <c r="AQ124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR124" s="23" t="n">
-        <v>14411</v>
+        <v>78.3</v>
+      </c>
+      <c r="AR124" s="20" t="n">
+        <v>1069</v>
       </c>
       <c r="AS124" s="13" t="n">
-        <v>20.6</v>
+        <v>85.2</v>
       </c>
       <c r="AT124" s="13" t="n">
         <v>-1</v>
@@ -39077,23 +39077,23 @@
       <c r="AU124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AV124" s="23" t="n">
-        <v>18839</v>
+      <c r="AV124" s="20" t="n">
+        <v>6427</v>
       </c>
       <c r="AW124" s="13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AX124" s="13" t="n">
-        <v>-1</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AX124" s="20" t="n">
+        <v>1911</v>
       </c>
       <c r="AY124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ124" s="20" t="n">
-        <v>3126</v>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AZ124" s="15" t="n">
+        <v>369</v>
       </c>
       <c r="BA124" s="13" t="n">
-        <v>76.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="BB124" s="13" t="n">
         <v>-1</v>
@@ -39101,178 +39101,173 @@
       <c r="BC124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BD124" s="20" t="n">
-        <v>2958</v>
+      <c r="BD124" s="14" t="n">
+        <v>193</v>
       </c>
       <c r="BE124" s="13" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="BF124" s="15" t="n">
-        <v>845</v>
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BF124" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BG124" s="13" t="n">
-        <v>91</v>
-      </c>
-      <c r="BH124" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BH124" s="15" t="n">
+        <v>542</v>
       </c>
       <c r="BI124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ124" s="14" t="n">
-        <v>211</v>
+        <v>91.7</v>
+      </c>
+      <c r="BJ124" s="23" t="n">
+        <v>6837</v>
       </c>
       <c r="BK124" s="13" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="BL124" s="13" t="n">
-        <v>-1</v>
+        <v>47.6</v>
+      </c>
+      <c r="BL124" s="23" t="n">
+        <v>13842</v>
       </c>
       <c r="BM124" s="13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN124" s="23" t="n">
-        <v>5468</v>
+        <v>15348</v>
       </c>
       <c r="BO124" s="13" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="BP124" s="15" t="n">
-        <v>1494</v>
+        <v>6.7</v>
+      </c>
+      <c r="BP124" s="23" t="n">
+        <v>9941</v>
       </c>
       <c r="BQ124" s="13" t="n">
-        <v>87</v>
-      </c>
-      <c r="BR124" s="14" t="n">
-        <v>131</v>
+        <v>31.7</v>
+      </c>
+      <c r="BR124" s="20" t="n">
+        <v>3387</v>
       </c>
       <c r="BS124" s="13" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="BT124" s="13" t="n">
-        <v>-1</v>
+        <v>72.5</v>
+      </c>
+      <c r="BT124" s="20" t="n">
+        <v>2711</v>
       </c>
       <c r="BU124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV124" s="13" t="n">
-        <v>-1</v>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BV124" s="15" t="n">
+        <v>2424</v>
       </c>
       <c r="BW124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX124" s="13" t="n">
-        <v>-1</v>
+        <v>81.8</v>
+      </c>
+      <c r="BX124" s="23" t="n">
+        <v>10075</v>
       </c>
       <c r="BY124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ124" s="13" t="n">
-        <v>-1</v>
+        <v>38.1</v>
+      </c>
+      <c r="BZ124" s="20" t="n">
+        <v>6072</v>
       </c>
       <c r="CA124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB124" s="13" t="n">
-        <v>-1</v>
+        <v>62.3</v>
+      </c>
+      <c r="CB124" s="20" t="n">
+        <v>3632</v>
       </c>
       <c r="CC124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD124" s="20" t="n">
-        <v>11707</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="CD124" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CE124" s="13" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="CF124" s="15" t="n">
-        <v>1797</v>
+        <v>0</v>
+      </c>
+      <c r="CF124" s="20" t="n">
+        <v>2977</v>
       </c>
       <c r="CG124" s="13" t="n">
-        <v>85.7</v>
+        <v>74.5</v>
       </c>
       <c r="CH124" s="20" t="n">
-        <v>1689</v>
+        <v>4707</v>
       </c>
       <c r="CI124" s="13" t="n">
-        <v>83</v>
-      </c>
-      <c r="CJ124" s="13" t="n">
-        <v>-1</v>
+        <v>70.5</v>
+      </c>
+      <c r="CJ124" s="20" t="n">
+        <v>2377</v>
       </c>
       <c r="CK124" s="13" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="CL124" s="13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CM124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CN124" s="23" t="n">
-        <v>11018</v>
+      <c r="CN124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="CO124" s="13" t="n">
-        <v>49.3</v>
+        <v>0</v>
       </c>
       <c r="CP124" s="13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="CQ124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CR124" s="15" t="n">
-        <v>229</v>
+      <c r="CR124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="CS124" s="13" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="CT124" s="15" t="n">
-        <v>662</v>
+        <v>0</v>
+      </c>
+      <c r="CT124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="CU124" s="13" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="CV124" s="20" t="n">
-        <v>2790</v>
+        <v>0</v>
+      </c>
+      <c r="CV124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="CW124" s="13" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="CX124" s="14" t="n">
-        <v>407</v>
+        <v>0</v>
+      </c>
+      <c r="CX124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="CY124" s="13" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="CZ124" s="15" t="n">
-        <v>98</v>
+        <v>0</v>
+      </c>
+      <c r="CZ124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="DA124" s="13" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="DB124" s="15" t="n">
-        <v>227</v>
+        <v>0</v>
+      </c>
+      <c r="DB124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="DC124" s="13" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="DD124" s="14" t="n">
-        <v>80</v>
+        <v>0</v>
+      </c>
+      <c r="DD124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="DE124" s="13" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="DF124" s="20" t="n">
-        <v>1523</v>
+        <v>0</v>
+      </c>
+      <c r="DF124" s="13" t="n">
+        <v>-2</v>
       </c>
       <c r="DG124" s="13" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="DH124" s="1" t="inlineStr">
-        <is>
-          <t>Baidu-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -39281,23 +39276,23 @@
       </c>
       <c r="B125" s="16" t="inlineStr">
         <is>
-          <t>roy_1127</t>
+          <t>cyzh</t>
         </is>
       </c>
       <c r="C125" s="17" t="n">
-        <v>1672</v>
+        <v>1387</v>
       </c>
       <c r="D125" s="27" t="n">
-        <v>1813</v>
+        <v>1867</v>
       </c>
       <c r="E125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="19" t="n">
-        <v>-1</v>
+        <v>4.2</v>
+      </c>
+      <c r="F125" s="23" t="n">
+        <v>19525</v>
       </c>
       <c r="G125" s="19" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H125" s="19" t="n">
         <v>-1</v>
@@ -39311,23 +39306,23 @@
       <c r="K125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L125" s="19" t="n">
-        <v>-1</v>
+      <c r="L125" s="23" t="n">
+        <v>16526</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" s="15" t="n">
-        <v>4024</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="O125" s="19" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="P125" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="P125" s="20" t="n">
+        <v>5611</v>
       </c>
       <c r="Q125" s="19" t="n">
-        <v>0</v>
+        <v>53.2</v>
       </c>
       <c r="R125" s="19" t="n">
         <v>-1</v>
@@ -39335,23 +39330,23 @@
       <c r="S125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="T125" s="20" t="n">
-        <v>4374</v>
+      <c r="T125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="U125" s="19" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="V125" s="20" t="n">
-        <v>5310</v>
+        <v>0</v>
+      </c>
+      <c r="V125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="W125" s="19" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="X125" s="20" t="n">
-        <v>6937</v>
+        <v>0</v>
+      </c>
+      <c r="X125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="Y125" s="19" t="n">
-        <v>52.2</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="19" t="n">
         <v>-1</v>
@@ -39359,35 +39354,35 @@
       <c r="AA125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AB125" s="20" t="n">
-        <v>3626</v>
+      <c r="AB125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AC125" s="19" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="AD125" s="20" t="n">
-        <v>8649</v>
+        <v>0</v>
+      </c>
+      <c r="AD125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AE125" s="19" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="AF125" s="20" t="n">
-        <v>5503</v>
+        <v>0</v>
+      </c>
+      <c r="AF125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AG125" s="19" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="AH125" s="23" t="n">
-        <v>13320</v>
+        <v>0</v>
+      </c>
+      <c r="AH125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AI125" s="19" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AJ125" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AJ125" s="20" t="n">
+        <v>9944</v>
       </c>
       <c r="AK125" s="19" t="n">
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="AL125" s="19" t="n">
         <v>-1</v>
@@ -39395,23 +39390,23 @@
       <c r="AM125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AN125" s="19" t="n">
-        <v>-1</v>
+      <c r="AN125" s="23" t="n">
+        <v>14016</v>
       </c>
       <c r="AO125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP125" s="20" t="n">
-        <v>5519</v>
+        <v>12.4</v>
+      </c>
+      <c r="AP125" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ125" s="19" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="AR125" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="AR125" s="23" t="n">
+        <v>14411</v>
       </c>
       <c r="AS125" s="19" t="n">
-        <v>0</v>
+        <v>20.6</v>
       </c>
       <c r="AT125" s="19" t="n">
         <v>-1</v>
@@ -39419,11 +39414,11 @@
       <c r="AU125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AV125" s="19" t="n">
-        <v>-1</v>
+      <c r="AV125" s="23" t="n">
+        <v>18839</v>
       </c>
       <c r="AW125" s="19" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="AX125" s="19" t="n">
         <v>-1</v>
@@ -39431,11 +39426,11 @@
       <c r="AY125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AZ125" s="19" t="n">
-        <v>-1</v>
+      <c r="AZ125" s="20" t="n">
+        <v>3126</v>
       </c>
       <c r="BA125" s="19" t="n">
-        <v>0</v>
+        <v>76.8</v>
       </c>
       <c r="BB125" s="19" t="n">
         <v>-1</v>
@@ -39443,17 +39438,17 @@
       <c r="BC125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD125" s="19" t="n">
-        <v>-1</v>
+      <c r="BD125" s="20" t="n">
+        <v>2958</v>
       </c>
       <c r="BE125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF125" s="19" t="n">
-        <v>-1</v>
+        <v>76.7</v>
+      </c>
+      <c r="BF125" s="15" t="n">
+        <v>845</v>
       </c>
       <c r="BG125" s="19" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="BH125" s="19" t="n">
         <v>-1</v>
@@ -39461,11 +39456,11 @@
       <c r="BI125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BJ125" s="19" t="n">
-        <v>-1</v>
+      <c r="BJ125" s="14" t="n">
+        <v>211</v>
       </c>
       <c r="BK125" s="19" t="n">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="BL125" s="19" t="n">
         <v>-1</v>
@@ -39473,23 +39468,23 @@
       <c r="BM125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BN125" s="19" t="n">
-        <v>-1</v>
+      <c r="BN125" s="23" t="n">
+        <v>5468</v>
       </c>
       <c r="BO125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP125" s="19" t="n">
-        <v>-1</v>
+        <v>57.1</v>
+      </c>
+      <c r="BP125" s="15" t="n">
+        <v>1494</v>
       </c>
       <c r="BQ125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR125" s="19" t="n">
-        <v>-1</v>
+        <v>87</v>
+      </c>
+      <c r="BR125" s="14" t="n">
+        <v>131</v>
       </c>
       <c r="BS125" s="19" t="n">
-        <v>0</v>
+        <v>99.3</v>
       </c>
       <c r="BT125" s="19" t="n">
         <v>-1</v>
@@ -39521,23 +39516,23 @@
       <c r="CC125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD125" s="19" t="n">
-        <v>-1</v>
+      <c r="CD125" s="20" t="n">
+        <v>11707</v>
       </c>
       <c r="CE125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF125" s="19" t="n">
-        <v>-1</v>
+        <v>44.3</v>
+      </c>
+      <c r="CF125" s="15" t="n">
+        <v>1797</v>
       </c>
       <c r="CG125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH125" s="19" t="n">
-        <v>-1</v>
+        <v>85.7</v>
+      </c>
+      <c r="CH125" s="20" t="n">
+        <v>1689</v>
       </c>
       <c r="CI125" s="19" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="CJ125" s="19" t="n">
         <v>-1</v>
@@ -39551,11 +39546,11 @@
       <c r="CM125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CN125" s="19" t="n">
-        <v>-1</v>
+      <c r="CN125" s="23" t="n">
+        <v>11018</v>
       </c>
       <c r="CO125" s="19" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="CP125" s="19" t="n">
         <v>-1</v>
@@ -39563,53 +39558,58 @@
       <c r="CQ125" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CR125" s="19" t="n">
-        <v>-1</v>
+      <c r="CR125" s="15" t="n">
+        <v>229</v>
       </c>
       <c r="CS125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT125" s="19" t="n">
-        <v>-1</v>
+        <v>94.2</v>
+      </c>
+      <c r="CT125" s="15" t="n">
+        <v>662</v>
       </c>
       <c r="CU125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV125" s="19" t="n">
-        <v>-1</v>
+        <v>92.8</v>
+      </c>
+      <c r="CV125" s="20" t="n">
+        <v>2790</v>
       </c>
       <c r="CW125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX125" s="19" t="n">
-        <v>-1</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="CX125" s="14" t="n">
+        <v>407</v>
       </c>
       <c r="CY125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ125" s="19" t="n">
-        <v>-1</v>
+        <v>98.7</v>
+      </c>
+      <c r="CZ125" s="15" t="n">
+        <v>98</v>
       </c>
       <c r="DA125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB125" s="19" t="n">
-        <v>-1</v>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="DB125" s="15" t="n">
+        <v>227</v>
       </c>
       <c r="DC125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD125" s="19" t="n">
-        <v>-1</v>
+        <v>94.3</v>
+      </c>
+      <c r="DD125" s="14" t="n">
+        <v>80</v>
       </c>
       <c r="DE125" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF125" s="19" t="n">
-        <v>-1</v>
+        <v>97.59999999999999</v>
+      </c>
+      <c r="DF125" s="20" t="n">
+        <v>1523</v>
       </c>
       <c r="DG125" s="19" t="n">
-        <v>0</v>
+        <v>45.5</v>
+      </c>
+      <c r="DH125" s="1" t="inlineStr">
+        <is>
+          <t>Baidu-Logo</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -39618,14 +39618,14 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>yuanlu0210</t>
+          <t>roy_1127</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>1644</v>
+        <v>1673</v>
       </c>
       <c r="D126" s="25" t="n">
-        <v>1881</v>
+        <v>1813</v>
       </c>
       <c r="E126" s="12" t="n">
         <v>0</v>
@@ -39654,83 +39654,83 @@
       <c r="M126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="N126" s="13" t="n">
-        <v>-1</v>
+      <c r="N126" s="15" t="n">
+        <v>4024</v>
       </c>
       <c r="O126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="20" t="n">
-        <v>3835</v>
+        <v>75.09999999999999</v>
+      </c>
+      <c r="P126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Q126" s="13" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="R126" s="20" t="n">
-        <v>3688</v>
+        <v>0</v>
+      </c>
+      <c r="R126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="S126" s="13" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="T126" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="T126" s="20" t="n">
+        <v>4374</v>
       </c>
       <c r="U126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" s="15" t="n">
-        <v>1869</v>
+        <v>68.3</v>
+      </c>
+      <c r="V126" s="20" t="n">
+        <v>5310</v>
       </c>
       <c r="W126" s="13" t="n">
-        <v>86.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="X126" s="20" t="n">
-        <v>6604</v>
+        <v>6937</v>
       </c>
       <c r="Y126" s="13" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z126" s="20" t="n">
-        <v>3997</v>
+        <v>52.2</v>
+      </c>
+      <c r="Z126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AA126" s="13" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="AB126" s="20" t="n">
-        <v>5901</v>
+        <v>3626</v>
       </c>
       <c r="AC126" s="13" t="n">
-        <v>44</v>
+        <v>61.7</v>
       </c>
       <c r="AD126" s="20" t="n">
-        <v>6464</v>
+        <v>8649</v>
       </c>
       <c r="AE126" s="13" t="n">
-        <v>61.2</v>
+        <v>51.4</v>
       </c>
       <c r="AF126" s="20" t="n">
-        <v>6609</v>
+        <v>5503</v>
       </c>
       <c r="AG126" s="13" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AH126" s="20" t="n">
-        <v>2517</v>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AH126" s="23" t="n">
+        <v>13320</v>
       </c>
       <c r="AI126" s="13" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="AJ126" s="20" t="n">
-        <v>6572</v>
+        <v>20.8</v>
+      </c>
+      <c r="AJ126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AK126" s="13" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="AL126" s="15" t="n">
-        <v>1949</v>
+        <v>0</v>
+      </c>
+      <c r="AL126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AM126" s="13" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN126" s="13" t="n">
         <v>-1</v>
@@ -39738,29 +39738,29 @@
       <c r="AO126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AP126" s="13" t="n">
-        <v>-1</v>
+      <c r="AP126" s="20" t="n">
+        <v>5519</v>
       </c>
       <c r="AQ126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" s="23" t="n">
-        <v>8047</v>
+        <v>67.2</v>
+      </c>
+      <c r="AR126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AS126" s="13" t="n">
-        <v>49</v>
-      </c>
-      <c r="AT126" s="20" t="n">
-        <v>13843</v>
+        <v>0</v>
+      </c>
+      <c r="AT126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AU126" s="13" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="AV126" s="20" t="n">
-        <v>2532</v>
+        <v>0</v>
+      </c>
+      <c r="AV126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AW126" s="13" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AX126" s="13" t="n">
         <v>-1</v>
@@ -39780,47 +39780,47 @@
       <c r="BC126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BD126" s="15" t="n">
-        <v>898</v>
+      <c r="BD126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BE126" s="13" t="n">
-        <v>91</v>
-      </c>
-      <c r="BF126" s="20" t="n">
-        <v>1649</v>
+        <v>0</v>
+      </c>
+      <c r="BF126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BG126" s="13" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="BH126" s="20" t="n">
-        <v>954</v>
+        <v>0</v>
+      </c>
+      <c r="BH126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BI126" s="13" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="BJ126" s="20" t="n">
-        <v>1675</v>
+        <v>0</v>
+      </c>
+      <c r="BJ126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BK126" s="13" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="BL126" s="14" t="n">
-        <v>660</v>
+        <v>0</v>
+      </c>
+      <c r="BL126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BM126" s="13" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="BN126" s="20" t="n">
-        <v>3234</v>
+        <v>0</v>
+      </c>
+      <c r="BN126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BO126" s="13" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="BP126" s="15" t="n">
-        <v>1260</v>
+        <v>0</v>
+      </c>
+      <c r="BP126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ126" s="13" t="n">
-        <v>88.2</v>
+        <v>0</v>
       </c>
       <c r="BR126" s="13" t="n">
         <v>-1</v>
@@ -39846,53 +39846,53 @@
       <c r="BY126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BZ126" s="15" t="n">
-        <v>3694</v>
+      <c r="BZ126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CA126" s="13" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="CB126" s="20" t="n">
-        <v>2513</v>
+        <v>0</v>
+      </c>
+      <c r="CB126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CC126" s="13" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="CD126" s="20" t="n">
-        <v>6727</v>
+        <v>0</v>
+      </c>
+      <c r="CD126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CE126" s="13" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="CF126" s="15" t="n">
-        <v>601</v>
+        <v>0</v>
+      </c>
+      <c r="CF126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CG126" s="13" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="CH126" s="20" t="n">
-        <v>2688</v>
+        <v>0</v>
+      </c>
+      <c r="CH126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CI126" s="13" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="CJ126" s="15" t="n">
-        <v>1800</v>
+        <v>0</v>
+      </c>
+      <c r="CJ126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CK126" s="13" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="CL126" s="14" t="n">
-        <v>2006</v>
+        <v>0</v>
+      </c>
+      <c r="CL126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CM126" s="13" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="CN126" s="20" t="n">
-        <v>3202</v>
+        <v>0</v>
+      </c>
+      <c r="CN126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CO126" s="13" t="n">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CP126" s="13" t="n">
         <v>-1</v>
@@ -39906,11 +39906,11 @@
       <c r="CS126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CT126" s="20" t="n">
-        <v>1727</v>
+      <c r="CT126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CU126" s="13" t="n">
-        <v>84.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CV126" s="13" t="n">
         <v>-1</v>
@@ -39918,23 +39918,23 @@
       <c r="CW126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CX126" s="15" t="n">
-        <v>1577</v>
+      <c r="CX126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CY126" s="13" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="CZ126" s="15" t="n">
-        <v>1341</v>
+        <v>0</v>
+      </c>
+      <c r="CZ126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DA126" s="13" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="DB126" s="20" t="n">
-        <v>2132</v>
+        <v>0</v>
+      </c>
+      <c r="DB126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DC126" s="13" t="n">
-        <v>83.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="DD126" s="13" t="n">
         <v>-1</v>
@@ -39942,16 +39942,11 @@
       <c r="DE126" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="DF126" s="15" t="n">
-        <v>1294</v>
+      <c r="DF126" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DG126" s="13" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="DH126" s="1" t="inlineStr">
-        <is>
-          <t>Dropbox-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -39960,14 +39955,14 @@
       </c>
       <c r="B127" s="16" t="inlineStr">
         <is>
-          <t>perry304</t>
+          <t>yuanlu0210</t>
         </is>
       </c>
       <c r="C127" s="17" t="n">
-        <v>1517</v>
-      </c>
-      <c r="D127" s="21" t="n">
-        <v>2462</v>
+        <v>1645</v>
+      </c>
+      <c r="D127" s="27" t="n">
+        <v>1881</v>
       </c>
       <c r="E127" s="12" t="n">
         <v>0</v>
@@ -40002,17 +39997,17 @@
       <c r="O127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P127" s="19" t="n">
-        <v>-1</v>
+      <c r="P127" s="20" t="n">
+        <v>3835</v>
       </c>
       <c r="Q127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="19" t="n">
-        <v>-1</v>
+        <v>64.8</v>
+      </c>
+      <c r="R127" s="20" t="n">
+        <v>3688</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="T127" s="19" t="n">
         <v>-1</v>
@@ -40020,59 +40015,59 @@
       <c r="U127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="19" t="n">
-        <v>-1</v>
+      <c r="V127" s="15" t="n">
+        <v>1869</v>
       </c>
       <c r="W127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" s="19" t="n">
-        <v>-1</v>
+        <v>86.5</v>
+      </c>
+      <c r="X127" s="20" t="n">
+        <v>6604</v>
       </c>
       <c r="Y127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" s="19" t="n">
-        <v>-1</v>
+        <v>54</v>
+      </c>
+      <c r="Z127" s="20" t="n">
+        <v>3997</v>
       </c>
       <c r="AA127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" s="19" t="n">
-        <v>-1</v>
+        <v>67.5</v>
+      </c>
+      <c r="AB127" s="20" t="n">
+        <v>5901</v>
       </c>
       <c r="AC127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" s="19" t="n">
-        <v>-1</v>
+        <v>44</v>
+      </c>
+      <c r="AD127" s="20" t="n">
+        <v>6464</v>
       </c>
       <c r="AE127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" s="14" t="n">
-        <v>262</v>
+        <v>61.2</v>
+      </c>
+      <c r="AF127" s="20" t="n">
+        <v>6609</v>
       </c>
       <c r="AG127" s="19" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="AH127" s="19" t="n">
-        <v>-1</v>
+        <v>62.5</v>
+      </c>
+      <c r="AH127" s="20" t="n">
+        <v>2517</v>
       </c>
       <c r="AI127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ127" s="19" t="n">
-        <v>-1</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="AJ127" s="20" t="n">
+        <v>6572</v>
       </c>
       <c r="AK127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL127" s="14" t="n">
-        <v>222</v>
+        <v>60.7</v>
+      </c>
+      <c r="AL127" s="15" t="n">
+        <v>1949</v>
       </c>
       <c r="AM127" s="19" t="n">
-        <v>99.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AN127" s="19" t="n">
         <v>-1</v>
@@ -40086,29 +40081,29 @@
       <c r="AQ127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AR127" s="15" t="n">
-        <v>372</v>
+      <c r="AR127" s="23" t="n">
+        <v>8047</v>
       </c>
       <c r="AS127" s="19" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="AT127" s="19" t="n">
-        <v>-1</v>
+        <v>49</v>
+      </c>
+      <c r="AT127" s="20" t="n">
+        <v>13843</v>
       </c>
       <c r="AU127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV127" s="19" t="n">
-        <v>-1</v>
+        <v>39.7</v>
+      </c>
+      <c r="AV127" s="20" t="n">
+        <v>2532</v>
       </c>
       <c r="AW127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX127" s="15" t="n">
-        <v>491</v>
+        <v>80</v>
+      </c>
+      <c r="AX127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="AY127" s="19" t="n">
-        <v>92.7</v>
+        <v>0</v>
       </c>
       <c r="AZ127" s="19" t="n">
         <v>-1</v>
@@ -40116,53 +40111,53 @@
       <c r="BA127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB127" s="15" t="n">
-        <v>724</v>
+      <c r="BB127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BC127" s="19" t="n">
-        <v>92</v>
-      </c>
-      <c r="BD127" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BD127" s="15" t="n">
+        <v>898</v>
       </c>
       <c r="BE127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF127" s="19" t="n">
-        <v>-1</v>
+        <v>91</v>
+      </c>
+      <c r="BF127" s="20" t="n">
+        <v>1649</v>
       </c>
       <c r="BG127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH127" s="19" t="n">
-        <v>-1</v>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="BH127" s="20" t="n">
+        <v>954</v>
       </c>
       <c r="BI127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ127" s="19" t="n">
-        <v>-1</v>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="BJ127" s="20" t="n">
+        <v>1675</v>
       </c>
       <c r="BK127" s="19" t="n">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="BL127" s="14" t="n">
-        <v>386</v>
+        <v>660</v>
       </c>
       <c r="BM127" s="19" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="BN127" s="19" t="n">
-        <v>-1</v>
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BN127" s="20" t="n">
+        <v>3234</v>
       </c>
       <c r="BO127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP127" s="19" t="n">
-        <v>-1</v>
+        <v>73.5</v>
+      </c>
+      <c r="BP127" s="15" t="n">
+        <v>1260</v>
       </c>
       <c r="BQ127" s="19" t="n">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="BR127" s="19" t="n">
         <v>-1</v>
@@ -40170,11 +40165,11 @@
       <c r="BS127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT127" s="15" t="n">
-        <v>430</v>
+      <c r="BT127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BU127" s="19" t="n">
-        <v>92.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV127" s="19" t="n">
         <v>-1</v>
@@ -40182,65 +40177,65 @@
       <c r="BW127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BX127" s="15" t="n">
-        <v>842</v>
+      <c r="BX127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BY127" s="19" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="BZ127" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="BZ127" s="15" t="n">
+        <v>3694</v>
       </c>
       <c r="CA127" s="19" t="n">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="CB127" s="20" t="n">
-        <v>2950</v>
+        <v>2513</v>
       </c>
       <c r="CC127" s="19" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="CD127" s="19" t="n">
-        <v>-1</v>
+        <v>74.5</v>
+      </c>
+      <c r="CD127" s="20" t="n">
+        <v>6727</v>
       </c>
       <c r="CE127" s="19" t="n">
-        <v>0</v>
+        <v>63.7</v>
       </c>
       <c r="CF127" s="15" t="n">
-        <v>504</v>
+        <v>601</v>
       </c>
       <c r="CG127" s="19" t="n">
-        <v>92.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="CH127" s="20" t="n">
-        <v>1317</v>
+        <v>2688</v>
       </c>
       <c r="CI127" s="19" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="CJ127" s="19" t="n">
-        <v>-1</v>
+        <v>78.90000000000001</v>
+      </c>
+      <c r="CJ127" s="15" t="n">
+        <v>1800</v>
       </c>
       <c r="CK127" s="19" t="n">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="CL127" s="14" t="n">
-        <v>566</v>
+        <v>2006</v>
       </c>
       <c r="CM127" s="19" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="CN127" s="19" t="n">
-        <v>-1</v>
+        <v>93.2</v>
+      </c>
+      <c r="CN127" s="20" t="n">
+        <v>3202</v>
       </c>
       <c r="CO127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP127" s="15" t="n">
-        <v>791</v>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="CP127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CQ127" s="19" t="n">
-        <v>92.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CR127" s="19" t="n">
         <v>-1</v>
@@ -40248,35 +40243,35 @@
       <c r="CS127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CT127" s="15" t="n">
-        <v>407</v>
+      <c r="CT127" s="20" t="n">
+        <v>1727</v>
       </c>
       <c r="CU127" s="19" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="CV127" s="15" t="n">
-        <v>322</v>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="CV127" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW127" s="19" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="CX127" s="19" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="CX127" s="15" t="n">
+        <v>1577</v>
       </c>
       <c r="CY127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ127" s="19" t="n">
-        <v>-1</v>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="CZ127" s="15" t="n">
+        <v>1341</v>
       </c>
       <c r="DA127" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB127" s="19" t="n">
-        <v>-1</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="DB127" s="20" t="n">
+        <v>2132</v>
       </c>
       <c r="DC127" s="19" t="n">
-        <v>0</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="DD127" s="19" t="n">
         <v>-1</v>
@@ -40284,11 +40279,16 @@
       <c r="DE127" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DF127" s="19" t="n">
-        <v>-1</v>
+      <c r="DF127" s="15" t="n">
+        <v>1294</v>
       </c>
       <c r="DG127" s="19" t="n">
-        <v>0</v>
+        <v>57.1</v>
+      </c>
+      <c r="DH127" s="1" t="inlineStr">
+        <is>
+          <t>Dropbox-Logo</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -40297,14 +40297,14 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>answerer</t>
+          <t>perry304</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>1361</v>
-      </c>
-      <c r="D128" s="25" t="n">
-        <v>1942</v>
+        <v>1518</v>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>2462</v>
       </c>
       <c r="E128" s="12" t="n">
         <v>0</v>
@@ -40333,11 +40333,11 @@
       <c r="M128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="N128" s="15" t="n">
-        <v>1049</v>
+      <c r="N128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="O128" s="13" t="n">
-        <v>89.8</v>
+        <v>0</v>
       </c>
       <c r="P128" s="13" t="n">
         <v>-1</v>
@@ -40345,17 +40345,17 @@
       <c r="Q128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="R128" s="20" t="n">
-        <v>2963</v>
+      <c r="R128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="S128" s="13" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="T128" s="20" t="n">
-        <v>2190</v>
+        <v>0</v>
+      </c>
+      <c r="T128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="U128" s="13" t="n">
-        <v>79.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="V128" s="13" t="n">
         <v>-1</v>
@@ -40363,17 +40363,17 @@
       <c r="W128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="20" t="n">
-        <v>1747</v>
+      <c r="X128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Y128" s="13" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Z128" s="20" t="n">
-        <v>2750</v>
+        <v>0</v>
+      </c>
+      <c r="Z128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AA128" s="13" t="n">
-        <v>74.5</v>
+        <v>0</v>
       </c>
       <c r="AB128" s="13" t="n">
         <v>-1</v>
@@ -40381,17 +40381,17 @@
       <c r="AC128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD128" s="20" t="n">
-        <v>5157</v>
+      <c r="AD128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AE128" s="13" t="n">
-        <v>67</v>
-      </c>
-      <c r="AF128" s="15" t="n">
-        <v>685</v>
+        <v>0</v>
+      </c>
+      <c r="AF128" s="14" t="n">
+        <v>262</v>
       </c>
       <c r="AG128" s="13" t="n">
-        <v>92.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AH128" s="13" t="n">
         <v>-1</v>
@@ -40399,143 +40399,143 @@
       <c r="AI128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ128" s="20" t="n">
-        <v>4559</v>
+      <c r="AJ128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AK128" s="13" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="AL128" s="15" t="n">
-        <v>1105</v>
+        <v>0</v>
+      </c>
+      <c r="AL128" s="14" t="n">
+        <v>222</v>
       </c>
       <c r="AM128" s="13" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AN128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" s="15" t="n">
+        <v>372</v>
+      </c>
+      <c r="AS128" s="13" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AT128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AU128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AW128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" s="15" t="n">
+        <v>491</v>
+      </c>
+      <c r="AY128" s="13" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="AZ128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" s="15" t="n">
+        <v>724</v>
+      </c>
+      <c r="BC128" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="BD128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL128" s="14" t="n">
+        <v>386</v>
+      </c>
+      <c r="BM128" s="13" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="BN128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BS128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT128" s="15" t="n">
+        <v>430</v>
+      </c>
+      <c r="BU128" s="13" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="BV128" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BW128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX128" s="15" t="n">
+        <v>842</v>
+      </c>
+      <c r="BY128" s="13" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="AN128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP128" s="15" t="n">
-        <v>958</v>
-      </c>
-      <c r="AQ128" s="13" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="AR128" s="20" t="n">
-        <v>2786</v>
-      </c>
-      <c r="AS128" s="13" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="AT128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AU128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV128" s="23" t="n">
-        <v>11049</v>
-      </c>
-      <c r="AW128" s="13" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="AX128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AY128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ128" s="20" t="n">
-        <v>1708</v>
-      </c>
-      <c r="BA128" s="13" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="BB128" s="23" t="n">
-        <v>7223</v>
-      </c>
-      <c r="BC128" s="13" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="BD128" s="23" t="n">
-        <v>3699</v>
-      </c>
-      <c r="BE128" s="13" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="BF128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH128" s="20" t="n">
-        <v>2375</v>
-      </c>
-      <c r="BI128" s="13" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="BJ128" s="15" t="n">
-        <v>766</v>
-      </c>
-      <c r="BK128" s="13" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="BL128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN128" s="20" t="n">
-        <v>2690</v>
-      </c>
-      <c r="BO128" s="13" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="BP128" s="15" t="n">
-        <v>2377</v>
-      </c>
-      <c r="BQ128" s="13" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="BR128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BS128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT128" s="15" t="n">
-        <v>2037</v>
-      </c>
-      <c r="BU128" s="13" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="BV128" s="15" t="n">
-        <v>584</v>
-      </c>
-      <c r="BW128" s="13" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="BX128" s="13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BY128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ128" s="15" t="n">
-        <v>735</v>
+      <c r="BZ128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CA128" s="13" t="n">
-        <v>91.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB128" s="20" t="n">
-        <v>1418</v>
+        <v>2950</v>
       </c>
       <c r="CC128" s="13" t="n">
-        <v>81.2</v>
+        <v>71.8</v>
       </c>
       <c r="CD128" s="13" t="n">
         <v>-1</v>
@@ -40543,41 +40543,41 @@
       <c r="CE128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CF128" s="20" t="n">
-        <v>4828</v>
+      <c r="CF128" s="15" t="n">
+        <v>504</v>
       </c>
       <c r="CG128" s="13" t="n">
-        <v>64.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="CH128" s="20" t="n">
-        <v>3047</v>
+        <v>1317</v>
       </c>
       <c r="CI128" s="13" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="CJ128" s="20" t="n">
-        <v>4895</v>
+        <v>84.5</v>
+      </c>
+      <c r="CJ128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CK128" s="13" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="CL128" s="13" t="n">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="CL128" s="14" t="n">
+        <v>566</v>
       </c>
       <c r="CM128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN128" s="15" t="n">
-        <v>888</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="CN128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CO128" s="13" t="n">
-        <v>92.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="CP128" s="15" t="n">
-        <v>3346</v>
+        <v>791</v>
       </c>
       <c r="CQ128" s="13" t="n">
-        <v>83.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="CR128" s="13" t="n">
         <v>-1</v>
@@ -40585,17 +40585,17 @@
       <c r="CS128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CT128" s="20" t="n">
-        <v>1659</v>
+      <c r="CT128" s="15" t="n">
+        <v>407</v>
       </c>
       <c r="CU128" s="13" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="CV128" s="20" t="n">
-        <v>2653</v>
+        <v>93.7</v>
+      </c>
+      <c r="CV128" s="15" t="n">
+        <v>322</v>
       </c>
       <c r="CW128" s="13" t="n">
-        <v>80.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="CX128" s="13" t="n">
         <v>-1</v>
@@ -40603,23 +40603,23 @@
       <c r="CY128" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CZ128" s="20" t="n">
-        <v>6719</v>
+      <c r="CZ128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DA128" s="13" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="DB128" s="20" t="n">
-        <v>797</v>
+        <v>0</v>
+      </c>
+      <c r="DB128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DC128" s="13" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="DD128" s="15" t="n">
-        <v>1105</v>
+        <v>0</v>
+      </c>
+      <c r="DD128" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DE128" s="13" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="DF128" s="13" t="n">
         <v>-1</v>
@@ -40634,14 +40634,14 @@
       </c>
       <c r="B129" s="16" t="inlineStr">
         <is>
-          <t>fatyuan</t>
+          <t>answerer</t>
         </is>
       </c>
       <c r="C129" s="17" t="n">
-        <v>1349</v>
+        <v>1362</v>
       </c>
       <c r="D129" s="27" t="n">
-        <v>1629</v>
+        <v>1942</v>
       </c>
       <c r="E129" s="12" t="n">
         <v>0</v>
@@ -40670,11 +40670,11 @@
       <c r="M129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="N129" s="19" t="n">
-        <v>-1</v>
+      <c r="N129" s="15" t="n">
+        <v>1049</v>
       </c>
       <c r="O129" s="19" t="n">
-        <v>0</v>
+        <v>89.8</v>
       </c>
       <c r="P129" s="19" t="n">
         <v>-1</v>
@@ -40682,17 +40682,17 @@
       <c r="Q129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R129" s="19" t="n">
-        <v>-1</v>
+      <c r="R129" s="20" t="n">
+        <v>2963</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="19" t="n">
-        <v>-1</v>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="T129" s="20" t="n">
+        <v>2190</v>
       </c>
       <c r="U129" s="19" t="n">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="V129" s="19" t="n">
         <v>-1</v>
@@ -40700,17 +40700,17 @@
       <c r="W129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="19" t="n">
-        <v>-1</v>
+      <c r="X129" s="20" t="n">
+        <v>1747</v>
       </c>
       <c r="Y129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" s="19" t="n">
-        <v>-1</v>
+        <v>80.5</v>
+      </c>
+      <c r="Z129" s="20" t="n">
+        <v>2750</v>
       </c>
       <c r="AA129" s="19" t="n">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="AB129" s="19" t="n">
         <v>-1</v>
@@ -40718,17 +40718,17 @@
       <c r="AC129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AD129" s="19" t="n">
-        <v>-1</v>
+      <c r="AD129" s="20" t="n">
+        <v>5157</v>
       </c>
       <c r="AE129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" s="19" t="n">
-        <v>-1</v>
+        <v>67</v>
+      </c>
+      <c r="AF129" s="15" t="n">
+        <v>685</v>
       </c>
       <c r="AG129" s="19" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AH129" s="19" t="n">
         <v>-1</v>
@@ -40736,17 +40736,17 @@
       <c r="AI129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ129" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ129" s="20" t="n">
+        <v>4559</v>
       </c>
       <c r="AK129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL129" s="19" t="n">
-        <v>-1</v>
+        <v>69.7</v>
+      </c>
+      <c r="AL129" s="15" t="n">
+        <v>1105</v>
       </c>
       <c r="AM129" s="19" t="n">
-        <v>0</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AN129" s="19" t="n">
         <v>-1</v>
@@ -40754,17 +40754,17 @@
       <c r="AO129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AP129" s="19" t="n">
-        <v>-1</v>
+      <c r="AP129" s="15" t="n">
+        <v>958</v>
       </c>
       <c r="AQ129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR129" s="19" t="n">
-        <v>-1</v>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="AR129" s="20" t="n">
+        <v>2786</v>
       </c>
       <c r="AS129" s="19" t="n">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="AT129" s="19" t="n">
         <v>-1</v>
@@ -40772,11 +40772,11 @@
       <c r="AU129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AV129" s="19" t="n">
-        <v>-1</v>
+      <c r="AV129" s="23" t="n">
+        <v>11049</v>
       </c>
       <c r="AW129" s="19" t="n">
-        <v>0</v>
+        <v>41.3</v>
       </c>
       <c r="AX129" s="19" t="n">
         <v>-1</v>
@@ -40784,23 +40784,23 @@
       <c r="AY129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AZ129" s="19" t="n">
-        <v>-1</v>
+      <c r="AZ129" s="20" t="n">
+        <v>1708</v>
       </c>
       <c r="BA129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB129" s="19" t="n">
-        <v>-1</v>
+        <v>82.8</v>
+      </c>
+      <c r="BB129" s="23" t="n">
+        <v>7223</v>
       </c>
       <c r="BC129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD129" s="19" t="n">
-        <v>-1</v>
+        <v>55.3</v>
+      </c>
+      <c r="BD129" s="23" t="n">
+        <v>3699</v>
       </c>
       <c r="BE129" s="19" t="n">
-        <v>0</v>
+        <v>68.3</v>
       </c>
       <c r="BF129" s="19" t="n">
         <v>-1</v>
@@ -40808,17 +40808,17 @@
       <c r="BG129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH129" s="19" t="n">
-        <v>-1</v>
+      <c r="BH129" s="20" t="n">
+        <v>2375</v>
       </c>
       <c r="BI129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ129" s="19" t="n">
-        <v>-1</v>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="BJ129" s="15" t="n">
+        <v>766</v>
       </c>
       <c r="BK129" s="19" t="n">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="BL129" s="19" t="n">
         <v>-1</v>
@@ -40826,17 +40826,17 @@
       <c r="BM129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BN129" s="19" t="n">
-        <v>-1</v>
+      <c r="BN129" s="20" t="n">
+        <v>2690</v>
       </c>
       <c r="BO129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP129" s="19" t="n">
-        <v>-1</v>
+        <v>76.3</v>
+      </c>
+      <c r="BP129" s="15" t="n">
+        <v>2377</v>
       </c>
       <c r="BQ129" s="19" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="BR129" s="19" t="n">
         <v>-1</v>
@@ -40844,17 +40844,17 @@
       <c r="BS129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT129" s="19" t="n">
-        <v>-1</v>
+      <c r="BT129" s="15" t="n">
+        <v>2037</v>
       </c>
       <c r="BU129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV129" s="19" t="n">
-        <v>-1</v>
+        <v>83.8</v>
+      </c>
+      <c r="BV129" s="15" t="n">
+        <v>584</v>
       </c>
       <c r="BW129" s="19" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="BX129" s="19" t="n">
         <v>-1</v>
@@ -40862,17 +40862,17 @@
       <c r="BY129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BZ129" s="19" t="n">
-        <v>-1</v>
+      <c r="BZ129" s="15" t="n">
+        <v>735</v>
       </c>
       <c r="CA129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB129" s="19" t="n">
-        <v>-1</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="CB129" s="20" t="n">
+        <v>1418</v>
       </c>
       <c r="CC129" s="19" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="CD129" s="19" t="n">
         <v>-1</v>
@@ -40880,23 +40880,23 @@
       <c r="CE129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CF129" s="19" t="n">
-        <v>-1</v>
+      <c r="CF129" s="20" t="n">
+        <v>4828</v>
       </c>
       <c r="CG129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH129" s="19" t="n">
-        <v>-1</v>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="CH129" s="20" t="n">
+        <v>3047</v>
       </c>
       <c r="CI129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ129" s="19" t="n">
-        <v>-1</v>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="CJ129" s="20" t="n">
+        <v>4895</v>
       </c>
       <c r="CK129" s="19" t="n">
-        <v>0</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="CL129" s="19" t="n">
         <v>-1</v>
@@ -40904,17 +40904,17 @@
       <c r="CM129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CN129" s="19" t="n">
-        <v>-1</v>
+      <c r="CN129" s="15" t="n">
+        <v>888</v>
       </c>
       <c r="CO129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP129" s="19" t="n">
-        <v>-1</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="CP129" s="15" t="n">
+        <v>3346</v>
       </c>
       <c r="CQ129" s="19" t="n">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="CR129" s="19" t="n">
         <v>-1</v>
@@ -40922,17 +40922,17 @@
       <c r="CS129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CT129" s="19" t="n">
-        <v>-1</v>
+      <c r="CT129" s="20" t="n">
+        <v>1659</v>
       </c>
       <c r="CU129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV129" s="19" t="n">
-        <v>-1</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="CV129" s="20" t="n">
+        <v>2653</v>
       </c>
       <c r="CW129" s="19" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="CX129" s="19" t="n">
         <v>-1</v>
@@ -40940,23 +40940,23 @@
       <c r="CY129" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CZ129" s="19" t="n">
-        <v>-1</v>
+      <c r="CZ129" s="20" t="n">
+        <v>6719</v>
       </c>
       <c r="DA129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB129" s="19" t="n">
-        <v>-1</v>
+        <v>65.59999999999999</v>
+      </c>
+      <c r="DB129" s="20" t="n">
+        <v>797</v>
       </c>
       <c r="DC129" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD129" s="19" t="n">
-        <v>-1</v>
+        <v>87.5</v>
+      </c>
+      <c r="DD129" s="15" t="n">
+        <v>1105</v>
       </c>
       <c r="DE129" s="19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="DF129" s="19" t="n">
         <v>-1</v>
@@ -40971,14 +40971,14 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>kirasj</t>
+          <t>fatyuan</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>1212</v>
+        <v>1350</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>1428</v>
+        <v>1629</v>
       </c>
       <c r="E130" s="12" t="n">
         <v>0</v>
@@ -41001,11 +41001,11 @@
       <c r="K130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L130" s="23" t="n">
-        <v>11970</v>
+      <c r="L130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="M130" s="13" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="N130" s="13" t="n">
         <v>-1</v>
@@ -41031,23 +41031,23 @@
       <c r="U130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="23" t="n">
-        <v>13527</v>
+      <c r="V130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="W130" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X130" s="23" t="n">
-        <v>12077</v>
+        <v>0</v>
+      </c>
+      <c r="X130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Y130" s="13" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Z130" s="23" t="n">
-        <v>9176</v>
+        <v>0</v>
+      </c>
+      <c r="Z130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AA130" s="13" t="n">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="AB130" s="13" t="n">
         <v>-1</v>
@@ -41055,17 +41055,17 @@
       <c r="AC130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD130" s="23" t="n">
-        <v>14328</v>
+      <c r="AD130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AE130" s="13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="AF130" s="23" t="n">
-        <v>15257</v>
+        <v>0</v>
+      </c>
+      <c r="AF130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AG130" s="13" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="AH130" s="13" t="n">
         <v>-1</v>
@@ -41073,47 +41073,47 @@
       <c r="AI130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ130" s="23" t="n">
-        <v>14900</v>
+      <c r="AJ130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AK130" s="13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL130" s="23" t="n">
-        <v>15003</v>
+        <v>0</v>
+      </c>
+      <c r="AL130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AM130" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN130" s="23" t="n">
-        <v>9481</v>
+        <v>0</v>
+      </c>
+      <c r="AN130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AO130" s="13" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="AP130" s="23" t="n">
-        <v>10478</v>
+        <v>0</v>
+      </c>
+      <c r="AP130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AQ130" s="13" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="AR130" s="23" t="n">
-        <v>10669</v>
+        <v>0</v>
+      </c>
+      <c r="AR130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AS130" s="13" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="AT130" s="20" t="n">
-        <v>4934</v>
+        <v>0</v>
+      </c>
+      <c r="AT130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AU130" s="13" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="AV130" s="23" t="n">
-        <v>13946</v>
+        <v>0</v>
+      </c>
+      <c r="AV130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AW130" s="13" t="n">
-        <v>29.8</v>
+        <v>0</v>
       </c>
       <c r="AX130" s="13" t="n">
         <v>-1</v>
@@ -41127,23 +41127,23 @@
       <c r="BA130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BB130" s="23" t="n">
-        <v>11501</v>
+      <c r="BB130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BC130" s="13" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="BD130" s="23" t="n">
-        <v>14888</v>
+        <v>0</v>
+      </c>
+      <c r="BD130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BE130" s="13" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="BF130" s="23" t="n">
-        <v>8331</v>
+        <v>0</v>
+      </c>
+      <c r="BF130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BG130" s="13" t="n">
-        <v>45.1</v>
+        <v>0</v>
       </c>
       <c r="BH130" s="13" t="n">
         <v>-1</v>
@@ -41151,41 +41151,41 @@
       <c r="BI130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BJ130" s="23" t="n">
-        <v>7601</v>
+      <c r="BJ130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BK130" s="13" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="BL130" s="23" t="n">
-        <v>12798</v>
+        <v>0</v>
+      </c>
+      <c r="BL130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BM130" s="13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN130" s="23" t="n">
-        <v>7083</v>
+        <v>0</v>
+      </c>
+      <c r="BN130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BO130" s="13" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="BP130" s="23" t="n">
-        <v>9259</v>
+        <v>0</v>
+      </c>
+      <c r="BP130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ130" s="13" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="BR130" s="23" t="n">
-        <v>7615</v>
+        <v>0</v>
+      </c>
+      <c r="BR130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BS130" s="13" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="BT130" s="23" t="n">
-        <v>10709</v>
+        <v>0</v>
+      </c>
+      <c r="BT130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BU130" s="13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BV130" s="13" t="n">
         <v>-1</v>
@@ -41211,11 +41211,11 @@
       <c r="CC130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CD130" s="23" t="n">
-        <v>20149</v>
+      <c r="CD130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CE130" s="13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="CF130" s="13" t="n">
         <v>-1</v>
@@ -41283,28 +41283,23 @@
       <c r="DA130" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="DB130" s="23" t="n">
-        <v>18968</v>
+      <c r="DB130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DC130" s="13" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="DD130" s="23" t="n">
-        <v>2389</v>
+        <v>0</v>
+      </c>
+      <c r="DD130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DE130" s="13" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="DF130" s="23" t="n">
-        <v>2563</v>
+        <v>0</v>
+      </c>
+      <c r="DF130" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="DG130" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="DH130" s="1" t="inlineStr">
-        <is>
-          <t>Google-Logo</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -41313,14 +41308,14 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>bill04128682</t>
+          <t>kirasj</t>
         </is>
       </c>
       <c r="C131" s="17" t="n">
-        <v>1106</v>
+        <v>1213</v>
       </c>
       <c r="D131" s="27" t="n">
-        <v>2014</v>
+        <v>1428</v>
       </c>
       <c r="E131" s="12" t="n">
         <v>0</v>
@@ -41343,11 +41338,11 @@
       <c r="K131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L131" s="19" t="n">
-        <v>-1</v>
+      <c r="L131" s="23" t="n">
+        <v>11970</v>
       </c>
       <c r="M131" s="19" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="N131" s="19" t="n">
         <v>-1</v>
@@ -41373,23 +41368,23 @@
       <c r="U131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="19" t="n">
-        <v>-1</v>
+      <c r="V131" s="23" t="n">
+        <v>13527</v>
       </c>
       <c r="W131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" s="19" t="n">
-        <v>-1</v>
+        <v>23.5</v>
+      </c>
+      <c r="X131" s="23" t="n">
+        <v>12077</v>
       </c>
       <c r="Y131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="19" t="n">
-        <v>-1</v>
+        <v>19.1</v>
+      </c>
+      <c r="Z131" s="23" t="n">
+        <v>9176</v>
       </c>
       <c r="AA131" s="19" t="n">
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="AB131" s="19" t="n">
         <v>-1</v>
@@ -41397,17 +41392,17 @@
       <c r="AC131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AD131" s="19" t="n">
-        <v>-1</v>
+      <c r="AD131" s="23" t="n">
+        <v>14328</v>
       </c>
       <c r="AE131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" s="19" t="n">
-        <v>-1</v>
+        <v>21.1</v>
+      </c>
+      <c r="AF131" s="23" t="n">
+        <v>15257</v>
       </c>
       <c r="AG131" s="19" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="AH131" s="19" t="n">
         <v>-1</v>
@@ -41415,47 +41410,47 @@
       <c r="AI131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ131" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ131" s="23" t="n">
+        <v>14900</v>
       </c>
       <c r="AK131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL131" s="19" t="n">
-        <v>-1</v>
+        <v>18.5</v>
+      </c>
+      <c r="AL131" s="23" t="n">
+        <v>15003</v>
       </c>
       <c r="AM131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN131" s="19" t="n">
-        <v>-1</v>
+        <v>32</v>
+      </c>
+      <c r="AN131" s="23" t="n">
+        <v>9481</v>
       </c>
       <c r="AO131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP131" s="19" t="n">
-        <v>-1</v>
+        <v>35.9</v>
+      </c>
+      <c r="AP131" s="23" t="n">
+        <v>10478</v>
       </c>
       <c r="AQ131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR131" s="19" t="n">
-        <v>-1</v>
+        <v>41.8</v>
+      </c>
+      <c r="AR131" s="23" t="n">
+        <v>10669</v>
       </c>
       <c r="AS131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT131" s="19" t="n">
-        <v>-1</v>
+        <v>37.3</v>
+      </c>
+      <c r="AT131" s="20" t="n">
+        <v>4934</v>
       </c>
       <c r="AU131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV131" s="19" t="n">
-        <v>-1</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AV131" s="23" t="n">
+        <v>13946</v>
       </c>
       <c r="AW131" s="19" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="AX131" s="19" t="n">
         <v>-1</v>
@@ -41469,23 +41464,23 @@
       <c r="BA131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BB131" s="19" t="n">
-        <v>-1</v>
+      <c r="BB131" s="23" t="n">
+        <v>11501</v>
       </c>
       <c r="BC131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD131" s="19" t="n">
-        <v>-1</v>
+        <v>37.7</v>
+      </c>
+      <c r="BD131" s="23" t="n">
+        <v>14888</v>
       </c>
       <c r="BE131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF131" s="19" t="n">
-        <v>-1</v>
+        <v>17.9</v>
+      </c>
+      <c r="BF131" s="23" t="n">
+        <v>8331</v>
       </c>
       <c r="BG131" s="19" t="n">
-        <v>0</v>
+        <v>45.1</v>
       </c>
       <c r="BH131" s="19" t="n">
         <v>-1</v>
@@ -41493,41 +41488,41 @@
       <c r="BI131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BJ131" s="19" t="n">
-        <v>-1</v>
+      <c r="BJ131" s="23" t="n">
+        <v>7601</v>
       </c>
       <c r="BK131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL131" s="19" t="n">
-        <v>-1</v>
+        <v>43.5</v>
+      </c>
+      <c r="BL131" s="23" t="n">
+        <v>12798</v>
       </c>
       <c r="BM131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN131" s="19" t="n">
-        <v>-1</v>
+        <v>14.5</v>
+      </c>
+      <c r="BN131" s="23" t="n">
+        <v>7083</v>
       </c>
       <c r="BO131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP131" s="19" t="n">
-        <v>-1</v>
+        <v>48.9</v>
+      </c>
+      <c r="BP131" s="23" t="n">
+        <v>9259</v>
       </c>
       <c r="BQ131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR131" s="19" t="n">
-        <v>-1</v>
+        <v>35.4</v>
+      </c>
+      <c r="BR131" s="23" t="n">
+        <v>7615</v>
       </c>
       <c r="BS131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT131" s="19" t="n">
-        <v>-1</v>
+        <v>45.7</v>
+      </c>
+      <c r="BT131" s="23" t="n">
+        <v>10709</v>
       </c>
       <c r="BU131" s="19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BV131" s="19" t="n">
         <v>-1</v>
@@ -41553,11 +41548,11 @@
       <c r="CC131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CD131" s="19" t="n">
-        <v>-1</v>
+      <c r="CD131" s="23" t="n">
+        <v>20149</v>
       </c>
       <c r="CE131" s="19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="CF131" s="19" t="n">
         <v>-1</v>
@@ -41565,11 +41560,11 @@
       <c r="CG131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CH131" s="20" t="n">
-        <v>5125</v>
+      <c r="CH131" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CI131" s="19" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="CJ131" s="19" t="n">
         <v>-1</v>
@@ -41625,27 +41620,27 @@
       <c r="DA131" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="DB131" s="19" t="n">
-        <v>-1</v>
+      <c r="DB131" s="23" t="n">
+        <v>18968</v>
       </c>
       <c r="DC131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD131" s="19" t="n">
-        <v>-1</v>
+        <v>26.5</v>
+      </c>
+      <c r="DD131" s="23" t="n">
+        <v>2389</v>
       </c>
       <c r="DE131" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF131" s="19" t="n">
-        <v>-1</v>
+        <v>13.7</v>
+      </c>
+      <c r="DF131" s="23" t="n">
+        <v>2563</v>
       </c>
       <c r="DG131" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DH131" s="1" t="inlineStr">
         <is>
-          <t>JumpTrade-Logo</t>
+          <t>Google-Logo</t>
         </is>
       </c>
     </row>
@@ -41655,14 +41650,14 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>deadstorm</t>
+          <t>bill04128682</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>989</v>
+        <v>1107</v>
       </c>
       <c r="D132" s="25" t="n">
-        <v>1433</v>
+        <v>2014</v>
       </c>
       <c r="E132" s="12" t="n">
         <v>0</v>
@@ -41907,11 +41902,11 @@
       <c r="CG132" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CH132" s="13" t="n">
-        <v>-1</v>
+      <c r="CH132" s="20" t="n">
+        <v>5125</v>
       </c>
       <c r="CI132" s="13" t="n">
-        <v>0</v>
+        <v>68.8</v>
       </c>
       <c r="CJ132" s="13" t="n">
         <v>-1</v>
@@ -41984,6 +41979,11 @@
       </c>
       <c r="DG132" s="13" t="n">
         <v>0</v>
+      </c>
+      <c r="DH132" s="1" t="inlineStr">
+        <is>
+          <t>JumpTrade-Logo</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -41992,14 +41992,14 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>wawawamei</t>
+          <t>deadstorm</t>
         </is>
       </c>
       <c r="C133" s="17" t="n">
-        <v>818</v>
+        <v>990</v>
       </c>
       <c r="D133" s="27" t="n">
-        <v>1411</v>
+        <v>1433</v>
       </c>
       <c r="E133" s="12" t="n">
         <v>0</v>
@@ -42166,11 +42166,11 @@
       <c r="BG133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BH133" s="23" t="n">
-        <v>10801</v>
+      <c r="BH133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="BI133" s="19" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="BJ133" s="19" t="n">
         <v>-1</v>
@@ -42238,11 +42238,11 @@
       <c r="CE133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CF133" s="20" t="n">
-        <v>4257</v>
+      <c r="CF133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG133" s="19" t="n">
-        <v>67.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="CH133" s="19" t="n">
         <v>-1</v>
@@ -42256,11 +42256,11 @@
       <c r="CK133" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CL133" s="23" t="n">
-        <v>21358</v>
+      <c r="CL133" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CM133" s="19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CN133" s="19" t="n">
         <v>-1</v>
@@ -42329,14 +42329,14 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>wangyxwyx</t>
+          <t>wawawamei</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>390</v>
+        <v>819</v>
       </c>
       <c r="D134" s="25" t="n">
-        <v>1650</v>
+        <v>1411</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>0</v>
@@ -42377,11 +42377,11 @@
       <c r="Q134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="R134" s="23" t="n">
-        <v>9657</v>
+      <c r="R134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="S134" s="13" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="T134" s="13" t="n">
         <v>-1</v>
@@ -42389,17 +42389,17 @@
       <c r="U134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="20" t="n">
-        <v>7694</v>
+      <c r="V134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="W134" s="13" t="n">
-        <v>55</v>
-      </c>
-      <c r="X134" s="20" t="n">
-        <v>2852</v>
+        <v>0</v>
+      </c>
+      <c r="X134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="Y134" s="13" t="n">
-        <v>74.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z134" s="13" t="n">
         <v>-1</v>
@@ -42407,11 +42407,11 @@
       <c r="AA134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AB134" s="20" t="n">
-        <v>1986</v>
+      <c r="AB134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AC134" s="13" t="n">
-        <v>74.5</v>
+        <v>0</v>
       </c>
       <c r="AD134" s="13" t="n">
         <v>-1</v>
@@ -42419,11 +42419,11 @@
       <c r="AE134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AF134" s="20" t="n">
-        <v>8327</v>
+      <c r="AF134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AG134" s="13" t="n">
-        <v>55.3</v>
+        <v>0</v>
       </c>
       <c r="AH134" s="13" t="n">
         <v>-1</v>
@@ -42431,11 +42431,11 @@
       <c r="AI134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ134" s="20" t="n">
-        <v>6609</v>
+      <c r="AJ134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AK134" s="13" t="n">
-        <v>60.5</v>
+        <v>0</v>
       </c>
       <c r="AL134" s="13" t="n">
         <v>-1</v>
@@ -42467,11 +42467,11 @@
       <c r="AU134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AV134" s="23" t="n">
-        <v>17257</v>
+      <c r="AV134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AW134" s="13" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="AX134" s="13" t="n">
         <v>-1</v>
@@ -42491,23 +42491,23 @@
       <c r="BC134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BD134" s="23" t="n">
-        <v>13058</v>
+      <c r="BD134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BE134" s="13" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="BF134" s="20" t="n">
-        <v>4497</v>
+        <v>0</v>
+      </c>
+      <c r="BF134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BG134" s="13" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="BH134" s="20" t="n">
-        <v>1188</v>
+        <v>0</v>
+      </c>
+      <c r="BH134" s="23" t="n">
+        <v>10801</v>
       </c>
       <c r="BI134" s="13" t="n">
-        <v>82.7</v>
+        <v>18.7</v>
       </c>
       <c r="BJ134" s="13" t="n">
         <v>-1</v>
@@ -42521,17 +42521,17 @@
       <c r="BM134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BN134" s="20" t="n">
-        <v>2688</v>
+      <c r="BN134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BO134" s="13" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="BP134" s="23" t="n">
-        <v>14751</v>
+        <v>0</v>
+      </c>
+      <c r="BP134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BQ134" s="13" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BR134" s="13" t="n">
         <v>-1</v>
@@ -42539,11 +42539,11 @@
       <c r="BS134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BT134" s="20" t="n">
-        <v>7963</v>
+      <c r="BT134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BU134" s="13" t="n">
-        <v>46.1</v>
+        <v>0</v>
       </c>
       <c r="BV134" s="13" t="n">
         <v>-1</v>
@@ -42551,17 +42551,17 @@
       <c r="BW134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="BX134" s="20" t="n">
-        <v>6946</v>
+      <c r="BX134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BY134" s="13" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="BZ134" s="20" t="n">
-        <v>5136</v>
+        <v>0</v>
+      </c>
+      <c r="BZ134" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="CA134" s="13" t="n">
-        <v>66.5</v>
+        <v>0</v>
       </c>
       <c r="CB134" s="13" t="n">
         <v>-1</v>
@@ -42575,11 +42575,11 @@
       <c r="CE134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CF134" s="13" t="n">
-        <v>-1</v>
+      <c r="CF134" s="20" t="n">
+        <v>4257</v>
       </c>
       <c r="CG134" s="13" t="n">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="CH134" s="13" t="n">
         <v>-1</v>
@@ -42593,11 +42593,11 @@
       <c r="CK134" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CL134" s="13" t="n">
-        <v>-1</v>
+      <c r="CL134" s="23" t="n">
+        <v>21358</v>
       </c>
       <c r="CM134" s="13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CN134" s="13" t="n">
         <v>-1</v>
@@ -42666,14 +42666,14 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Q2PPSElacY</t>
+          <t>wangyxwyx</t>
         </is>
       </c>
       <c r="C135" s="17" t="n">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="D135" s="27" t="n">
-        <v>1731</v>
+        <v>1650</v>
       </c>
       <c r="E135" s="12" t="n">
         <v>0</v>
@@ -42714,11 +42714,11 @@
       <c r="Q135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="R135" s="19" t="n">
-        <v>-1</v>
+      <c r="R135" s="23" t="n">
+        <v>9657</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>0</v>
+        <v>30.9</v>
       </c>
       <c r="T135" s="19" t="n">
         <v>-1</v>
@@ -42726,17 +42726,17 @@
       <c r="U135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="19" t="n">
-        <v>-1</v>
+      <c r="V135" s="20" t="n">
+        <v>7694</v>
       </c>
       <c r="W135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="19" t="n">
-        <v>-1</v>
+        <v>55</v>
+      </c>
+      <c r="X135" s="20" t="n">
+        <v>2852</v>
       </c>
       <c r="Y135" s="19" t="n">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Z135" s="19" t="n">
         <v>-1</v>
@@ -42744,11 +42744,11 @@
       <c r="AA135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AB135" s="19" t="n">
-        <v>-1</v>
+      <c r="AB135" s="20" t="n">
+        <v>1986</v>
       </c>
       <c r="AC135" s="19" t="n">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="AD135" s="19" t="n">
         <v>-1</v>
@@ -42756,11 +42756,11 @@
       <c r="AE135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AF135" s="19" t="n">
-        <v>-1</v>
+      <c r="AF135" s="20" t="n">
+        <v>8327</v>
       </c>
       <c r="AG135" s="19" t="n">
-        <v>0</v>
+        <v>55.3</v>
       </c>
       <c r="AH135" s="19" t="n">
         <v>-1</v>
@@ -42768,11 +42768,11 @@
       <c r="AI135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ135" s="19" t="n">
-        <v>-1</v>
+      <c r="AJ135" s="20" t="n">
+        <v>6609</v>
       </c>
       <c r="AK135" s="19" t="n">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="AL135" s="19" t="n">
         <v>-1</v>
@@ -42804,11 +42804,11 @@
       <c r="AU135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="AV135" s="19" t="n">
-        <v>-1</v>
+      <c r="AV135" s="23" t="n">
+        <v>17257</v>
       </c>
       <c r="AW135" s="19" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="AX135" s="19" t="n">
         <v>-1</v>
@@ -42828,23 +42828,23 @@
       <c r="BC135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BD135" s="19" t="n">
-        <v>-1</v>
+      <c r="BD135" s="23" t="n">
+        <v>13058</v>
       </c>
       <c r="BE135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF135" s="19" t="n">
-        <v>-1</v>
+        <v>26.2</v>
+      </c>
+      <c r="BF135" s="20" t="n">
+        <v>4497</v>
       </c>
       <c r="BG135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH135" s="19" t="n">
-        <v>-1</v>
+        <v>68.5</v>
+      </c>
+      <c r="BH135" s="20" t="n">
+        <v>1188</v>
       </c>
       <c r="BI135" s="19" t="n">
-        <v>0</v>
+        <v>82.7</v>
       </c>
       <c r="BJ135" s="19" t="n">
         <v>-1</v>
@@ -42858,17 +42858,17 @@
       <c r="BM135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BN135" s="19" t="n">
-        <v>-1</v>
+      <c r="BN135" s="20" t="n">
+        <v>2688</v>
       </c>
       <c r="BO135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP135" s="19" t="n">
-        <v>-1</v>
+        <v>76.3</v>
+      </c>
+      <c r="BP135" s="23" t="n">
+        <v>14751</v>
       </c>
       <c r="BQ135" s="19" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BR135" s="19" t="n">
         <v>-1</v>
@@ -42876,11 +42876,11 @@
       <c r="BS135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BT135" s="19" t="n">
-        <v>-1</v>
+      <c r="BT135" s="20" t="n">
+        <v>7963</v>
       </c>
       <c r="BU135" s="19" t="n">
-        <v>0</v>
+        <v>46.1</v>
       </c>
       <c r="BV135" s="19" t="n">
         <v>-1</v>
@@ -42888,17 +42888,17 @@
       <c r="BW135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="BX135" s="19" t="n">
-        <v>-1</v>
+      <c r="BX135" s="20" t="n">
+        <v>6946</v>
       </c>
       <c r="BY135" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ135" s="19" t="n">
-        <v>-1</v>
+        <v>57.7</v>
+      </c>
+      <c r="BZ135" s="20" t="n">
+        <v>5136</v>
       </c>
       <c r="CA135" s="19" t="n">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="CB135" s="19" t="n">
         <v>-1</v>
@@ -42912,11 +42912,11 @@
       <c r="CE135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CF135" s="20" t="n">
-        <v>2005</v>
+      <c r="CF135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CG135" s="19" t="n">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="CH135" s="19" t="n">
         <v>-1</v>
@@ -42960,38 +42960,38 @@
       <c r="CU135" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="CV135" s="20" t="n">
-        <v>3161</v>
+      <c r="CV135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CW135" s="19" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="CX135" s="20" t="n">
-        <v>7063</v>
+        <v>0</v>
+      </c>
+      <c r="CX135" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="CY135" s="19" t="n">
-        <v>67.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="CZ135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DA135" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DB135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DC135" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DD135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DE135" s="19" t="n">
         <v>0</v>
       </c>
       <c r="DF135" s="19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="DG135" s="19" t="n">
         <v>0</v>
@@ -43003,14 +43003,14 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Andy0315</t>
+          <t>Q2PPSElacY</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>190</v>
+        <v>339</v>
       </c>
       <c r="D136" s="25" t="n">
-        <v>1500</v>
+        <v>1731</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>0</v>
@@ -43039,11 +43039,11 @@
       <c r="M136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="N136" s="23" t="n">
-        <v>12761</v>
+      <c r="N136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="O136" s="13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P136" s="13" t="n">
         <v>-1</v>
@@ -43087,17 +43087,17 @@
       <c r="AC136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AD136" s="20" t="n">
-        <v>7949</v>
+      <c r="AD136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AE136" s="13" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="AF136" s="20" t="n">
-        <v>5348</v>
+        <v>0</v>
+      </c>
+      <c r="AF136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AG136" s="13" t="n">
-        <v>67.7</v>
+        <v>0</v>
       </c>
       <c r="AH136" s="13" t="n">
         <v>-1</v>
@@ -43111,11 +43111,11 @@
       <c r="AK136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AL136" s="20" t="n">
-        <v>9462</v>
+      <c r="AL136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AM136" s="13" t="n">
-        <v>56.6</v>
+        <v>0</v>
       </c>
       <c r="AN136" s="13" t="n">
         <v>-1</v>
@@ -43129,17 +43129,17 @@
       <c r="AQ136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AR136" s="20" t="n">
-        <v>3824</v>
+      <c r="AR136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AS136" s="13" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="AT136" s="23" t="n">
-        <v>15746</v>
+        <v>0</v>
+      </c>
+      <c r="AT136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="AU136" s="13" t="n">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="AV136" s="13" t="n">
         <v>-1</v>
@@ -43153,29 +43153,29 @@
       <c r="AY136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AZ136" s="23" t="n">
-        <v>6290</v>
+      <c r="AZ136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BA136" s="13" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="BB136" s="23" t="n">
-        <v>8443</v>
+        <v>0</v>
+      </c>
+      <c r="BB136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BC136" s="13" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="BD136" s="23" t="n">
-        <v>9197</v>
+        <v>0</v>
+      </c>
+      <c r="BD136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BE136" s="13" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="BF136" s="23" t="n">
-        <v>13804</v>
+        <v>0</v>
+      </c>
+      <c r="BF136" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="BG136" s="13" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="BH136" s="13" t="n">
         <v>-1</v>
@@ -43184,130 +43184,130 @@
         <v>0</v>
       </c>
       <c r="BJ136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BK136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BL136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BM136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BN136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BO136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BP136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BQ136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BR136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BS136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BT136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BU136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BV136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BW136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BX136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="BY136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BZ136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CA136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CB136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CC136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CD136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CE136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CF136" s="13" t="n">
-        <v>-2</v>
+      <c r="CF136" s="20" t="n">
+        <v>2005</v>
       </c>
       <c r="CG136" s="13" t="n">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="CH136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CI136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CJ136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CK136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CL136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CM136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CN136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CO136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CP136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CQ136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CR136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CS136" s="13" t="n">
         <v>0</v>
       </c>
       <c r="CT136" s="13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CU136" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="CV136" s="13" t="n">
-        <v>-2</v>
+      <c r="CV136" s="20" t="n">
+        <v>3161</v>
       </c>
       <c r="CW136" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX136" s="13" t="n">
-        <v>-2</v>
+        <v>78.2</v>
+      </c>
+      <c r="CX136" s="20" t="n">
+        <v>7063</v>
       </c>
       <c r="CY136" s="13" t="n">
-        <v>0</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="CZ136" s="13" t="n">
         <v>-2</v>
@@ -43344,7 +43344,7 @@
         </is>
       </c>
       <c r="C137" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D137" s="27" t="n">
         <v>1975</v>

--- a/generateEXCEL/index.xlsx
+++ b/generateEXCEL/index.xlsx
@@ -977,7 +977,7 @@
         <v>1223</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>2980</v>
+        <v>3057</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>100</v>
@@ -1314,7 +1314,7 @@
         <v>2258</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>2906</v>
+        <v>2952</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>99.90000000000001</v>
@@ -2340,7 +2340,7 @@
         <v>2087</v>
       </c>
       <c r="D16" s="23" t="n">
-        <v>2554</v>
+        <v>2617</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>99.8</v>
@@ -3019,7 +3019,7 @@
         <v>1111</v>
       </c>
       <c r="D18" s="23" t="n">
-        <v>2635</v>
+        <v>2693</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>99.8</v>
@@ -3356,7 +3356,7 @@
         <v>1009</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>2488</v>
+        <v>2581</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>99.8</v>
@@ -3693,7 +3693,7 @@
         <v>239</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>2608</v>
+        <v>2648</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>99.8</v>
@@ -4030,7 +4030,7 @@
         <v>2617</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>2414</v>
+        <v>2494</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>99.7</v>
@@ -4372,7 +4372,7 @@
         <v>2030</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>2759</v>
+        <v>2779</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>99.7</v>
@@ -5046,7 +5046,7 @@
         <v>364</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>2563</v>
+        <v>2598</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>99.59999999999999</v>
@@ -5382,8 +5382,8 @@
       <c r="C25" s="17" t="n">
         <v>914</v>
       </c>
-      <c r="D25" s="18" t="n">
-        <v>2707</v>
+      <c r="D25" s="20" t="n">
+        <v>2696</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>99.5</v>
@@ -5720,7 +5720,7 @@
         <v>1702</v>
       </c>
       <c r="D26" s="23" t="n">
-        <v>2653</v>
+        <v>2571</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>99.40000000000001</v>
@@ -6057,7 +6057,7 @@
         <v>1166</v>
       </c>
       <c r="D27" s="20" t="n">
-        <v>2668</v>
+        <v>2697</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>99.40000000000001</v>
@@ -6394,7 +6394,7 @@
         <v>2567</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>2772</v>
+        <v>2815</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>99.3</v>
@@ -7073,7 +7073,7 @@
         <v>2492</v>
       </c>
       <c r="D30" s="23" t="n">
-        <v>2443</v>
+        <v>2417</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>99</v>
@@ -7415,7 +7415,7 @@
         <v>839</v>
       </c>
       <c r="D31" s="20" t="n">
-        <v>2595</v>
+        <v>2620</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>99</v>
@@ -7752,7 +7752,7 @@
         <v>1398</v>
       </c>
       <c r="D32" s="24" t="n">
-        <v>2287</v>
+        <v>2348</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>98.90000000000001</v>
@@ -8093,8 +8093,8 @@
       <c r="C33" s="17" t="n">
         <v>1299</v>
       </c>
-      <c r="D33" s="20" t="n">
-        <v>2412</v>
+      <c r="D33" s="25" t="n">
+        <v>2393</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>98.8</v>
@@ -8430,8 +8430,8 @@
       <c r="C34" s="10" t="n">
         <v>259</v>
       </c>
-      <c r="D34" s="24" t="n">
-        <v>2393</v>
+      <c r="D34" s="23" t="n">
+        <v>2402</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>98.8</v>
@@ -8768,7 +8768,7 @@
         <v>248</v>
       </c>
       <c r="D35" s="20" t="n">
-        <v>2510</v>
+        <v>2526</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>98.8</v>
@@ -9110,7 +9110,7 @@
         <v>1584</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>2545</v>
+        <v>2536</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>98.7</v>
@@ -9451,8 +9451,8 @@
       <c r="C37" s="17" t="n">
         <v>1042</v>
       </c>
-      <c r="D37" s="25" t="n">
-        <v>2374</v>
+      <c r="D37" s="20" t="n">
+        <v>2404</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>98.40000000000001</v>
@@ -10126,7 +10126,7 @@
         <v>16</v>
       </c>
       <c r="D39" s="26" t="n">
-        <v>1500</v>
+        <v>1653</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>97.2</v>
@@ -10463,7 +10463,7 @@
         <v>1391</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>2189</v>
+        <v>2282</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>96.2</v>
@@ -10800,7 +10800,7 @@
         <v>860</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>2134</v>
+        <v>2178</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>96</v>
@@ -11474,7 +11474,7 @@
         <v>1746</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>2225</v>
+        <v>2242</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>95.59999999999999</v>
@@ -11816,7 +11816,7 @@
         <v>1438</v>
       </c>
       <c r="D44" s="24" t="n">
-        <v>2268</v>
+        <v>2303</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>95.40000000000001</v>
@@ -12157,8 +12157,8 @@
       <c r="C45" s="17" t="n">
         <v>2534</v>
       </c>
-      <c r="D45" s="26" t="n">
-        <v>2053</v>
+      <c r="D45" s="25" t="n">
+        <v>2127</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>95.2</v>
@@ -12494,8 +12494,8 @@
       <c r="C46" s="10" t="n">
         <v>230</v>
       </c>
-      <c r="D46" s="27" t="n">
-        <v>2023</v>
+      <c r="D46" s="24" t="n">
+        <v>2143</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>95.2</v>
@@ -12836,8 +12836,8 @@
       <c r="C47" s="17" t="n">
         <v>1027</v>
       </c>
-      <c r="D47" s="26" t="n">
-        <v>2091</v>
+      <c r="D47" s="25" t="n">
+        <v>2164</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>94.3</v>
@@ -13174,7 +13174,7 @@
         <v>2385</v>
       </c>
       <c r="D48" s="24" t="n">
-        <v>2186</v>
+        <v>2203</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>93.90000000000001</v>
@@ -13516,7 +13516,7 @@
         <v>1756</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>2060</v>
+        <v>2045</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>93.40000000000001</v>
@@ -13853,7 +13853,7 @@
         <v>1870</v>
       </c>
       <c r="D50" s="24" t="n">
-        <v>2287</v>
+        <v>2307</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>93</v>
@@ -14190,7 +14190,7 @@
         <v>1213</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>2181</v>
+        <v>2227</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>92.5</v>
@@ -14532,7 +14532,7 @@
         <v>534</v>
       </c>
       <c r="D52" s="24" t="n">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>92.40000000000001</v>
@@ -14874,7 +14874,7 @@
         <v>1847</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>2125</v>
+        <v>2158</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>92</v>
@@ -15216,7 +15216,7 @@
         <v>1918</v>
       </c>
       <c r="D54" s="24" t="n">
-        <v>2167</v>
+        <v>2193</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>91.8</v>
@@ -15558,7 +15558,7 @@
         <v>2092</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>2179</v>
+        <v>2188</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>91.7</v>
@@ -15900,7 +15900,7 @@
         <v>1306</v>
       </c>
       <c r="D56" s="27" t="n">
-        <v>1823</v>
+        <v>1925</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>91.40000000000001</v>
@@ -16237,7 +16237,7 @@
         <v>2356</v>
       </c>
       <c r="D57" s="26" t="n">
-        <v>2048</v>
+        <v>2068</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>91.2</v>
@@ -16579,7 +16579,7 @@
         <v>2002</v>
       </c>
       <c r="D58" s="27" t="n">
-        <v>2015</v>
+        <v>2071</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>91.2</v>
@@ -16921,7 +16921,7 @@
         <v>1159</v>
       </c>
       <c r="D59" s="20" t="n">
-        <v>2587</v>
+        <v>2570</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>91.2</v>
@@ -17258,7 +17258,7 @@
         <v>274</v>
       </c>
       <c r="D60" s="24" t="n">
-        <v>2346</v>
+        <v>2309</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>91</v>
@@ -17599,8 +17599,8 @@
       <c r="C61" s="17" t="n">
         <v>1909</v>
       </c>
-      <c r="D61" s="25" t="n">
-        <v>2113</v>
+      <c r="D61" s="26" t="n">
+        <v>2080</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>90.90000000000001</v>
@@ -17942,7 +17942,7 @@
         <v>322</v>
       </c>
       <c r="D62" s="27" t="n">
-        <v>1906</v>
+        <v>1980</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>90.8</v>
@@ -18279,7 +18279,7 @@
         <v>1434</v>
       </c>
       <c r="D63" s="26" t="n">
-        <v>1970</v>
+        <v>2018</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>90.5</v>
@@ -18615,8 +18615,8 @@
       <c r="C64" s="10" t="n">
         <v>1413</v>
       </c>
-      <c r="D64" s="23" t="n">
-        <v>2421</v>
+      <c r="D64" s="24" t="n">
+        <v>2368</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>90.5</v>
@@ -18953,7 +18953,7 @@
         <v>1766</v>
       </c>
       <c r="D65" s="25" t="n">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>90.40000000000001</v>
@@ -19627,7 +19627,7 @@
         <v>1264</v>
       </c>
       <c r="D67" s="20" t="n">
-        <v>2417</v>
+        <v>2401</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>90.2</v>
@@ -19964,7 +19964,7 @@
         <v>1041</v>
       </c>
       <c r="D68" s="24" t="n">
-        <v>2285</v>
+        <v>2234</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>90.09999999999999</v>
@@ -20301,7 +20301,7 @@
         <v>663</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>2218</v>
+        <v>2183</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>90</v>
@@ -20643,7 +20643,7 @@
         <v>2255</v>
       </c>
       <c r="D70" s="27" t="n">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>89.90000000000001</v>
@@ -20985,7 +20985,7 @@
         <v>1372</v>
       </c>
       <c r="D71" s="26" t="n">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>89.7</v>
@@ -21322,7 +21322,7 @@
         <v>1034</v>
       </c>
       <c r="D72" s="27" t="n">
-        <v>1910</v>
+        <v>1972</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>89.40000000000001</v>
@@ -21659,7 +21659,7 @@
         <v>1213</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>2125</v>
+        <v>2120</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>88.7</v>
@@ -21996,7 +21996,7 @@
         <v>201</v>
       </c>
       <c r="D74" s="27" t="n">
-        <v>1858</v>
+        <v>1839</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>87.5</v>
@@ -22333,7 +22333,7 @@
         <v>1959</v>
       </c>
       <c r="D75" s="26" t="n">
-        <v>2017</v>
+        <v>2000</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>87.2</v>
@@ -22675,7 +22675,7 @@
         <v>1642</v>
       </c>
       <c r="D76" s="27" t="n">
-        <v>1699</v>
+        <v>1800</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>87.2</v>
@@ -23017,7 +23017,7 @@
         <v>727</v>
       </c>
       <c r="D77" s="26" t="n">
-        <v>1882</v>
+        <v>1930</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>87</v>
@@ -23359,7 +23359,7 @@
         <v>2272</v>
       </c>
       <c r="D78" s="27" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>86.90000000000001</v>
@@ -23696,7 +23696,7 @@
         <v>926</v>
       </c>
       <c r="D79" s="26" t="n">
-        <v>2046</v>
+        <v>1991</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>85.7</v>
@@ -24033,7 +24033,7 @@
         <v>979</v>
       </c>
       <c r="D80" s="24" t="n">
-        <v>2202</v>
+        <v>2156</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>84.8</v>
@@ -24370,7 +24370,7 @@
         <v>1940</v>
       </c>
       <c r="D81" s="26" t="n">
-        <v>1500</v>
+        <v>1591</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>84</v>
@@ -24712,7 +24712,7 @@
         <v>304</v>
       </c>
       <c r="D82" s="27" t="n">
-        <v>1911</v>
+        <v>1923</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>83.40000000000001</v>
@@ -25054,7 +25054,7 @@
         <v>69</v>
       </c>
       <c r="D83" s="26" t="n">
-        <v>1937</v>
+        <v>1908</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>82.8</v>
@@ -25396,7 +25396,7 @@
         <v>1094</v>
       </c>
       <c r="D84" s="27" t="n">
-        <v>1788</v>
+        <v>1858</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>82.5</v>
@@ -25733,7 +25733,7 @@
         <v>2599</v>
       </c>
       <c r="D85" s="26" t="n">
-        <v>2024</v>
+        <v>2034</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>81</v>
@@ -26075,7 +26075,7 @@
         <v>2244</v>
       </c>
       <c r="D86" s="27" t="n">
-        <v>1859</v>
+        <v>1848</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>81</v>
@@ -26417,7 +26417,7 @@
         <v>2435</v>
       </c>
       <c r="D87" s="26" t="n">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>79.40000000000001</v>
@@ -26754,7 +26754,7 @@
         <v>1809</v>
       </c>
       <c r="D88" s="27" t="n">
-        <v>1819</v>
+        <v>1790</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>78.7</v>
@@ -27096,7 +27096,7 @@
         <v>17</v>
       </c>
       <c r="D89" s="26" t="n">
-        <v>1500</v>
+        <v>1793</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>77.40000000000001</v>
@@ -27438,7 +27438,7 @@
         <v>431</v>
       </c>
       <c r="D90" s="27" t="n">
-        <v>1774</v>
+        <v>1799</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>75.3</v>
@@ -27775,7 +27775,7 @@
         <v>1343</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>2131</v>
+        <v>2118</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>75.09999999999999</v>
@@ -28112,7 +28112,7 @@
         <v>2304</v>
       </c>
       <c r="D92" s="27" t="n">
-        <v>1780</v>
+        <v>1818</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>74.8</v>
@@ -28454,7 +28454,7 @@
         <v>222</v>
       </c>
       <c r="D93" s="26" t="n">
-        <v>1747</v>
+        <v>1757</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>74.2</v>
@@ -28791,7 +28791,7 @@
         <v>114</v>
       </c>
       <c r="D94" s="27" t="n">
-        <v>1804</v>
+        <v>1814</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>74.2</v>
@@ -29133,7 +29133,7 @@
         <v>1337</v>
       </c>
       <c r="D95" s="26" t="n">
-        <v>1988</v>
+        <v>1937</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>73.90000000000001</v>
@@ -29470,7 +29470,7 @@
         <v>853</v>
       </c>
       <c r="D96" s="27" t="n">
-        <v>1776</v>
+        <v>1795</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>73.3</v>
@@ -29807,7 +29807,7 @@
         <v>1159</v>
       </c>
       <c r="D97" s="26" t="n">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>73</v>
@@ -30149,7 +30149,7 @@
         <v>1274</v>
       </c>
       <c r="D98" s="27" t="n">
-        <v>1939</v>
+        <v>1917</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>71.5</v>
@@ -30486,7 +30486,7 @@
         <v>1473</v>
       </c>
       <c r="D99" s="26" t="n">
-        <v>1899</v>
+        <v>1906</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>71.2</v>
@@ -30823,7 +30823,7 @@
         <v>1765</v>
       </c>
       <c r="D100" s="27" t="n">
-        <v>1875</v>
+        <v>1831</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>70.09999999999999</v>
@@ -31160,7 +31160,7 @@
         <v>1874</v>
       </c>
       <c r="D101" s="26" t="n">
-        <v>1703</v>
+        <v>1739</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>68.2</v>
@@ -31502,7 +31502,7 @@
         <v>2509</v>
       </c>
       <c r="D102" s="27" t="n">
-        <v>1870</v>
+        <v>1806</v>
       </c>
       <c r="E102" s="12" t="n">
         <v>64.90000000000001</v>
@@ -31844,7 +31844,7 @@
         <v>739</v>
       </c>
       <c r="D103" s="26" t="n">
-        <v>2039</v>
+        <v>1980</v>
       </c>
       <c r="E103" s="12" t="n">
         <v>63.1</v>
@@ -32186,7 +32186,7 @@
         <v>1511</v>
       </c>
       <c r="D104" s="27" t="n">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E104" s="12" t="n">
         <v>61.3</v>
@@ -32523,7 +32523,7 @@
         <v>40</v>
       </c>
       <c r="D105" s="26" t="n">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="E105" s="12" t="n">
         <v>58.6</v>
@@ -32860,7 +32860,7 @@
         <v>403</v>
       </c>
       <c r="D106" s="27" t="n">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="E106" s="12" t="n">
         <v>58</v>
@@ -33197,7 +33197,7 @@
         <v>2386</v>
       </c>
       <c r="D107" s="26" t="n">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="E107" s="12" t="n">
         <v>57.2</v>
@@ -33539,7 +33539,7 @@
         <v>503</v>
       </c>
       <c r="D108" s="27" t="n">
-        <v>1697</v>
+        <v>1680</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>55.7</v>
@@ -33876,7 +33876,7 @@
         <v>450</v>
       </c>
       <c r="D109" s="26" t="n">
-        <v>1731</v>
+        <v>1819</v>
       </c>
       <c r="E109" s="12" t="n">
         <v>48.6</v>
@@ -34213,7 +34213,7 @@
         <v>1334</v>
       </c>
       <c r="D110" s="24" t="n">
-        <v>2206</v>
+        <v>2244</v>
       </c>
       <c r="E110" s="12" t="n">
         <v>47</v>
@@ -34549,8 +34549,8 @@
       <c r="C111" s="17" t="n">
         <v>321</v>
       </c>
-      <c r="D111" s="26" t="n">
-        <v>2019</v>
+      <c r="D111" s="25" t="n">
+        <v>2125</v>
       </c>
       <c r="E111" s="12" t="n">
         <v>47</v>
@@ -34887,7 +34887,7 @@
         <v>1475</v>
       </c>
       <c r="D112" s="24" t="n">
-        <v>2129</v>
+        <v>2123</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>45.6</v>
@@ -35224,7 +35224,7 @@
         <v>400</v>
       </c>
       <c r="D113" s="26" t="n">
-        <v>1902</v>
+        <v>1938</v>
       </c>
       <c r="E113" s="12" t="n">
         <v>45.5</v>
@@ -35561,7 +35561,7 @@
         <v>1399</v>
       </c>
       <c r="D114" s="27" t="n">
-        <v>1961</v>
+        <v>1835</v>
       </c>
       <c r="E114" s="12" t="n">
         <v>44.2</v>
@@ -35903,7 +35903,7 @@
         <v>1570</v>
       </c>
       <c r="D115" s="26" t="n">
-        <v>1613</v>
+        <v>1522</v>
       </c>
       <c r="E115" s="12" t="n">
         <v>33.2</v>
@@ -36245,7 +36245,7 @@
         <v>1324</v>
       </c>
       <c r="D116" s="27" t="n">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="E116" s="12" t="n">
         <v>31.6</v>
@@ -36929,7 +36929,7 @@
         <v>502</v>
       </c>
       <c r="D118" s="27" t="n">
-        <v>1673</v>
+        <v>1650</v>
       </c>
       <c r="E118" s="12" t="n">
         <v>19.1</v>
@@ -37266,7 +37266,7 @@
         <v>930</v>
       </c>
       <c r="D119" s="26" t="n">
-        <v>1489</v>
+        <v>1463</v>
       </c>
       <c r="E119" s="12" t="n">
         <v>3.6</v>
